--- a/data/Apr/InternalDailyReport.xlsx
+++ b/data/Apr/InternalDailyReport.xlsx
@@ -8,15 +8,17 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\Work\Freelance\TextInputter\data\Apr\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{506A13AB-E286-495C-BFD0-7AB26D30326D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{72497BD4-F563-4F32-820E-39EA6BEF65F3}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="01-04" sheetId="2" r:id="rId1"/>
+    <sheet name="02-04" sheetId="6" r:id="rId2"/>
   </sheets>
   <definedNames>
     <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'01-04'!$A$2:$P$23</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'02-04'!$A$2:$P$24</definedName>
   </definedNames>
   <calcPr calcId="191029"/>
   <extLst>
@@ -36,7 +38,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="216" uniqueCount="110">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="443" uniqueCount="177">
   <si>
     <t>Tình trạng TT</t>
   </si>
@@ -366,6 +368,207 @@
   </si>
   <si>
     <t>CK Đủ 100%</t>
+  </si>
+  <si>
+    <t>Soipin - Hiền Đăng</t>
+  </si>
+  <si>
+    <t>Xe Anh Khương</t>
+  </si>
+  <si>
+    <t>02-04-2026</t>
+  </si>
+  <si>
+    <t>Hoàng anh</t>
+  </si>
+  <si>
+    <t>71/39/31 Nguyễn Bặc, Phường 3</t>
+  </si>
+  <si>
+    <t>c.hieu</t>
+  </si>
+  <si>
+    <t>Nt hai yen</t>
+  </si>
+  <si>
+    <t>132 khu dân cư Tân tiến, Tân Thới Hiệp</t>
+  </si>
+  <si>
+    <t>Phương Thảo</t>
+  </si>
+  <si>
+    <t xml:space="preserve">189/46a Bạch Đằng, phường Hạnh Thông </t>
+  </si>
+  <si>
+    <t>Bình Trần</t>
+  </si>
+  <si>
+    <t>41/8 Mai Lão Bạng, Phường 13</t>
+  </si>
+  <si>
+    <t>Mén HM</t>
+  </si>
+  <si>
+    <t>HD006947</t>
+  </si>
+  <si>
+    <t>Toà landmark 2</t>
+  </si>
+  <si>
+    <t>Thùy Dương</t>
+  </si>
+  <si>
+    <t>HD007101</t>
+  </si>
+  <si>
+    <t>2087 Huỳnh Tấn Phát</t>
+  </si>
+  <si>
+    <t>nha be</t>
+  </si>
+  <si>
+    <t>AT 02-04</t>
+  </si>
+  <si>
+    <t>Hồng Khanh fb Hoàng Thị Lộc</t>
+  </si>
+  <si>
+    <t>HD007069</t>
+  </si>
+  <si>
+    <t>1080, Đỗ Mười, phường linh trung</t>
+  </si>
+  <si>
+    <t>thu duc</t>
+  </si>
+  <si>
+    <t>Nguyễn Thị Kim Thoa</t>
+  </si>
+  <si>
+    <t>HD007091</t>
+  </si>
+  <si>
+    <t>số 25a đường 22 sình hưng hòa a</t>
+  </si>
+  <si>
+    <t>Nguyệt Nguyễn Thị Minh</t>
+  </si>
+  <si>
+    <t>HD007068</t>
+  </si>
+  <si>
+    <t>35 Lý Văn Phức phường Tân Định</t>
+  </si>
+  <si>
+    <t>Lê Quốc Khánh_FE: My Le</t>
+  </si>
+  <si>
+    <t>HD006896</t>
+  </si>
+  <si>
+    <t>Hẻm 132, 132/78 nguyễn hữu cảnh</t>
+  </si>
+  <si>
+    <t>HD007115</t>
+  </si>
+  <si>
+    <t>3/51/4 thành thái p14</t>
+  </si>
+  <si>
+    <t>Linh Hạ</t>
+  </si>
+  <si>
+    <t>HD006999</t>
+  </si>
+  <si>
+    <t>854 tạ quang bửu chung cư gia việt phường 5</t>
+  </si>
+  <si>
+    <t>Nguyễn Trương Phương Oanh</t>
+  </si>
+  <si>
+    <t>HD006977</t>
+  </si>
+  <si>
+    <t>125/42/2 Bùi Đình Tuý, phường 14</t>
+  </si>
+  <si>
+    <t>Yến Oanh</t>
+  </si>
+  <si>
+    <t>HD005268</t>
+  </si>
+  <si>
+    <t>33 Đ Ng~ hữu thọ Tân hưng</t>
+  </si>
+  <si>
+    <t>Kim Minh</t>
+  </si>
+  <si>
+    <t>HD006908</t>
+  </si>
+  <si>
+    <t>Địa chỉ : 189A Cống Quỳnh p.Cầu Ông Lãnh</t>
+  </si>
+  <si>
+    <t>Cẩm Tú</t>
+  </si>
+  <si>
+    <t>HD006777</t>
+  </si>
+  <si>
+    <t>Chung cư west gate an gia Cẩm Tú</t>
+  </si>
+  <si>
+    <t>binh chanh</t>
+  </si>
+  <si>
+    <t>Phương Kim</t>
+  </si>
+  <si>
+    <t>HD007131</t>
+  </si>
+  <si>
+    <t>213/6 đường số 1,p6</t>
+  </si>
+  <si>
+    <t>Hiếu Lee</t>
+  </si>
+  <si>
+    <t>HD007067</t>
+  </si>
+  <si>
+    <t>Chung cu folita him lam</t>
+  </si>
+  <si>
+    <t>Tuyết Mai</t>
+  </si>
+  <si>
+    <t>HD007102</t>
+  </si>
+  <si>
+    <t>276/3/45/11/17 Mã lò, Phường Bình Trị Đông A</t>
+  </si>
+  <si>
+    <t>Linh Tiêu</t>
+  </si>
+  <si>
+    <t>HD006958</t>
+  </si>
+  <si>
+    <t>97 Ký Con,p Nguyễn Thái Bình</t>
+  </si>
+  <si>
+    <t>Nguyễn Thị Thùy Trang</t>
+  </si>
+  <si>
+    <t>HD007013</t>
+  </si>
+  <si>
+    <t>41A huỳnh tịnh của p19</t>
+  </si>
+  <si>
+    <t>at 02-04</t>
   </si>
 </sst>
 </file>
@@ -445,13 +648,13 @@
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="0" fillId="3" borderId="0" xfId="0" applyFill="1"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="1" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="0" fillId="3" borderId="0" xfId="0" applyFill="1"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
     <xf numFmtId="3" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
-    <xf numFmtId="0" fontId="1" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="1" fillId="4" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
-    <xf numFmtId="0" fontId="0" fillId="3" borderId="0" xfId="0" applyFill="1"/>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="0" fillId="5" borderId="0" xfId="0" applyFill="1"/>
     <xf numFmtId="0" fontId="1" fillId="6" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
   </cellXfs>
@@ -778,52 +981,52 @@
   </cols>
   <sheetData>
     <row r="2" spans="1:17" x14ac:dyDescent="0.25">
-      <c r="A2" s="6" t="s">
-        <v>0</v>
-      </c>
-      <c r="B2" s="6" t="s">
-        <v>1</v>
-      </c>
-      <c r="C2" s="6" t="s">
+      <c r="A2" s="10" t="s">
+        <v>0</v>
+      </c>
+      <c r="B2" s="10" t="s">
+        <v>1</v>
+      </c>
+      <c r="C2" s="10" t="s">
         <v>2</v>
       </c>
-      <c r="D2" s="6" t="s">
+      <c r="D2" s="10" t="s">
         <v>3</v>
       </c>
-      <c r="E2" s="6" t="s">
+      <c r="E2" s="10" t="s">
         <v>4</v>
       </c>
-      <c r="F2" s="6" t="s">
+      <c r="F2" s="10" t="s">
         <v>5</v>
       </c>
-      <c r="G2" s="6" t="s">
+      <c r="G2" s="10" t="s">
         <v>6</v>
       </c>
-      <c r="H2" s="6" t="s">
+      <c r="H2" s="10" t="s">
         <v>7</v>
       </c>
-      <c r="I2" s="6" t="s">
+      <c r="I2" s="10" t="s">
         <v>8</v>
       </c>
-      <c r="J2" s="6" t="s">
+      <c r="J2" s="10" t="s">
         <v>9</v>
       </c>
-      <c r="K2" s="6" t="s">
+      <c r="K2" s="10" t="s">
         <v>10</v>
       </c>
-      <c r="L2" s="6" t="s">
+      <c r="L2" s="10" t="s">
         <v>11</v>
       </c>
-      <c r="M2" s="6" t="s">
+      <c r="M2" s="10" t="s">
         <v>12</v>
       </c>
-      <c r="N2" s="6" t="s">
+      <c r="N2" s="10" t="s">
         <v>13</v>
       </c>
-      <c r="O2" s="6" t="s">
+      <c r="O2" s="10" t="s">
         <v>14</v>
       </c>
-      <c r="P2" s="6" t="s">
+      <c r="P2" s="10" t="s">
         <v>15</v>
       </c>
     </row>
@@ -843,13 +1046,13 @@
       <c r="F3" t="s">
         <v>20</v>
       </c>
-      <c r="G3" s="7">
-        <v>0</v>
-      </c>
-      <c r="H3" s="7">
+      <c r="G3" s="11">
+        <v>0</v>
+      </c>
+      <c r="H3" s="11">
         <v>30</v>
       </c>
-      <c r="I3" s="7">
+      <c r="I3" s="11">
         <f>-H3</f>
         <v>-30</v>
       </c>
@@ -879,16 +1082,16 @@
       <c r="E4" t="s">
         <v>26</v>
       </c>
-      <c r="F4" s="7">
+      <c r="F4" s="11">
         <v>7</v>
       </c>
-      <c r="G4" s="7">
+      <c r="G4" s="11">
         <v>850</v>
       </c>
-      <c r="H4" s="7">
+      <c r="H4" s="11">
         <v>30</v>
       </c>
-      <c r="I4" s="7">
+      <c r="I4" s="11">
         <f>G4-H4</f>
         <v>820</v>
       </c>
@@ -918,16 +1121,16 @@
       <c r="E5" t="s">
         <v>29</v>
       </c>
-      <c r="F5" s="7">
+      <c r="F5" s="11">
         <v>3</v>
       </c>
-      <c r="G5" s="7">
+      <c r="G5" s="11">
         <v>695</v>
       </c>
-      <c r="H5" s="7">
+      <c r="H5" s="11">
         <v>25</v>
       </c>
-      <c r="I5" s="7">
+      <c r="I5" s="11">
         <f>G5-H5</f>
         <v>670</v>
       </c>
@@ -957,16 +1160,16 @@
       <c r="E6" t="s">
         <v>32</v>
       </c>
-      <c r="F6" s="7">
+      <c r="F6" s="11">
         <v>7</v>
       </c>
-      <c r="G6" s="7">
+      <c r="G6" s="11">
         <v>740</v>
       </c>
-      <c r="H6" s="7">
+      <c r="H6" s="11">
         <v>30</v>
       </c>
-      <c r="I6" s="7">
+      <c r="I6" s="11">
         <f>G6-H6</f>
         <v>710</v>
       </c>
@@ -999,13 +1202,13 @@
       <c r="F7" t="s">
         <v>36</v>
       </c>
-      <c r="G7" s="7">
-        <v>0</v>
-      </c>
-      <c r="H7" s="7">
+      <c r="G7" s="11">
+        <v>0</v>
+      </c>
+      <c r="H7" s="11">
         <v>20</v>
       </c>
-      <c r="I7" s="7">
+      <c r="I7" s="11">
         <f>-H7</f>
         <v>-20</v>
       </c>
@@ -1035,16 +1238,16 @@
       <c r="E8" t="s">
         <v>39</v>
       </c>
-      <c r="F8" s="7">
+      <c r="F8" s="11">
         <v>9</v>
       </c>
-      <c r="G8" s="7">
+      <c r="G8" s="11">
         <v>780</v>
       </c>
-      <c r="H8" s="7">
+      <c r="H8" s="11">
         <v>30</v>
       </c>
-      <c r="I8" s="7">
+      <c r="I8" s="11">
         <f>G8-H8</f>
         <v>750</v>
       </c>
@@ -1077,13 +1280,13 @@
       <c r="F9" t="s">
         <v>44</v>
       </c>
-      <c r="G9" s="7">
+      <c r="G9" s="11">
         <v>615</v>
       </c>
-      <c r="H9" s="7">
+      <c r="H9" s="11">
         <v>25</v>
       </c>
-      <c r="I9" s="7">
+      <c r="I9" s="11">
         <f>G9-H9</f>
         <v>590</v>
       </c>
@@ -1116,13 +1319,13 @@
       <c r="F10" t="s">
         <v>20</v>
       </c>
-      <c r="G10" s="7">
+      <c r="G10" s="11">
         <v>610</v>
       </c>
-      <c r="H10" s="7">
+      <c r="H10" s="11">
         <v>30</v>
       </c>
-      <c r="I10" s="7">
+      <c r="I10" s="11">
         <f>G10-H10</f>
         <v>580</v>
       </c>
@@ -1152,16 +1355,16 @@
       <c r="E11" t="s">
         <v>50</v>
       </c>
-      <c r="F11" s="7">
+      <c r="F11" s="11">
         <v>8</v>
       </c>
-      <c r="G11" s="7">
-        <v>0</v>
-      </c>
-      <c r="H11" s="7">
+      <c r="G11" s="11">
+        <v>0</v>
+      </c>
+      <c r="H11" s="11">
         <v>25</v>
       </c>
-      <c r="I11" s="7">
+      <c r="I11" s="11">
         <f>-H11</f>
         <v>-25</v>
       </c>
@@ -1191,16 +1394,16 @@
       <c r="E12" t="s">
         <v>53</v>
       </c>
-      <c r="F12" s="7">
-        <v>1</v>
-      </c>
-      <c r="G12" s="7">
+      <c r="F12" s="11">
+        <v>1</v>
+      </c>
+      <c r="G12" s="11">
         <v>845</v>
       </c>
-      <c r="H12" s="7">
+      <c r="H12" s="11">
         <v>25</v>
       </c>
-      <c r="I12" s="7">
+      <c r="I12" s="11">
         <f t="shared" ref="I12:I21" si="0">G12-H12</f>
         <v>820</v>
       </c>
@@ -1230,16 +1433,16 @@
       <c r="E13" t="s">
         <v>56</v>
       </c>
-      <c r="F13" s="7">
+      <c r="F13" s="11">
         <v>12</v>
       </c>
-      <c r="G13" s="7">
+      <c r="G13" s="11">
         <v>750</v>
       </c>
-      <c r="H13" s="7">
+      <c r="H13" s="11">
         <v>30</v>
       </c>
-      <c r="I13" s="7">
+      <c r="I13" s="11">
         <f t="shared" si="0"/>
         <v>720</v>
       </c>
@@ -1272,13 +1475,13 @@
       <c r="F14" t="s">
         <v>36</v>
       </c>
-      <c r="G14" s="7">
+      <c r="G14" s="11">
         <v>1630</v>
       </c>
-      <c r="H14" s="7">
+      <c r="H14" s="11">
         <v>20</v>
       </c>
-      <c r="I14" s="7">
+      <c r="I14" s="11">
         <f t="shared" si="0"/>
         <v>1610</v>
       </c>
@@ -1308,16 +1511,16 @@
       <c r="E15" t="s">
         <v>62</v>
       </c>
-      <c r="F15" s="7">
+      <c r="F15" s="11">
         <v>3</v>
       </c>
-      <c r="G15" s="7">
+      <c r="G15" s="11">
         <v>405</v>
       </c>
-      <c r="H15" s="7">
+      <c r="H15" s="11">
         <v>25</v>
       </c>
-      <c r="I15" s="7">
+      <c r="I15" s="11">
         <f t="shared" si="0"/>
         <v>380</v>
       </c>
@@ -1347,16 +1550,16 @@
       <c r="E16" t="s">
         <v>65</v>
       </c>
-      <c r="F16" s="7">
+      <c r="F16" s="11">
         <v>7</v>
       </c>
-      <c r="G16" s="7">
+      <c r="G16" s="11">
         <v>30</v>
       </c>
-      <c r="H16" s="7">
+      <c r="H16" s="11">
         <v>30</v>
       </c>
-      <c r="I16" s="7">
+      <c r="I16" s="11">
         <f t="shared" si="0"/>
         <v>0</v>
       </c>
@@ -1389,16 +1592,16 @@
       <c r="E17" t="s">
         <v>69</v>
       </c>
-      <c r="F17" s="7">
+      <c r="F17" s="11">
         <v>7</v>
       </c>
-      <c r="G17" s="7">
+      <c r="G17" s="11">
         <v>1640</v>
       </c>
-      <c r="H17" s="7">
+      <c r="H17" s="11">
         <v>30</v>
       </c>
-      <c r="I17" s="7">
+      <c r="I17" s="11">
         <f t="shared" si="0"/>
         <v>1610</v>
       </c>
@@ -1428,16 +1631,16 @@
       <c r="E18" t="s">
         <v>72</v>
       </c>
-      <c r="F18" s="7">
+      <c r="F18" s="11">
         <v>12</v>
       </c>
-      <c r="G18" s="7">
+      <c r="G18" s="11">
         <v>590</v>
       </c>
-      <c r="H18" s="7">
+      <c r="H18" s="11">
         <v>30</v>
       </c>
-      <c r="I18" s="7">
+      <c r="I18" s="11">
         <f t="shared" si="0"/>
         <v>560</v>
       </c>
@@ -1467,16 +1670,16 @@
       <c r="E19" t="s">
         <v>75</v>
       </c>
-      <c r="F19" s="7">
+      <c r="F19" s="11">
         <v>7</v>
       </c>
-      <c r="G19" s="7">
+      <c r="G19" s="11">
         <v>850</v>
       </c>
-      <c r="H19" s="7">
+      <c r="H19" s="11">
         <v>30</v>
       </c>
-      <c r="I19" s="7">
+      <c r="I19" s="11">
         <f t="shared" si="0"/>
         <v>820</v>
       </c>
@@ -1509,13 +1712,13 @@
       <c r="F20" t="s">
         <v>79</v>
       </c>
-      <c r="G20" s="7">
+      <c r="G20" s="11">
         <v>20</v>
       </c>
-      <c r="H20" s="7">
+      <c r="H20" s="11">
         <v>20</v>
       </c>
-      <c r="I20" s="7">
+      <c r="I20" s="11">
         <f t="shared" si="0"/>
         <v>0</v>
       </c>
@@ -1551,13 +1754,13 @@
       <c r="F21" t="s">
         <v>20</v>
       </c>
-      <c r="G21" s="7">
+      <c r="G21" s="11">
         <v>820</v>
       </c>
-      <c r="H21" s="7">
+      <c r="H21" s="11">
         <v>30</v>
       </c>
-      <c r="I21" s="7">
+      <c r="I21" s="11">
         <f t="shared" si="0"/>
         <v>790</v>
       </c>
@@ -1590,13 +1793,13 @@
       <c r="F22" t="s">
         <v>86</v>
       </c>
-      <c r="G22" s="7">
-        <v>0</v>
-      </c>
-      <c r="H22" s="7">
+      <c r="G22" s="11">
+        <v>0</v>
+      </c>
+      <c r="H22" s="11">
         <v>30</v>
       </c>
-      <c r="I22" s="7">
+      <c r="I22" s="11">
         <f>-H22</f>
         <v>-30</v>
       </c>
@@ -1626,16 +1829,16 @@
       <c r="E23" t="s">
         <v>88</v>
       </c>
-      <c r="F23" s="7">
+      <c r="F23" s="11">
         <v>6</v>
       </c>
-      <c r="G23" s="7">
-        <v>0</v>
-      </c>
-      <c r="H23" s="7">
+      <c r="G23" s="11">
+        <v>0</v>
+      </c>
+      <c r="H23" s="11">
         <v>30</v>
       </c>
-      <c r="I23" s="7">
+      <c r="I23" s="11">
         <f>-H23</f>
         <v>-30</v>
       </c>
@@ -1653,51 +1856,51 @@
       </c>
     </row>
     <row r="25" spans="1:17" x14ac:dyDescent="0.25">
-      <c r="D25" s="8">
+      <c r="D25" s="6">
         <f>COUNTA(D3:D23)</f>
         <v>19</v>
       </c>
-      <c r="G25" s="8">
+      <c r="G25" s="6">
         <f t="shared" ref="G25:Q25" si="1">SUBTOTAL(9,G3:G23)</f>
         <v>11870</v>
       </c>
-      <c r="H25" s="8">
+      <c r="H25" s="6">
         <f t="shared" si="1"/>
         <v>575</v>
       </c>
-      <c r="I25" s="8">
+      <c r="I25" s="6">
         <f t="shared" si="1"/>
         <v>11295</v>
       </c>
-      <c r="J25" s="8">
+      <c r="J25" s="6">
         <f t="shared" si="1"/>
         <v>0</v>
       </c>
-      <c r="K25" s="8">
+      <c r="K25" s="6">
         <f t="shared" si="1"/>
         <v>0</v>
       </c>
-      <c r="L25" s="8">
+      <c r="L25" s="6">
         <f t="shared" si="1"/>
         <v>0</v>
       </c>
-      <c r="M25" s="8">
+      <c r="M25" s="6">
         <f t="shared" si="1"/>
         <v>0</v>
       </c>
-      <c r="N25" s="8">
+      <c r="N25" s="6">
         <f t="shared" si="1"/>
         <v>0</v>
       </c>
-      <c r="O25" s="8">
+      <c r="O25" s="6">
         <f t="shared" si="1"/>
         <v>0</v>
       </c>
-      <c r="P25" s="8">
+      <c r="P25" s="6">
         <f t="shared" si="1"/>
         <v>0</v>
       </c>
-      <c r="Q25" s="8">
+      <c r="Q25" s="6">
         <f t="shared" si="1"/>
         <v>21</v>
       </c>
@@ -1709,7 +1912,7 @@
       </c>
     </row>
     <row r="27" spans="1:17" x14ac:dyDescent="0.25">
-      <c r="A27" s="8" t="s">
+      <c r="A27" s="6" t="s">
         <v>16</v>
       </c>
       <c r="C27" s="5" t="s">
@@ -1723,13 +1926,13 @@
         <f>-5*25</f>
         <v>-125</v>
       </c>
-      <c r="K27" s="10" t="s">
+      <c r="K27" s="12" t="s">
         <v>21</v>
       </c>
-      <c r="L27" s="10" t="s">
+      <c r="L27" s="12" t="s">
         <v>91</v>
       </c>
-      <c r="M27" s="10" t="s">
+      <c r="M27" s="12" t="s">
         <v>90</v>
       </c>
       <c r="O27" s="9" t="s">
@@ -1740,7 +1943,7 @@
       <c r="A28" t="s">
         <v>23</v>
       </c>
-      <c r="B28" s="11" t="s">
+      <c r="B28" s="8" t="s">
         <v>93</v>
       </c>
       <c r="C28" s="4">
@@ -1748,7 +1951,7 @@
         <v>11295</v>
       </c>
       <c r="D28" s="4"/>
-      <c r="E28" s="11">
+      <c r="E28" s="8">
         <f>SUMIFS(Q$3:Q$23,B$3:B$23,A$27,L$3:L$23,A$28)</f>
         <v>21</v>
       </c>
@@ -1775,7 +1978,7 @@
       </c>
     </row>
     <row r="29" spans="1:17" x14ac:dyDescent="0.25">
-      <c r="B29" s="12" t="s">
+      <c r="B29" s="7" t="s">
         <v>97</v>
       </c>
       <c r="C29" s="3">
@@ -1802,7 +2005,7 @@
       </c>
     </row>
     <row r="30" spans="1:17" x14ac:dyDescent="0.25">
-      <c r="B30" s="12" t="s">
+      <c r="B30" s="7" t="s">
         <v>99</v>
       </c>
       <c r="C30" s="3">
@@ -1810,7 +2013,7 @@
         <v>0</v>
       </c>
       <c r="D30" s="3"/>
-      <c r="E30" s="12">
+      <c r="E30" s="7">
         <f>SUMIFS(Q$3:Q$23,B$3:B$23,A$27,P$3:P$23,"xx",N$3:N$23,"x")</f>
         <v>0</v>
       </c>
@@ -1838,7 +2041,7 @@
         <f>E28</f>
         <v>21</v>
       </c>
-      <c r="K31" s="12" t="s">
+      <c r="K31" s="7" t="s">
         <v>102</v>
       </c>
       <c r="O31" t="s">
@@ -1850,12 +2053,12 @@
       </c>
     </row>
     <row r="32" spans="1:17" x14ac:dyDescent="0.25">
-      <c r="B32" s="12" t="s">
+      <c r="B32" s="7" t="s">
         <v>104</v>
       </c>
       <c r="C32" s="2"/>
       <c r="D32" s="2"/>
-      <c r="K32" s="12" t="s">
+      <c r="K32" s="7" t="s">
         <v>105</v>
       </c>
       <c r="O32" s="9" t="s">
@@ -1882,7 +2085,7 @@
       </c>
     </row>
     <row r="35" spans="2:13" x14ac:dyDescent="0.25">
-      <c r="B35" s="8" t="s">
+      <c r="B35" s="6" t="s">
         <v>108</v>
       </c>
       <c r="C35" s="1">
@@ -1890,16 +2093,16 @@
         <v>11295</v>
       </c>
       <c r="D35" s="1"/>
-      <c r="E35" s="8" t="s">
+      <c r="E35" s="6" t="s">
         <v>109</v>
       </c>
-      <c r="K35" s="10" t="s">
-        <v>22</v>
-      </c>
-      <c r="L35" s="10" t="s">
+      <c r="K35" s="12" t="s">
+        <v>22</v>
+      </c>
+      <c r="L35" s="12" t="s">
         <v>91</v>
       </c>
-      <c r="M35" s="10" t="s">
+      <c r="M35" s="12" t="s">
         <v>90</v>
       </c>
     </row>
@@ -1943,12 +2146,12 @@
       </c>
     </row>
     <row r="39" spans="2:13" x14ac:dyDescent="0.25">
-      <c r="K39" s="12" t="s">
+      <c r="K39" s="7" t="s">
         <v>102</v>
       </c>
     </row>
     <row r="40" spans="2:13" x14ac:dyDescent="0.25">
-      <c r="K40" s="12" t="s">
+      <c r="K40" s="7" t="s">
         <v>105</v>
       </c>
     </row>
@@ -1963,13 +2166,13 @@
       </c>
     </row>
     <row r="43" spans="2:13" x14ac:dyDescent="0.25">
-      <c r="K43" s="10" t="s">
+      <c r="K43" s="12" t="s">
         <v>40</v>
       </c>
-      <c r="L43" s="10" t="s">
+      <c r="L43" s="12" t="s">
         <v>91</v>
       </c>
-      <c r="M43" s="10" t="s">
+      <c r="M43" s="12" t="s">
         <v>90</v>
       </c>
     </row>
@@ -2005,12 +2208,12 @@
       </c>
     </row>
     <row r="47" spans="2:13" x14ac:dyDescent="0.25">
-      <c r="K47" s="12" t="s">
+      <c r="K47" s="7" t="s">
         <v>102</v>
       </c>
     </row>
     <row r="48" spans="2:13" x14ac:dyDescent="0.25">
-      <c r="K48" s="12" t="s">
+      <c r="K48" s="7" t="s">
         <v>105</v>
       </c>
     </row>
@@ -2038,4 +2241,1334 @@
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="0.75" bottom="0.5" header="0.5" footer="0.75"/>
 </worksheet>
+</file>
+
+<file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0100-000000000000}">
+  <dimension ref="A2:Q50"/>
+  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <cols>
+    <col min="1" max="1" width="12.7109375" customWidth="1"/>
+    <col min="2" max="2" width="17.7109375" customWidth="1"/>
+    <col min="3" max="3" width="28.140625" customWidth="1"/>
+    <col min="4" max="4" width="9.85546875" customWidth="1"/>
+    <col min="5" max="5" width="43.28515625" customWidth="1"/>
+    <col min="6" max="6" width="10.85546875" customWidth="1"/>
+    <col min="7" max="7" width="9.140625" customWidth="1"/>
+    <col min="8" max="8" width="9.5703125" customWidth="1"/>
+    <col min="9" max="9" width="10.5703125" customWidth="1"/>
+    <col min="10" max="10" width="9.7109375" customWidth="1"/>
+    <col min="11" max="11" width="10.85546875" customWidth="1"/>
+    <col min="12" max="12" width="10.42578125" customWidth="1"/>
+    <col min="13" max="13" width="8.7109375" customWidth="1"/>
+    <col min="14" max="14" width="9.7109375" customWidth="1"/>
+    <col min="15" max="15" width="10.42578125" customWidth="1"/>
+    <col min="16" max="16" width="7" bestFit="1" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="2" spans="1:17" x14ac:dyDescent="0.25">
+      <c r="A2" s="10" t="s">
+        <v>0</v>
+      </c>
+      <c r="B2" s="10" t="s">
+        <v>1</v>
+      </c>
+      <c r="C2" s="10" t="s">
+        <v>2</v>
+      </c>
+      <c r="D2" s="10" t="s">
+        <v>3</v>
+      </c>
+      <c r="E2" s="10" t="s">
+        <v>4</v>
+      </c>
+      <c r="F2" s="10" t="s">
+        <v>5</v>
+      </c>
+      <c r="G2" s="10" t="s">
+        <v>6</v>
+      </c>
+      <c r="H2" s="10" t="s">
+        <v>7</v>
+      </c>
+      <c r="I2" s="10" t="s">
+        <v>8</v>
+      </c>
+      <c r="J2" s="10" t="s">
+        <v>9</v>
+      </c>
+      <c r="K2" s="10" t="s">
+        <v>10</v>
+      </c>
+      <c r="L2" s="10" t="s">
+        <v>11</v>
+      </c>
+      <c r="M2" s="10" t="s">
+        <v>12</v>
+      </c>
+      <c r="N2" s="10" t="s">
+        <v>13</v>
+      </c>
+      <c r="O2" s="10" t="s">
+        <v>14</v>
+      </c>
+      <c r="P2" s="10" t="s">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="3" spans="1:17" x14ac:dyDescent="0.25">
+      <c r="B3" t="s">
+        <v>16</v>
+      </c>
+      <c r="C3" t="s">
+        <v>125</v>
+      </c>
+      <c r="D3" t="s">
+        <v>126</v>
+      </c>
+      <c r="E3" t="s">
+        <v>127</v>
+      </c>
+      <c r="F3" t="s">
+        <v>128</v>
+      </c>
+      <c r="G3" s="11">
+        <v>35</v>
+      </c>
+      <c r="H3" s="11">
+        <v>35</v>
+      </c>
+      <c r="I3" s="11">
+        <f>G3-H3</f>
+        <v>0</v>
+      </c>
+      <c r="J3" t="s">
+        <v>129</v>
+      </c>
+      <c r="K3" t="s">
+        <v>22</v>
+      </c>
+      <c r="L3" t="s">
+        <v>112</v>
+      </c>
+      <c r="M3" t="s">
+        <v>66</v>
+      </c>
+      <c r="Q3">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="4" spans="1:17" x14ac:dyDescent="0.25">
+      <c r="B4" t="s">
+        <v>16</v>
+      </c>
+      <c r="C4" t="s">
+        <v>134</v>
+      </c>
+      <c r="D4" t="s">
+        <v>135</v>
+      </c>
+      <c r="E4" t="s">
+        <v>136</v>
+      </c>
+      <c r="F4" t="s">
+        <v>20</v>
+      </c>
+      <c r="G4" s="11">
+        <v>870</v>
+      </c>
+      <c r="H4" s="11">
+        <v>30</v>
+      </c>
+      <c r="I4" s="11">
+        <f>G4-H4</f>
+        <v>840</v>
+      </c>
+      <c r="J4" t="s">
+        <v>129</v>
+      </c>
+      <c r="K4" t="s">
+        <v>22</v>
+      </c>
+      <c r="L4" t="s">
+        <v>112</v>
+      </c>
+      <c r="Q4">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="5" spans="1:17" x14ac:dyDescent="0.25">
+      <c r="B5" t="s">
+        <v>16</v>
+      </c>
+      <c r="C5" t="s">
+        <v>145</v>
+      </c>
+      <c r="D5" t="s">
+        <v>146</v>
+      </c>
+      <c r="E5" t="s">
+        <v>147</v>
+      </c>
+      <c r="F5" s="11">
+        <v>8</v>
+      </c>
+      <c r="G5" s="11">
+        <v>0</v>
+      </c>
+      <c r="H5" s="11">
+        <v>25</v>
+      </c>
+      <c r="I5" s="11">
+        <f>-H5</f>
+        <v>-25</v>
+      </c>
+      <c r="J5" t="s">
+        <v>129</v>
+      </c>
+      <c r="K5" t="s">
+        <v>22</v>
+      </c>
+      <c r="L5" t="s">
+        <v>112</v>
+      </c>
+      <c r="Q5">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="6" spans="1:17" x14ac:dyDescent="0.25">
+      <c r="B6" t="s">
+        <v>16</v>
+      </c>
+      <c r="C6" t="s">
+        <v>151</v>
+      </c>
+      <c r="D6" t="s">
+        <v>152</v>
+      </c>
+      <c r="E6" t="s">
+        <v>153</v>
+      </c>
+      <c r="F6" s="11">
+        <v>7</v>
+      </c>
+      <c r="G6" s="11">
+        <v>650</v>
+      </c>
+      <c r="H6" s="11">
+        <v>30</v>
+      </c>
+      <c r="I6" s="11">
+        <f>G6-H6</f>
+        <v>620</v>
+      </c>
+      <c r="J6" t="s">
+        <v>129</v>
+      </c>
+      <c r="K6" t="s">
+        <v>22</v>
+      </c>
+      <c r="L6" t="s">
+        <v>112</v>
+      </c>
+      <c r="Q6">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="7" spans="1:17" x14ac:dyDescent="0.25">
+      <c r="B7" t="s">
+        <v>16</v>
+      </c>
+      <c r="C7" t="s">
+        <v>157</v>
+      </c>
+      <c r="D7" t="s">
+        <v>158</v>
+      </c>
+      <c r="E7" t="s">
+        <v>159</v>
+      </c>
+      <c r="F7" t="s">
+        <v>160</v>
+      </c>
+      <c r="G7" s="11">
+        <v>1215</v>
+      </c>
+      <c r="H7" s="11">
+        <v>35</v>
+      </c>
+      <c r="I7" s="11">
+        <f>G7-H7</f>
+        <v>1180</v>
+      </c>
+      <c r="J7" t="s">
+        <v>129</v>
+      </c>
+      <c r="K7" t="s">
+        <v>22</v>
+      </c>
+      <c r="L7" t="s">
+        <v>112</v>
+      </c>
+      <c r="Q7">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="8" spans="1:17" x14ac:dyDescent="0.25">
+      <c r="B8" t="s">
+        <v>16</v>
+      </c>
+      <c r="C8" t="s">
+        <v>164</v>
+      </c>
+      <c r="D8" t="s">
+        <v>165</v>
+      </c>
+      <c r="E8" t="s">
+        <v>166</v>
+      </c>
+      <c r="F8" s="11">
+        <v>7</v>
+      </c>
+      <c r="G8" s="11">
+        <v>740</v>
+      </c>
+      <c r="H8" s="11">
+        <v>30</v>
+      </c>
+      <c r="I8" s="11">
+        <f>G8-H8</f>
+        <v>710</v>
+      </c>
+      <c r="J8" t="s">
+        <v>129</v>
+      </c>
+      <c r="K8" t="s">
+        <v>22</v>
+      </c>
+      <c r="L8" t="s">
+        <v>112</v>
+      </c>
+      <c r="Q8">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="9" spans="1:17" x14ac:dyDescent="0.25">
+      <c r="B9" t="s">
+        <v>16</v>
+      </c>
+      <c r="C9" t="s">
+        <v>167</v>
+      </c>
+      <c r="D9" t="s">
+        <v>168</v>
+      </c>
+      <c r="E9" t="s">
+        <v>169</v>
+      </c>
+      <c r="F9" t="s">
+        <v>20</v>
+      </c>
+      <c r="G9" s="11">
+        <v>770</v>
+      </c>
+      <c r="H9" s="11">
+        <v>30</v>
+      </c>
+      <c r="I9" s="11">
+        <f>G9-H9</f>
+        <v>740</v>
+      </c>
+      <c r="J9" t="s">
+        <v>129</v>
+      </c>
+      <c r="K9" t="s">
+        <v>22</v>
+      </c>
+      <c r="L9" t="s">
+        <v>112</v>
+      </c>
+      <c r="Q9">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="10" spans="1:17" x14ac:dyDescent="0.25">
+      <c r="A10" t="s">
+        <v>83</v>
+      </c>
+      <c r="B10" t="s">
+        <v>16</v>
+      </c>
+      <c r="C10" t="s">
+        <v>110</v>
+      </c>
+      <c r="E10" t="s">
+        <v>111</v>
+      </c>
+      <c r="F10" s="11">
+        <v>6</v>
+      </c>
+      <c r="G10" s="11">
+        <v>70</v>
+      </c>
+      <c r="H10" s="11">
+        <v>70</v>
+      </c>
+      <c r="I10" s="11">
+        <f>G10-H10</f>
+        <v>0</v>
+      </c>
+      <c r="J10" t="s">
+        <v>22</v>
+      </c>
+      <c r="K10" t="s">
+        <v>22</v>
+      </c>
+      <c r="L10" t="s">
+        <v>112</v>
+      </c>
+      <c r="Q10">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="11" spans="1:17" x14ac:dyDescent="0.25">
+      <c r="A11" t="s">
+        <v>83</v>
+      </c>
+      <c r="B11" t="s">
+        <v>16</v>
+      </c>
+      <c r="C11" t="s">
+        <v>116</v>
+      </c>
+      <c r="E11" t="s">
+        <v>117</v>
+      </c>
+      <c r="F11" s="11">
+        <v>12</v>
+      </c>
+      <c r="G11" s="11">
+        <v>0</v>
+      </c>
+      <c r="H11" s="11">
+        <v>30</v>
+      </c>
+      <c r="I11" s="11">
+        <f>-H11</f>
+        <v>-30</v>
+      </c>
+      <c r="J11" t="s">
+        <v>22</v>
+      </c>
+      <c r="K11" t="s">
+        <v>22</v>
+      </c>
+      <c r="L11" t="s">
+        <v>112</v>
+      </c>
+      <c r="Q11">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="12" spans="1:17" x14ac:dyDescent="0.25">
+      <c r="A12" t="s">
+        <v>83</v>
+      </c>
+      <c r="B12" t="s">
+        <v>16</v>
+      </c>
+      <c r="C12" t="s">
+        <v>118</v>
+      </c>
+      <c r="E12" t="s">
+        <v>119</v>
+      </c>
+      <c r="F12" t="s">
+        <v>44</v>
+      </c>
+      <c r="G12" s="11">
+        <v>30</v>
+      </c>
+      <c r="H12" s="11">
+        <v>30</v>
+      </c>
+      <c r="I12" s="11">
+        <f>G12-H12</f>
+        <v>0</v>
+      </c>
+      <c r="J12" t="s">
+        <v>22</v>
+      </c>
+      <c r="K12" t="s">
+        <v>22</v>
+      </c>
+      <c r="L12" t="s">
+        <v>112</v>
+      </c>
+      <c r="Q12">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="13" spans="1:17" x14ac:dyDescent="0.25">
+      <c r="A13" t="s">
+        <v>83</v>
+      </c>
+      <c r="B13" t="s">
+        <v>16</v>
+      </c>
+      <c r="C13" t="s">
+        <v>120</v>
+      </c>
+      <c r="E13" t="s">
+        <v>121</v>
+      </c>
+      <c r="F13" t="s">
+        <v>86</v>
+      </c>
+      <c r="G13" s="11">
+        <v>530</v>
+      </c>
+      <c r="H13" s="11">
+        <v>30</v>
+      </c>
+      <c r="I13" s="11">
+        <f>G13-H13</f>
+        <v>500</v>
+      </c>
+      <c r="J13" t="s">
+        <v>22</v>
+      </c>
+      <c r="K13" t="s">
+        <v>22</v>
+      </c>
+      <c r="L13" t="s">
+        <v>112</v>
+      </c>
+      <c r="Q13">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="14" spans="1:17" x14ac:dyDescent="0.25">
+      <c r="B14" t="s">
+        <v>16</v>
+      </c>
+      <c r="C14" t="s">
+        <v>122</v>
+      </c>
+      <c r="D14" t="s">
+        <v>123</v>
+      </c>
+      <c r="E14" t="s">
+        <v>124</v>
+      </c>
+      <c r="F14" t="s">
+        <v>36</v>
+      </c>
+      <c r="G14" s="11">
+        <v>740</v>
+      </c>
+      <c r="H14" s="11">
+        <v>20</v>
+      </c>
+      <c r="I14" s="11">
+        <f>G14-H14</f>
+        <v>720</v>
+      </c>
+      <c r="J14" t="s">
+        <v>22</v>
+      </c>
+      <c r="K14" t="s">
+        <v>22</v>
+      </c>
+      <c r="L14" t="s">
+        <v>112</v>
+      </c>
+      <c r="Q14">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="15" spans="1:17" x14ac:dyDescent="0.25">
+      <c r="B15" t="s">
+        <v>16</v>
+      </c>
+      <c r="C15" t="s">
+        <v>130</v>
+      </c>
+      <c r="D15" t="s">
+        <v>131</v>
+      </c>
+      <c r="E15" t="s">
+        <v>132</v>
+      </c>
+      <c r="F15" t="s">
+        <v>133</v>
+      </c>
+      <c r="G15" s="11">
+        <v>0</v>
+      </c>
+      <c r="H15" s="11">
+        <v>30</v>
+      </c>
+      <c r="I15" s="11">
+        <f>-H15</f>
+        <v>-30</v>
+      </c>
+      <c r="J15" t="s">
+        <v>22</v>
+      </c>
+      <c r="K15" t="s">
+        <v>22</v>
+      </c>
+      <c r="L15" t="s">
+        <v>112</v>
+      </c>
+      <c r="Q15">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="16" spans="1:17" x14ac:dyDescent="0.25">
+      <c r="B16" t="s">
+        <v>16</v>
+      </c>
+      <c r="C16" t="s">
+        <v>140</v>
+      </c>
+      <c r="D16" t="s">
+        <v>141</v>
+      </c>
+      <c r="E16" t="s">
+        <v>142</v>
+      </c>
+      <c r="F16" t="s">
+        <v>36</v>
+      </c>
+      <c r="G16" s="11">
+        <v>510</v>
+      </c>
+      <c r="H16" s="11">
+        <v>20</v>
+      </c>
+      <c r="I16" s="11">
+        <f>G16-H16</f>
+        <v>490</v>
+      </c>
+      <c r="J16" t="s">
+        <v>22</v>
+      </c>
+      <c r="K16" t="s">
+        <v>22</v>
+      </c>
+      <c r="L16" t="s">
+        <v>112</v>
+      </c>
+      <c r="Q16">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="17" spans="1:17" x14ac:dyDescent="0.25">
+      <c r="B17" t="s">
+        <v>16</v>
+      </c>
+      <c r="C17" t="s">
+        <v>148</v>
+      </c>
+      <c r="D17" t="s">
+        <v>149</v>
+      </c>
+      <c r="E17" t="s">
+        <v>150</v>
+      </c>
+      <c r="F17" t="s">
+        <v>36</v>
+      </c>
+      <c r="G17" s="11">
+        <v>0</v>
+      </c>
+      <c r="H17" s="11">
+        <v>20</v>
+      </c>
+      <c r="I17" s="11">
+        <f>-H17</f>
+        <v>-20</v>
+      </c>
+      <c r="J17" t="s">
+        <v>22</v>
+      </c>
+      <c r="K17" t="s">
+        <v>22</v>
+      </c>
+      <c r="L17" t="s">
+        <v>112</v>
+      </c>
+      <c r="Q17">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="18" spans="1:17" x14ac:dyDescent="0.25">
+      <c r="B18" t="s">
+        <v>16</v>
+      </c>
+      <c r="C18" t="s">
+        <v>161</v>
+      </c>
+      <c r="D18" t="s">
+        <v>162</v>
+      </c>
+      <c r="E18" t="s">
+        <v>163</v>
+      </c>
+      <c r="F18" t="s">
+        <v>44</v>
+      </c>
+      <c r="G18" s="11">
+        <v>915</v>
+      </c>
+      <c r="H18" s="11">
+        <v>25</v>
+      </c>
+      <c r="I18" s="11">
+        <f>G18-H18</f>
+        <v>890</v>
+      </c>
+      <c r="J18" t="s">
+        <v>22</v>
+      </c>
+      <c r="K18" t="s">
+        <v>22</v>
+      </c>
+      <c r="L18" t="s">
+        <v>112</v>
+      </c>
+      <c r="Q18">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="19" spans="1:17" x14ac:dyDescent="0.25">
+      <c r="B19" t="s">
+        <v>16</v>
+      </c>
+      <c r="C19" t="s">
+        <v>173</v>
+      </c>
+      <c r="D19" t="s">
+        <v>174</v>
+      </c>
+      <c r="E19" t="s">
+        <v>175</v>
+      </c>
+      <c r="F19" t="s">
+        <v>36</v>
+      </c>
+      <c r="G19" s="11">
+        <v>0</v>
+      </c>
+      <c r="H19" s="11">
+        <v>20</v>
+      </c>
+      <c r="I19" s="11">
+        <f>-H19</f>
+        <v>-20</v>
+      </c>
+      <c r="J19" t="s">
+        <v>22</v>
+      </c>
+      <c r="K19" t="s">
+        <v>22</v>
+      </c>
+      <c r="L19" t="s">
+        <v>112</v>
+      </c>
+      <c r="Q19">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="20" spans="1:17" x14ac:dyDescent="0.25">
+      <c r="A20" t="s">
+        <v>83</v>
+      </c>
+      <c r="B20" t="s">
+        <v>16</v>
+      </c>
+      <c r="C20" t="s">
+        <v>113</v>
+      </c>
+      <c r="E20" t="s">
+        <v>114</v>
+      </c>
+      <c r="F20" t="s">
+        <v>86</v>
+      </c>
+      <c r="G20" s="11">
+        <v>0</v>
+      </c>
+      <c r="H20" s="11">
+        <v>30</v>
+      </c>
+      <c r="I20" s="11">
+        <f>-H20</f>
+        <v>-30</v>
+      </c>
+      <c r="J20" t="s">
+        <v>115</v>
+      </c>
+      <c r="K20" t="s">
+        <v>22</v>
+      </c>
+      <c r="L20" t="s">
+        <v>112</v>
+      </c>
+      <c r="Q20">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="21" spans="1:17" x14ac:dyDescent="0.25">
+      <c r="B21" t="s">
+        <v>16</v>
+      </c>
+      <c r="C21" t="s">
+        <v>137</v>
+      </c>
+      <c r="D21" t="s">
+        <v>138</v>
+      </c>
+      <c r="E21" t="s">
+        <v>139</v>
+      </c>
+      <c r="F21" s="11">
+        <v>1</v>
+      </c>
+      <c r="G21" s="11">
+        <v>695</v>
+      </c>
+      <c r="H21" s="11">
+        <v>25</v>
+      </c>
+      <c r="I21" s="11">
+        <f>G21-H21</f>
+        <v>670</v>
+      </c>
+      <c r="J21" t="s">
+        <v>115</v>
+      </c>
+      <c r="K21" t="s">
+        <v>22</v>
+      </c>
+      <c r="L21" t="s">
+        <v>112</v>
+      </c>
+      <c r="Q21">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="22" spans="1:17" x14ac:dyDescent="0.25">
+      <c r="B22" t="s">
+        <v>16</v>
+      </c>
+      <c r="C22" t="s">
+        <v>118</v>
+      </c>
+      <c r="D22" t="s">
+        <v>143</v>
+      </c>
+      <c r="E22" t="s">
+        <v>144</v>
+      </c>
+      <c r="F22" s="11">
+        <v>10</v>
+      </c>
+      <c r="G22" s="11">
+        <v>775</v>
+      </c>
+      <c r="H22" s="11">
+        <v>25</v>
+      </c>
+      <c r="I22" s="11">
+        <f>G22-H22</f>
+        <v>750</v>
+      </c>
+      <c r="J22" t="s">
+        <v>115</v>
+      </c>
+      <c r="K22" t="s">
+        <v>22</v>
+      </c>
+      <c r="L22" t="s">
+        <v>112</v>
+      </c>
+      <c r="Q22">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="23" spans="1:17" x14ac:dyDescent="0.25">
+      <c r="B23" t="s">
+        <v>16</v>
+      </c>
+      <c r="C23" t="s">
+        <v>154</v>
+      </c>
+      <c r="D23" t="s">
+        <v>155</v>
+      </c>
+      <c r="E23" t="s">
+        <v>156</v>
+      </c>
+      <c r="F23" s="11">
+        <v>1</v>
+      </c>
+      <c r="G23" s="11">
+        <v>895</v>
+      </c>
+      <c r="H23" s="11">
+        <v>25</v>
+      </c>
+      <c r="I23" s="11">
+        <f>G23-H23</f>
+        <v>870</v>
+      </c>
+      <c r="J23" t="s">
+        <v>115</v>
+      </c>
+      <c r="K23" t="s">
+        <v>22</v>
+      </c>
+      <c r="L23" t="s">
+        <v>112</v>
+      </c>
+      <c r="Q23">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="24" spans="1:17" x14ac:dyDescent="0.25">
+      <c r="B24" t="s">
+        <v>16</v>
+      </c>
+      <c r="C24" t="s">
+        <v>170</v>
+      </c>
+      <c r="D24" t="s">
+        <v>171</v>
+      </c>
+      <c r="E24" t="s">
+        <v>172</v>
+      </c>
+      <c r="F24" s="11">
+        <v>1</v>
+      </c>
+      <c r="G24" s="11">
+        <v>695</v>
+      </c>
+      <c r="H24" s="11">
+        <v>25</v>
+      </c>
+      <c r="I24" s="11">
+        <f>G24-H24</f>
+        <v>670</v>
+      </c>
+      <c r="J24" t="s">
+        <v>115</v>
+      </c>
+      <c r="K24" t="s">
+        <v>22</v>
+      </c>
+      <c r="L24" t="s">
+        <v>112</v>
+      </c>
+      <c r="Q24">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="26" spans="1:17" x14ac:dyDescent="0.25">
+      <c r="D26" s="6">
+        <f>COUNTA(D3:D24)</f>
+        <v>17</v>
+      </c>
+      <c r="G26" s="6">
+        <f t="shared" ref="G26:Q26" si="0">SUBTOTAL(9,G3:G24)</f>
+        <v>10135</v>
+      </c>
+      <c r="H26" s="6">
+        <f t="shared" si="0"/>
+        <v>640</v>
+      </c>
+      <c r="I26" s="6">
+        <f t="shared" si="0"/>
+        <v>9495</v>
+      </c>
+      <c r="J26" s="6">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+      <c r="K26" s="6">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+      <c r="L26" s="6">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+      <c r="M26" s="6">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+      <c r="N26" s="6">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+      <c r="O26" s="6">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+      <c r="P26" s="6">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+      <c r="Q26" s="6">
+        <f t="shared" si="0"/>
+        <v>22</v>
+      </c>
+    </row>
+    <row r="27" spans="1:17" x14ac:dyDescent="0.25">
+      <c r="H27">
+        <f>-3*17</f>
+        <v>-51</v>
+      </c>
+    </row>
+    <row r="28" spans="1:17" x14ac:dyDescent="0.25">
+      <c r="A28" s="6" t="s">
+        <v>16</v>
+      </c>
+      <c r="C28" s="5" t="s">
+        <v>89</v>
+      </c>
+      <c r="D28" s="5"/>
+      <c r="E28" s="9" t="s">
+        <v>90</v>
+      </c>
+      <c r="H28">
+        <f>-2*25</f>
+        <v>-50</v>
+      </c>
+      <c r="K28" s="12" t="s">
+        <v>22</v>
+      </c>
+      <c r="L28" s="12" t="s">
+        <v>91</v>
+      </c>
+      <c r="M28" s="12" t="s">
+        <v>90</v>
+      </c>
+      <c r="O28" s="9" t="s">
+        <v>92</v>
+      </c>
+    </row>
+    <row r="29" spans="1:17" x14ac:dyDescent="0.25">
+      <c r="A29" t="s">
+        <v>112</v>
+      </c>
+      <c r="B29" s="8" t="s">
+        <v>93</v>
+      </c>
+      <c r="C29" s="4">
+        <f>SUMIFS(I$3:I$24,B$3:B$24,A$28,L$3:L$24,A$29)</f>
+        <v>9495</v>
+      </c>
+      <c r="D29" s="4"/>
+      <c r="E29" s="8">
+        <f>SUMIFS(Q$3:Q$24,B$3:B$24,A$28,L$3:L$24,A$29)</f>
+        <v>22</v>
+      </c>
+      <c r="F29" t="s">
+        <v>94</v>
+      </c>
+      <c r="H29">
+        <f>-2*30</f>
+        <v>-60</v>
+      </c>
+      <c r="K29" t="s">
+        <v>95</v>
+      </c>
+      <c r="L29">
+        <f>SUMIFS(G$3:G$24,J$3:J$24,K$28)</f>
+        <v>2795</v>
+      </c>
+      <c r="M29">
+        <f>SUMIFS(Q$3:Q$24,J$3:J$24,K$28)</f>
+        <v>10</v>
+      </c>
+      <c r="O29" t="s">
+        <v>22</v>
+      </c>
+      <c r="P29">
+        <f>L34</f>
+        <v>2506</v>
+      </c>
+    </row>
+    <row r="30" spans="1:17" x14ac:dyDescent="0.25">
+      <c r="B30" s="7" t="s">
+        <v>97</v>
+      </c>
+      <c r="C30" s="3">
+        <v>0</v>
+      </c>
+      <c r="D30" s="3"/>
+      <c r="K30" t="s">
+        <v>98</v>
+      </c>
+      <c r="L30">
+        <f>-SUMIFS(H$3:H$24,J$3:J$24,K$28)+M30*5</f>
+        <v>-245</v>
+      </c>
+      <c r="M30">
+        <f>SUMIFS(Q$3:Q$24,J$3:J$24,K$28)-COUNTIFS(J$3:J$24,K$28,M$3:M$24,"*gộp*")</f>
+        <v>10</v>
+      </c>
+      <c r="O30" t="s">
+        <v>115</v>
+      </c>
+      <c r="P30">
+        <f>L42</f>
+        <v>2955</v>
+      </c>
+    </row>
+    <row r="31" spans="1:17" x14ac:dyDescent="0.25">
+      <c r="B31" s="7" t="s">
+        <v>99</v>
+      </c>
+      <c r="C31" s="3">
+        <f>-SUMIFS(I$3:I$24,B$3:B$24,A$28,P$3:P$24,"xx",N$3:N$24,"x")</f>
+        <v>0</v>
+      </c>
+      <c r="D31" s="3"/>
+      <c r="E31" s="7">
+        <f>SUMIFS(Q$3:Q$24,B$3:B$24,A$28,P$3:P$24,"xx",N$3:N$24,"x")</f>
+        <v>0</v>
+      </c>
+      <c r="K31" t="s">
+        <v>100</v>
+      </c>
+      <c r="L31">
+        <f>-M31*2</f>
+        <v>-44</v>
+      </c>
+      <c r="M31">
+        <f>Q26-(COUNTIFS(M$3:M$24,"*gộp*")/2)-COUNTIFS(P$3:P$24,"*xx*")</f>
+        <v>22</v>
+      </c>
+      <c r="O31" t="s">
+        <v>176</v>
+      </c>
+      <c r="P31">
+        <f>L50</f>
+        <v>4119</v>
+      </c>
+    </row>
+    <row r="32" spans="1:17" x14ac:dyDescent="0.25">
+      <c r="B32" s="9" t="s">
+        <v>101</v>
+      </c>
+      <c r="C32" s="5">
+        <f>SUBTOTAL(9,C29:C31)</f>
+        <v>9495</v>
+      </c>
+      <c r="D32" s="5"/>
+      <c r="E32">
+        <f>E29</f>
+        <v>22</v>
+      </c>
+      <c r="K32" s="7" t="s">
+        <v>102</v>
+      </c>
+      <c r="O32" t="s">
+        <v>103</v>
+      </c>
+      <c r="P32">
+        <f>-C36</f>
+        <v>-9495</v>
+      </c>
+    </row>
+    <row r="33" spans="2:16" x14ac:dyDescent="0.25">
+      <c r="B33" s="7" t="s">
+        <v>104</v>
+      </c>
+      <c r="C33" s="2"/>
+      <c r="D33" s="2"/>
+      <c r="K33" s="7" t="s">
+        <v>105</v>
+      </c>
+      <c r="O33" s="9" t="s">
+        <v>106</v>
+      </c>
+      <c r="P33" s="9">
+        <f>SUBTOTAL(9,P29:P32)</f>
+        <v>85</v>
+      </c>
+    </row>
+    <row r="34" spans="2:16" x14ac:dyDescent="0.25">
+      <c r="B34" s="13" t="s">
+        <v>107</v>
+      </c>
+      <c r="C34" s="2"/>
+      <c r="D34" s="2"/>
+      <c r="L34" s="14">
+        <f>SUBTOTAL(9,L29:L33)</f>
+        <v>2506</v>
+      </c>
+      <c r="M34" s="14">
+        <f>M29</f>
+        <v>10</v>
+      </c>
+    </row>
+    <row r="36" spans="2:16" x14ac:dyDescent="0.25">
+      <c r="B36" s="6" t="s">
+        <v>108</v>
+      </c>
+      <c r="C36" s="1">
+        <f>C32+C33+C34</f>
+        <v>9495</v>
+      </c>
+      <c r="D36" s="1"/>
+      <c r="E36" s="6" t="s">
+        <v>109</v>
+      </c>
+      <c r="K36" s="12" t="s">
+        <v>115</v>
+      </c>
+      <c r="L36" s="12" t="s">
+        <v>91</v>
+      </c>
+      <c r="M36" s="12" t="s">
+        <v>90</v>
+      </c>
+    </row>
+    <row r="37" spans="2:16" x14ac:dyDescent="0.25">
+      <c r="K37" t="s">
+        <v>95</v>
+      </c>
+      <c r="L37">
+        <f>SUMIFS(G$3:G$24,J$3:J$24,K$36)</f>
+        <v>3060</v>
+      </c>
+      <c r="M37">
+        <f>SUMIFS(Q$3:Q$24,J$3:J$24,K$36)</f>
+        <v>5</v>
+      </c>
+    </row>
+    <row r="38" spans="2:16" x14ac:dyDescent="0.25">
+      <c r="K38" t="s">
+        <v>98</v>
+      </c>
+      <c r="L38">
+        <f>-SUMIFS(H$3:H$24,J$3:J$24,K$36)+M38*5</f>
+        <v>-105</v>
+      </c>
+      <c r="M38">
+        <f>SUMIFS(Q$3:Q$24,J$3:J$24,K$36)-COUNTIFS(J$3:J$24,K$36,M$3:M$24,"*gộp*")</f>
+        <v>5</v>
+      </c>
+    </row>
+    <row r="39" spans="2:16" x14ac:dyDescent="0.25">
+      <c r="K39" t="s">
+        <v>100</v>
+      </c>
+    </row>
+    <row r="40" spans="2:16" x14ac:dyDescent="0.25">
+      <c r="K40" s="7" t="s">
+        <v>102</v>
+      </c>
+    </row>
+    <row r="41" spans="2:16" x14ac:dyDescent="0.25">
+      <c r="K41" s="7" t="s">
+        <v>105</v>
+      </c>
+    </row>
+    <row r="42" spans="2:16" x14ac:dyDescent="0.25">
+      <c r="L42" s="14">
+        <f>SUBTOTAL(9,L37:L41)</f>
+        <v>2955</v>
+      </c>
+      <c r="M42" s="14">
+        <f>M37</f>
+        <v>5</v>
+      </c>
+    </row>
+    <row r="44" spans="2:16" x14ac:dyDescent="0.25">
+      <c r="K44" s="12" t="s">
+        <v>129</v>
+      </c>
+      <c r="L44" s="12" t="s">
+        <v>91</v>
+      </c>
+      <c r="M44" s="12" t="s">
+        <v>90</v>
+      </c>
+    </row>
+    <row r="45" spans="2:16" x14ac:dyDescent="0.25">
+      <c r="K45" t="s">
+        <v>95</v>
+      </c>
+      <c r="L45">
+        <f>SUMIFS(G$3:G$24,J$3:J$24,K$44)</f>
+        <v>4280</v>
+      </c>
+      <c r="M45">
+        <f>SUMIFS(Q$3:Q$24,J$3:J$24,K$44)</f>
+        <v>7</v>
+      </c>
+    </row>
+    <row r="46" spans="2:16" x14ac:dyDescent="0.25">
+      <c r="K46" t="s">
+        <v>98</v>
+      </c>
+      <c r="L46">
+        <f>SUM(H27:H29)</f>
+        <v>-161</v>
+      </c>
+      <c r="M46">
+        <f>SUMIFS(Q$3:Q$24,J$3:J$24,K$44)</f>
+        <v>7</v>
+      </c>
+    </row>
+    <row r="47" spans="2:16" x14ac:dyDescent="0.25">
+      <c r="K47" t="s">
+        <v>100</v>
+      </c>
+    </row>
+    <row r="48" spans="2:16" x14ac:dyDescent="0.25">
+      <c r="K48" s="7" t="s">
+        <v>102</v>
+      </c>
+    </row>
+    <row r="49" spans="11:13" x14ac:dyDescent="0.25">
+      <c r="K49" s="7" t="s">
+        <v>105</v>
+      </c>
+    </row>
+    <row r="50" spans="11:13" x14ac:dyDescent="0.25">
+      <c r="L50" s="14">
+        <f>SUBTOTAL(9,L45:L49)</f>
+        <v>4119</v>
+      </c>
+      <c r="M50" s="14">
+        <f>M45</f>
+        <v>7</v>
+      </c>
+    </row>
+  </sheetData>
+  <autoFilter ref="A2:P24" xr:uid="{00000000-0009-0000-0000-000001000000}">
+    <sortState xmlns:xlrd2="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata2" ref="A3:P24">
+      <sortCondition ref="J2:J24"/>
+    </sortState>
+  </autoFilter>
+  <mergeCells count="8">
+    <mergeCell ref="C33:D33"/>
+    <mergeCell ref="C34:D34"/>
+    <mergeCell ref="C36:D36"/>
+    <mergeCell ref="C28:D28"/>
+    <mergeCell ref="C29:D29"/>
+    <mergeCell ref="C30:D30"/>
+    <mergeCell ref="C31:D31"/>
+    <mergeCell ref="C32:D32"/>
+  </mergeCells>
+  <pageMargins left="0.75" right="0.75" top="0.75" bottom="0.5" header="0.5" footer="0.75"/>
+</worksheet>
 </file>
--- a/data/Apr/InternalDailyReport.xlsx
+++ b/data/Apr/InternalDailyReport.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\Work\Freelance\TextInputter\data\Apr\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{B470E9D5-A55B-42A0-9E9A-48F3F6EB7BB5}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{59C4206F-BE86-4528-ADEA-D17132EDA031}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" activeTab="4" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" activeTab="5" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="01-04" sheetId="2" r:id="rId1"/>
@@ -18,6 +18,7 @@
     <sheet name="03-04" sheetId="7" r:id="rId3"/>
     <sheet name="04-04" sheetId="8" r:id="rId4"/>
     <sheet name="06-04" sheetId="10" r:id="rId5"/>
+    <sheet name="07-04" sheetId="11" r:id="rId6"/>
   </sheets>
   <definedNames>
     <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'01-04'!$A$2:$P$23</definedName>
@@ -25,6 +26,7 @@
     <definedName name="_xlnm._FilterDatabase" localSheetId="2" hidden="1">'03-04'!$A$2:$P$53</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="3" hidden="1">'04-04'!$A$2:$P$44</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="4" hidden="1">'06-04'!$A$2:$P$55</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="5" hidden="1">'07-04'!$A$2:$P$29</definedName>
   </definedNames>
   <calcPr calcId="191029"/>
   <extLst>
@@ -44,7 +46,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1746" uniqueCount="594">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2015" uniqueCount="663">
   <si>
     <t>Tình trạng TT</t>
   </si>
@@ -1826,13 +1828,220 @@
   </si>
   <si>
     <t>at 06-04</t>
+  </si>
+  <si>
+    <t>Hồng Hoa</t>
+  </si>
+  <si>
+    <t>HD008716</t>
+  </si>
+  <si>
+    <t>chung cư Feliz en vista số 1 lệ hiến mai p thạnh mỹ lợi</t>
+  </si>
+  <si>
+    <t>07-04-2026</t>
+  </si>
+  <si>
+    <t>Thỏ Bunny</t>
+  </si>
+  <si>
+    <t>HD007988</t>
+  </si>
+  <si>
+    <t>Vinhomes Golden River - Aqua 2, Ton Duc Thang, ward Ben Nghe</t>
+  </si>
+  <si>
+    <t>Winnie</t>
+  </si>
+  <si>
+    <t>HD008429</t>
+  </si>
+  <si>
+    <t>79/27 Trần Văn Đang, P. Nhiêu Lộc</t>
+  </si>
+  <si>
+    <t>Tracyy An</t>
+  </si>
+  <si>
+    <t>HD008658</t>
+  </si>
+  <si>
+    <t>226 gò dưa tam bình</t>
+  </si>
+  <si>
+    <t>Trần Hy Kim Ngân</t>
+  </si>
+  <si>
+    <t>HD008694</t>
+  </si>
+  <si>
+    <t>125/16/33 bùi đình tuy phường 14</t>
+  </si>
+  <si>
+    <t>Phan Nhi</t>
+  </si>
+  <si>
+    <t>HD008516</t>
+  </si>
+  <si>
+    <t>107/189 quang trung, f.10</t>
+  </si>
+  <si>
+    <t>Vy Nguyên</t>
+  </si>
+  <si>
+    <t>HD008724</t>
+  </si>
+  <si>
+    <t>101 đường cn 11, phường sơn kỳ</t>
+  </si>
+  <si>
+    <t>AT 07-04</t>
+  </si>
+  <si>
+    <t>Nany Nany</t>
+  </si>
+  <si>
+    <t>HD008494</t>
+  </si>
+  <si>
+    <t>616/5/6 lê trọng tấn phường Bình Hưng Hòa</t>
+  </si>
+  <si>
+    <t>phuong phuong (inst bedaunee)</t>
+  </si>
+  <si>
+    <t>HD008639</t>
+  </si>
+  <si>
+    <t>479 trần xuân soạn, phường tân kiểng</t>
+  </si>
+  <si>
+    <t>Minh Hải zalo cẩm ngân</t>
+  </si>
+  <si>
+    <t>HD008644</t>
+  </si>
+  <si>
+    <t>17 Đường Số 13 Phường Bình Hưng Hòa</t>
+  </si>
+  <si>
+    <t>Ivy Dao</t>
+  </si>
+  <si>
+    <t>HD008553</t>
+  </si>
+  <si>
+    <t>238/3 trường chinh, đông hưng thuận</t>
+  </si>
+  <si>
+    <t>Lam Nguyên</t>
+  </si>
+  <si>
+    <t>HD008721</t>
+  </si>
+  <si>
+    <t>M37/15 Cư Xá Phú Lâm A Phường 12</t>
+  </si>
+  <si>
+    <t>Jessie Beauty</t>
+  </si>
+  <si>
+    <t>HD008545</t>
+  </si>
+  <si>
+    <t>71/2/13 Nguyễn Bặc, Phường 3</t>
+  </si>
+  <si>
+    <t>tran Bảo Châu</t>
+  </si>
+  <si>
+    <t>HD008482</t>
+  </si>
+  <si>
+    <t>654/6 lạc long quân p9</t>
+  </si>
+  <si>
+    <t>Châu Phạm</t>
+  </si>
+  <si>
+    <t>HD008691</t>
+  </si>
+  <si>
+    <t>2050 phạm thể hiển p6</t>
+  </si>
+  <si>
+    <t>HD008669</t>
+  </si>
+  <si>
+    <t>Đào Hạnh nhận hộ An Hy</t>
+  </si>
+  <si>
+    <t>HD008648</t>
+  </si>
+  <si>
+    <t>24 Yên Thế, Phường 2</t>
+  </si>
+  <si>
+    <t>Võ Diễm My</t>
+  </si>
+  <si>
+    <t>HD008657</t>
+  </si>
+  <si>
+    <t>121 hiệp bình - p hiệp bình chánh</t>
+  </si>
+  <si>
+    <t>Nhung Lê</t>
+  </si>
+  <si>
+    <t>HD008600</t>
+  </si>
+  <si>
+    <t>188/15 đường số 4 phường 16</t>
+  </si>
+  <si>
+    <t>NGÂN HÀ</t>
+  </si>
+  <si>
+    <t>40 đường 53 p10</t>
+  </si>
+  <si>
+    <t>UYÊN MI</t>
+  </si>
+  <si>
+    <t>93/1 Nguyễn Chí Thanh P9</t>
+  </si>
+  <si>
+    <t>A nam</t>
+  </si>
+  <si>
+    <t>40/11B ấp 42 xã bà điểm</t>
+  </si>
+  <si>
+    <t>jenny bouti</t>
+  </si>
+  <si>
+    <t>401 Quang trung f10</t>
+  </si>
+  <si>
+    <t>HCM warehouse address</t>
+  </si>
+  <si>
+    <t>14 Lam Thi Ho, Tan Chanh Hiep Ward</t>
+  </si>
+  <si>
+    <t>Pachara (BN6994) hạnh Narin</t>
+  </si>
+  <si>
+    <t>at 07-04</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="4" x14ac:knownFonts="1">
+  <fonts count="5" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color rgb="FF000000"/>
@@ -1857,6 +2066,13 @@
       <color rgb="FF00B050"/>
       <name val="Calibri"/>
       <family val="2"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FFFF0000"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+      <scheme val="minor"/>
     </font>
   </fonts>
   <fills count="8">
@@ -1910,13 +2126,8 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyBorder="0"/>
   </cellStyleXfs>
-  <cellXfs count="19">
+  <cellXfs count="23">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
-    <xf numFmtId="0" fontId="1" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="0" fontId="0" fillId="3" borderId="0" xfId="0" applyFill="1"/>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="1" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="0" fillId="3" borderId="0" xfId="0" applyFill="1"/>
@@ -1932,6 +2143,15 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment horizontal="right"/>
     </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="3" fontId="4" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
+    <xf numFmtId="49" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
+    <xf numFmtId="49" fontId="2" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
+    <xf numFmtId="0" fontId="1" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="0" fillId="3" borderId="0" xfId="0" applyFill="1"/>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -2256,52 +2476,52 @@
   </cols>
   <sheetData>
     <row r="2" spans="1:17" x14ac:dyDescent="0.25">
-      <c r="A2" s="10" t="s">
+      <c r="A2" s="5" t="s">
         <v>0</v>
       </c>
-      <c r="B2" s="10" t="s">
-        <v>1</v>
-      </c>
-      <c r="C2" s="10" t="s">
+      <c r="B2" s="5" t="s">
+        <v>1</v>
+      </c>
+      <c r="C2" s="5" t="s">
         <v>2</v>
       </c>
-      <c r="D2" s="10" t="s">
+      <c r="D2" s="5" t="s">
         <v>3</v>
       </c>
-      <c r="E2" s="10" t="s">
+      <c r="E2" s="5" t="s">
         <v>4</v>
       </c>
-      <c r="F2" s="10" t="s">
+      <c r="F2" s="5" t="s">
         <v>5</v>
       </c>
-      <c r="G2" s="10" t="s">
+      <c r="G2" s="5" t="s">
         <v>6</v>
       </c>
-      <c r="H2" s="10" t="s">
+      <c r="H2" s="5" t="s">
         <v>7</v>
       </c>
-      <c r="I2" s="10" t="s">
+      <c r="I2" s="5" t="s">
         <v>8</v>
       </c>
-      <c r="J2" s="10" t="s">
+      <c r="J2" s="5" t="s">
         <v>9</v>
       </c>
-      <c r="K2" s="10" t="s">
+      <c r="K2" s="5" t="s">
         <v>10</v>
       </c>
-      <c r="L2" s="10" t="s">
+      <c r="L2" s="5" t="s">
         <v>11</v>
       </c>
-      <c r="M2" s="10" t="s">
+      <c r="M2" s="5" t="s">
         <v>12</v>
       </c>
-      <c r="N2" s="10" t="s">
+      <c r="N2" s="5" t="s">
         <v>13</v>
       </c>
-      <c r="O2" s="10" t="s">
+      <c r="O2" s="5" t="s">
         <v>14</v>
       </c>
-      <c r="P2" s="10" t="s">
+      <c r="P2" s="5" t="s">
         <v>15</v>
       </c>
     </row>
@@ -2321,13 +2541,13 @@
       <c r="F3" t="s">
         <v>20</v>
       </c>
-      <c r="G3" s="11">
+      <c r="G3" s="6">
         <v>0</v>
       </c>
-      <c r="H3" s="11">
+      <c r="H3" s="6">
         <v>30</v>
       </c>
-      <c r="I3" s="11">
+      <c r="I3" s="6">
         <f>-H3</f>
         <v>-30</v>
       </c>
@@ -2357,16 +2577,16 @@
       <c r="E4" t="s">
         <v>26</v>
       </c>
-      <c r="F4" s="11">
+      <c r="F4" s="6">
         <v>7</v>
       </c>
-      <c r="G4" s="11">
+      <c r="G4" s="6">
         <v>850</v>
       </c>
-      <c r="H4" s="11">
+      <c r="H4" s="6">
         <v>30</v>
       </c>
-      <c r="I4" s="11">
+      <c r="I4" s="6">
         <f>G4-H4</f>
         <v>820</v>
       </c>
@@ -2396,16 +2616,16 @@
       <c r="E5" t="s">
         <v>29</v>
       </c>
-      <c r="F5" s="11">
+      <c r="F5" s="6">
         <v>3</v>
       </c>
-      <c r="G5" s="11">
+      <c r="G5" s="6">
         <v>695</v>
       </c>
-      <c r="H5" s="11">
+      <c r="H5" s="6">
         <v>25</v>
       </c>
-      <c r="I5" s="11">
+      <c r="I5" s="6">
         <f>G5-H5</f>
         <v>670</v>
       </c>
@@ -2435,16 +2655,16 @@
       <c r="E6" t="s">
         <v>32</v>
       </c>
-      <c r="F6" s="11">
+      <c r="F6" s="6">
         <v>7</v>
       </c>
-      <c r="G6" s="11">
+      <c r="G6" s="6">
         <v>740</v>
       </c>
-      <c r="H6" s="11">
+      <c r="H6" s="6">
         <v>30</v>
       </c>
-      <c r="I6" s="11">
+      <c r="I6" s="6">
         <f>G6-H6</f>
         <v>710</v>
       </c>
@@ -2477,13 +2697,13 @@
       <c r="F7" t="s">
         <v>36</v>
       </c>
-      <c r="G7" s="11">
+      <c r="G7" s="6">
         <v>0</v>
       </c>
-      <c r="H7" s="11">
+      <c r="H7" s="6">
         <v>20</v>
       </c>
-      <c r="I7" s="11">
+      <c r="I7" s="6">
         <f>-H7</f>
         <v>-20</v>
       </c>
@@ -2513,16 +2733,16 @@
       <c r="E8" t="s">
         <v>39</v>
       </c>
-      <c r="F8" s="11">
+      <c r="F8" s="6">
         <v>9</v>
       </c>
-      <c r="G8" s="11">
+      <c r="G8" s="6">
         <v>780</v>
       </c>
-      <c r="H8" s="11">
+      <c r="H8" s="6">
         <v>30</v>
       </c>
-      <c r="I8" s="11">
+      <c r="I8" s="6">
         <f>G8-H8</f>
         <v>750</v>
       </c>
@@ -2555,13 +2775,13 @@
       <c r="F9" t="s">
         <v>44</v>
       </c>
-      <c r="G9" s="11">
+      <c r="G9" s="6">
         <v>615</v>
       </c>
-      <c r="H9" s="11">
+      <c r="H9" s="6">
         <v>25</v>
       </c>
-      <c r="I9" s="11">
+      <c r="I9" s="6">
         <f>G9-H9</f>
         <v>590</v>
       </c>
@@ -2594,13 +2814,13 @@
       <c r="F10" t="s">
         <v>20</v>
       </c>
-      <c r="G10" s="11">
+      <c r="G10" s="6">
         <v>610</v>
       </c>
-      <c r="H10" s="11">
+      <c r="H10" s="6">
         <v>30</v>
       </c>
-      <c r="I10" s="11">
+      <c r="I10" s="6">
         <f>G10-H10</f>
         <v>580</v>
       </c>
@@ -2630,16 +2850,16 @@
       <c r="E11" t="s">
         <v>50</v>
       </c>
-      <c r="F11" s="11">
+      <c r="F11" s="6">
         <v>8</v>
       </c>
-      <c r="G11" s="11">
+      <c r="G11" s="6">
         <v>0</v>
       </c>
-      <c r="H11" s="11">
+      <c r="H11" s="6">
         <v>25</v>
       </c>
-      <c r="I11" s="11">
+      <c r="I11" s="6">
         <f>-H11</f>
         <v>-25</v>
       </c>
@@ -2669,16 +2889,16 @@
       <c r="E12" t="s">
         <v>53</v>
       </c>
-      <c r="F12" s="11">
-        <v>1</v>
-      </c>
-      <c r="G12" s="11">
+      <c r="F12" s="6">
+        <v>1</v>
+      </c>
+      <c r="G12" s="6">
         <v>845</v>
       </c>
-      <c r="H12" s="11">
+      <c r="H12" s="6">
         <v>25</v>
       </c>
-      <c r="I12" s="11">
+      <c r="I12" s="6">
         <f t="shared" ref="I12:I21" si="0">G12-H12</f>
         <v>820</v>
       </c>
@@ -2708,16 +2928,16 @@
       <c r="E13" t="s">
         <v>56</v>
       </c>
-      <c r="F13" s="11">
+      <c r="F13" s="6">
         <v>12</v>
       </c>
-      <c r="G13" s="11">
+      <c r="G13" s="6">
         <v>750</v>
       </c>
-      <c r="H13" s="11">
+      <c r="H13" s="6">
         <v>30</v>
       </c>
-      <c r="I13" s="11">
+      <c r="I13" s="6">
         <f t="shared" si="0"/>
         <v>720</v>
       </c>
@@ -2750,13 +2970,13 @@
       <c r="F14" t="s">
         <v>36</v>
       </c>
-      <c r="G14" s="11">
+      <c r="G14" s="6">
         <v>1630</v>
       </c>
-      <c r="H14" s="11">
+      <c r="H14" s="6">
         <v>20</v>
       </c>
-      <c r="I14" s="11">
+      <c r="I14" s="6">
         <f t="shared" si="0"/>
         <v>1610</v>
       </c>
@@ -2786,16 +3006,16 @@
       <c r="E15" t="s">
         <v>62</v>
       </c>
-      <c r="F15" s="11">
+      <c r="F15" s="6">
         <v>3</v>
       </c>
-      <c r="G15" s="11">
+      <c r="G15" s="6">
         <v>405</v>
       </c>
-      <c r="H15" s="11">
+      <c r="H15" s="6">
         <v>25</v>
       </c>
-      <c r="I15" s="11">
+      <c r="I15" s="6">
         <f t="shared" si="0"/>
         <v>380</v>
       </c>
@@ -2825,16 +3045,16 @@
       <c r="E16" t="s">
         <v>65</v>
       </c>
-      <c r="F16" s="11">
+      <c r="F16" s="6">
         <v>7</v>
       </c>
-      <c r="G16" s="11">
+      <c r="G16" s="6">
         <v>30</v>
       </c>
-      <c r="H16" s="11">
+      <c r="H16" s="6">
         <v>30</v>
       </c>
-      <c r="I16" s="11">
+      <c r="I16" s="6">
         <f t="shared" si="0"/>
         <v>0</v>
       </c>
@@ -2867,16 +3087,16 @@
       <c r="E17" t="s">
         <v>69</v>
       </c>
-      <c r="F17" s="11">
+      <c r="F17" s="6">
         <v>7</v>
       </c>
-      <c r="G17" s="11">
+      <c r="G17" s="6">
         <v>1640</v>
       </c>
-      <c r="H17" s="11">
+      <c r="H17" s="6">
         <v>30</v>
       </c>
-      <c r="I17" s="11">
+      <c r="I17" s="6">
         <f t="shared" si="0"/>
         <v>1610</v>
       </c>
@@ -2906,16 +3126,16 @@
       <c r="E18" t="s">
         <v>72</v>
       </c>
-      <c r="F18" s="11">
+      <c r="F18" s="6">
         <v>12</v>
       </c>
-      <c r="G18" s="11">
+      <c r="G18" s="6">
         <v>590</v>
       </c>
-      <c r="H18" s="11">
+      <c r="H18" s="6">
         <v>30</v>
       </c>
-      <c r="I18" s="11">
+      <c r="I18" s="6">
         <f t="shared" si="0"/>
         <v>560</v>
       </c>
@@ -2945,16 +3165,16 @@
       <c r="E19" t="s">
         <v>75</v>
       </c>
-      <c r="F19" s="11">
+      <c r="F19" s="6">
         <v>7</v>
       </c>
-      <c r="G19" s="11">
+      <c r="G19" s="6">
         <v>850</v>
       </c>
-      <c r="H19" s="11">
+      <c r="H19" s="6">
         <v>30</v>
       </c>
-      <c r="I19" s="11">
+      <c r="I19" s="6">
         <f t="shared" si="0"/>
         <v>820</v>
       </c>
@@ -2987,13 +3207,13 @@
       <c r="F20" t="s">
         <v>79</v>
       </c>
-      <c r="G20" s="11">
+      <c r="G20" s="6">
         <v>20</v>
       </c>
-      <c r="H20" s="11">
+      <c r="H20" s="6">
         <v>20</v>
       </c>
-      <c r="I20" s="11">
+      <c r="I20" s="6">
         <f t="shared" si="0"/>
         <v>0</v>
       </c>
@@ -3029,13 +3249,13 @@
       <c r="F21" t="s">
         <v>20</v>
       </c>
-      <c r="G21" s="11">
+      <c r="G21" s="6">
         <v>820</v>
       </c>
-      <c r="H21" s="11">
+      <c r="H21" s="6">
         <v>30</v>
       </c>
-      <c r="I21" s="11">
+      <c r="I21" s="6">
         <f t="shared" si="0"/>
         <v>790</v>
       </c>
@@ -3068,13 +3288,13 @@
       <c r="F22" t="s">
         <v>86</v>
       </c>
-      <c r="G22" s="11">
+      <c r="G22" s="6">
         <v>0</v>
       </c>
-      <c r="H22" s="11">
+      <c r="H22" s="6">
         <v>30</v>
       </c>
-      <c r="I22" s="11">
+      <c r="I22" s="6">
         <f>-H22</f>
         <v>-30</v>
       </c>
@@ -3104,16 +3324,16 @@
       <c r="E23" t="s">
         <v>88</v>
       </c>
-      <c r="F23" s="11">
+      <c r="F23" s="6">
         <v>6</v>
       </c>
-      <c r="G23" s="11">
+      <c r="G23" s="6">
         <v>0</v>
       </c>
-      <c r="H23" s="11">
+      <c r="H23" s="6">
         <v>30</v>
       </c>
-      <c r="I23" s="11">
+      <c r="I23" s="6">
         <f>-H23</f>
         <v>-30</v>
       </c>
@@ -3131,51 +3351,51 @@
       </c>
     </row>
     <row r="25" spans="1:17" x14ac:dyDescent="0.25">
-      <c r="D25" s="6">
+      <c r="D25" s="1">
         <f>COUNTA(D3:D23)</f>
         <v>19</v>
       </c>
-      <c r="G25" s="6">
+      <c r="G25" s="1">
         <f t="shared" ref="G25:Q25" si="1">SUBTOTAL(9,G3:G23)</f>
         <v>11870</v>
       </c>
-      <c r="H25" s="6">
+      <c r="H25" s="1">
         <f t="shared" si="1"/>
         <v>575</v>
       </c>
-      <c r="I25" s="6">
+      <c r="I25" s="1">
         <f t="shared" si="1"/>
         <v>11295</v>
       </c>
-      <c r="J25" s="6">
+      <c r="J25" s="1">
         <f t="shared" si="1"/>
         <v>0</v>
       </c>
-      <c r="K25" s="6">
+      <c r="K25" s="1">
         <f t="shared" si="1"/>
         <v>0</v>
       </c>
-      <c r="L25" s="6">
+      <c r="L25" s="1">
         <f t="shared" si="1"/>
         <v>0</v>
       </c>
-      <c r="M25" s="6">
+      <c r="M25" s="1">
         <f t="shared" si="1"/>
         <v>0</v>
       </c>
-      <c r="N25" s="6">
+      <c r="N25" s="1">
         <f t="shared" si="1"/>
         <v>0</v>
       </c>
-      <c r="O25" s="6">
+      <c r="O25" s="1">
         <f t="shared" si="1"/>
         <v>0</v>
       </c>
-      <c r="P25" s="6">
+      <c r="P25" s="1">
         <f t="shared" si="1"/>
         <v>0</v>
       </c>
-      <c r="Q25" s="6">
+      <c r="Q25" s="1">
         <f t="shared" si="1"/>
         <v>21</v>
       </c>
@@ -3187,30 +3407,30 @@
       </c>
     </row>
     <row r="27" spans="1:17" x14ac:dyDescent="0.25">
-      <c r="A27" s="6" t="s">
-        <v>16</v>
-      </c>
-      <c r="C27" s="5" t="s">
+      <c r="A27" s="1" t="s">
+        <v>16</v>
+      </c>
+      <c r="C27" s="20" t="s">
         <v>89</v>
       </c>
-      <c r="D27" s="5"/>
-      <c r="E27" s="9" t="s">
+      <c r="D27" s="20"/>
+      <c r="E27" s="4" t="s">
         <v>90</v>
       </c>
       <c r="H27">
         <f>-5*25</f>
         <v>-125</v>
       </c>
-      <c r="K27" s="12" t="s">
+      <c r="K27" s="7" t="s">
         <v>21</v>
       </c>
-      <c r="L27" s="12" t="s">
+      <c r="L27" s="7" t="s">
         <v>91</v>
       </c>
-      <c r="M27" s="12" t="s">
+      <c r="M27" s="7" t="s">
         <v>90</v>
       </c>
-      <c r="O27" s="9" t="s">
+      <c r="O27" s="4" t="s">
         <v>92</v>
       </c>
     </row>
@@ -3218,15 +3438,15 @@
       <c r="A28" t="s">
         <v>23</v>
       </c>
-      <c r="B28" s="8" t="s">
+      <c r="B28" s="3" t="s">
         <v>93</v>
       </c>
-      <c r="C28" s="4">
+      <c r="C28" s="21">
         <f>SUMIFS(I$3:I$23,B$3:B$23,A$27,L$3:L$23,A$28)</f>
         <v>11295</v>
       </c>
-      <c r="D28" s="4"/>
-      <c r="E28" s="8">
+      <c r="D28" s="21"/>
+      <c r="E28" s="3">
         <f>SUMIFS(Q$3:Q$23,B$3:B$23,A$27,L$3:L$23,A$28)</f>
         <v>21</v>
       </c>
@@ -3253,13 +3473,13 @@
       </c>
     </row>
     <row r="29" spans="1:17" x14ac:dyDescent="0.25">
-      <c r="B29" s="7" t="s">
+      <c r="B29" s="2" t="s">
         <v>97</v>
       </c>
-      <c r="C29" s="3">
+      <c r="C29" s="22">
         <v>0</v>
       </c>
-      <c r="D29" s="3"/>
+      <c r="D29" s="22"/>
       <c r="K29" t="s">
         <v>98</v>
       </c>
@@ -3280,15 +3500,15 @@
       </c>
     </row>
     <row r="30" spans="1:17" x14ac:dyDescent="0.25">
-      <c r="B30" s="7" t="s">
+      <c r="B30" s="2" t="s">
         <v>99</v>
       </c>
-      <c r="C30" s="3">
+      <c r="C30" s="22">
         <f>-SUMIFS(I$3:I$23,B$3:B$23,A$27,P$3:P$23,"xx",N$3:N$23,"x")</f>
         <v>0</v>
       </c>
-      <c r="D30" s="3"/>
-      <c r="E30" s="7">
+      <c r="D30" s="22"/>
+      <c r="E30" s="2">
         <f>SUMIFS(Q$3:Q$23,B$3:B$23,A$27,P$3:P$23,"xx",N$3:N$23,"x")</f>
         <v>0</v>
       </c>
@@ -3304,19 +3524,19 @@
       </c>
     </row>
     <row r="31" spans="1:17" x14ac:dyDescent="0.25">
-      <c r="B31" s="9" t="s">
+      <c r="B31" s="4" t="s">
         <v>101</v>
       </c>
-      <c r="C31" s="5">
+      <c r="C31" s="20">
         <f>SUBTOTAL(9,C28:C30)</f>
         <v>11295</v>
       </c>
-      <c r="D31" s="5"/>
+      <c r="D31" s="20"/>
       <c r="E31">
         <f>E28</f>
         <v>21</v>
       </c>
-      <c r="K31" s="7" t="s">
+      <c r="K31" s="2" t="s">
         <v>102</v>
       </c>
       <c r="O31" t="s">
@@ -3328,56 +3548,56 @@
       </c>
     </row>
     <row r="32" spans="1:17" x14ac:dyDescent="0.25">
-      <c r="B32" s="7" t="s">
+      <c r="B32" s="2" t="s">
         <v>104</v>
       </c>
-      <c r="C32" s="2"/>
-      <c r="D32" s="2"/>
-      <c r="K32" s="7" t="s">
+      <c r="C32" s="18"/>
+      <c r="D32" s="18"/>
+      <c r="K32" s="2" t="s">
         <v>105</v>
       </c>
-      <c r="O32" s="9" t="s">
+      <c r="O32" s="4" t="s">
         <v>106</v>
       </c>
-      <c r="P32" s="9">
+      <c r="P32" s="4">
         <f>SUBTOTAL(9,P28:P31)</f>
         <v>117</v>
       </c>
     </row>
     <row r="33" spans="2:13" x14ac:dyDescent="0.25">
-      <c r="B33" s="13" t="s">
+      <c r="B33" s="8" t="s">
         <v>107</v>
       </c>
-      <c r="C33" s="2"/>
-      <c r="D33" s="2"/>
-      <c r="L33" s="14">
+      <c r="C33" s="18"/>
+      <c r="D33" s="18"/>
+      <c r="L33" s="9">
         <f>SUBTOTAL(9,L28:L32)</f>
         <v>7314</v>
       </c>
-      <c r="M33" s="14">
+      <c r="M33" s="9">
         <f>M28</f>
         <v>13</v>
       </c>
     </row>
     <row r="35" spans="2:13" x14ac:dyDescent="0.25">
-      <c r="B35" s="6" t="s">
+      <c r="B35" s="1" t="s">
         <v>108</v>
       </c>
-      <c r="C35" s="1">
+      <c r="C35" s="19">
         <f>C31+C32+C33</f>
         <v>11295</v>
       </c>
-      <c r="D35" s="1"/>
-      <c r="E35" s="6" t="s">
+      <c r="D35" s="19"/>
+      <c r="E35" s="1" t="s">
         <v>109</v>
       </c>
-      <c r="K35" s="12" t="s">
-        <v>22</v>
-      </c>
-      <c r="L35" s="12" t="s">
+      <c r="K35" s="7" t="s">
+        <v>22</v>
+      </c>
+      <c r="L35" s="7" t="s">
         <v>91</v>
       </c>
-      <c r="M35" s="12" t="s">
+      <c r="M35" s="7" t="s">
         <v>90</v>
       </c>
     </row>
@@ -3421,33 +3641,33 @@
       </c>
     </row>
     <row r="39" spans="2:13" x14ac:dyDescent="0.25">
-      <c r="K39" s="7" t="s">
+      <c r="K39" s="2" t="s">
         <v>102</v>
       </c>
     </row>
     <row r="40" spans="2:13" x14ac:dyDescent="0.25">
-      <c r="K40" s="7" t="s">
+      <c r="K40" s="2" t="s">
         <v>105</v>
       </c>
     </row>
     <row r="41" spans="2:13" x14ac:dyDescent="0.25">
-      <c r="L41" s="14">
+      <c r="L41" s="9">
         <f>SUBTOTAL(9,L36:L40)</f>
         <v>3343</v>
       </c>
-      <c r="M41" s="14">
+      <c r="M41" s="9">
         <f>M36</f>
         <v>7</v>
       </c>
     </row>
     <row r="43" spans="2:13" x14ac:dyDescent="0.25">
-      <c r="K43" s="12" t="s">
+      <c r="K43" s="7" t="s">
         <v>40</v>
       </c>
-      <c r="L43" s="12" t="s">
+      <c r="L43" s="7" t="s">
         <v>91</v>
       </c>
-      <c r="M43" s="12" t="s">
+      <c r="M43" s="7" t="s">
         <v>90</v>
       </c>
     </row>
@@ -3483,21 +3703,21 @@
       </c>
     </row>
     <row r="47" spans="2:13" x14ac:dyDescent="0.25">
-      <c r="K47" s="7" t="s">
+      <c r="K47" s="2" t="s">
         <v>102</v>
       </c>
     </row>
     <row r="48" spans="2:13" x14ac:dyDescent="0.25">
-      <c r="K48" s="7" t="s">
+      <c r="K48" s="2" t="s">
         <v>105</v>
       </c>
     </row>
     <row r="49" spans="12:13" x14ac:dyDescent="0.25">
-      <c r="L49" s="14">
+      <c r="L49" s="9">
         <f>SUBTOTAL(9,L44:L48)</f>
         <v>755</v>
       </c>
-      <c r="M49" s="14">
+      <c r="M49" s="9">
         <f>M44</f>
         <v>1</v>
       </c>
@@ -3542,52 +3762,52 @@
   </cols>
   <sheetData>
     <row r="2" spans="1:17" x14ac:dyDescent="0.25">
-      <c r="A2" s="10" t="s">
+      <c r="A2" s="5" t="s">
         <v>0</v>
       </c>
-      <c r="B2" s="10" t="s">
-        <v>1</v>
-      </c>
-      <c r="C2" s="10" t="s">
+      <c r="B2" s="5" t="s">
+        <v>1</v>
+      </c>
+      <c r="C2" s="5" t="s">
         <v>2</v>
       </c>
-      <c r="D2" s="10" t="s">
+      <c r="D2" s="5" t="s">
         <v>3</v>
       </c>
-      <c r="E2" s="10" t="s">
+      <c r="E2" s="5" t="s">
         <v>4</v>
       </c>
-      <c r="F2" s="10" t="s">
+      <c r="F2" s="5" t="s">
         <v>5</v>
       </c>
-      <c r="G2" s="10" t="s">
+      <c r="G2" s="5" t="s">
         <v>6</v>
       </c>
-      <c r="H2" s="10" t="s">
+      <c r="H2" s="5" t="s">
         <v>7</v>
       </c>
-      <c r="I2" s="10" t="s">
+      <c r="I2" s="5" t="s">
         <v>8</v>
       </c>
-      <c r="J2" s="10" t="s">
+      <c r="J2" s="5" t="s">
         <v>9</v>
       </c>
-      <c r="K2" s="10" t="s">
+      <c r="K2" s="5" t="s">
         <v>10</v>
       </c>
-      <c r="L2" s="10" t="s">
+      <c r="L2" s="5" t="s">
         <v>11</v>
       </c>
-      <c r="M2" s="10" t="s">
+      <c r="M2" s="5" t="s">
         <v>12</v>
       </c>
-      <c r="N2" s="10" t="s">
+      <c r="N2" s="5" t="s">
         <v>13</v>
       </c>
-      <c r="O2" s="10" t="s">
+      <c r="O2" s="5" t="s">
         <v>14</v>
       </c>
-      <c r="P2" s="10" t="s">
+      <c r="P2" s="5" t="s">
         <v>15</v>
       </c>
     </row>
@@ -3607,13 +3827,13 @@
       <c r="F3" t="s">
         <v>113</v>
       </c>
-      <c r="G3" s="11">
+      <c r="G3" s="6">
         <v>35</v>
       </c>
-      <c r="H3" s="11">
+      <c r="H3" s="6">
         <v>35</v>
       </c>
-      <c r="I3" s="11">
+      <c r="I3" s="6">
         <f t="shared" ref="I3:I24" si="0">G3-H3</f>
         <v>0</v>
       </c>
@@ -3649,13 +3869,13 @@
       <c r="F4" t="s">
         <v>20</v>
       </c>
-      <c r="G4" s="11">
+      <c r="G4" s="6">
         <v>870</v>
       </c>
-      <c r="H4" s="11">
+      <c r="H4" s="6">
         <v>30</v>
       </c>
-      <c r="I4" s="11">
+      <c r="I4" s="6">
         <f t="shared" si="0"/>
         <v>840</v>
       </c>
@@ -3685,16 +3905,16 @@
       <c r="E5" t="s">
         <v>121</v>
       </c>
-      <c r="F5" s="11">
+      <c r="F5" s="6">
         <v>8</v>
       </c>
-      <c r="G5" s="11">
+      <c r="G5" s="6">
         <v>0</v>
       </c>
-      <c r="H5" s="11">
+      <c r="H5" s="6">
         <v>25</v>
       </c>
-      <c r="I5" s="11">
+      <c r="I5" s="6">
         <f t="shared" si="0"/>
         <v>-25</v>
       </c>
@@ -3724,16 +3944,16 @@
       <c r="E6" t="s">
         <v>124</v>
       </c>
-      <c r="F6" s="11">
+      <c r="F6" s="6">
         <v>7</v>
       </c>
-      <c r="G6" s="11">
+      <c r="G6" s="6">
         <v>650</v>
       </c>
-      <c r="H6" s="11">
+      <c r="H6" s="6">
         <v>30</v>
       </c>
-      <c r="I6" s="11">
+      <c r="I6" s="6">
         <f t="shared" si="0"/>
         <v>620</v>
       </c>
@@ -3766,13 +3986,13 @@
       <c r="F7" t="s">
         <v>128</v>
       </c>
-      <c r="G7" s="11">
+      <c r="G7" s="6">
         <v>0</v>
       </c>
-      <c r="H7" s="11">
+      <c r="H7" s="6">
         <v>35</v>
       </c>
-      <c r="I7" s="11">
+      <c r="I7" s="6">
         <f t="shared" si="0"/>
         <v>-35</v>
       </c>
@@ -3805,16 +4025,16 @@
       <c r="E8" t="s">
         <v>132</v>
       </c>
-      <c r="F8" s="11">
+      <c r="F8" s="6">
         <v>7</v>
       </c>
-      <c r="G8" s="11">
+      <c r="G8" s="6">
         <v>740</v>
       </c>
-      <c r="H8" s="11">
+      <c r="H8" s="6">
         <v>30</v>
       </c>
-      <c r="I8" s="11">
+      <c r="I8" s="6">
         <f t="shared" si="0"/>
         <v>710</v>
       </c>
@@ -3847,13 +4067,13 @@
       <c r="F9" t="s">
         <v>20</v>
       </c>
-      <c r="G9" s="11">
+      <c r="G9" s="6">
         <v>770</v>
       </c>
-      <c r="H9" s="11">
+      <c r="H9" s="6">
         <v>30</v>
       </c>
-      <c r="I9" s="11">
+      <c r="I9" s="6">
         <f t="shared" si="0"/>
         <v>740</v>
       </c>
@@ -3886,13 +4106,13 @@
       <c r="F10" t="s">
         <v>36</v>
       </c>
-      <c r="G10" s="11">
+      <c r="G10" s="6">
         <v>0</v>
       </c>
-      <c r="H10" s="11">
+      <c r="H10" s="6">
         <v>20</v>
       </c>
-      <c r="I10" s="11">
+      <c r="I10" s="6">
         <f t="shared" si="0"/>
         <v>-20</v>
       </c>
@@ -3922,16 +4142,16 @@
       <c r="E11" t="s">
         <v>140</v>
       </c>
-      <c r="F11" s="11">
+      <c r="F11" s="6">
         <v>6</v>
       </c>
-      <c r="G11" s="11">
+      <c r="G11" s="6">
         <v>70</v>
       </c>
-      <c r="H11" s="11">
+      <c r="H11" s="6">
         <v>70</v>
       </c>
-      <c r="I11" s="11">
+      <c r="I11" s="6">
         <f t="shared" si="0"/>
         <v>0</v>
       </c>
@@ -3961,16 +4181,16 @@
       <c r="E12" t="s">
         <v>142</v>
       </c>
-      <c r="F12" s="11">
+      <c r="F12" s="6">
         <v>12</v>
       </c>
-      <c r="G12" s="11">
+      <c r="G12" s="6">
         <v>30</v>
       </c>
-      <c r="H12" s="11">
+      <c r="H12" s="6">
         <v>30</v>
       </c>
-      <c r="I12" s="11">
+      <c r="I12" s="6">
         <f t="shared" si="0"/>
         <v>0</v>
       </c>
@@ -4003,13 +4223,13 @@
       <c r="F13" t="s">
         <v>44</v>
       </c>
-      <c r="G13" s="11">
+      <c r="G13" s="6">
         <v>30</v>
       </c>
-      <c r="H13" s="11">
+      <c r="H13" s="6">
         <v>30</v>
       </c>
-      <c r="I13" s="11">
+      <c r="I13" s="6">
         <f t="shared" si="0"/>
         <v>0</v>
       </c>
@@ -4042,13 +4262,13 @@
       <c r="F14" t="s">
         <v>86</v>
       </c>
-      <c r="G14" s="11">
+      <c r="G14" s="6">
         <v>530</v>
       </c>
-      <c r="H14" s="11">
+      <c r="H14" s="6">
         <v>30</v>
       </c>
-      <c r="I14" s="11">
+      <c r="I14" s="6">
         <f t="shared" si="0"/>
         <v>500</v>
       </c>
@@ -4081,13 +4301,13 @@
       <c r="F15" t="s">
         <v>36</v>
       </c>
-      <c r="G15" s="11">
+      <c r="G15" s="6">
         <v>740</v>
       </c>
-      <c r="H15" s="11">
+      <c r="H15" s="6">
         <v>20</v>
       </c>
-      <c r="I15" s="11">
+      <c r="I15" s="6">
         <f t="shared" si="0"/>
         <v>720</v>
       </c>
@@ -4120,13 +4340,13 @@
       <c r="F16" t="s">
         <v>153</v>
       </c>
-      <c r="G16" s="11">
+      <c r="G16" s="6">
         <v>0</v>
       </c>
-      <c r="H16" s="11">
+      <c r="H16" s="6">
         <v>30</v>
       </c>
-      <c r="I16" s="11">
+      <c r="I16" s="6">
         <f t="shared" si="0"/>
         <v>-30</v>
       </c>
@@ -4159,13 +4379,13 @@
       <c r="F17" t="s">
         <v>36</v>
       </c>
-      <c r="G17" s="11">
+      <c r="G17" s="6">
         <v>510</v>
       </c>
-      <c r="H17" s="11">
+      <c r="H17" s="6">
         <v>20</v>
       </c>
-      <c r="I17" s="11">
+      <c r="I17" s="6">
         <f t="shared" si="0"/>
         <v>490</v>
       </c>
@@ -4198,13 +4418,13 @@
       <c r="F18" t="s">
         <v>44</v>
       </c>
-      <c r="G18" s="11">
+      <c r="G18" s="6">
         <v>745</v>
       </c>
-      <c r="H18" s="11">
+      <c r="H18" s="6">
         <v>25</v>
       </c>
-      <c r="I18" s="11">
+      <c r="I18" s="6">
         <f t="shared" si="0"/>
         <v>720</v>
       </c>
@@ -4237,13 +4457,13 @@
       <c r="F19" t="s">
         <v>36</v>
       </c>
-      <c r="G19" s="11">
+      <c r="G19" s="6">
         <v>0</v>
       </c>
-      <c r="H19" s="11">
+      <c r="H19" s="6">
         <v>20</v>
       </c>
-      <c r="I19" s="11">
+      <c r="I19" s="6">
         <f t="shared" si="0"/>
         <v>-20</v>
       </c>
@@ -4276,13 +4496,13 @@
       <c r="F20" t="s">
         <v>86</v>
       </c>
-      <c r="G20" s="11">
+      <c r="G20" s="6">
         <v>30</v>
       </c>
-      <c r="H20" s="11">
+      <c r="H20" s="6">
         <v>30</v>
       </c>
-      <c r="I20" s="11">
+      <c r="I20" s="6">
         <f t="shared" si="0"/>
         <v>0</v>
       </c>
@@ -4312,16 +4532,16 @@
       <c r="E21" t="s">
         <v>168</v>
       </c>
-      <c r="F21" s="11">
-        <v>1</v>
-      </c>
-      <c r="G21" s="11">
+      <c r="F21" s="6">
+        <v>1</v>
+      </c>
+      <c r="G21" s="6">
         <v>695</v>
       </c>
-      <c r="H21" s="11">
+      <c r="H21" s="6">
         <v>25</v>
       </c>
-      <c r="I21" s="11">
+      <c r="I21" s="6">
         <f t="shared" si="0"/>
         <v>670</v>
       </c>
@@ -4351,16 +4571,16 @@
       <c r="E22" t="s">
         <v>170</v>
       </c>
-      <c r="F22" s="11">
+      <c r="F22" s="6">
         <v>10</v>
       </c>
-      <c r="G22" s="11">
+      <c r="G22" s="6">
         <v>775</v>
       </c>
-      <c r="H22" s="11">
+      <c r="H22" s="6">
         <v>25</v>
       </c>
-      <c r="I22" s="11">
+      <c r="I22" s="6">
         <f t="shared" si="0"/>
         <v>750</v>
       </c>
@@ -4390,16 +4610,16 @@
       <c r="E23" t="s">
         <v>173</v>
       </c>
-      <c r="F23" s="11">
-        <v>1</v>
-      </c>
-      <c r="G23" s="11">
+      <c r="F23" s="6">
+        <v>1</v>
+      </c>
+      <c r="G23" s="6">
         <v>0</v>
       </c>
-      <c r="H23" s="11">
+      <c r="H23" s="6">
         <v>25</v>
       </c>
-      <c r="I23" s="11">
+      <c r="I23" s="6">
         <f t="shared" si="0"/>
         <v>-25</v>
       </c>
@@ -4432,16 +4652,16 @@
       <c r="E24" t="s">
         <v>177</v>
       </c>
-      <c r="F24" s="11">
-        <v>1</v>
-      </c>
-      <c r="G24" s="11">
+      <c r="F24" s="6">
+        <v>1</v>
+      </c>
+      <c r="G24" s="6">
         <v>695</v>
       </c>
-      <c r="H24" s="11">
+      <c r="H24" s="6">
         <v>25</v>
       </c>
-      <c r="I24" s="11">
+      <c r="I24" s="6">
         <f t="shared" si="0"/>
         <v>670</v>
       </c>
@@ -4459,51 +4679,51 @@
       </c>
     </row>
     <row r="26" spans="1:17" x14ac:dyDescent="0.25">
-      <c r="D26" s="6">
+      <c r="D26" s="1">
         <f>COUNTA(D3:D24)</f>
         <v>17</v>
       </c>
-      <c r="G26" s="6">
+      <c r="G26" s="1">
         <f t="shared" ref="G26:Q26" si="1">SUBTOTAL(9,G3:G24)</f>
         <v>7915</v>
       </c>
-      <c r="H26" s="6">
+      <c r="H26" s="1">
         <f t="shared" si="1"/>
         <v>640</v>
       </c>
-      <c r="I26" s="6">
+      <c r="I26" s="1">
         <f t="shared" si="1"/>
         <v>7275</v>
       </c>
-      <c r="J26" s="6">
+      <c r="J26" s="1">
         <f t="shared" si="1"/>
         <v>0</v>
       </c>
-      <c r="K26" s="6">
+      <c r="K26" s="1">
         <f t="shared" si="1"/>
         <v>0</v>
       </c>
-      <c r="L26" s="6">
+      <c r="L26" s="1">
         <f t="shared" si="1"/>
         <v>0</v>
       </c>
-      <c r="M26" s="6">
+      <c r="M26" s="1">
         <f t="shared" si="1"/>
         <v>0</v>
       </c>
-      <c r="N26" s="6">
+      <c r="N26" s="1">
         <f t="shared" si="1"/>
         <v>0</v>
       </c>
-      <c r="O26" s="6">
+      <c r="O26" s="1">
         <f t="shared" si="1"/>
         <v>0</v>
       </c>
-      <c r="P26" s="6">
+      <c r="P26" s="1">
         <f t="shared" si="1"/>
         <v>0</v>
       </c>
-      <c r="Q26" s="6">
+      <c r="Q26" s="1">
         <f t="shared" si="1"/>
         <v>22</v>
       </c>
@@ -4515,30 +4735,30 @@
       </c>
     </row>
     <row r="28" spans="1:17" x14ac:dyDescent="0.25">
-      <c r="A28" s="6" t="s">
-        <v>16</v>
-      </c>
-      <c r="C28" s="5" t="s">
+      <c r="A28" s="1" t="s">
+        <v>16</v>
+      </c>
+      <c r="C28" s="20" t="s">
         <v>89</v>
       </c>
-      <c r="D28" s="5"/>
-      <c r="E28" s="9" t="s">
+      <c r="D28" s="20"/>
+      <c r="E28" s="4" t="s">
         <v>90</v>
       </c>
       <c r="H28">
         <f>-2*25</f>
         <v>-50</v>
       </c>
-      <c r="K28" s="12" t="s">
-        <v>22</v>
-      </c>
-      <c r="L28" s="12" t="s">
+      <c r="K28" s="7" t="s">
+        <v>22</v>
+      </c>
+      <c r="L28" s="7" t="s">
         <v>91</v>
       </c>
-      <c r="M28" s="12" t="s">
+      <c r="M28" s="7" t="s">
         <v>90</v>
       </c>
-      <c r="O28" s="9" t="s">
+      <c r="O28" s="4" t="s">
         <v>92</v>
       </c>
     </row>
@@ -4546,15 +4766,15 @@
       <c r="A29" t="s">
         <v>115</v>
       </c>
-      <c r="B29" s="8" t="s">
+      <c r="B29" s="3" t="s">
         <v>93</v>
       </c>
-      <c r="C29" s="4">
+      <c r="C29" s="21">
         <f>SUMIFS(I$3:I$24,B$3:B$24,A$28,L$3:L$24,A$29)</f>
         <v>7275</v>
       </c>
-      <c r="D29" s="4"/>
-      <c r="E29" s="8">
+      <c r="D29" s="21"/>
+      <c r="E29" s="3">
         <f>SUMIFS(Q$3:Q$24,B$3:B$24,A$28,L$3:L$24,A$29)</f>
         <v>22</v>
       </c>
@@ -4585,13 +4805,13 @@
       </c>
     </row>
     <row r="30" spans="1:17" x14ac:dyDescent="0.25">
-      <c r="B30" s="7" t="s">
+      <c r="B30" s="2" t="s">
         <v>97</v>
       </c>
-      <c r="C30" s="3">
+      <c r="C30" s="22">
         <v>0</v>
       </c>
-      <c r="D30" s="3"/>
+      <c r="D30" s="22"/>
       <c r="K30" t="s">
         <v>98</v>
       </c>
@@ -4612,15 +4832,15 @@
       </c>
     </row>
     <row r="31" spans="1:17" x14ac:dyDescent="0.25">
-      <c r="B31" s="7" t="s">
+      <c r="B31" s="2" t="s">
         <v>99</v>
       </c>
-      <c r="C31" s="3">
+      <c r="C31" s="22">
         <f>-SUMIFS(I$3:I$24,B$3:B$24,A$28,P$3:P$24,"xx",N$3:N$24,"x")</f>
         <v>0</v>
       </c>
-      <c r="D31" s="3"/>
-      <c r="E31" s="7">
+      <c r="D31" s="22"/>
+      <c r="E31" s="2">
         <f>SUMIFS(Q$3:Q$24,B$3:B$24,A$28,P$3:P$24,"xx",N$3:N$24,"x")</f>
         <v>0</v>
       </c>
@@ -4644,19 +4864,19 @@
       </c>
     </row>
     <row r="32" spans="1:17" x14ac:dyDescent="0.25">
-      <c r="B32" s="9" t="s">
+      <c r="B32" s="4" t="s">
         <v>101</v>
       </c>
-      <c r="C32" s="5">
+      <c r="C32" s="20">
         <f>SUBTOTAL(9,C29:C31)</f>
         <v>7275</v>
       </c>
-      <c r="D32" s="5"/>
+      <c r="D32" s="20"/>
       <c r="E32">
         <f>E29</f>
         <v>22</v>
       </c>
-      <c r="K32" s="7" t="s">
+      <c r="K32" s="2" t="s">
         <v>102</v>
       </c>
       <c r="O32" t="s">
@@ -4668,56 +4888,56 @@
       </c>
     </row>
     <row r="33" spans="2:16" x14ac:dyDescent="0.25">
-      <c r="B33" s="7" t="s">
+      <c r="B33" s="2" t="s">
         <v>104</v>
       </c>
-      <c r="C33" s="2"/>
-      <c r="D33" s="2"/>
-      <c r="K33" s="7" t="s">
+      <c r="C33" s="18"/>
+      <c r="D33" s="18"/>
+      <c r="K33" s="2" t="s">
         <v>105</v>
       </c>
-      <c r="O33" s="9" t="s">
+      <c r="O33" s="4" t="s">
         <v>106</v>
       </c>
-      <c r="P33" s="9">
+      <c r="P33" s="4">
         <f>SUBTOTAL(9,P29:P32)</f>
         <v>85</v>
       </c>
     </row>
     <row r="34" spans="2:16" x14ac:dyDescent="0.25">
-      <c r="B34" s="13" t="s">
+      <c r="B34" s="8" t="s">
         <v>107</v>
       </c>
-      <c r="C34" s="2"/>
-      <c r="D34" s="2"/>
-      <c r="L34" s="14">
+      <c r="C34" s="18"/>
+      <c r="D34" s="18"/>
+      <c r="L34" s="9">
         <f>SUBTOTAL(9,L29:L33)</f>
         <v>2366</v>
       </c>
-      <c r="M34" s="14">
+      <c r="M34" s="9">
         <f>M29</f>
         <v>10</v>
       </c>
     </row>
     <row r="36" spans="2:16" x14ac:dyDescent="0.25">
-      <c r="B36" s="6" t="s">
+      <c r="B36" s="1" t="s">
         <v>108</v>
       </c>
-      <c r="C36" s="1">
+      <c r="C36" s="19">
         <f>C32+C33+C34</f>
         <v>7275</v>
       </c>
-      <c r="D36" s="1"/>
-      <c r="E36" s="6" t="s">
+      <c r="D36" s="19"/>
+      <c r="E36" s="1" t="s">
         <v>109</v>
       </c>
-      <c r="K36" s="12" t="s">
+      <c r="K36" s="7" t="s">
         <v>165</v>
       </c>
-      <c r="L36" s="12" t="s">
+      <c r="L36" s="7" t="s">
         <v>91</v>
       </c>
-      <c r="M36" s="12" t="s">
+      <c r="M36" s="7" t="s">
         <v>90</v>
       </c>
     </row>
@@ -4753,33 +4973,33 @@
       </c>
     </row>
     <row r="40" spans="2:16" x14ac:dyDescent="0.25">
-      <c r="K40" s="7" t="s">
+      <c r="K40" s="2" t="s">
         <v>102</v>
       </c>
     </row>
     <row r="41" spans="2:16" x14ac:dyDescent="0.25">
-      <c r="K41" s="7" t="s">
+      <c r="K41" s="2" t="s">
         <v>105</v>
       </c>
     </row>
     <row r="42" spans="2:16" x14ac:dyDescent="0.25">
-      <c r="L42" s="14">
+      <c r="L42" s="9">
         <f>SUBTOTAL(9,L37:L41)</f>
         <v>2090</v>
       </c>
-      <c r="M42" s="14">
+      <c r="M42" s="9">
         <f>M37</f>
         <v>5</v>
       </c>
     </row>
     <row r="44" spans="2:16" x14ac:dyDescent="0.25">
-      <c r="K44" s="12" t="s">
+      <c r="K44" s="7" t="s">
         <v>114</v>
       </c>
-      <c r="L44" s="12" t="s">
+      <c r="L44" s="7" t="s">
         <v>91</v>
       </c>
-      <c r="M44" s="12" t="s">
+      <c r="M44" s="7" t="s">
         <v>90</v>
       </c>
     </row>
@@ -4815,21 +5035,21 @@
       </c>
     </row>
     <row r="48" spans="2:16" x14ac:dyDescent="0.25">
-      <c r="K48" s="7" t="s">
+      <c r="K48" s="2" t="s">
         <v>102</v>
       </c>
     </row>
     <row r="49" spans="11:13" x14ac:dyDescent="0.25">
-      <c r="K49" s="7" t="s">
+      <c r="K49" s="2" t="s">
         <v>105</v>
       </c>
     </row>
     <row r="50" spans="11:13" x14ac:dyDescent="0.25">
-      <c r="L50" s="14">
+      <c r="L50" s="9">
         <f>SUBTOTAL(9,L45:L49)</f>
         <v>2904</v>
       </c>
-      <c r="M50" s="14">
+      <c r="M50" s="9">
         <f>M45</f>
         <v>7</v>
       </c>
@@ -4878,52 +5098,52 @@
   </cols>
   <sheetData>
     <row r="2" spans="1:17" x14ac:dyDescent="0.25">
-      <c r="A2" s="10" t="s">
+      <c r="A2" s="5" t="s">
         <v>0</v>
       </c>
-      <c r="B2" s="10" t="s">
-        <v>1</v>
-      </c>
-      <c r="C2" s="10" t="s">
+      <c r="B2" s="5" t="s">
+        <v>1</v>
+      </c>
+      <c r="C2" s="5" t="s">
         <v>2</v>
       </c>
-      <c r="D2" s="10" t="s">
+      <c r="D2" s="5" t="s">
         <v>3</v>
       </c>
-      <c r="E2" s="10" t="s">
+      <c r="E2" s="5" t="s">
         <v>4</v>
       </c>
-      <c r="F2" s="10" t="s">
+      <c r="F2" s="5" t="s">
         <v>5</v>
       </c>
-      <c r="G2" s="10" t="s">
+      <c r="G2" s="5" t="s">
         <v>6</v>
       </c>
-      <c r="H2" s="10" t="s">
+      <c r="H2" s="5" t="s">
         <v>7</v>
       </c>
-      <c r="I2" s="10" t="s">
+      <c r="I2" s="5" t="s">
         <v>8</v>
       </c>
-      <c r="J2" s="10" t="s">
+      <c r="J2" s="5" t="s">
         <v>9</v>
       </c>
-      <c r="K2" s="10" t="s">
+      <c r="K2" s="5" t="s">
         <v>10</v>
       </c>
-      <c r="L2" s="10" t="s">
+      <c r="L2" s="5" t="s">
         <v>11</v>
       </c>
-      <c r="M2" s="10" t="s">
+      <c r="M2" s="5" t="s">
         <v>12</v>
       </c>
-      <c r="N2" s="10" t="s">
+      <c r="N2" s="5" t="s">
         <v>13</v>
       </c>
-      <c r="O2" s="10" t="s">
+      <c r="O2" s="5" t="s">
         <v>14</v>
       </c>
-      <c r="P2" s="10" t="s">
+      <c r="P2" s="5" t="s">
         <v>15</v>
       </c>
     </row>
@@ -4940,16 +5160,16 @@
       <c r="E3" t="s">
         <v>181</v>
       </c>
-      <c r="F3" s="11">
+      <c r="F3" s="6">
         <v>9</v>
       </c>
-      <c r="G3" s="11">
+      <c r="G3" s="6">
         <v>30</v>
       </c>
-      <c r="H3" s="11">
+      <c r="H3" s="6">
         <v>30</v>
       </c>
-      <c r="I3" s="11">
+      <c r="I3" s="6">
         <f>G3-H3</f>
         <v>0</v>
       </c>
@@ -4979,16 +5199,16 @@
       <c r="E4" t="s">
         <v>185</v>
       </c>
-      <c r="F4" s="11">
+      <c r="F4" s="6">
         <v>9</v>
       </c>
-      <c r="G4" s="11">
+      <c r="G4" s="6">
         <v>920</v>
       </c>
-      <c r="H4" s="11">
+      <c r="H4" s="6">
         <v>30</v>
       </c>
-      <c r="I4" s="11">
+      <c r="I4" s="6">
         <f>G4-H4</f>
         <v>890</v>
       </c>
@@ -5018,16 +5238,16 @@
       <c r="E5" t="s">
         <v>188</v>
       </c>
-      <c r="F5" s="11">
+      <c r="F5" s="6">
         <v>9</v>
       </c>
-      <c r="G5" s="11">
+      <c r="G5" s="6">
         <v>0</v>
       </c>
-      <c r="H5" s="11">
+      <c r="H5" s="6">
         <v>30</v>
       </c>
-      <c r="I5" s="11">
+      <c r="I5" s="6">
         <f>-H5</f>
         <v>-30</v>
       </c>
@@ -5057,16 +5277,16 @@
       <c r="E6" t="s">
         <v>191</v>
       </c>
-      <c r="F6" s="11">
+      <c r="F6" s="6">
         <v>9</v>
       </c>
-      <c r="G6" s="11">
+      <c r="G6" s="6">
         <v>690</v>
       </c>
-      <c r="H6" s="11">
+      <c r="H6" s="6">
         <v>30</v>
       </c>
-      <c r="I6" s="11">
+      <c r="I6" s="6">
         <f t="shared" ref="I6:I29" si="0">G6-H6</f>
         <v>660</v>
       </c>
@@ -5096,16 +5316,16 @@
       <c r="E7" t="s">
         <v>194</v>
       </c>
-      <c r="F7" s="11">
+      <c r="F7" s="6">
         <v>5</v>
       </c>
-      <c r="G7" s="11">
+      <c r="G7" s="6">
         <v>20</v>
       </c>
-      <c r="H7" s="11">
+      <c r="H7" s="6">
         <v>20</v>
       </c>
-      <c r="I7" s="11">
+      <c r="I7" s="6">
         <f t="shared" si="0"/>
         <v>0</v>
       </c>
@@ -5135,16 +5355,16 @@
       <c r="E8" t="s">
         <v>198</v>
       </c>
-      <c r="F8" s="11">
+      <c r="F8" s="6">
         <v>12</v>
       </c>
-      <c r="G8" s="11">
+      <c r="G8" s="6">
         <v>820</v>
       </c>
-      <c r="H8" s="11">
+      <c r="H8" s="6">
         <v>30</v>
       </c>
-      <c r="I8" s="11">
+      <c r="I8" s="6">
         <f t="shared" si="0"/>
         <v>790</v>
       </c>
@@ -5174,16 +5394,16 @@
       <c r="E9" t="s">
         <v>201</v>
       </c>
-      <c r="F9" s="11">
+      <c r="F9" s="6">
         <v>7</v>
       </c>
-      <c r="G9" s="11">
+      <c r="G9" s="6">
         <v>1330</v>
       </c>
-      <c r="H9" s="11">
+      <c r="H9" s="6">
         <v>30</v>
       </c>
-      <c r="I9" s="11">
+      <c r="I9" s="6">
         <f t="shared" si="0"/>
         <v>1300</v>
       </c>
@@ -5216,13 +5436,13 @@
       <c r="F10" t="s">
         <v>86</v>
       </c>
-      <c r="G10" s="11">
+      <c r="G10" s="6">
         <v>375</v>
       </c>
-      <c r="H10" s="11">
+      <c r="H10" s="6">
         <v>25</v>
       </c>
-      <c r="I10" s="11">
+      <c r="I10" s="6">
         <f t="shared" si="0"/>
         <v>350</v>
       </c>
@@ -5252,16 +5472,16 @@
       <c r="E11" t="s">
         <v>207</v>
       </c>
-      <c r="F11" s="11">
+      <c r="F11" s="6">
         <v>7</v>
       </c>
-      <c r="G11" s="11">
+      <c r="G11" s="6">
         <v>850</v>
       </c>
-      <c r="H11" s="11">
+      <c r="H11" s="6">
         <v>30</v>
       </c>
-      <c r="I11" s="11">
+      <c r="I11" s="6">
         <f t="shared" si="0"/>
         <v>820</v>
       </c>
@@ -5291,16 +5511,16 @@
       <c r="E12" t="s">
         <v>210</v>
       </c>
-      <c r="F12" s="11">
+      <c r="F12" s="6">
         <v>12</v>
       </c>
-      <c r="G12" s="11">
+      <c r="G12" s="6">
         <v>380</v>
       </c>
-      <c r="H12" s="11">
+      <c r="H12" s="6">
         <v>30</v>
       </c>
-      <c r="I12" s="11">
+      <c r="I12" s="6">
         <f t="shared" si="0"/>
         <v>350</v>
       </c>
@@ -5330,16 +5550,16 @@
       <c r="E13" t="s">
         <v>213</v>
       </c>
-      <c r="F13" s="11">
+      <c r="F13" s="6">
         <v>7</v>
       </c>
-      <c r="G13" s="11">
+      <c r="G13" s="6">
         <v>670</v>
       </c>
-      <c r="H13" s="11">
+      <c r="H13" s="6">
         <v>30</v>
       </c>
-      <c r="I13" s="11">
+      <c r="I13" s="6">
         <f t="shared" si="0"/>
         <v>640</v>
       </c>
@@ -5372,13 +5592,13 @@
       <c r="F14" t="s">
         <v>217</v>
       </c>
-      <c r="G14" s="11">
+      <c r="G14" s="6">
         <v>365</v>
       </c>
-      <c r="H14" s="11">
+      <c r="H14" s="6">
         <v>25</v>
       </c>
-      <c r="I14" s="11">
+      <c r="I14" s="6">
         <f t="shared" si="0"/>
         <v>340</v>
       </c>
@@ -5408,16 +5628,16 @@
       <c r="E15" t="s">
         <v>220</v>
       </c>
-      <c r="F15" s="11">
+      <c r="F15" s="6">
         <v>8</v>
       </c>
-      <c r="G15" s="11">
+      <c r="G15" s="6">
         <v>1460</v>
       </c>
-      <c r="H15" s="11">
+      <c r="H15" s="6">
         <v>30</v>
       </c>
-      <c r="I15" s="11">
+      <c r="I15" s="6">
         <f t="shared" si="0"/>
         <v>1430</v>
       </c>
@@ -5447,16 +5667,16 @@
       <c r="E16" t="s">
         <v>223</v>
       </c>
-      <c r="F16" s="11">
+      <c r="F16" s="6">
         <v>8</v>
       </c>
-      <c r="G16" s="11">
+      <c r="G16" s="6">
         <v>1440</v>
       </c>
-      <c r="H16" s="11">
+      <c r="H16" s="6">
         <v>30</v>
       </c>
-      <c r="I16" s="11">
+      <c r="I16" s="6">
         <f t="shared" si="0"/>
         <v>1410</v>
       </c>
@@ -5486,16 +5706,16 @@
       <c r="E17" t="s">
         <v>226</v>
       </c>
-      <c r="F17" s="11">
+      <c r="F17" s="6">
         <v>10</v>
       </c>
-      <c r="G17" s="11">
+      <c r="G17" s="6">
         <v>375</v>
       </c>
-      <c r="H17" s="11">
+      <c r="H17" s="6">
         <v>25</v>
       </c>
-      <c r="I17" s="11">
+      <c r="I17" s="6">
         <f t="shared" si="0"/>
         <v>350</v>
       </c>
@@ -5525,16 +5745,16 @@
       <c r="E18" t="s">
         <v>229</v>
       </c>
-      <c r="F18" s="11">
+      <c r="F18" s="6">
         <v>10</v>
       </c>
-      <c r="G18" s="11">
+      <c r="G18" s="6">
         <v>745</v>
       </c>
-      <c r="H18" s="11">
+      <c r="H18" s="6">
         <v>25</v>
       </c>
-      <c r="I18" s="11">
+      <c r="I18" s="6">
         <f t="shared" si="0"/>
         <v>720</v>
       </c>
@@ -5564,16 +5784,16 @@
       <c r="E19" t="s">
         <v>232</v>
       </c>
-      <c r="F19" s="11">
+      <c r="F19" s="6">
         <v>5</v>
       </c>
-      <c r="G19" s="11">
+      <c r="G19" s="6">
         <v>30</v>
       </c>
-      <c r="H19" s="11">
+      <c r="H19" s="6">
         <v>30</v>
       </c>
-      <c r="I19" s="11">
+      <c r="I19" s="6">
         <f t="shared" si="0"/>
         <v>0</v>
       </c>
@@ -5609,13 +5829,13 @@
       <c r="F20" t="s">
         <v>128</v>
       </c>
-      <c r="G20" s="11">
+      <c r="G20" s="6">
         <v>695</v>
       </c>
-      <c r="H20" s="11">
+      <c r="H20" s="6">
         <v>35</v>
       </c>
-      <c r="I20" s="11">
+      <c r="I20" s="6">
         <f t="shared" si="0"/>
         <v>660</v>
       </c>
@@ -5645,16 +5865,16 @@
       <c r="E21" t="s">
         <v>238</v>
       </c>
-      <c r="F21" s="11">
+      <c r="F21" s="6">
         <v>10</v>
       </c>
-      <c r="G21" s="11">
+      <c r="G21" s="6">
         <v>765</v>
       </c>
-      <c r="H21" s="11">
+      <c r="H21" s="6">
         <v>25</v>
       </c>
-      <c r="I21" s="11">
+      <c r="I21" s="6">
         <f t="shared" si="0"/>
         <v>740</v>
       </c>
@@ -5684,16 +5904,16 @@
       <c r="E22" t="s">
         <v>241</v>
       </c>
-      <c r="F22" s="11">
-        <v>1</v>
-      </c>
-      <c r="G22" s="11">
+      <c r="F22" s="6">
+        <v>1</v>
+      </c>
+      <c r="G22" s="6">
         <v>680</v>
       </c>
-      <c r="H22" s="11">
+      <c r="H22" s="6">
         <v>20</v>
       </c>
-      <c r="I22" s="11">
+      <c r="I22" s="6">
         <f t="shared" si="0"/>
         <v>660</v>
       </c>
@@ -5723,16 +5943,16 @@
       <c r="E23" t="s">
         <v>244</v>
       </c>
-      <c r="F23" s="11">
+      <c r="F23" s="6">
         <v>10</v>
       </c>
-      <c r="G23" s="11">
+      <c r="G23" s="6">
         <v>815</v>
       </c>
-      <c r="H23" s="11">
+      <c r="H23" s="6">
         <v>25</v>
       </c>
-      <c r="I23" s="11">
+      <c r="I23" s="6">
         <f t="shared" si="0"/>
         <v>790</v>
       </c>
@@ -5762,16 +5982,16 @@
       <c r="E24" t="s">
         <v>246</v>
       </c>
-      <c r="F24" s="11">
+      <c r="F24" s="6">
         <v>12</v>
       </c>
-      <c r="G24" s="11">
+      <c r="G24" s="6">
         <v>690</v>
       </c>
-      <c r="H24" s="11">
+      <c r="H24" s="6">
         <v>30</v>
       </c>
-      <c r="I24" s="11">
+      <c r="I24" s="6">
         <f t="shared" si="0"/>
         <v>660</v>
       </c>
@@ -5804,13 +6024,13 @@
       <c r="F25" t="s">
         <v>128</v>
       </c>
-      <c r="G25" s="11">
+      <c r="G25" s="6">
         <v>765</v>
       </c>
-      <c r="H25" s="11">
+      <c r="H25" s="6">
         <v>35</v>
       </c>
-      <c r="I25" s="11">
+      <c r="I25" s="6">
         <f t="shared" si="0"/>
         <v>730</v>
       </c>
@@ -5843,13 +6063,13 @@
       <c r="F26" t="s">
         <v>20</v>
       </c>
-      <c r="G26" s="11">
+      <c r="G26" s="6">
         <v>690</v>
       </c>
-      <c r="H26" s="11">
+      <c r="H26" s="6">
         <v>30</v>
       </c>
-      <c r="I26" s="11">
+      <c r="I26" s="6">
         <f t="shared" si="0"/>
         <v>660</v>
       </c>
@@ -5879,16 +6099,16 @@
       <c r="E27" t="s">
         <v>255</v>
       </c>
-      <c r="F27" s="11">
+      <c r="F27" s="6">
         <v>7</v>
       </c>
-      <c r="G27" s="11">
+      <c r="G27" s="6">
         <v>890</v>
       </c>
-      <c r="H27" s="11">
+      <c r="H27" s="6">
         <v>30</v>
       </c>
-      <c r="I27" s="11">
+      <c r="I27" s="6">
         <f t="shared" si="0"/>
         <v>860</v>
       </c>
@@ -5921,13 +6141,13 @@
       <c r="F28" t="s">
         <v>259</v>
       </c>
-      <c r="G28" s="11">
+      <c r="G28" s="6">
         <v>695</v>
       </c>
-      <c r="H28" s="11">
+      <c r="H28" s="6">
         <v>35</v>
       </c>
-      <c r="I28" s="11">
+      <c r="I28" s="6">
         <f t="shared" si="0"/>
         <v>660</v>
       </c>
@@ -5957,16 +6177,16 @@
       <c r="E29" t="s">
         <v>262</v>
       </c>
-      <c r="F29" s="11">
+      <c r="F29" s="6">
         <v>8</v>
       </c>
-      <c r="G29" s="11">
+      <c r="G29" s="6">
         <v>845</v>
       </c>
-      <c r="H29" s="11">
+      <c r="H29" s="6">
         <v>25</v>
       </c>
-      <c r="I29" s="11">
+      <c r="I29" s="6">
         <f t="shared" si="0"/>
         <v>820</v>
       </c>
@@ -5996,16 +6216,16 @@
       <c r="E30" t="s">
         <v>88</v>
       </c>
-      <c r="F30" s="11">
+      <c r="F30" s="6">
         <v>6</v>
       </c>
-      <c r="G30" s="11">
+      <c r="G30" s="6">
         <v>0</v>
       </c>
-      <c r="H30" s="11">
+      <c r="H30" s="6">
         <v>30</v>
       </c>
-      <c r="I30" s="11">
+      <c r="I30" s="6">
         <f>-H30</f>
         <v>-30</v>
       </c>
@@ -6035,16 +6255,16 @@
       <c r="E31" t="s">
         <v>264</v>
       </c>
-      <c r="F31" s="11">
+      <c r="F31" s="6">
         <v>12</v>
       </c>
-      <c r="G31" s="11">
+      <c r="G31" s="6">
         <v>0</v>
       </c>
-      <c r="H31" s="11">
+      <c r="H31" s="6">
         <v>35</v>
       </c>
-      <c r="I31" s="11">
+      <c r="I31" s="6">
         <f>-H31</f>
         <v>-35</v>
       </c>
@@ -6074,16 +6294,16 @@
       <c r="E32" t="s">
         <v>266</v>
       </c>
-      <c r="F32" s="11">
+      <c r="F32" s="6">
         <v>6</v>
       </c>
-      <c r="G32" s="11">
+      <c r="G32" s="6">
         <v>35</v>
       </c>
-      <c r="H32" s="11">
+      <c r="H32" s="6">
         <v>35</v>
       </c>
-      <c r="I32" s="11">
+      <c r="I32" s="6">
         <f>G32-H32</f>
         <v>0</v>
       </c>
@@ -6113,16 +6333,16 @@
       <c r="E33" t="s">
         <v>268</v>
       </c>
-      <c r="F33" s="11">
+      <c r="F33" s="6">
         <v>6</v>
       </c>
-      <c r="G33" s="11">
+      <c r="G33" s="6">
         <v>0</v>
       </c>
-      <c r="H33" s="11">
+      <c r="H33" s="6">
         <v>30</v>
       </c>
-      <c r="I33" s="11">
+      <c r="I33" s="6">
         <f>-H33</f>
         <v>-30</v>
       </c>
@@ -6158,13 +6378,13 @@
       <c r="F34" t="s">
         <v>79</v>
       </c>
-      <c r="G34" s="11">
+      <c r="G34" s="6">
         <v>680</v>
       </c>
-      <c r="H34" s="11">
+      <c r="H34" s="6">
         <v>20</v>
       </c>
-      <c r="I34" s="11">
+      <c r="I34" s="6">
         <f>G34-H34</f>
         <v>660</v>
       </c>
@@ -6197,13 +6417,13 @@
       <c r="F35" t="s">
         <v>86</v>
       </c>
-      <c r="G35" s="11">
+      <c r="G35" s="6">
         <v>685</v>
       </c>
-      <c r="H35" s="11">
+      <c r="H35" s="6">
         <v>25</v>
       </c>
-      <c r="I35" s="11">
+      <c r="I35" s="6">
         <f>G35-H35</f>
         <v>660</v>
       </c>
@@ -6233,16 +6453,16 @@
       <c r="E36" t="s">
         <v>277</v>
       </c>
-      <c r="F36" s="11">
+      <c r="F36" s="6">
         <v>2</v>
       </c>
-      <c r="G36" s="11">
+      <c r="G36" s="6">
         <v>1500</v>
       </c>
-      <c r="H36" s="11">
+      <c r="H36" s="6">
         <v>30</v>
       </c>
-      <c r="I36" s="11">
+      <c r="I36" s="6">
         <f>G36-H36</f>
         <v>1470</v>
       </c>
@@ -6275,13 +6495,13 @@
       <c r="F37" t="s">
         <v>44</v>
       </c>
-      <c r="G37" s="11">
+      <c r="G37" s="6">
         <v>0</v>
       </c>
-      <c r="H37" s="11">
+      <c r="H37" s="6">
         <v>25</v>
       </c>
-      <c r="I37" s="11">
+      <c r="I37" s="6">
         <f>-H37</f>
         <v>-25</v>
       </c>
@@ -6314,13 +6534,13 @@
       <c r="F38" t="s">
         <v>79</v>
       </c>
-      <c r="G38" s="11">
+      <c r="G38" s="6">
         <v>0</v>
       </c>
-      <c r="H38" s="11">
+      <c r="H38" s="6">
         <v>20</v>
       </c>
-      <c r="I38" s="11">
+      <c r="I38" s="6">
         <f>-H38</f>
         <v>-20</v>
       </c>
@@ -6353,13 +6573,13 @@
       <c r="F39" t="s">
         <v>153</v>
       </c>
-      <c r="G39" s="11">
+      <c r="G39" s="6">
         <v>690</v>
       </c>
-      <c r="H39" s="11">
+      <c r="H39" s="6">
         <v>30</v>
       </c>
-      <c r="I39" s="11">
+      <c r="I39" s="6">
         <f>G39-H39</f>
         <v>660</v>
       </c>
@@ -6392,13 +6612,13 @@
       <c r="F40" t="s">
         <v>153</v>
       </c>
-      <c r="G40" s="11">
+      <c r="G40" s="6">
         <v>0</v>
       </c>
-      <c r="H40" s="11">
+      <c r="H40" s="6">
         <v>30</v>
       </c>
-      <c r="I40" s="11">
+      <c r="I40" s="6">
         <f>-H40</f>
         <v>-30</v>
       </c>
@@ -6431,13 +6651,13 @@
       <c r="F41" t="s">
         <v>36</v>
       </c>
-      <c r="G41" s="11">
+      <c r="G41" s="6">
         <v>0</v>
       </c>
-      <c r="H41" s="11">
+      <c r="H41" s="6">
         <v>20</v>
       </c>
-      <c r="I41" s="11">
+      <c r="I41" s="6">
         <f>-H41</f>
         <v>-20</v>
       </c>
@@ -6467,16 +6687,16 @@
       <c r="E42" t="s">
         <v>293</v>
       </c>
-      <c r="F42" s="11">
+      <c r="F42" s="6">
         <v>2</v>
       </c>
-      <c r="G42" s="11">
+      <c r="G42" s="6">
         <v>1480</v>
       </c>
-      <c r="H42" s="11">
+      <c r="H42" s="6">
         <v>30</v>
       </c>
-      <c r="I42" s="11">
+      <c r="I42" s="6">
         <f t="shared" ref="I42:I53" si="1">G42-H42</f>
         <v>1450</v>
       </c>
@@ -6506,16 +6726,16 @@
       <c r="E43" t="s">
         <v>296</v>
       </c>
-      <c r="F43" s="11">
+      <c r="F43" s="6">
         <v>3</v>
       </c>
-      <c r="G43" s="11">
+      <c r="G43" s="6">
         <v>685</v>
       </c>
-      <c r="H43" s="11">
+      <c r="H43" s="6">
         <v>25</v>
       </c>
-      <c r="I43" s="11">
+      <c r="I43" s="6">
         <f t="shared" si="1"/>
         <v>660</v>
       </c>
@@ -6548,13 +6768,13 @@
       <c r="F44" t="s">
         <v>36</v>
       </c>
-      <c r="G44" s="11">
+      <c r="G44" s="6">
         <v>770</v>
       </c>
-      <c r="H44" s="11">
+      <c r="H44" s="6">
         <v>20</v>
       </c>
-      <c r="I44" s="11">
+      <c r="I44" s="6">
         <f t="shared" si="1"/>
         <v>750</v>
       </c>
@@ -6587,13 +6807,13 @@
       <c r="F45" t="s">
         <v>36</v>
       </c>
-      <c r="G45" s="11">
+      <c r="G45" s="6">
         <v>680</v>
       </c>
-      <c r="H45" s="11">
+      <c r="H45" s="6">
         <v>20</v>
       </c>
-      <c r="I45" s="11">
+      <c r="I45" s="6">
         <f t="shared" si="1"/>
         <v>660</v>
       </c>
@@ -6626,13 +6846,13 @@
       <c r="F46" t="s">
         <v>153</v>
       </c>
-      <c r="G46" s="11">
+      <c r="G46" s="6">
         <v>1030</v>
       </c>
-      <c r="H46" s="11">
+      <c r="H46" s="6">
         <v>30</v>
       </c>
-      <c r="I46" s="11">
+      <c r="I46" s="6">
         <f t="shared" si="1"/>
         <v>1000</v>
       </c>
@@ -6665,13 +6885,13 @@
       <c r="F47" t="s">
         <v>36</v>
       </c>
-      <c r="G47" s="11">
+      <c r="G47" s="6">
         <v>680</v>
       </c>
-      <c r="H47" s="11">
+      <c r="H47" s="6">
         <v>20</v>
       </c>
-      <c r="I47" s="11">
+      <c r="I47" s="6">
         <f t="shared" si="1"/>
         <v>660</v>
       </c>
@@ -6704,13 +6924,13 @@
       <c r="F48" t="s">
         <v>44</v>
       </c>
-      <c r="G48" s="11">
+      <c r="G48" s="6">
         <v>685</v>
       </c>
-      <c r="H48" s="11">
+      <c r="H48" s="6">
         <v>25</v>
       </c>
-      <c r="I48" s="11">
+      <c r="I48" s="6">
         <f t="shared" si="1"/>
         <v>660</v>
       </c>
@@ -6746,13 +6966,13 @@
       <c r="F49" t="s">
         <v>86</v>
       </c>
-      <c r="G49" s="11">
+      <c r="G49" s="6">
         <v>820</v>
       </c>
-      <c r="H49" s="11">
+      <c r="H49" s="6">
         <v>0</v>
       </c>
-      <c r="I49" s="11">
+      <c r="I49" s="6">
         <f t="shared" si="1"/>
         <v>820</v>
       </c>
@@ -6788,13 +7008,13 @@
       <c r="F50" t="s">
         <v>86</v>
       </c>
-      <c r="G50" s="11">
+      <c r="G50" s="6">
         <v>1585</v>
       </c>
-      <c r="H50" s="11">
+      <c r="H50" s="6">
         <v>25</v>
       </c>
-      <c r="I50" s="11">
+      <c r="I50" s="6">
         <f t="shared" si="1"/>
         <v>1560</v>
       </c>
@@ -6830,13 +7050,13 @@
       <c r="F51" t="s">
         <v>44</v>
       </c>
-      <c r="G51" s="11">
+      <c r="G51" s="6">
         <v>1050</v>
       </c>
-      <c r="H51" s="11">
+      <c r="H51" s="6">
         <v>0</v>
       </c>
-      <c r="I51" s="11">
+      <c r="I51" s="6">
         <f t="shared" si="1"/>
         <v>1050</v>
       </c>
@@ -6872,13 +7092,13 @@
       <c r="F52" t="s">
         <v>44</v>
       </c>
-      <c r="G52" s="11">
+      <c r="G52" s="6">
         <v>30</v>
       </c>
-      <c r="H52" s="11">
+      <c r="H52" s="6">
         <v>30</v>
       </c>
-      <c r="I52" s="11">
+      <c r="I52" s="6">
         <f t="shared" si="1"/>
         <v>0</v>
       </c>
@@ -6911,13 +7131,13 @@
       <c r="F53" t="s">
         <v>44</v>
       </c>
-      <c r="G53" s="11">
+      <c r="G53" s="6">
         <v>30</v>
       </c>
-      <c r="H53" s="11">
+      <c r="H53" s="6">
         <v>30</v>
       </c>
-      <c r="I53" s="11">
+      <c r="I53" s="6">
         <f t="shared" si="1"/>
         <v>0</v>
       </c>
@@ -6935,51 +7155,51 @@
       </c>
     </row>
     <row r="55" spans="1:17" x14ac:dyDescent="0.25">
-      <c r="D55" s="6">
+      <c r="D55" s="1">
         <f>COUNTA(D3:D53)</f>
         <v>45</v>
       </c>
-      <c r="G55" s="6">
+      <c r="G55" s="1">
         <f t="shared" ref="G55:Q55" si="2">SUBTOTAL(9,G3:G53)</f>
         <v>31145</v>
       </c>
-      <c r="H55" s="6">
+      <c r="H55" s="1">
         <f t="shared" si="2"/>
         <v>1355</v>
       </c>
-      <c r="I55" s="6">
+      <c r="I55" s="1">
         <f t="shared" si="2"/>
         <v>29790</v>
       </c>
-      <c r="J55" s="6">
+      <c r="J55" s="1">
         <f t="shared" si="2"/>
         <v>0</v>
       </c>
-      <c r="K55" s="6">
+      <c r="K55" s="1">
         <f t="shared" si="2"/>
         <v>0</v>
       </c>
-      <c r="L55" s="6">
+      <c r="L55" s="1">
         <f t="shared" si="2"/>
         <v>0</v>
       </c>
-      <c r="M55" s="6">
+      <c r="M55" s="1">
         <f t="shared" si="2"/>
         <v>0</v>
       </c>
-      <c r="N55" s="6">
+      <c r="N55" s="1">
         <f t="shared" si="2"/>
         <v>0</v>
       </c>
-      <c r="O55" s="6">
+      <c r="O55" s="1">
         <f t="shared" si="2"/>
         <v>0</v>
       </c>
-      <c r="P55" s="6">
+      <c r="P55" s="1">
         <f t="shared" si="2"/>
         <v>0</v>
       </c>
-      <c r="Q55" s="6">
+      <c r="Q55" s="1">
         <f t="shared" si="2"/>
         <v>51</v>
       </c>
@@ -6991,30 +7211,30 @@
       </c>
     </row>
     <row r="57" spans="1:17" x14ac:dyDescent="0.25">
-      <c r="A57" s="6" t="s">
-        <v>16</v>
-      </c>
-      <c r="C57" s="5" t="s">
+      <c r="A57" s="1" t="s">
+        <v>16</v>
+      </c>
+      <c r="C57" s="20" t="s">
         <v>89</v>
       </c>
-      <c r="D57" s="5"/>
-      <c r="E57" s="9" t="s">
+      <c r="D57" s="20"/>
+      <c r="E57" s="4" t="s">
         <v>90</v>
       </c>
       <c r="H57">
         <f>-5*25</f>
         <v>-125</v>
       </c>
-      <c r="K57" s="12" t="s">
-        <v>22</v>
-      </c>
-      <c r="L57" s="12" t="s">
+      <c r="K57" s="7" t="s">
+        <v>22</v>
+      </c>
+      <c r="L57" s="7" t="s">
         <v>91</v>
       </c>
-      <c r="M57" s="12" t="s">
+      <c r="M57" s="7" t="s">
         <v>90</v>
       </c>
-      <c r="O57" s="9" t="s">
+      <c r="O57" s="4" t="s">
         <v>92</v>
       </c>
     </row>
@@ -7022,15 +7242,15 @@
       <c r="A58" t="s">
         <v>182</v>
       </c>
-      <c r="B58" s="8" t="s">
+      <c r="B58" s="3" t="s">
         <v>93</v>
       </c>
-      <c r="C58" s="4">
+      <c r="C58" s="21">
         <f>SUMIFS(I$3:I$53,B$3:B$53,A$57,L$3:L$53,A$58)</f>
         <v>29790</v>
       </c>
-      <c r="D58" s="4"/>
-      <c r="E58" s="8">
+      <c r="D58" s="21"/>
+      <c r="E58" s="3">
         <f>SUMIFS(Q$3:Q$53,B$3:B$53,A$57,L$3:L$53,A$58)</f>
         <v>51</v>
       </c>
@@ -7061,13 +7281,13 @@
       </c>
     </row>
     <row r="59" spans="1:17" x14ac:dyDescent="0.25">
-      <c r="B59" s="7" t="s">
+      <c r="B59" s="2" t="s">
         <v>97</v>
       </c>
-      <c r="C59" s="3">
+      <c r="C59" s="22">
         <v>0</v>
       </c>
-      <c r="D59" s="3"/>
+      <c r="D59" s="22"/>
       <c r="K59" t="s">
         <v>98</v>
       </c>
@@ -7088,15 +7308,15 @@
       </c>
     </row>
     <row r="60" spans="1:17" x14ac:dyDescent="0.25">
-      <c r="B60" s="7" t="s">
+      <c r="B60" s="2" t="s">
         <v>99</v>
       </c>
-      <c r="C60" s="3">
+      <c r="C60" s="22">
         <f>-SUMIFS(I$3:I$53,B$3:B$53,A$57,P$3:P$53,"xx",N$3:N$53,"x")</f>
         <v>0</v>
       </c>
-      <c r="D60" s="3"/>
-      <c r="E60" s="7">
+      <c r="D60" s="22"/>
+      <c r="E60" s="2">
         <f>SUMIFS(Q$3:Q$53,B$3:B$53,A$57,P$3:P$53,"xx",N$3:N$53,"x")</f>
         <v>0</v>
       </c>
@@ -7120,19 +7340,19 @@
       </c>
     </row>
     <row r="61" spans="1:17" x14ac:dyDescent="0.25">
-      <c r="B61" s="9" t="s">
+      <c r="B61" s="4" t="s">
         <v>101</v>
       </c>
-      <c r="C61" s="5">
+      <c r="C61" s="20">
         <f>SUBTOTAL(9,C58:C60)</f>
         <v>29790</v>
       </c>
-      <c r="D61" s="5"/>
+      <c r="D61" s="20"/>
       <c r="E61">
         <f>E58</f>
         <v>51</v>
       </c>
-      <c r="K61" s="7" t="s">
+      <c r="K61" s="2" t="s">
         <v>102</v>
       </c>
       <c r="O61" t="s">
@@ -7144,29 +7364,29 @@
       </c>
     </row>
     <row r="62" spans="1:17" x14ac:dyDescent="0.25">
-      <c r="B62" s="7" t="s">
+      <c r="B62" s="2" t="s">
         <v>104</v>
       </c>
-      <c r="C62" s="2"/>
-      <c r="D62" s="2"/>
-      <c r="K62" s="7" t="s">
+      <c r="C62" s="18"/>
+      <c r="D62" s="18"/>
+      <c r="K62" s="2" t="s">
         <v>105</v>
       </c>
-      <c r="O62" s="9" t="s">
+      <c r="O62" s="4" t="s">
         <v>106</v>
       </c>
-      <c r="P62" s="9">
+      <c r="P62" s="4">
         <f>SUBTOTAL(9,P58:P61)</f>
         <v>274</v>
       </c>
     </row>
     <row r="63" spans="1:17" x14ac:dyDescent="0.25">
-      <c r="B63" s="13" t="s">
+      <c r="B63" s="8" t="s">
         <v>107</v>
       </c>
-      <c r="C63" s="2"/>
-      <c r="D63" s="2"/>
-      <c r="K63" s="15" t="s">
+      <c r="C63" s="18"/>
+      <c r="D63" s="18"/>
+      <c r="K63" s="10" t="s">
         <v>323</v>
       </c>
       <c r="L63">
@@ -7174,39 +7394,39 @@
       </c>
     </row>
     <row r="64" spans="1:17" x14ac:dyDescent="0.25">
-      <c r="L64" s="14">
+      <c r="L64" s="9">
         <f>SUBTOTAL(9,L58:L63)</f>
         <v>12637</v>
       </c>
-      <c r="M64" s="14">
+      <c r="M64" s="9">
         <f>M58</f>
         <v>20</v>
       </c>
     </row>
     <row r="65" spans="2:13" x14ac:dyDescent="0.25">
-      <c r="B65" s="6" t="s">
+      <c r="B65" s="1" t="s">
         <v>108</v>
       </c>
-      <c r="C65" s="1">
+      <c r="C65" s="19">
         <f>C61+C62+C63</f>
         <v>29790</v>
       </c>
-      <c r="D65" s="1"/>
-      <c r="E65" s="6" t="s">
+      <c r="D65" s="19"/>
+      <c r="E65" s="1" t="s">
         <v>109</v>
       </c>
-      <c r="K65" s="16"/>
-      <c r="L65" s="16"/>
-      <c r="M65" s="16"/>
+      <c r="K65" s="11"/>
+      <c r="L65" s="11"/>
+      <c r="M65" s="11"/>
     </row>
     <row r="66" spans="2:13" x14ac:dyDescent="0.25">
-      <c r="K66" s="12" t="s">
+      <c r="K66" s="7" t="s">
         <v>195</v>
       </c>
-      <c r="L66" s="12" t="s">
+      <c r="L66" s="7" t="s">
         <v>91</v>
       </c>
-      <c r="M66" s="12" t="s">
+      <c r="M66" s="7" t="s">
         <v>90</v>
       </c>
     </row>
@@ -7242,33 +7462,33 @@
       </c>
     </row>
     <row r="70" spans="2:13" x14ac:dyDescent="0.25">
-      <c r="K70" s="7" t="s">
+      <c r="K70" s="2" t="s">
         <v>102</v>
       </c>
     </row>
     <row r="71" spans="2:13" x14ac:dyDescent="0.25">
-      <c r="K71" s="7" t="s">
+      <c r="K71" s="2" t="s">
         <v>105</v>
       </c>
     </row>
     <row r="72" spans="2:13" x14ac:dyDescent="0.25">
-      <c r="L72" s="14">
+      <c r="L72" s="9">
         <f>SUBTOTAL(9,L67:L71)</f>
         <v>15887</v>
       </c>
-      <c r="M72" s="14">
+      <c r="M72" s="9">
         <f>M67</f>
         <v>27</v>
       </c>
     </row>
     <row r="74" spans="2:13" x14ac:dyDescent="0.25">
-      <c r="K74" s="12" t="s">
+      <c r="K74" s="7" t="s">
         <v>40</v>
       </c>
-      <c r="L74" s="12" t="s">
+      <c r="L74" s="7" t="s">
         <v>91</v>
       </c>
-      <c r="M74" s="12" t="s">
+      <c r="M74" s="7" t="s">
         <v>90</v>
       </c>
     </row>
@@ -7304,21 +7524,21 @@
       </c>
     </row>
     <row r="78" spans="2:13" x14ac:dyDescent="0.25">
-      <c r="K78" s="7" t="s">
+      <c r="K78" s="2" t="s">
         <v>102</v>
       </c>
     </row>
     <row r="79" spans="2:13" x14ac:dyDescent="0.25">
-      <c r="K79" s="7" t="s">
+      <c r="K79" s="2" t="s">
         <v>105</v>
       </c>
     </row>
     <row r="80" spans="2:13" x14ac:dyDescent="0.25">
-      <c r="L80" s="14">
+      <c r="L80" s="9">
         <f>SUBTOTAL(9,L75:L79)</f>
         <v>1540</v>
       </c>
-      <c r="M80" s="14">
+      <c r="M80" s="9">
         <f>M75</f>
         <v>4</v>
       </c>
@@ -7368,55 +7588,55 @@
   </cols>
   <sheetData>
     <row r="2" spans="1:17" x14ac:dyDescent="0.25">
-      <c r="A2" s="10" t="s">
+      <c r="A2" s="5" t="s">
         <v>0</v>
       </c>
-      <c r="B2" s="10" t="s">
-        <v>1</v>
-      </c>
-      <c r="C2" s="10" t="s">
+      <c r="B2" s="5" t="s">
+        <v>1</v>
+      </c>
+      <c r="C2" s="5" t="s">
         <v>2</v>
       </c>
-      <c r="D2" s="10" t="s">
+      <c r="D2" s="5" t="s">
         <v>3</v>
       </c>
-      <c r="E2" s="10" t="s">
+      <c r="E2" s="5" t="s">
         <v>4</v>
       </c>
-      <c r="F2" s="10" t="s">
+      <c r="F2" s="5" t="s">
         <v>5</v>
       </c>
-      <c r="G2" s="10" t="s">
+      <c r="G2" s="5" t="s">
         <v>6</v>
       </c>
-      <c r="H2" s="10" t="s">
+      <c r="H2" s="5" t="s">
         <v>7</v>
       </c>
-      <c r="I2" s="10" t="s">
+      <c r="I2" s="5" t="s">
         <v>8</v>
       </c>
-      <c r="J2" s="10" t="s">
+      <c r="J2" s="5" t="s">
         <v>9</v>
       </c>
-      <c r="K2" s="10" t="s">
+      <c r="K2" s="5" t="s">
         <v>10</v>
       </c>
-      <c r="L2" s="10" t="s">
+      <c r="L2" s="5" t="s">
         <v>11</v>
       </c>
-      <c r="M2" s="10" t="s">
+      <c r="M2" s="5" t="s">
         <v>12</v>
       </c>
-      <c r="N2" s="10" t="s">
+      <c r="N2" s="5" t="s">
         <v>13</v>
       </c>
-      <c r="O2" s="10" t="s">
+      <c r="O2" s="5" t="s">
         <v>14</v>
       </c>
-      <c r="P2" s="10" t="s">
+      <c r="P2" s="5" t="s">
         <v>15</v>
       </c>
-      <c r="Q2" s="10" t="s">
+      <c r="Q2" s="5" t="s">
         <v>324</v>
       </c>
     </row>
@@ -7436,13 +7656,13 @@
       <c r="F3" t="s">
         <v>259</v>
       </c>
-      <c r="G3" s="11">
+      <c r="G3" s="6">
         <v>735</v>
       </c>
-      <c r="H3" s="11">
+      <c r="H3" s="6">
         <v>35</v>
       </c>
-      <c r="I3" s="11">
+      <c r="I3" s="6">
         <f t="shared" ref="I3:I44" si="0">G3-H3</f>
         <v>700</v>
       </c>
@@ -7475,13 +7695,13 @@
       <c r="F4" t="s">
         <v>153</v>
       </c>
-      <c r="G4" s="11">
+      <c r="G4" s="6">
         <v>700</v>
       </c>
-      <c r="H4" s="11">
+      <c r="H4" s="6">
         <v>30</v>
       </c>
-      <c r="I4" s="11">
+      <c r="I4" s="6">
         <f t="shared" si="0"/>
         <v>670</v>
       </c>
@@ -7511,16 +7731,16 @@
       <c r="E5" t="s">
         <v>334</v>
       </c>
-      <c r="F5" s="11">
+      <c r="F5" s="6">
         <v>12</v>
       </c>
-      <c r="G5" s="11">
+      <c r="G5" s="6">
         <v>760</v>
       </c>
-      <c r="H5" s="11">
+      <c r="H5" s="6">
         <v>30</v>
       </c>
-      <c r="I5" s="11">
+      <c r="I5" s="6">
         <f t="shared" si="0"/>
         <v>730</v>
       </c>
@@ -7550,16 +7770,16 @@
       <c r="E6" t="s">
         <v>337</v>
       </c>
-      <c r="F6" s="11">
+      <c r="F6" s="6">
         <v>7</v>
       </c>
-      <c r="G6" s="11">
+      <c r="G6" s="6">
         <v>690</v>
       </c>
-      <c r="H6" s="11">
+      <c r="H6" s="6">
         <v>30</v>
       </c>
-      <c r="I6" s="11">
+      <c r="I6" s="6">
         <f t="shared" si="0"/>
         <v>660</v>
       </c>
@@ -7589,16 +7809,16 @@
       <c r="E7" t="s">
         <v>340</v>
       </c>
-      <c r="F7" s="11">
+      <c r="F7" s="6">
         <v>7</v>
       </c>
-      <c r="G7" s="11">
+      <c r="G7" s="6">
         <v>920</v>
       </c>
-      <c r="H7" s="11">
+      <c r="H7" s="6">
         <v>30</v>
       </c>
-      <c r="I7" s="11">
+      <c r="I7" s="6">
         <f t="shared" si="0"/>
         <v>890</v>
       </c>
@@ -7628,16 +7848,16 @@
       <c r="E8" t="s">
         <v>343</v>
       </c>
-      <c r="F8" s="11">
+      <c r="F8" s="6">
         <v>3</v>
       </c>
-      <c r="G8" s="11">
+      <c r="G8" s="6">
         <v>0</v>
       </c>
-      <c r="H8" s="11">
+      <c r="H8" s="6">
         <v>25</v>
       </c>
-      <c r="I8" s="11">
+      <c r="I8" s="6">
         <f t="shared" si="0"/>
         <v>-25</v>
       </c>
@@ -7667,16 +7887,16 @@
       <c r="E9" t="s">
         <v>346</v>
       </c>
-      <c r="F9" s="11">
+      <c r="F9" s="6">
         <v>11</v>
       </c>
-      <c r="G9" s="11">
+      <c r="G9" s="6">
         <v>375</v>
       </c>
-      <c r="H9" s="11">
+      <c r="H9" s="6">
         <v>25</v>
       </c>
-      <c r="I9" s="11">
+      <c r="I9" s="6">
         <f t="shared" si="0"/>
         <v>350</v>
       </c>
@@ -7706,16 +7926,16 @@
       <c r="E10" t="s">
         <v>349</v>
       </c>
-      <c r="F10" s="11">
+      <c r="F10" s="6">
         <v>2</v>
       </c>
-      <c r="G10" s="11">
+      <c r="G10" s="6">
         <v>720</v>
       </c>
-      <c r="H10" s="11">
+      <c r="H10" s="6">
         <v>30</v>
       </c>
-      <c r="I10" s="11">
+      <c r="I10" s="6">
         <f t="shared" si="0"/>
         <v>690</v>
       </c>
@@ -7748,13 +7968,13 @@
       <c r="F11" t="s">
         <v>20</v>
       </c>
-      <c r="G11" s="11">
+      <c r="G11" s="6">
         <v>720</v>
       </c>
-      <c r="H11" s="11">
+      <c r="H11" s="6">
         <v>30</v>
       </c>
-      <c r="I11" s="11">
+      <c r="I11" s="6">
         <f t="shared" si="0"/>
         <v>690</v>
       </c>
@@ -7787,13 +8007,13 @@
       <c r="F12" t="s">
         <v>153</v>
       </c>
-      <c r="G12" s="11">
+      <c r="G12" s="6">
         <v>730</v>
       </c>
-      <c r="H12" s="11">
+      <c r="H12" s="6">
         <v>30</v>
       </c>
-      <c r="I12" s="11">
+      <c r="I12" s="6">
         <f t="shared" si="0"/>
         <v>700</v>
       </c>
@@ -7826,13 +8046,13 @@
       <c r="F13" t="s">
         <v>153</v>
       </c>
-      <c r="G13" s="11">
+      <c r="G13" s="6">
         <v>890</v>
       </c>
-      <c r="H13" s="11">
+      <c r="H13" s="6">
         <v>30</v>
       </c>
-      <c r="I13" s="11">
+      <c r="I13" s="6">
         <f t="shared" si="0"/>
         <v>860</v>
       </c>
@@ -7865,13 +8085,13 @@
       <c r="F14" t="s">
         <v>113</v>
       </c>
-      <c r="G14" s="11">
+      <c r="G14" s="6">
         <v>1775</v>
       </c>
-      <c r="H14" s="11">
+      <c r="H14" s="6">
         <v>35</v>
       </c>
-      <c r="I14" s="11">
+      <c r="I14" s="6">
         <f t="shared" si="0"/>
         <v>1740</v>
       </c>
@@ -7901,16 +8121,16 @@
       <c r="E15" t="s">
         <v>364</v>
       </c>
-      <c r="F15" s="11">
-        <v>1</v>
-      </c>
-      <c r="G15" s="11">
+      <c r="F15" s="6">
+        <v>1</v>
+      </c>
+      <c r="G15" s="6">
         <v>885</v>
       </c>
-      <c r="H15" s="11">
+      <c r="H15" s="6">
         <v>25</v>
       </c>
-      <c r="I15" s="11">
+      <c r="I15" s="6">
         <f t="shared" si="0"/>
         <v>860</v>
       </c>
@@ -7940,16 +8160,16 @@
       <c r="E16" t="s">
         <v>367</v>
       </c>
-      <c r="F16" s="11">
+      <c r="F16" s="6">
         <v>9</v>
       </c>
-      <c r="G16" s="11">
+      <c r="G16" s="6">
         <v>690</v>
       </c>
-      <c r="H16" s="11">
+      <c r="H16" s="6">
         <v>30</v>
       </c>
-      <c r="I16" s="11">
+      <c r="I16" s="6">
         <f t="shared" si="0"/>
         <v>660</v>
       </c>
@@ -7982,13 +8202,13 @@
       <c r="F17" t="s">
         <v>44</v>
       </c>
-      <c r="G17" s="11">
+      <c r="G17" s="6">
         <v>685</v>
       </c>
-      <c r="H17" s="11">
+      <c r="H17" s="6">
         <v>25</v>
       </c>
-      <c r="I17" s="11">
+      <c r="I17" s="6">
         <f t="shared" si="0"/>
         <v>660</v>
       </c>
@@ -8021,13 +8241,13 @@
       <c r="F18" t="s">
         <v>44</v>
       </c>
-      <c r="G18" s="11">
+      <c r="G18" s="6">
         <v>0</v>
       </c>
-      <c r="H18" s="11">
+      <c r="H18" s="6">
         <v>25</v>
       </c>
-      <c r="I18" s="11">
+      <c r="I18" s="6">
         <f t="shared" si="0"/>
         <v>-25</v>
       </c>
@@ -8057,16 +8277,16 @@
       <c r="E19" t="s">
         <v>376</v>
       </c>
-      <c r="F19" s="11">
+      <c r="F19" s="6">
         <v>12</v>
       </c>
-      <c r="G19" s="11">
+      <c r="G19" s="6">
         <v>870</v>
       </c>
-      <c r="H19" s="11">
+      <c r="H19" s="6">
         <v>30</v>
       </c>
-      <c r="I19" s="11">
+      <c r="I19" s="6">
         <f t="shared" si="0"/>
         <v>840</v>
       </c>
@@ -8099,15 +8319,15 @@
       <c r="F20" t="s">
         <v>44</v>
       </c>
-      <c r="G20" s="11">
-        <v>2370</v>
-      </c>
-      <c r="H20" s="11">
+      <c r="G20" s="6">
+        <v>0</v>
+      </c>
+      <c r="H20" s="6">
         <v>25</v>
       </c>
-      <c r="I20" s="11">
+      <c r="I20" s="6">
         <f t="shared" si="0"/>
-        <v>2345</v>
+        <v>-25</v>
       </c>
       <c r="J20" t="s">
         <v>22</v>
@@ -8141,13 +8361,13 @@
       <c r="F21" t="s">
         <v>36</v>
       </c>
-      <c r="G21" s="11">
+      <c r="G21" s="6">
         <v>910</v>
       </c>
-      <c r="H21" s="11">
+      <c r="H21" s="6">
         <v>20</v>
       </c>
-      <c r="I21" s="11">
+      <c r="I21" s="6">
         <f t="shared" si="0"/>
         <v>890</v>
       </c>
@@ -8177,16 +8397,16 @@
       <c r="E22" t="s">
         <v>386</v>
       </c>
-      <c r="F22" s="11">
+      <c r="F22" s="6">
         <v>4</v>
       </c>
-      <c r="G22" s="11">
+      <c r="G22" s="6">
         <v>375</v>
       </c>
-      <c r="H22" s="11">
+      <c r="H22" s="6">
         <v>25</v>
       </c>
-      <c r="I22" s="11">
+      <c r="I22" s="6">
         <f t="shared" si="0"/>
         <v>350</v>
       </c>
@@ -8216,16 +8436,16 @@
       <c r="E23" t="s">
         <v>389</v>
       </c>
-      <c r="F23" s="11">
+      <c r="F23" s="6">
         <v>12</v>
       </c>
-      <c r="G23" s="11">
+      <c r="G23" s="6">
         <v>720</v>
       </c>
-      <c r="H23" s="11">
+      <c r="H23" s="6">
         <v>30</v>
       </c>
-      <c r="I23" s="11">
+      <c r="I23" s="6">
         <f t="shared" si="0"/>
         <v>690</v>
       </c>
@@ -8255,16 +8475,16 @@
       <c r="E24" t="s">
         <v>392</v>
       </c>
-      <c r="F24" s="11">
+      <c r="F24" s="6">
         <v>7</v>
       </c>
-      <c r="G24" s="11">
+      <c r="G24" s="6">
         <v>690</v>
       </c>
-      <c r="H24" s="11">
+      <c r="H24" s="6">
         <v>30</v>
       </c>
-      <c r="I24" s="11">
+      <c r="I24" s="6">
         <f t="shared" si="0"/>
         <v>660</v>
       </c>
@@ -8294,16 +8514,16 @@
       <c r="E25" t="s">
         <v>395</v>
       </c>
-      <c r="F25" s="11">
+      <c r="F25" s="6">
         <v>7</v>
       </c>
-      <c r="G25" s="11">
+      <c r="G25" s="6">
         <v>0</v>
       </c>
-      <c r="H25" s="11">
+      <c r="H25" s="6">
         <v>30</v>
       </c>
-      <c r="I25" s="11">
+      <c r="I25" s="6">
         <f t="shared" si="0"/>
         <v>-30</v>
       </c>
@@ -8333,16 +8553,16 @@
       <c r="E26" t="s">
         <v>398</v>
       </c>
-      <c r="F26" s="11">
+      <c r="F26" s="6">
         <v>10</v>
       </c>
-      <c r="G26" s="11">
+      <c r="G26" s="6">
         <v>815</v>
       </c>
-      <c r="H26" s="11">
+      <c r="H26" s="6">
         <v>25</v>
       </c>
-      <c r="I26" s="11">
+      <c r="I26" s="6">
         <f t="shared" si="0"/>
         <v>790</v>
       </c>
@@ -8372,16 +8592,16 @@
       <c r="E27" t="s">
         <v>401</v>
       </c>
-      <c r="F27" s="11">
+      <c r="F27" s="6">
         <v>2</v>
       </c>
-      <c r="G27" s="11">
+      <c r="G27" s="6">
         <v>0</v>
       </c>
-      <c r="H27" s="11">
+      <c r="H27" s="6">
         <v>30</v>
       </c>
-      <c r="I27" s="11">
+      <c r="I27" s="6">
         <f t="shared" si="0"/>
         <v>-30</v>
       </c>
@@ -8411,16 +8631,16 @@
       <c r="E28" t="s">
         <v>404</v>
       </c>
-      <c r="F28" s="11">
+      <c r="F28" s="6">
         <v>4</v>
       </c>
-      <c r="G28" s="11">
+      <c r="G28" s="6">
         <v>775</v>
       </c>
-      <c r="H28" s="11">
+      <c r="H28" s="6">
         <v>25</v>
       </c>
-      <c r="I28" s="11">
+      <c r="I28" s="6">
         <f t="shared" si="0"/>
         <v>750</v>
       </c>
@@ -8450,16 +8670,16 @@
       <c r="E29" t="s">
         <v>407</v>
       </c>
-      <c r="F29" s="11">
+      <c r="F29" s="6">
         <v>8</v>
       </c>
-      <c r="G29" s="11">
+      <c r="G29" s="6">
         <v>820</v>
       </c>
-      <c r="H29" s="11">
+      <c r="H29" s="6">
         <v>30</v>
       </c>
-      <c r="I29" s="11">
+      <c r="I29" s="6">
         <f t="shared" si="0"/>
         <v>790</v>
       </c>
@@ -8492,13 +8712,13 @@
       <c r="F30" t="s">
         <v>20</v>
       </c>
-      <c r="G30" s="11">
+      <c r="G30" s="6">
         <v>690</v>
       </c>
-      <c r="H30" s="11">
+      <c r="H30" s="6">
         <v>30</v>
       </c>
-      <c r="I30" s="11">
+      <c r="I30" s="6">
         <f t="shared" si="0"/>
         <v>660</v>
       </c>
@@ -8531,13 +8751,13 @@
       <c r="F31" t="s">
         <v>86</v>
       </c>
-      <c r="G31" s="11">
+      <c r="G31" s="6">
         <v>885</v>
       </c>
-      <c r="H31" s="11">
+      <c r="H31" s="6">
         <v>25</v>
       </c>
-      <c r="I31" s="11">
+      <c r="I31" s="6">
         <f t="shared" si="0"/>
         <v>860</v>
       </c>
@@ -8570,13 +8790,13 @@
       <c r="F32" t="s">
         <v>36</v>
       </c>
-      <c r="G32" s="11">
+      <c r="G32" s="6">
         <v>680</v>
       </c>
-      <c r="H32" s="11">
+      <c r="H32" s="6">
         <v>20</v>
       </c>
-      <c r="I32" s="11">
+      <c r="I32" s="6">
         <f t="shared" si="0"/>
         <v>660</v>
       </c>
@@ -8609,13 +8829,13 @@
       <c r="F33" t="s">
         <v>36</v>
       </c>
-      <c r="G33" s="11">
+      <c r="G33" s="6">
         <v>840</v>
       </c>
-      <c r="H33" s="11">
+      <c r="H33" s="6">
         <v>20</v>
       </c>
-      <c r="I33" s="11">
+      <c r="I33" s="6">
         <f t="shared" si="0"/>
         <v>820</v>
       </c>
@@ -8648,13 +8868,13 @@
       <c r="F34" t="s">
         <v>86</v>
       </c>
-      <c r="G34" s="11">
+      <c r="G34" s="6">
         <v>0</v>
       </c>
-      <c r="H34" s="11">
+      <c r="H34" s="6">
         <v>25</v>
       </c>
-      <c r="I34" s="11">
+      <c r="I34" s="6">
         <f t="shared" si="0"/>
         <v>-25</v>
       </c>
@@ -8684,16 +8904,16 @@
       <c r="E35" t="s">
         <v>425</v>
       </c>
-      <c r="F35" s="11">
+      <c r="F35" s="6">
         <v>12</v>
       </c>
-      <c r="G35" s="11">
+      <c r="G35" s="6">
         <v>0</v>
       </c>
-      <c r="H35" s="11">
+      <c r="H35" s="6">
         <v>40</v>
       </c>
-      <c r="I35" s="11">
+      <c r="I35" s="6">
         <f t="shared" si="0"/>
         <v>-40</v>
       </c>
@@ -8726,13 +8946,13 @@
       <c r="F36" t="s">
         <v>79</v>
       </c>
-      <c r="G36" s="11">
+      <c r="G36" s="6">
         <v>680</v>
       </c>
-      <c r="H36" s="11">
+      <c r="H36" s="6">
         <v>20</v>
       </c>
-      <c r="I36" s="11">
+      <c r="I36" s="6">
         <f t="shared" si="0"/>
         <v>660</v>
       </c>
@@ -8762,16 +8982,16 @@
       <c r="E37" t="s">
         <v>431</v>
       </c>
-      <c r="F37" s="11">
+      <c r="F37" s="6">
         <v>5</v>
       </c>
-      <c r="G37" s="11">
+      <c r="G37" s="6">
         <v>715</v>
       </c>
-      <c r="H37" s="11">
+      <c r="H37" s="6">
         <v>25</v>
       </c>
-      <c r="I37" s="11">
+      <c r="I37" s="6">
         <f t="shared" si="0"/>
         <v>690</v>
       </c>
@@ -8801,16 +9021,16 @@
       <c r="E38" t="s">
         <v>434</v>
       </c>
-      <c r="F38" s="11">
-        <v>1</v>
-      </c>
-      <c r="G38" s="11">
+      <c r="F38" s="6">
+        <v>1</v>
+      </c>
+      <c r="G38" s="6">
         <v>0</v>
       </c>
-      <c r="H38" s="11">
+      <c r="H38" s="6">
         <v>25</v>
       </c>
-      <c r="I38" s="11">
+      <c r="I38" s="6">
         <f t="shared" si="0"/>
         <v>-25</v>
       </c>
@@ -8843,13 +9063,13 @@
       <c r="F39" t="s">
         <v>86</v>
       </c>
-      <c r="G39" s="11">
+      <c r="G39" s="6">
         <v>30</v>
       </c>
-      <c r="H39" s="11">
+      <c r="H39" s="6">
         <v>30</v>
       </c>
-      <c r="I39" s="11">
+      <c r="I39" s="6">
         <f t="shared" si="0"/>
         <v>0</v>
       </c>
@@ -8882,13 +9102,13 @@
       <c r="F40" t="s">
         <v>217</v>
       </c>
-      <c r="G40" s="11">
+      <c r="G40" s="6">
         <v>30</v>
       </c>
-      <c r="H40" s="11">
+      <c r="H40" s="6">
         <v>30</v>
       </c>
-      <c r="I40" s="11">
+      <c r="I40" s="6">
         <f t="shared" si="0"/>
         <v>0</v>
       </c>
@@ -8918,16 +9138,16 @@
       <c r="E41" t="s">
         <v>440</v>
       </c>
-      <c r="F41" s="11">
+      <c r="F41" s="6">
         <v>9</v>
       </c>
-      <c r="G41" s="11">
+      <c r="G41" s="6">
         <v>35</v>
       </c>
-      <c r="H41" s="11">
+      <c r="H41" s="6">
         <v>35</v>
       </c>
-      <c r="I41" s="11">
+      <c r="I41" s="6">
         <f t="shared" si="0"/>
         <v>0</v>
       </c>
@@ -8960,13 +9180,13 @@
       <c r="F42" t="s">
         <v>20</v>
       </c>
-      <c r="G42" s="11">
+      <c r="G42" s="6">
         <v>40</v>
       </c>
-      <c r="H42" s="11">
+      <c r="H42" s="6">
         <v>40</v>
       </c>
-      <c r="I42" s="11">
+      <c r="I42" s="6">
         <f t="shared" si="0"/>
         <v>0</v>
       </c>
@@ -8983,154 +9203,154 @@
         <v>1</v>
       </c>
     </row>
-    <row r="43" spans="1:17" s="7" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="B43" s="7" t="s">
-        <v>16</v>
-      </c>
-      <c r="C43" s="7" t="s">
+    <row r="43" spans="1:17" s="2" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="B43" s="2" t="s">
+        <v>16</v>
+      </c>
+      <c r="C43" s="2" t="s">
         <v>443</v>
       </c>
-      <c r="D43" s="7" t="s">
+      <c r="D43" s="2" t="s">
         <v>444</v>
       </c>
-      <c r="E43" s="7" t="s">
+      <c r="E43" s="2" t="s">
         <v>445</v>
       </c>
-      <c r="F43" s="7" t="s">
+      <c r="F43" s="2" t="s">
         <v>79</v>
       </c>
-      <c r="G43" s="17">
+      <c r="G43" s="12">
         <v>370</v>
       </c>
-      <c r="H43" s="17">
+      <c r="H43" s="12">
         <v>20</v>
       </c>
-      <c r="I43" s="17">
+      <c r="I43" s="12">
         <f t="shared" si="0"/>
         <v>350</v>
       </c>
-      <c r="J43" s="7" t="s">
+      <c r="J43" s="2" t="s">
         <v>446</v>
       </c>
-      <c r="K43" s="7" t="s">
-        <v>22</v>
-      </c>
-      <c r="L43" s="7" t="s">
+      <c r="K43" s="2" t="s">
+        <v>22</v>
+      </c>
+      <c r="L43" s="2" t="s">
         <v>447</v>
       </c>
-      <c r="M43" s="7" t="s">
+      <c r="M43" s="2" t="s">
         <v>102</v>
       </c>
-      <c r="N43" s="7" t="s">
+      <c r="N43" s="2" t="s">
         <v>448</v>
       </c>
-      <c r="O43" s="7" t="s">
+      <c r="O43" s="2" t="s">
         <v>448</v>
       </c>
-      <c r="P43" s="7" t="s">
+      <c r="P43" s="2" t="s">
         <v>449</v>
       </c>
-      <c r="Q43" s="17">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="44" spans="1:17" s="7" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="B44" s="7" t="s">
-        <v>16</v>
-      </c>
-      <c r="C44" s="7" t="s">
+      <c r="Q43" s="12">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="44" spans="1:17" s="2" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="B44" s="2" t="s">
+        <v>16</v>
+      </c>
+      <c r="C44" s="2" t="s">
         <v>122</v>
       </c>
-      <c r="D44" s="7" t="s">
+      <c r="D44" s="2" t="s">
         <v>123</v>
       </c>
-      <c r="E44" s="7" t="s">
+      <c r="E44" s="2" t="s">
         <v>124</v>
       </c>
-      <c r="F44" s="17">
+      <c r="F44" s="12">
         <v>7</v>
       </c>
-      <c r="G44" s="17">
+      <c r="G44" s="12">
         <v>650</v>
       </c>
-      <c r="H44" s="17">
+      <c r="H44" s="12">
         <v>30</v>
       </c>
-      <c r="I44" s="17">
+      <c r="I44" s="12">
         <f t="shared" si="0"/>
         <v>620</v>
       </c>
-      <c r="J44" s="7" t="s">
+      <c r="J44" s="2" t="s">
         <v>446</v>
       </c>
-      <c r="K44" s="7" t="s">
-        <v>22</v>
-      </c>
-      <c r="L44" s="7" t="s">
+      <c r="K44" s="2" t="s">
+        <v>22</v>
+      </c>
+      <c r="L44" s="2" t="s">
         <v>115</v>
       </c>
-      <c r="M44" s="7" t="s">
+      <c r="M44" s="2" t="s">
         <v>102</v>
       </c>
-      <c r="N44" s="7" t="s">
+      <c r="N44" s="2" t="s">
         <v>448</v>
       </c>
-      <c r="O44" s="7" t="s">
+      <c r="O44" s="2" t="s">
         <v>448</v>
       </c>
-      <c r="P44" s="7" t="s">
+      <c r="P44" s="2" t="s">
         <v>449</v>
       </c>
-      <c r="Q44" s="17">
+      <c r="Q44" s="12">
         <v>1</v>
       </c>
     </row>
     <row r="46" spans="1:17" x14ac:dyDescent="0.25">
-      <c r="D46" s="6">
+      <c r="D46" s="1">
         <f>COUNTA(D3:D44)</f>
         <v>38</v>
       </c>
-      <c r="G46" s="6">
+      <c r="G46" s="1">
         <f t="shared" ref="G46:Q46" si="1">SUBTOTAL(9,G3:G44)</f>
-        <v>25265</v>
-      </c>
-      <c r="H46" s="6">
+        <v>22895</v>
+      </c>
+      <c r="H46" s="1">
         <f t="shared" si="1"/>
         <v>1180</v>
       </c>
-      <c r="I46" s="6">
+      <c r="I46" s="1">
         <f t="shared" si="1"/>
-        <v>24085</v>
-      </c>
-      <c r="J46" s="6">
+        <v>21715</v>
+      </c>
+      <c r="J46" s="1">
         <f t="shared" si="1"/>
         <v>0</v>
       </c>
-      <c r="K46" s="6">
+      <c r="K46" s="1">
         <f t="shared" si="1"/>
         <v>0</v>
       </c>
-      <c r="L46" s="6">
+      <c r="L46" s="1">
         <f t="shared" si="1"/>
         <v>0</v>
       </c>
-      <c r="M46" s="6">
+      <c r="M46" s="1">
         <f t="shared" si="1"/>
         <v>0</v>
       </c>
-      <c r="N46" s="6">
+      <c r="N46" s="1">
         <f t="shared" si="1"/>
         <v>0</v>
       </c>
-      <c r="O46" s="6">
+      <c r="O46" s="1">
         <f t="shared" si="1"/>
         <v>0</v>
       </c>
-      <c r="P46" s="6">
+      <c r="P46" s="1">
         <f t="shared" si="1"/>
         <v>0</v>
       </c>
-      <c r="Q46" s="6">
+      <c r="Q46" s="1">
         <f t="shared" si="1"/>
         <v>42</v>
       </c>
@@ -9142,30 +9362,30 @@
       </c>
     </row>
     <row r="48" spans="1:17" x14ac:dyDescent="0.25">
-      <c r="A48" s="6" t="s">
-        <v>16</v>
-      </c>
-      <c r="C48" s="5" t="s">
+      <c r="A48" s="1" t="s">
+        <v>16</v>
+      </c>
+      <c r="C48" s="20" t="s">
         <v>89</v>
       </c>
-      <c r="D48" s="5"/>
-      <c r="E48" s="9" t="s">
+      <c r="D48" s="20"/>
+      <c r="E48" s="4" t="s">
         <v>90</v>
       </c>
       <c r="H48">
         <f>-5*25</f>
         <v>-125</v>
       </c>
-      <c r="K48" s="12" t="s">
+      <c r="K48" s="7" t="s">
         <v>327</v>
       </c>
-      <c r="L48" s="12" t="s">
+      <c r="L48" s="7" t="s">
         <v>91</v>
       </c>
-      <c r="M48" s="12" t="s">
+      <c r="M48" s="7" t="s">
         <v>90</v>
       </c>
-      <c r="O48" s="9" t="s">
+      <c r="O48" s="4" t="s">
         <v>92</v>
       </c>
     </row>
@@ -9173,15 +9393,15 @@
       <c r="A49" t="s">
         <v>328</v>
       </c>
-      <c r="B49" s="8" t="s">
+      <c r="B49" s="3" t="s">
         <v>93</v>
       </c>
-      <c r="C49" s="4">
+      <c r="C49" s="21">
         <f>SUMIFS(I$3:I$44,B$3:B$44,A$48,L$3:L$44,A$49)</f>
-        <v>23115</v>
-      </c>
-      <c r="D49" s="4"/>
-      <c r="E49" s="8">
+        <v>20745</v>
+      </c>
+      <c r="D49" s="21"/>
+      <c r="E49" s="3">
         <f>SUMIFS(Q$3:Q$44,B$3:B$44,A$48,L$3:L$44,A$49)</f>
         <v>40</v>
       </c>
@@ -9212,13 +9432,13 @@
       </c>
     </row>
     <row r="50" spans="1:16" x14ac:dyDescent="0.25">
-      <c r="B50" s="7" t="s">
+      <c r="B50" s="2" t="s">
         <v>97</v>
       </c>
-      <c r="C50" s="3">
+      <c r="C50" s="22">
         <v>0</v>
       </c>
-      <c r="D50" s="3"/>
+      <c r="D50" s="22"/>
       <c r="K50" t="s">
         <v>98</v>
       </c>
@@ -9235,19 +9455,19 @@
       </c>
       <c r="P50">
         <f>L62</f>
-        <v>9005</v>
+        <v>6635</v>
       </c>
     </row>
     <row r="51" spans="1:16" x14ac:dyDescent="0.25">
-      <c r="B51" s="7" t="s">
+      <c r="B51" s="2" t="s">
         <v>99</v>
       </c>
-      <c r="C51" s="3">
+      <c r="C51" s="22">
         <f>-SUMIFS(I$3:I$44,B$3:B$44,A$48,P$3:P$44,"xx",N$3:N$44,"x")</f>
         <v>-970</v>
       </c>
-      <c r="D51" s="3"/>
-      <c r="E51" s="7">
+      <c r="D51" s="22"/>
+      <c r="E51" s="2">
         <f>SUMIFS(Q$3:Q$44,B$3:B$44,A$48,P$3:P$44,"xx",N$3:N$44,"x")</f>
         <v>2</v>
       </c>
@@ -9263,25 +9483,25 @@
       </c>
     </row>
     <row r="52" spans="1:16" x14ac:dyDescent="0.25">
-      <c r="B52" s="9" t="s">
+      <c r="B52" s="4" t="s">
         <v>101</v>
       </c>
-      <c r="C52" s="5">
+      <c r="C52" s="20">
         <f>SUBTOTAL(9,C49:C51)</f>
-        <v>22145</v>
-      </c>
-      <c r="D52" s="5"/>
+        <v>19775</v>
+      </c>
+      <c r="D52" s="20"/>
       <c r="E52">
         <f>E49</f>
         <v>40</v>
       </c>
-      <c r="K52" s="7" t="s">
+      <c r="K52" s="2" t="s">
         <v>102</v>
       </c>
-      <c r="L52" s="7">
+      <c r="L52" s="2">
         <v>-637</v>
       </c>
-      <c r="M52" s="18" t="s">
+      <c r="M52" s="13" t="s">
         <v>451</v>
       </c>
       <c r="O52" t="s">
@@ -9293,12 +9513,12 @@
       </c>
     </row>
     <row r="53" spans="1:16" x14ac:dyDescent="0.25">
-      <c r="B53" s="7" t="s">
+      <c r="B53" s="2" t="s">
         <v>104</v>
       </c>
-      <c r="C53" s="2"/>
-      <c r="D53" s="2"/>
-      <c r="K53" s="7" t="s">
+      <c r="C53" s="18"/>
+      <c r="D53" s="18"/>
+      <c r="K53" s="2" t="s">
         <v>105</v>
       </c>
       <c r="O53" t="s">
@@ -9306,50 +9526,50 @@
       </c>
       <c r="P53">
         <f>-C56</f>
-        <v>-22145</v>
+        <v>-19775</v>
       </c>
     </row>
     <row r="54" spans="1:16" x14ac:dyDescent="0.25">
-      <c r="B54" s="13" t="s">
+      <c r="B54" s="8" t="s">
         <v>107</v>
       </c>
-      <c r="C54" s="2"/>
-      <c r="D54" s="2"/>
-      <c r="L54" s="14">
+      <c r="C54" s="18"/>
+      <c r="D54" s="18"/>
+      <c r="L54" s="9">
         <f>SUBTOTAL(9,L49:L53)</f>
         <v>8722</v>
       </c>
-      <c r="M54" s="14">
+      <c r="M54" s="9">
         <f>M49</f>
         <v>15</v>
       </c>
-      <c r="O54" s="9" t="s">
+      <c r="O54" s="4" t="s">
         <v>106</v>
       </c>
-      <c r="P54" s="9">
+      <c r="P54" s="4">
         <f>SUBTOTAL(9,P49:P53)</f>
         <v>162</v>
       </c>
     </row>
     <row r="56" spans="1:16" x14ac:dyDescent="0.25">
-      <c r="B56" s="6" t="s">
+      <c r="B56" s="1" t="s">
         <v>108</v>
       </c>
-      <c r="C56" s="1">
+      <c r="C56" s="19">
         <f>C52+C53+C54</f>
-        <v>22145</v>
-      </c>
-      <c r="D56" s="1"/>
-      <c r="E56" s="6" t="s">
+        <v>19775</v>
+      </c>
+      <c r="D56" s="19"/>
+      <c r="E56" s="1" t="s">
         <v>109</v>
       </c>
-      <c r="K56" s="12" t="s">
-        <v>22</v>
-      </c>
-      <c r="L56" s="12" t="s">
+      <c r="K56" s="7" t="s">
+        <v>22</v>
+      </c>
+      <c r="L56" s="7" t="s">
         <v>91</v>
       </c>
-      <c r="M56" s="12" t="s">
+      <c r="M56" s="7" t="s">
         <v>90</v>
       </c>
     </row>
@@ -9359,7 +9579,7 @@
       </c>
       <c r="L57">
         <f>SUMIFS(G$3:G$44,J$3:J$44,K$56)</f>
-        <v>9395</v>
+        <v>7025</v>
       </c>
       <c r="M57">
         <f>SUMIFS(Q$3:Q$44,J$3:J$44,K$56)</f>
@@ -9393,33 +9613,33 @@
       </c>
     </row>
     <row r="60" spans="1:16" x14ac:dyDescent="0.25">
-      <c r="K60" s="7" t="s">
+      <c r="K60" s="2" t="s">
         <v>102</v>
       </c>
     </row>
     <row r="61" spans="1:16" x14ac:dyDescent="0.25">
-      <c r="K61" s="7" t="s">
+      <c r="K61" s="2" t="s">
         <v>105</v>
       </c>
     </row>
     <row r="62" spans="1:16" x14ac:dyDescent="0.25">
-      <c r="L62" s="14">
+      <c r="L62" s="9">
         <f>SUBTOTAL(9,L57:L61)</f>
-        <v>9005</v>
-      </c>
-      <c r="M62" s="14">
+        <v>6635</v>
+      </c>
+      <c r="M62" s="9">
         <f>M57</f>
         <v>14</v>
       </c>
     </row>
     <row r="64" spans="1:16" x14ac:dyDescent="0.25">
-      <c r="K64" s="12" t="s">
+      <c r="K64" s="7" t="s">
         <v>165</v>
       </c>
-      <c r="L64" s="12" t="s">
+      <c r="L64" s="7" t="s">
         <v>91</v>
       </c>
-      <c r="M64" s="12" t="s">
+      <c r="M64" s="7" t="s">
         <v>90</v>
       </c>
     </row>
@@ -9455,39 +9675,39 @@
       </c>
     </row>
     <row r="68" spans="11:13" x14ac:dyDescent="0.25">
-      <c r="K68" s="7" t="s">
+      <c r="K68" s="2" t="s">
         <v>102</v>
       </c>
-      <c r="L68" s="7">
+      <c r="L68" s="2">
         <v>-355</v>
       </c>
-      <c r="M68" s="18" t="s">
+      <c r="M68" s="13" t="s">
         <v>451</v>
       </c>
     </row>
     <row r="69" spans="11:13" x14ac:dyDescent="0.25">
-      <c r="K69" s="7" t="s">
+      <c r="K69" s="2" t="s">
         <v>105</v>
       </c>
     </row>
     <row r="70" spans="11:13" x14ac:dyDescent="0.25">
-      <c r="L70" s="14">
+      <c r="L70" s="9">
         <f>SUBTOTAL(9,L65:L69)</f>
         <v>3910</v>
       </c>
-      <c r="M70" s="14">
+      <c r="M70" s="9">
         <f>M65</f>
         <v>9</v>
       </c>
     </row>
     <row r="72" spans="11:13" x14ac:dyDescent="0.25">
-      <c r="K72" s="12" t="s">
+      <c r="K72" s="7" t="s">
         <v>40</v>
       </c>
-      <c r="L72" s="12" t="s">
+      <c r="L72" s="7" t="s">
         <v>91</v>
       </c>
-      <c r="M72" s="12" t="s">
+      <c r="M72" s="7" t="s">
         <v>90</v>
       </c>
     </row>
@@ -9523,21 +9743,21 @@
       </c>
     </row>
     <row r="76" spans="11:13" x14ac:dyDescent="0.25">
-      <c r="K76" s="7" t="s">
+      <c r="K76" s="2" t="s">
         <v>102</v>
       </c>
     </row>
     <row r="77" spans="11:13" x14ac:dyDescent="0.25">
-      <c r="K77" s="7" t="s">
+      <c r="K77" s="2" t="s">
         <v>105</v>
       </c>
     </row>
     <row r="78" spans="11:13" x14ac:dyDescent="0.25">
-      <c r="L78" s="14">
+      <c r="L78" s="9">
         <f>SUBTOTAL(9,L73:L77)</f>
         <v>670</v>
       </c>
-      <c r="M78" s="14">
+      <c r="M78" s="9">
         <f>M73</f>
         <v>2</v>
       </c>
@@ -9584,55 +9804,55 @@
   </cols>
   <sheetData>
     <row r="2" spans="1:17" x14ac:dyDescent="0.25">
-      <c r="A2" s="10" t="s">
+      <c r="A2" s="5" t="s">
         <v>0</v>
       </c>
-      <c r="B2" s="10" t="s">
-        <v>1</v>
-      </c>
-      <c r="C2" s="10" t="s">
+      <c r="B2" s="5" t="s">
+        <v>1</v>
+      </c>
+      <c r="C2" s="5" t="s">
         <v>2</v>
       </c>
-      <c r="D2" s="10" t="s">
+      <c r="D2" s="5" t="s">
         <v>3</v>
       </c>
-      <c r="E2" s="10" t="s">
+      <c r="E2" s="5" t="s">
         <v>4</v>
       </c>
-      <c r="F2" s="10" t="s">
+      <c r="F2" s="5" t="s">
         <v>5</v>
       </c>
-      <c r="G2" s="10" t="s">
+      <c r="G2" s="5" t="s">
         <v>6</v>
       </c>
-      <c r="H2" s="10" t="s">
+      <c r="H2" s="5" t="s">
         <v>7</v>
       </c>
-      <c r="I2" s="10" t="s">
+      <c r="I2" s="5" t="s">
         <v>8</v>
       </c>
-      <c r="J2" s="10" t="s">
+      <c r="J2" s="5" t="s">
         <v>9</v>
       </c>
-      <c r="K2" s="10" t="s">
+      <c r="K2" s="5" t="s">
         <v>10</v>
       </c>
-      <c r="L2" s="10" t="s">
+      <c r="L2" s="5" t="s">
         <v>11</v>
       </c>
-      <c r="M2" s="10" t="s">
+      <c r="M2" s="5" t="s">
         <v>12</v>
       </c>
-      <c r="N2" s="10" t="s">
+      <c r="N2" s="5" t="s">
         <v>13</v>
       </c>
-      <c r="O2" s="10" t="s">
+      <c r="O2" s="5" t="s">
         <v>14</v>
       </c>
-      <c r="P2" s="10" t="s">
+      <c r="P2" s="5" t="s">
         <v>15</v>
       </c>
-      <c r="Q2" s="10" t="s">
+      <c r="Q2" s="5" t="s">
         <v>324</v>
       </c>
     </row>
@@ -9652,15 +9872,15 @@
       <c r="F3" t="s">
         <v>86</v>
       </c>
-      <c r="G3" s="11">
-        <v>2390</v>
-      </c>
-      <c r="H3" s="11">
-        <v>30</v>
-      </c>
-      <c r="I3" s="11">
+      <c r="G3" s="6">
+        <v>0</v>
+      </c>
+      <c r="H3" s="6">
+        <v>25</v>
+      </c>
+      <c r="I3" s="6">
         <f>G3-H3</f>
-        <v>2360</v>
+        <v>-25</v>
       </c>
       <c r="J3" t="s">
         <v>22</v>
@@ -9674,7 +9894,7 @@
       <c r="M3" t="s">
         <v>380</v>
       </c>
-      <c r="Q3" s="11">
+      <c r="Q3" s="6">
         <v>1</v>
       </c>
     </row>
@@ -9691,16 +9911,16 @@
       <c r="E4" t="s">
         <v>458</v>
       </c>
-      <c r="F4" s="11">
+      <c r="F4" s="6">
         <v>7</v>
       </c>
-      <c r="G4" s="11">
+      <c r="G4" s="6">
         <v>470</v>
       </c>
-      <c r="H4" s="11">
+      <c r="H4" s="6">
         <v>30</v>
       </c>
-      <c r="I4" s="11">
+      <c r="I4" s="6">
         <f>G4-H4</f>
         <v>440</v>
       </c>
@@ -9713,7 +9933,7 @@
       <c r="L4" t="s">
         <v>455</v>
       </c>
-      <c r="Q4" s="11">
+      <c r="Q4" s="6">
         <v>1</v>
       </c>
     </row>
@@ -9733,13 +9953,13 @@
       <c r="F5" t="s">
         <v>153</v>
       </c>
-      <c r="G5" s="11">
+      <c r="G5" s="6">
         <v>1710</v>
       </c>
-      <c r="H5" s="11">
+      <c r="H5" s="6">
         <v>30</v>
       </c>
-      <c r="I5" s="11">
+      <c r="I5" s="6">
         <f>G5-H5</f>
         <v>1680</v>
       </c>
@@ -9752,7 +9972,7 @@
       <c r="L5" t="s">
         <v>455</v>
       </c>
-      <c r="Q5" s="11">
+      <c r="Q5" s="6">
         <v>1</v>
       </c>
     </row>
@@ -9772,13 +9992,13 @@
       <c r="F6" t="s">
         <v>20</v>
       </c>
-      <c r="G6" s="11">
+      <c r="G6" s="6">
         <v>820</v>
       </c>
-      <c r="H6" s="11">
+      <c r="H6" s="6">
         <v>30</v>
       </c>
-      <c r="I6" s="11">
+      <c r="I6" s="6">
         <f>G6-H6</f>
         <v>790</v>
       </c>
@@ -9791,7 +10011,7 @@
       <c r="L6" t="s">
         <v>455</v>
       </c>
-      <c r="Q6" s="11">
+      <c r="Q6" s="6">
         <v>1</v>
       </c>
     </row>
@@ -9808,16 +10028,16 @@
       <c r="E7" t="s">
         <v>468</v>
       </c>
-      <c r="F7" s="11">
+      <c r="F7" s="6">
         <v>8</v>
       </c>
-      <c r="G7" s="11">
+      <c r="G7" s="6">
         <v>0</v>
       </c>
-      <c r="H7" s="11">
+      <c r="H7" s="6">
         <v>25</v>
       </c>
-      <c r="I7" s="11">
+      <c r="I7" s="6">
         <f>-H7</f>
         <v>-25</v>
       </c>
@@ -9830,7 +10050,7 @@
       <c r="L7" t="s">
         <v>455</v>
       </c>
-      <c r="Q7" s="11">
+      <c r="Q7" s="6">
         <v>1</v>
       </c>
     </row>
@@ -9847,16 +10067,16 @@
       <c r="E8" t="s">
         <v>471</v>
       </c>
-      <c r="F8" s="11">
+      <c r="F8" s="6">
         <v>6</v>
       </c>
-      <c r="G8" s="11">
+      <c r="G8" s="6">
         <v>1515</v>
       </c>
-      <c r="H8" s="11">
+      <c r="H8" s="6">
         <v>25</v>
       </c>
-      <c r="I8" s="11">
+      <c r="I8" s="6">
         <f t="shared" ref="I8:I16" si="0">G8-H8</f>
         <v>1490</v>
       </c>
@@ -9869,7 +10089,7 @@
       <c r="L8" t="s">
         <v>455</v>
       </c>
-      <c r="Q8" s="11">
+      <c r="Q8" s="6">
         <v>1</v>
       </c>
     </row>
@@ -9889,13 +10109,13 @@
       <c r="F9" t="s">
         <v>20</v>
       </c>
-      <c r="G9" s="11">
+      <c r="G9" s="6">
         <v>890</v>
       </c>
-      <c r="H9" s="11">
+      <c r="H9" s="6">
         <v>30</v>
       </c>
-      <c r="I9" s="11">
+      <c r="I9" s="6">
         <f t="shared" si="0"/>
         <v>860</v>
       </c>
@@ -9908,7 +10128,7 @@
       <c r="L9" t="s">
         <v>455</v>
       </c>
-      <c r="Q9" s="11">
+      <c r="Q9" s="6">
         <v>1</v>
       </c>
     </row>
@@ -9928,13 +10148,13 @@
       <c r="F10" t="s">
         <v>20</v>
       </c>
-      <c r="G10" s="11">
+      <c r="G10" s="6">
         <v>470</v>
       </c>
-      <c r="H10" s="11">
+      <c r="H10" s="6">
         <v>30</v>
       </c>
-      <c r="I10" s="11">
+      <c r="I10" s="6">
         <f t="shared" si="0"/>
         <v>440</v>
       </c>
@@ -9947,7 +10167,7 @@
       <c r="L10" t="s">
         <v>455</v>
       </c>
-      <c r="Q10" s="11">
+      <c r="Q10" s="6">
         <v>1</v>
       </c>
     </row>
@@ -9964,16 +10184,16 @@
       <c r="E11" t="s">
         <v>480</v>
       </c>
-      <c r="F11" s="11">
+      <c r="F11" s="6">
         <v>10</v>
       </c>
-      <c r="G11" s="11">
+      <c r="G11" s="6">
         <v>1505</v>
       </c>
-      <c r="H11" s="11">
+      <c r="H11" s="6">
         <v>25</v>
       </c>
-      <c r="I11" s="11">
+      <c r="I11" s="6">
         <f t="shared" si="0"/>
         <v>1480</v>
       </c>
@@ -9986,7 +10206,7 @@
       <c r="L11" t="s">
         <v>455</v>
       </c>
-      <c r="Q11" s="11">
+      <c r="Q11" s="6">
         <v>1</v>
       </c>
     </row>
@@ -10003,16 +10223,16 @@
       <c r="E12" t="s">
         <v>483</v>
       </c>
-      <c r="F12" s="11">
+      <c r="F12" s="6">
         <v>4</v>
       </c>
-      <c r="G12" s="11">
+      <c r="G12" s="6">
         <v>815</v>
       </c>
-      <c r="H12" s="11">
+      <c r="H12" s="6">
         <v>25</v>
       </c>
-      <c r="I12" s="11">
+      <c r="I12" s="6">
         <f t="shared" si="0"/>
         <v>790</v>
       </c>
@@ -10025,7 +10245,7 @@
       <c r="L12" t="s">
         <v>455</v>
       </c>
-      <c r="Q12" s="11">
+      <c r="Q12" s="6">
         <v>1</v>
       </c>
     </row>
@@ -10042,16 +10262,16 @@
       <c r="E13" t="s">
         <v>486</v>
       </c>
-      <c r="F13" s="11">
+      <c r="F13" s="6">
         <v>2</v>
       </c>
-      <c r="G13" s="11">
+      <c r="G13" s="6">
         <v>1510</v>
       </c>
-      <c r="H13" s="11">
+      <c r="H13" s="6">
         <v>30</v>
       </c>
-      <c r="I13" s="11">
+      <c r="I13" s="6">
         <f t="shared" si="0"/>
         <v>1480</v>
       </c>
@@ -10064,7 +10284,7 @@
       <c r="L13" t="s">
         <v>455</v>
       </c>
-      <c r="Q13" s="11">
+      <c r="Q13" s="6">
         <v>1</v>
       </c>
     </row>
@@ -10084,13 +10304,13 @@
       <c r="F14" t="s">
         <v>20</v>
       </c>
-      <c r="G14" s="11">
+      <c r="G14" s="6">
         <v>920</v>
       </c>
-      <c r="H14" s="11">
+      <c r="H14" s="6">
         <v>30</v>
       </c>
-      <c r="I14" s="11">
+      <c r="I14" s="6">
         <f t="shared" si="0"/>
         <v>890</v>
       </c>
@@ -10103,7 +10323,7 @@
       <c r="L14" t="s">
         <v>455</v>
       </c>
-      <c r="Q14" s="11">
+      <c r="Q14" s="6">
         <v>1</v>
       </c>
     </row>
@@ -10123,13 +10343,13 @@
       <c r="F15" t="s">
         <v>36</v>
       </c>
-      <c r="G15" s="11">
+      <c r="G15" s="6">
         <v>680</v>
       </c>
-      <c r="H15" s="11">
+      <c r="H15" s="6">
         <v>20</v>
       </c>
-      <c r="I15" s="11">
+      <c r="I15" s="6">
         <f t="shared" si="0"/>
         <v>660</v>
       </c>
@@ -10142,7 +10362,7 @@
       <c r="L15" t="s">
         <v>455</v>
       </c>
-      <c r="Q15" s="11">
+      <c r="Q15" s="6">
         <v>1</v>
       </c>
     </row>
@@ -10162,13 +10382,13 @@
       <c r="F16" t="s">
         <v>153</v>
       </c>
-      <c r="G16" s="11">
+      <c r="G16" s="6">
         <v>1020</v>
       </c>
-      <c r="H16" s="11">
+      <c r="H16" s="6">
         <v>30</v>
       </c>
-      <c r="I16" s="11">
+      <c r="I16" s="6">
         <f t="shared" si="0"/>
         <v>990</v>
       </c>
@@ -10181,7 +10401,7 @@
       <c r="L16" t="s">
         <v>455</v>
       </c>
-      <c r="Q16" s="11">
+      <c r="Q16" s="6">
         <v>1</v>
       </c>
     </row>
@@ -10201,13 +10421,13 @@
       <c r="F17" t="s">
         <v>153</v>
       </c>
-      <c r="G17" s="11">
+      <c r="G17" s="6">
         <v>0</v>
       </c>
-      <c r="H17" s="11">
+      <c r="H17" s="6">
         <v>30</v>
       </c>
-      <c r="I17" s="11">
+      <c r="I17" s="6">
         <f>-H17</f>
         <v>-30</v>
       </c>
@@ -10220,7 +10440,7 @@
       <c r="L17" t="s">
         <v>455</v>
       </c>
-      <c r="Q17" s="11">
+      <c r="Q17" s="6">
         <v>1</v>
       </c>
     </row>
@@ -10237,16 +10457,16 @@
       <c r="E18" t="s">
         <v>499</v>
       </c>
-      <c r="F18" s="11">
+      <c r="F18" s="6">
         <v>8</v>
       </c>
-      <c r="G18" s="11">
+      <c r="G18" s="6">
         <v>820</v>
       </c>
-      <c r="H18" s="11">
+      <c r="H18" s="6">
         <v>30</v>
       </c>
-      <c r="I18" s="11">
+      <c r="I18" s="6">
         <f t="shared" ref="I18:I24" si="1">G18-H18</f>
         <v>790</v>
       </c>
@@ -10259,7 +10479,7 @@
       <c r="L18" t="s">
         <v>455</v>
       </c>
-      <c r="Q18" s="11">
+      <c r="Q18" s="6">
         <v>1</v>
       </c>
     </row>
@@ -10279,13 +10499,13 @@
       <c r="F19" t="s">
         <v>86</v>
       </c>
-      <c r="G19" s="11">
+      <c r="G19" s="6">
         <v>845</v>
       </c>
-      <c r="H19" s="11">
+      <c r="H19" s="6">
         <v>25</v>
       </c>
-      <c r="I19" s="11">
+      <c r="I19" s="6">
         <f t="shared" si="1"/>
         <v>820</v>
       </c>
@@ -10298,7 +10518,7 @@
       <c r="L19" t="s">
         <v>455</v>
       </c>
-      <c r="Q19" s="11">
+      <c r="Q19" s="6">
         <v>1</v>
       </c>
     </row>
@@ -10315,16 +10535,16 @@
       <c r="E20" t="s">
         <v>505</v>
       </c>
-      <c r="F20" s="11">
+      <c r="F20" s="6">
         <v>6</v>
       </c>
-      <c r="G20" s="11">
+      <c r="G20" s="6">
         <v>695</v>
       </c>
-      <c r="H20" s="11">
+      <c r="H20" s="6">
         <v>25</v>
       </c>
-      <c r="I20" s="11">
+      <c r="I20" s="6">
         <f t="shared" si="1"/>
         <v>670</v>
       </c>
@@ -10337,7 +10557,7 @@
       <c r="L20" t="s">
         <v>455</v>
       </c>
-      <c r="Q20" s="11">
+      <c r="Q20" s="6">
         <v>1</v>
       </c>
     </row>
@@ -10354,16 +10574,16 @@
       <c r="E21" t="s">
         <v>508</v>
       </c>
-      <c r="F21" s="11">
+      <c r="F21" s="6">
         <v>7</v>
       </c>
-      <c r="G21" s="11">
+      <c r="G21" s="6">
         <v>700</v>
       </c>
-      <c r="H21" s="11">
+      <c r="H21" s="6">
         <v>30</v>
       </c>
-      <c r="I21" s="11">
+      <c r="I21" s="6">
         <f t="shared" si="1"/>
         <v>670</v>
       </c>
@@ -10376,7 +10596,7 @@
       <c r="L21" t="s">
         <v>455</v>
       </c>
-      <c r="Q21" s="11">
+      <c r="Q21" s="6">
         <v>1</v>
       </c>
     </row>
@@ -10393,16 +10613,16 @@
       <c r="E22" t="s">
         <v>511</v>
       </c>
-      <c r="F22" s="11">
+      <c r="F22" s="6">
         <v>4</v>
       </c>
-      <c r="G22" s="11">
+      <c r="G22" s="6">
         <v>735</v>
       </c>
-      <c r="H22" s="11">
+      <c r="H22" s="6">
         <v>25</v>
       </c>
-      <c r="I22" s="11">
+      <c r="I22" s="6">
         <f t="shared" si="1"/>
         <v>710</v>
       </c>
@@ -10415,7 +10635,7 @@
       <c r="L22" t="s">
         <v>455</v>
       </c>
-      <c r="Q22" s="11">
+      <c r="Q22" s="6">
         <v>1</v>
       </c>
     </row>
@@ -10432,16 +10652,16 @@
       <c r="E23" t="s">
         <v>514</v>
       </c>
-      <c r="F23" s="11">
+      <c r="F23" s="6">
         <v>4</v>
       </c>
-      <c r="G23" s="11">
+      <c r="G23" s="6">
         <v>75</v>
       </c>
-      <c r="H23" s="11">
+      <c r="H23" s="6">
         <v>25</v>
       </c>
-      <c r="I23" s="11">
+      <c r="I23" s="6">
         <f t="shared" si="1"/>
         <v>50</v>
       </c>
@@ -10457,7 +10677,7 @@
       <c r="M23" t="s">
         <v>66</v>
       </c>
-      <c r="Q23" s="11">
+      <c r="Q23" s="6">
         <v>1</v>
       </c>
     </row>
@@ -10474,16 +10694,16 @@
       <c r="E24" t="s">
         <v>517</v>
       </c>
-      <c r="F24" s="11">
+      <c r="F24" s="6">
         <v>4</v>
       </c>
-      <c r="G24" s="11">
+      <c r="G24" s="6">
         <v>715</v>
       </c>
-      <c r="H24" s="11">
+      <c r="H24" s="6">
         <v>25</v>
       </c>
-      <c r="I24" s="11">
+      <c r="I24" s="6">
         <f t="shared" si="1"/>
         <v>690</v>
       </c>
@@ -10496,7 +10716,7 @@
       <c r="L24" t="s">
         <v>455</v>
       </c>
-      <c r="Q24" s="11">
+      <c r="Q24" s="6">
         <v>1</v>
       </c>
     </row>
@@ -10513,16 +10733,16 @@
       <c r="E25" t="s">
         <v>520</v>
       </c>
-      <c r="F25" s="11">
+      <c r="F25" s="6">
         <v>7</v>
       </c>
-      <c r="G25" s="11">
+      <c r="G25" s="6">
         <v>0</v>
       </c>
-      <c r="H25" s="11">
+      <c r="H25" s="6">
         <v>30</v>
       </c>
-      <c r="I25" s="11">
+      <c r="I25" s="6">
         <f>-H25</f>
         <v>-30</v>
       </c>
@@ -10535,7 +10755,7 @@
       <c r="L25" t="s">
         <v>455</v>
       </c>
-      <c r="Q25" s="11">
+      <c r="Q25" s="6">
         <v>1</v>
       </c>
     </row>
@@ -10552,16 +10772,16 @@
       <c r="E26" t="s">
         <v>523</v>
       </c>
-      <c r="F26" s="11">
+      <c r="F26" s="6">
         <v>5</v>
       </c>
-      <c r="G26" s="11">
+      <c r="G26" s="6">
         <v>685</v>
       </c>
-      <c r="H26" s="11">
+      <c r="H26" s="6">
         <v>25</v>
       </c>
-      <c r="I26" s="11">
+      <c r="I26" s="6">
         <f>G26-H26</f>
         <v>660</v>
       </c>
@@ -10574,7 +10794,7 @@
       <c r="L26" t="s">
         <v>455</v>
       </c>
-      <c r="Q26" s="11">
+      <c r="Q26" s="6">
         <v>1</v>
       </c>
     </row>
@@ -10594,13 +10814,13 @@
       <c r="F27" t="s">
         <v>20</v>
       </c>
-      <c r="G27" s="11">
+      <c r="G27" s="6">
         <v>1020</v>
       </c>
-      <c r="H27" s="11">
+      <c r="H27" s="6">
         <v>30</v>
       </c>
-      <c r="I27" s="11">
+      <c r="I27" s="6">
         <f>G27-H27</f>
         <v>990</v>
       </c>
@@ -10613,7 +10833,7 @@
       <c r="L27" t="s">
         <v>455</v>
       </c>
-      <c r="Q27" s="11">
+      <c r="Q27" s="6">
         <v>1</v>
       </c>
     </row>
@@ -10630,16 +10850,16 @@
       <c r="E28" t="s">
         <v>529</v>
       </c>
-      <c r="F28" s="11">
+      <c r="F28" s="6">
         <v>5</v>
       </c>
-      <c r="G28" s="11">
+      <c r="G28" s="6">
         <v>1185</v>
       </c>
-      <c r="H28" s="11">
+      <c r="H28" s="6">
         <v>25</v>
       </c>
-      <c r="I28" s="11">
+      <c r="I28" s="6">
         <f>G28-H28</f>
         <v>1160</v>
       </c>
@@ -10652,7 +10872,7 @@
       <c r="L28" t="s">
         <v>455</v>
       </c>
-      <c r="Q28" s="11">
+      <c r="Q28" s="6">
         <v>1</v>
       </c>
     </row>
@@ -10669,16 +10889,16 @@
       <c r="E29" t="s">
         <v>532</v>
       </c>
-      <c r="F29" s="11">
-        <v>1</v>
-      </c>
-      <c r="G29" s="11">
+      <c r="F29" s="6">
+        <v>1</v>
+      </c>
+      <c r="G29" s="6">
         <v>745</v>
       </c>
-      <c r="H29" s="11">
+      <c r="H29" s="6">
         <v>25</v>
       </c>
-      <c r="I29" s="11">
+      <c r="I29" s="6">
         <f>G29-H29</f>
         <v>720</v>
       </c>
@@ -10691,7 +10911,7 @@
       <c r="L29" t="s">
         <v>455</v>
       </c>
-      <c r="Q29" s="11">
+      <c r="Q29" s="6">
         <v>1</v>
       </c>
     </row>
@@ -10708,16 +10928,16 @@
       <c r="E30" t="s">
         <v>535</v>
       </c>
-      <c r="F30" s="11">
+      <c r="F30" s="6">
         <v>10</v>
       </c>
-      <c r="G30" s="11">
+      <c r="G30" s="6">
         <v>1255</v>
       </c>
-      <c r="H30" s="11">
+      <c r="H30" s="6">
         <v>25</v>
       </c>
-      <c r="I30" s="11">
+      <c r="I30" s="6">
         <f>G30-H30</f>
         <v>1230</v>
       </c>
@@ -10730,7 +10950,7 @@
       <c r="L30" t="s">
         <v>455</v>
       </c>
-      <c r="Q30" s="11">
+      <c r="Q30" s="6">
         <v>1</v>
       </c>
     </row>
@@ -10750,13 +10970,13 @@
       <c r="F31" t="s">
         <v>86</v>
       </c>
-      <c r="G31" s="11">
+      <c r="G31" s="6">
         <v>0</v>
       </c>
-      <c r="H31" s="11">
+      <c r="H31" s="6">
         <v>25</v>
       </c>
-      <c r="I31" s="11">
+      <c r="I31" s="6">
         <f>-H31</f>
         <v>-25</v>
       </c>
@@ -10769,7 +10989,7 @@
       <c r="L31" t="s">
         <v>455</v>
       </c>
-      <c r="Q31" s="11">
+      <c r="Q31" s="6">
         <v>1</v>
       </c>
     </row>
@@ -10789,13 +11009,13 @@
       <c r="F32" t="s">
         <v>79</v>
       </c>
-      <c r="G32" s="11">
+      <c r="G32" s="6">
         <v>370</v>
       </c>
-      <c r="H32" s="11">
+      <c r="H32" s="6">
         <v>20</v>
       </c>
-      <c r="I32" s="11">
+      <c r="I32" s="6">
         <f t="shared" ref="I32:I38" si="2">G32-H32</f>
         <v>350</v>
       </c>
@@ -10808,7 +11028,7 @@
       <c r="L32" t="s">
         <v>455</v>
       </c>
-      <c r="Q32" s="11">
+      <c r="Q32" s="6">
         <v>1</v>
       </c>
     </row>
@@ -10825,16 +11045,16 @@
       <c r="E33" t="s">
         <v>541</v>
       </c>
-      <c r="F33" s="11">
-        <v>1</v>
-      </c>
-      <c r="G33" s="11">
+      <c r="F33" s="6">
+        <v>1</v>
+      </c>
+      <c r="G33" s="6">
         <v>915</v>
       </c>
-      <c r="H33" s="11">
+      <c r="H33" s="6">
         <v>25</v>
       </c>
-      <c r="I33" s="11">
+      <c r="I33" s="6">
         <f t="shared" si="2"/>
         <v>890</v>
       </c>
@@ -10847,7 +11067,7 @@
       <c r="L33" t="s">
         <v>455</v>
       </c>
-      <c r="Q33" s="11">
+      <c r="Q33" s="6">
         <v>1</v>
       </c>
     </row>
@@ -10864,16 +11084,16 @@
       <c r="E34" t="s">
         <v>544</v>
       </c>
-      <c r="F34" s="11">
-        <v>1</v>
-      </c>
-      <c r="G34" s="11">
+      <c r="F34" s="6">
+        <v>1</v>
+      </c>
+      <c r="G34" s="6">
         <v>1635</v>
       </c>
-      <c r="H34" s="11">
+      <c r="H34" s="6">
         <v>25</v>
       </c>
-      <c r="I34" s="11">
+      <c r="I34" s="6">
         <f t="shared" si="2"/>
         <v>1610</v>
       </c>
@@ -10886,7 +11106,7 @@
       <c r="L34" t="s">
         <v>455</v>
       </c>
-      <c r="Q34" s="11">
+      <c r="Q34" s="6">
         <v>1</v>
       </c>
     </row>
@@ -10906,13 +11126,13 @@
       <c r="F35" t="s">
         <v>128</v>
       </c>
-      <c r="G35" s="11">
+      <c r="G35" s="6">
         <v>475</v>
       </c>
-      <c r="H35" s="11">
+      <c r="H35" s="6">
         <v>35</v>
       </c>
-      <c r="I35" s="11">
+      <c r="I35" s="6">
         <f t="shared" si="2"/>
         <v>440</v>
       </c>
@@ -10925,7 +11145,7 @@
       <c r="L35" t="s">
         <v>455</v>
       </c>
-      <c r="Q35" s="11">
+      <c r="Q35" s="6">
         <v>1</v>
       </c>
     </row>
@@ -10942,16 +11162,16 @@
       <c r="E36" t="s">
         <v>550</v>
       </c>
-      <c r="F36" s="11">
+      <c r="F36" s="6">
         <v>2</v>
       </c>
-      <c r="G36" s="11">
+      <c r="G36" s="6">
         <v>820</v>
       </c>
-      <c r="H36" s="11">
+      <c r="H36" s="6">
         <v>30</v>
       </c>
-      <c r="I36" s="11">
+      <c r="I36" s="6">
         <f t="shared" si="2"/>
         <v>790</v>
       </c>
@@ -10964,7 +11184,7 @@
       <c r="L36" t="s">
         <v>455</v>
       </c>
-      <c r="Q36" s="11">
+      <c r="Q36" s="6">
         <v>1</v>
       </c>
     </row>
@@ -10981,16 +11201,16 @@
       <c r="E37" t="s">
         <v>553</v>
       </c>
-      <c r="F37" s="11">
+      <c r="F37" s="6">
         <v>10</v>
       </c>
-      <c r="G37" s="11">
+      <c r="G37" s="6">
         <v>465</v>
       </c>
-      <c r="H37" s="11">
+      <c r="H37" s="6">
         <v>25</v>
       </c>
-      <c r="I37" s="11">
+      <c r="I37" s="6">
         <f t="shared" si="2"/>
         <v>440</v>
       </c>
@@ -11003,7 +11223,7 @@
       <c r="L37" t="s">
         <v>455</v>
       </c>
-      <c r="Q37" s="11">
+      <c r="Q37" s="6">
         <v>1</v>
       </c>
     </row>
@@ -11020,16 +11240,16 @@
       <c r="E38" t="s">
         <v>556</v>
       </c>
-      <c r="F38" s="11">
+      <c r="F38" s="6">
         <v>6</v>
       </c>
-      <c r="G38" s="11">
+      <c r="G38" s="6">
         <v>2220</v>
       </c>
-      <c r="H38" s="11">
+      <c r="H38" s="6">
         <v>30</v>
       </c>
-      <c r="I38" s="11">
+      <c r="I38" s="6">
         <f t="shared" si="2"/>
         <v>2190</v>
       </c>
@@ -11045,7 +11265,7 @@
       <c r="M38" t="s">
         <v>380</v>
       </c>
-      <c r="Q38" s="11">
+      <c r="Q38" s="6">
         <v>1</v>
       </c>
     </row>
@@ -11065,13 +11285,13 @@
       <c r="F39" t="s">
         <v>86</v>
       </c>
-      <c r="G39" s="11">
+      <c r="G39" s="6">
         <v>0</v>
       </c>
-      <c r="H39" s="11">
+      <c r="H39" s="6">
         <v>25</v>
       </c>
-      <c r="I39" s="11">
+      <c r="I39" s="6">
         <f>-H39</f>
         <v>-25</v>
       </c>
@@ -11084,7 +11304,7 @@
       <c r="L39" t="s">
         <v>455</v>
       </c>
-      <c r="Q39" s="11">
+      <c r="Q39" s="6">
         <v>1</v>
       </c>
     </row>
@@ -11101,16 +11321,16 @@
       <c r="E40" t="s">
         <v>562</v>
       </c>
-      <c r="F40" s="11">
+      <c r="F40" s="6">
         <v>4</v>
       </c>
-      <c r="G40" s="11">
+      <c r="G40" s="6">
         <v>0</v>
       </c>
-      <c r="H40" s="11">
+      <c r="H40" s="6">
         <v>25</v>
       </c>
-      <c r="I40" s="11">
+      <c r="I40" s="6">
         <f>-H40</f>
         <v>-25</v>
       </c>
@@ -11123,7 +11343,7 @@
       <c r="L40" t="s">
         <v>455</v>
       </c>
-      <c r="Q40" s="11">
+      <c r="Q40" s="6">
         <v>1</v>
       </c>
     </row>
@@ -11143,13 +11363,13 @@
       <c r="F41" t="s">
         <v>20</v>
       </c>
-      <c r="G41" s="11">
+      <c r="G41" s="6">
         <v>720</v>
       </c>
-      <c r="H41" s="11">
+      <c r="H41" s="6">
         <v>30</v>
       </c>
-      <c r="I41" s="11">
+      <c r="I41" s="6">
         <f t="shared" ref="I41:I49" si="3">G41-H41</f>
         <v>690</v>
       </c>
@@ -11162,7 +11382,7 @@
       <c r="L41" t="s">
         <v>455</v>
       </c>
-      <c r="Q41" s="11">
+      <c r="Q41" s="6">
         <v>1</v>
       </c>
     </row>
@@ -11182,13 +11402,13 @@
       <c r="F42" t="s">
         <v>20</v>
       </c>
-      <c r="G42" s="11">
+      <c r="G42" s="6">
         <v>750</v>
       </c>
-      <c r="H42" s="11">
+      <c r="H42" s="6">
         <v>30</v>
       </c>
-      <c r="I42" s="11">
+      <c r="I42" s="6">
         <f t="shared" si="3"/>
         <v>720</v>
       </c>
@@ -11201,7 +11421,7 @@
       <c r="L42" t="s">
         <v>455</v>
       </c>
-      <c r="Q42" s="11">
+      <c r="Q42" s="6">
         <v>1</v>
       </c>
     </row>
@@ -11218,16 +11438,16 @@
       <c r="E43" t="s">
         <v>570</v>
       </c>
-      <c r="F43" s="11">
+      <c r="F43" s="6">
         <v>8</v>
       </c>
-      <c r="G43" s="11">
+      <c r="G43" s="6">
         <v>390</v>
       </c>
-      <c r="H43" s="11">
+      <c r="H43" s="6">
         <v>30</v>
       </c>
-      <c r="I43" s="11">
+      <c r="I43" s="6">
         <f t="shared" si="3"/>
         <v>360</v>
       </c>
@@ -11240,7 +11460,7 @@
       <c r="L43" t="s">
         <v>455</v>
       </c>
-      <c r="Q43" s="11">
+      <c r="Q43" s="6">
         <v>1</v>
       </c>
     </row>
@@ -11257,16 +11477,16 @@
       <c r="E44" t="s">
         <v>573</v>
       </c>
-      <c r="F44" s="11">
+      <c r="F44" s="6">
         <v>2</v>
       </c>
-      <c r="G44" s="11">
+      <c r="G44" s="6">
         <v>1020</v>
       </c>
-      <c r="H44" s="11">
+      <c r="H44" s="6">
         <v>30</v>
       </c>
-      <c r="I44" s="11">
+      <c r="I44" s="6">
         <f t="shared" si="3"/>
         <v>990</v>
       </c>
@@ -11279,7 +11499,7 @@
       <c r="L44" t="s">
         <v>455</v>
       </c>
-      <c r="Q44" s="11">
+      <c r="Q44" s="6">
         <v>1</v>
       </c>
     </row>
@@ -11296,16 +11516,16 @@
       <c r="E45" t="s">
         <v>575</v>
       </c>
-      <c r="F45" s="11">
+      <c r="F45" s="6">
         <v>2</v>
       </c>
-      <c r="G45" s="11">
+      <c r="G45" s="6">
         <v>380</v>
       </c>
-      <c r="H45" s="11">
+      <c r="H45" s="6">
         <v>30</v>
       </c>
-      <c r="I45" s="11">
+      <c r="I45" s="6">
         <f t="shared" si="3"/>
         <v>350</v>
       </c>
@@ -11318,7 +11538,7 @@
       <c r="L45" t="s">
         <v>455</v>
       </c>
-      <c r="Q45" s="11">
+      <c r="Q45" s="6">
         <v>1</v>
       </c>
     </row>
@@ -11335,16 +11555,16 @@
       <c r="E46" t="s">
         <v>578</v>
       </c>
-      <c r="F46" s="11">
+      <c r="F46" s="6">
         <v>12</v>
       </c>
-      <c r="G46" s="11">
+      <c r="G46" s="6">
         <v>1020</v>
       </c>
-      <c r="H46" s="11">
+      <c r="H46" s="6">
         <v>30</v>
       </c>
-      <c r="I46" s="11">
+      <c r="I46" s="6">
         <f t="shared" si="3"/>
         <v>990</v>
       </c>
@@ -11357,7 +11577,7 @@
       <c r="L46" t="s">
         <v>455</v>
       </c>
-      <c r="Q46" s="11">
+      <c r="Q46" s="6">
         <v>1</v>
       </c>
     </row>
@@ -11377,13 +11597,13 @@
       <c r="F47" t="s">
         <v>20</v>
       </c>
-      <c r="G47" s="11">
+      <c r="G47" s="6">
         <v>820</v>
       </c>
-      <c r="H47" s="11">
+      <c r="H47" s="6">
         <v>30</v>
       </c>
-      <c r="I47" s="11">
+      <c r="I47" s="6">
         <f t="shared" si="3"/>
         <v>790</v>
       </c>
@@ -11396,7 +11616,7 @@
       <c r="L47" t="s">
         <v>455</v>
       </c>
-      <c r="Q47" s="11">
+      <c r="Q47" s="6">
         <v>1</v>
       </c>
     </row>
@@ -11416,13 +11636,13 @@
       <c r="F48" t="s">
         <v>44</v>
       </c>
-      <c r="G48" s="11">
+      <c r="G48" s="6">
         <v>30</v>
       </c>
-      <c r="H48" s="11">
+      <c r="H48" s="6">
         <v>30</v>
       </c>
-      <c r="I48" s="11">
+      <c r="I48" s="6">
         <f t="shared" si="3"/>
         <v>0</v>
       </c>
@@ -11435,7 +11655,7 @@
       <c r="L48" t="s">
         <v>455</v>
       </c>
-      <c r="Q48" s="11">
+      <c r="Q48" s="6">
         <v>1</v>
       </c>
     </row>
@@ -11452,16 +11672,16 @@
       <c r="E49" t="s">
         <v>585</v>
       </c>
-      <c r="F49" s="11">
+      <c r="F49" s="6">
         <v>4</v>
       </c>
-      <c r="G49" s="11">
+      <c r="G49" s="6">
         <v>30</v>
       </c>
-      <c r="H49" s="11">
+      <c r="H49" s="6">
         <v>30</v>
       </c>
-      <c r="I49" s="11">
+      <c r="I49" s="6">
         <f t="shared" si="3"/>
         <v>0</v>
       </c>
@@ -11474,7 +11694,7 @@
       <c r="L49" t="s">
         <v>455</v>
       </c>
-      <c r="Q49" s="11">
+      <c r="Q49" s="6">
         <v>1</v>
       </c>
     </row>
@@ -11491,16 +11711,16 @@
       <c r="E50" t="s">
         <v>587</v>
       </c>
-      <c r="F50" s="11">
+      <c r="F50" s="6">
         <v>12</v>
       </c>
-      <c r="G50" s="11">
+      <c r="G50" s="6">
         <v>0</v>
       </c>
-      <c r="H50" s="11">
+      <c r="H50" s="6">
         <v>35</v>
       </c>
-      <c r="I50" s="11">
+      <c r="I50" s="6">
         <f>-H50</f>
         <v>-35</v>
       </c>
@@ -11513,7 +11733,7 @@
       <c r="L50" t="s">
         <v>455</v>
       </c>
-      <c r="Q50" s="11">
+      <c r="Q50" s="6">
         <v>1</v>
       </c>
     </row>
@@ -11533,13 +11753,13 @@
       <c r="F51" t="s">
         <v>217</v>
       </c>
-      <c r="G51" s="11">
+      <c r="G51" s="6">
         <v>30</v>
       </c>
-      <c r="H51" s="11">
+      <c r="H51" s="6">
         <v>30</v>
       </c>
-      <c r="I51" s="11">
+      <c r="I51" s="6">
         <f>G51-H51</f>
         <v>0</v>
       </c>
@@ -11552,7 +11772,7 @@
       <c r="L51" t="s">
         <v>455</v>
       </c>
-      <c r="Q51" s="11">
+      <c r="Q51" s="6">
         <v>1</v>
       </c>
     </row>
@@ -11569,16 +11789,16 @@
       <c r="E52" t="s">
         <v>590</v>
       </c>
-      <c r="F52" s="11">
+      <c r="F52" s="6">
         <v>6</v>
       </c>
-      <c r="G52" s="11">
+      <c r="G52" s="6">
         <v>30</v>
       </c>
-      <c r="H52" s="11">
+      <c r="H52" s="6">
         <v>30</v>
       </c>
-      <c r="I52" s="11">
+      <c r="I52" s="6">
         <f>G52-H52</f>
         <v>0</v>
       </c>
@@ -11591,7 +11811,7 @@
       <c r="L52" t="s">
         <v>455</v>
       </c>
-      <c r="Q52" s="11">
+      <c r="Q52" s="6">
         <v>1</v>
       </c>
     </row>
@@ -11611,13 +11831,13 @@
       <c r="F53" t="s">
         <v>44</v>
       </c>
-      <c r="G53" s="11">
+      <c r="G53" s="6">
         <v>30</v>
       </c>
-      <c r="H53" s="11">
+      <c r="H53" s="6">
         <v>30</v>
       </c>
-      <c r="I53" s="11">
+      <c r="I53" s="6">
         <f>G53-H53</f>
         <v>0</v>
       </c>
@@ -11630,7 +11850,7 @@
       <c r="L53" t="s">
         <v>455</v>
       </c>
-      <c r="Q53" s="11">
+      <c r="Q53" s="6">
         <v>1</v>
       </c>
     </row>
@@ -11650,13 +11870,13 @@
       <c r="F54" t="s">
         <v>153</v>
       </c>
-      <c r="G54" s="11">
+      <c r="G54" s="6">
         <v>1015</v>
       </c>
-      <c r="H54" s="11">
+      <c r="H54" s="6">
         <v>35</v>
       </c>
-      <c r="I54" s="11">
+      <c r="I54" s="6">
         <f>G54-H54</f>
         <v>980</v>
       </c>
@@ -11669,108 +11889,108 @@
       <c r="L54" t="s">
         <v>455</v>
       </c>
-      <c r="Q54" s="11">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="55" spans="1:17" s="7" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="B55" s="7" t="s">
-        <v>16</v>
-      </c>
-      <c r="C55" s="7" t="s">
+      <c r="Q54" s="6">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="55" spans="1:17" s="2" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="B55" s="2" t="s">
+        <v>16</v>
+      </c>
+      <c r="C55" s="2" t="s">
         <v>362</v>
       </c>
-      <c r="D55" s="7" t="s">
+      <c r="D55" s="2" t="s">
         <v>363</v>
       </c>
-      <c r="E55" s="7" t="s">
+      <c r="E55" s="2" t="s">
         <v>364</v>
       </c>
-      <c r="F55" s="17">
-        <v>1</v>
-      </c>
-      <c r="G55" s="17">
+      <c r="F55" s="12">
+        <v>1</v>
+      </c>
+      <c r="G55" s="12">
         <v>885</v>
       </c>
-      <c r="H55" s="17">
+      <c r="H55" s="12">
         <v>25</v>
       </c>
-      <c r="I55" s="17">
+      <c r="I55" s="12">
         <f>G55-H55</f>
         <v>860</v>
       </c>
-      <c r="J55" s="7" t="s">
+      <c r="J55" s="2" t="s">
         <v>446</v>
       </c>
-      <c r="K55" s="7" t="s">
-        <v>22</v>
-      </c>
-      <c r="L55" s="7" t="s">
+      <c r="K55" s="2" t="s">
+        <v>22</v>
+      </c>
+      <c r="L55" s="2" t="s">
         <v>328</v>
       </c>
-      <c r="M55" s="7" t="s">
+      <c r="M55" s="2" t="s">
         <v>102</v>
       </c>
-      <c r="N55" s="7" t="s">
+      <c r="N55" s="2" t="s">
         <v>448</v>
       </c>
-      <c r="O55" s="7" t="s">
+      <c r="O55" s="2" t="s">
         <v>448</v>
       </c>
-      <c r="P55" s="7" t="s">
+      <c r="P55" s="2" t="s">
         <v>449</v>
       </c>
-      <c r="Q55" s="17">
+      <c r="Q55" s="12">
         <v>1</v>
       </c>
     </row>
     <row r="57" spans="1:17" x14ac:dyDescent="0.25">
-      <c r="D57" s="6">
+      <c r="D57" s="1">
         <f>COUNTA(D3:D55)</f>
         <v>46</v>
       </c>
-      <c r="G57" s="6">
-        <f>SUBTOTAL(9,G3:G55)</f>
-        <v>38240</v>
-      </c>
-      <c r="H57" s="6">
-        <f>SUBTOTAL(9,H3:H55)</f>
-        <v>1485</v>
-      </c>
-      <c r="I57" s="6">
-        <f>SUBTOTAL(9,I3:I55)</f>
-        <v>36755</v>
-      </c>
-      <c r="J57" s="6">
-        <f>SUBTOTAL(9,J3:J55)</f>
+      <c r="G57" s="1">
+        <f t="shared" ref="G57:Q57" si="4">SUBTOTAL(9,G3:G55)</f>
+        <v>35850</v>
+      </c>
+      <c r="H57" s="1">
+        <f t="shared" si="4"/>
+        <v>1480</v>
+      </c>
+      <c r="I57" s="1">
+        <f t="shared" si="4"/>
+        <v>34370</v>
+      </c>
+      <c r="J57" s="1">
+        <f t="shared" si="4"/>
         <v>0</v>
       </c>
-      <c r="K57" s="6">
-        <f>SUBTOTAL(9,K3:K55)</f>
+      <c r="K57" s="1">
+        <f t="shared" si="4"/>
         <v>0</v>
       </c>
-      <c r="L57" s="6">
-        <f>SUBTOTAL(9,L3:L55)</f>
+      <c r="L57" s="1">
+        <f t="shared" si="4"/>
         <v>0</v>
       </c>
-      <c r="M57" s="6">
-        <f>SUBTOTAL(9,M3:M55)</f>
+      <c r="M57" s="1">
+        <f t="shared" si="4"/>
         <v>0</v>
       </c>
-      <c r="N57" s="6">
-        <f>SUBTOTAL(9,N3:N55)</f>
+      <c r="N57" s="1">
+        <f t="shared" si="4"/>
         <v>0</v>
       </c>
-      <c r="O57" s="6">
-        <f>SUBTOTAL(9,O3:O55)</f>
+      <c r="O57" s="1">
+        <f t="shared" si="4"/>
         <v>0</v>
       </c>
-      <c r="P57" s="6">
-        <f>SUBTOTAL(9,P3:P55)</f>
+      <c r="P57" s="1">
+        <f t="shared" si="4"/>
         <v>0</v>
       </c>
-      <c r="Q57" s="6">
-        <f>SUBTOTAL(9,Q3:Q55)</f>
+      <c r="Q57" s="1">
+        <f t="shared" si="4"/>
         <v>53</v>
       </c>
     </row>
@@ -11781,30 +12001,30 @@
       </c>
     </row>
     <row r="59" spans="1:17" x14ac:dyDescent="0.25">
-      <c r="A59" s="6" t="s">
-        <v>16</v>
-      </c>
-      <c r="C59" s="5" t="s">
+      <c r="A59" s="1" t="s">
+        <v>16</v>
+      </c>
+      <c r="C59" s="20" t="s">
         <v>89</v>
       </c>
-      <c r="D59" s="5"/>
-      <c r="E59" s="9" t="s">
+      <c r="D59" s="20"/>
+      <c r="E59" s="4" t="s">
         <v>90</v>
       </c>
       <c r="H59">
         <f>-8*25</f>
         <v>-200</v>
       </c>
-      <c r="K59" s="12" t="s">
-        <v>22</v>
-      </c>
-      <c r="L59" s="12" t="s">
+      <c r="K59" s="7" t="s">
+        <v>22</v>
+      </c>
+      <c r="L59" s="7" t="s">
         <v>91</v>
       </c>
-      <c r="M59" s="12" t="s">
+      <c r="M59" s="7" t="s">
         <v>90</v>
       </c>
-      <c r="O59" s="9" t="s">
+      <c r="O59" s="4" t="s">
         <v>92</v>
       </c>
     </row>
@@ -11812,15 +12032,15 @@
       <c r="A60" t="s">
         <v>455</v>
       </c>
-      <c r="B60" s="8" t="s">
+      <c r="B60" s="3" t="s">
         <v>93</v>
       </c>
-      <c r="C60" s="4">
+      <c r="C60" s="21">
         <f>SUMIFS(I$3:I$55,B$3:B$55,A$59,L$3:L$55,A$60)</f>
-        <v>35895</v>
-      </c>
-      <c r="D60" s="4"/>
-      <c r="E60" s="8">
+        <v>33510</v>
+      </c>
+      <c r="D60" s="21"/>
+      <c r="E60" s="3">
         <f>SUMIFS(Q$3:Q$55,B$3:B$55,A$59,L$3:L$55,A$60)</f>
         <v>52</v>
       </c>
@@ -11836,7 +12056,7 @@
       </c>
       <c r="L60">
         <f>SUMIFS(G$3:G$55,J$3:J$55,K$59)</f>
-        <v>11625</v>
+        <v>9235</v>
       </c>
       <c r="M60">
         <f>SUMIFS(Q$3:Q$55,J$3:J$55,K$59)</f>
@@ -11847,23 +12067,23 @@
       </c>
       <c r="P60">
         <f>L65</f>
-        <v>11131</v>
+        <v>8746</v>
       </c>
     </row>
     <row r="61" spans="1:17" x14ac:dyDescent="0.25">
-      <c r="B61" s="7" t="s">
+      <c r="B61" s="2" t="s">
         <v>97</v>
       </c>
-      <c r="C61" s="3">
+      <c r="C61" s="22">
         <v>0</v>
       </c>
-      <c r="D61" s="3"/>
+      <c r="D61" s="22"/>
       <c r="K61" t="s">
         <v>98</v>
       </c>
       <c r="L61">
         <f>-SUMIFS(H$3:H$55,J$3:J$55,K$59)+M61*5</f>
-        <v>-390</v>
+        <v>-385</v>
       </c>
       <c r="M61">
         <f>SUMIFS(Q$3:Q$55,J$3:J$55,K$59)-COUNTIFS(J$3:J$55,K$59,M$3:M$55,"*gộp*")</f>
@@ -11878,15 +12098,15 @@
       </c>
     </row>
     <row r="62" spans="1:17" x14ac:dyDescent="0.25">
-      <c r="B62" s="7" t="s">
+      <c r="B62" s="2" t="s">
         <v>99</v>
       </c>
-      <c r="C62" s="3">
+      <c r="C62" s="22">
         <f>-SUMIFS(I$3:I$55,B$3:B$55,A$59,P$3:P$55,"xx",N$3:N$55,"x")</f>
         <v>-860</v>
       </c>
-      <c r="D62" s="3"/>
-      <c r="E62" s="7">
+      <c r="D62" s="22"/>
+      <c r="E62" s="2">
         <f>SUMIFS(Q$3:Q$55,B$3:B$55,A$59,P$3:P$55,"xx",N$3:N$55,"x")</f>
         <v>1</v>
       </c>
@@ -11910,19 +12130,19 @@
       </c>
     </row>
     <row r="63" spans="1:17" x14ac:dyDescent="0.25">
-      <c r="B63" s="9" t="s">
+      <c r="B63" s="4" t="s">
         <v>101</v>
       </c>
-      <c r="C63" s="5">
+      <c r="C63" s="20">
         <f>SUBTOTAL(9,C60:C62)</f>
-        <v>35035</v>
-      </c>
-      <c r="D63" s="5"/>
+        <v>32650</v>
+      </c>
+      <c r="D63" s="20"/>
       <c r="E63">
         <f>E60</f>
         <v>52</v>
       </c>
-      <c r="K63" s="7" t="s">
+      <c r="K63" s="2" t="s">
         <v>102</v>
       </c>
       <c r="O63" t="s">
@@ -11930,60 +12150,60 @@
       </c>
       <c r="P63">
         <f>-C67</f>
-        <v>-35035</v>
+        <v>-32650</v>
       </c>
     </row>
     <row r="64" spans="1:17" x14ac:dyDescent="0.25">
-      <c r="B64" s="7" t="s">
+      <c r="B64" s="2" t="s">
         <v>104</v>
       </c>
-      <c r="C64" s="2"/>
-      <c r="D64" s="2"/>
-      <c r="K64" s="7" t="s">
+      <c r="C64" s="18"/>
+      <c r="D64" s="18"/>
+      <c r="K64" s="2" t="s">
         <v>105</v>
       </c>
-      <c r="O64" s="9" t="s">
+      <c r="O64" s="4" t="s">
         <v>106</v>
       </c>
-      <c r="P64" s="9">
+      <c r="P64" s="4">
         <f>SUBTOTAL(9,P60:P63)</f>
         <v>216</v>
       </c>
     </row>
     <row r="65" spans="2:13" x14ac:dyDescent="0.25">
-      <c r="B65" s="13" t="s">
+      <c r="B65" s="8" t="s">
         <v>107</v>
       </c>
-      <c r="C65" s="2"/>
-      <c r="D65" s="2"/>
-      <c r="L65" s="14">
+      <c r="C65" s="18"/>
+      <c r="D65" s="18"/>
+      <c r="L65" s="9">
         <f>SUBTOTAL(9,L60:L64)</f>
-        <v>11131</v>
-      </c>
-      <c r="M65" s="14">
+        <v>8746</v>
+      </c>
+      <c r="M65" s="9">
         <f>M60</f>
         <v>16</v>
       </c>
     </row>
     <row r="67" spans="2:13" x14ac:dyDescent="0.25">
-      <c r="B67" s="6" t="s">
+      <c r="B67" s="1" t="s">
         <v>108</v>
       </c>
-      <c r="C67" s="1">
+      <c r="C67" s="19">
         <f>C63+C64+C65</f>
-        <v>35035</v>
-      </c>
-      <c r="D67" s="1"/>
-      <c r="E67" s="6" t="s">
+        <v>32650</v>
+      </c>
+      <c r="D67" s="19"/>
+      <c r="E67" s="1" t="s">
         <v>109</v>
       </c>
-      <c r="K67" s="12" t="s">
+      <c r="K67" s="7" t="s">
         <v>459</v>
       </c>
-      <c r="L67" s="12" t="s">
+      <c r="L67" s="7" t="s">
         <v>91</v>
       </c>
-      <c r="M67" s="12" t="s">
+      <c r="M67" s="7" t="s">
         <v>90</v>
       </c>
     </row>
@@ -12019,33 +12239,33 @@
       </c>
     </row>
     <row r="71" spans="2:13" x14ac:dyDescent="0.25">
-      <c r="K71" s="7" t="s">
+      <c r="K71" s="2" t="s">
         <v>102</v>
       </c>
     </row>
     <row r="72" spans="2:13" x14ac:dyDescent="0.25">
-      <c r="K72" s="7" t="s">
+      <c r="K72" s="2" t="s">
         <v>105</v>
       </c>
     </row>
     <row r="73" spans="2:13" x14ac:dyDescent="0.25">
-      <c r="L73" s="14">
+      <c r="L73" s="9">
         <f>SUBTOTAL(9,L68:L72)</f>
         <v>12535</v>
       </c>
-      <c r="M73" s="14">
+      <c r="M73" s="9">
         <f>M68</f>
         <v>19</v>
       </c>
     </row>
     <row r="75" spans="2:13" x14ac:dyDescent="0.25">
-      <c r="K75" s="12" t="s">
+      <c r="K75" s="7" t="s">
         <v>165</v>
       </c>
-      <c r="L75" s="12" t="s">
+      <c r="L75" s="7" t="s">
         <v>91</v>
       </c>
-      <c r="M75" s="12" t="s">
+      <c r="M75" s="7" t="s">
         <v>90</v>
       </c>
     </row>
@@ -12081,27 +12301,27 @@
       </c>
     </row>
     <row r="79" spans="2:13" x14ac:dyDescent="0.25">
-      <c r="K79" s="7" t="s">
+      <c r="K79" s="2" t="s">
         <v>102</v>
       </c>
-      <c r="L79" s="7">
+      <c r="L79" s="2">
         <v>-865</v>
       </c>
-      <c r="M79" t="s">
+      <c r="M79" s="13" t="s">
         <v>451</v>
       </c>
     </row>
     <row r="80" spans="2:13" x14ac:dyDescent="0.25">
-      <c r="K80" s="7" t="s">
+      <c r="K80" s="2" t="s">
         <v>105</v>
       </c>
     </row>
     <row r="81" spans="12:13" x14ac:dyDescent="0.25">
-      <c r="L81" s="14">
+      <c r="L81" s="9">
         <f>SUBTOTAL(9,L76:L80)</f>
         <v>11585</v>
       </c>
-      <c r="M81" s="14">
+      <c r="M81" s="9">
         <f>M76</f>
         <v>17</v>
       </c>
@@ -12120,4 +12340,1556 @@
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="0.75" bottom="0.5" header="0.5" footer="0.75"/>
 </worksheet>
+</file>
+
+<file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0500-000000000000}">
+  <dimension ref="A2:Q55"/>
+  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <cols>
+    <col min="1" max="1" width="12.7109375" customWidth="1"/>
+    <col min="2" max="2" width="17.7109375" customWidth="1"/>
+    <col min="3" max="3" width="30" customWidth="1"/>
+    <col min="4" max="4" width="9.85546875" customWidth="1"/>
+    <col min="5" max="5" width="58.85546875" customWidth="1"/>
+    <col min="6" max="6" width="10.7109375" customWidth="1"/>
+    <col min="7" max="7" width="9.140625" customWidth="1"/>
+    <col min="8" max="8" width="9.5703125" customWidth="1"/>
+    <col min="9" max="9" width="10.5703125" customWidth="1"/>
+    <col min="10" max="10" width="9.7109375" customWidth="1"/>
+    <col min="11" max="11" width="10.85546875" customWidth="1"/>
+    <col min="12" max="12" width="10.42578125" customWidth="1"/>
+    <col min="13" max="13" width="13.85546875" customWidth="1"/>
+    <col min="14" max="14" width="9.7109375" customWidth="1"/>
+    <col min="15" max="15" width="10.42578125" customWidth="1"/>
+    <col min="16" max="16" width="7" bestFit="1" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="2" spans="1:17" x14ac:dyDescent="0.25">
+      <c r="A2" s="5" t="s">
+        <v>0</v>
+      </c>
+      <c r="B2" s="5" t="s">
+        <v>1</v>
+      </c>
+      <c r="C2" s="5" t="s">
+        <v>2</v>
+      </c>
+      <c r="D2" s="5" t="s">
+        <v>3</v>
+      </c>
+      <c r="E2" s="5" t="s">
+        <v>4</v>
+      </c>
+      <c r="F2" s="5" t="s">
+        <v>5</v>
+      </c>
+      <c r="G2" s="5" t="s">
+        <v>6</v>
+      </c>
+      <c r="H2" s="5" t="s">
+        <v>7</v>
+      </c>
+      <c r="I2" s="5" t="s">
+        <v>8</v>
+      </c>
+      <c r="J2" s="5" t="s">
+        <v>9</v>
+      </c>
+      <c r="K2" s="5" t="s">
+        <v>10</v>
+      </c>
+      <c r="L2" s="5" t="s">
+        <v>11</v>
+      </c>
+      <c r="M2" s="5" t="s">
+        <v>12</v>
+      </c>
+      <c r="N2" s="5" t="s">
+        <v>13</v>
+      </c>
+      <c r="O2" s="5" t="s">
+        <v>14</v>
+      </c>
+      <c r="P2" s="5" t="s">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="3" spans="1:17" x14ac:dyDescent="0.25">
+      <c r="B3" t="s">
+        <v>16</v>
+      </c>
+      <c r="C3" t="s">
+        <v>613</v>
+      </c>
+      <c r="D3" t="s">
+        <v>614</v>
+      </c>
+      <c r="E3" t="s">
+        <v>615</v>
+      </c>
+      <c r="F3" t="s">
+        <v>217</v>
+      </c>
+      <c r="G3" s="6">
+        <v>1035</v>
+      </c>
+      <c r="H3" s="6">
+        <v>25</v>
+      </c>
+      <c r="I3" s="6">
+        <f t="shared" ref="I3:I15" si="0">G3-H3</f>
+        <v>1010</v>
+      </c>
+      <c r="J3" t="s">
+        <v>616</v>
+      </c>
+      <c r="K3" t="s">
+        <v>22</v>
+      </c>
+      <c r="L3" t="s">
+        <v>597</v>
+      </c>
+      <c r="Q3">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="4" spans="1:17" x14ac:dyDescent="0.25">
+      <c r="B4" t="s">
+        <v>16</v>
+      </c>
+      <c r="C4" t="s">
+        <v>617</v>
+      </c>
+      <c r="D4" t="s">
+        <v>618</v>
+      </c>
+      <c r="E4" t="s">
+        <v>619</v>
+      </c>
+      <c r="F4" t="s">
+        <v>20</v>
+      </c>
+      <c r="G4" s="6">
+        <v>820</v>
+      </c>
+      <c r="H4" s="6">
+        <v>30</v>
+      </c>
+      <c r="I4" s="6">
+        <f t="shared" si="0"/>
+        <v>790</v>
+      </c>
+      <c r="J4" t="s">
+        <v>616</v>
+      </c>
+      <c r="K4" t="s">
+        <v>22</v>
+      </c>
+      <c r="L4" t="s">
+        <v>597</v>
+      </c>
+      <c r="Q4">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="5" spans="1:17" x14ac:dyDescent="0.25">
+      <c r="B5" t="s">
+        <v>16</v>
+      </c>
+      <c r="C5" t="s">
+        <v>620</v>
+      </c>
+      <c r="D5" t="s">
+        <v>621</v>
+      </c>
+      <c r="E5" t="s">
+        <v>622</v>
+      </c>
+      <c r="F5" s="6">
+        <v>7</v>
+      </c>
+      <c r="G5" s="6">
+        <v>780</v>
+      </c>
+      <c r="H5" s="6">
+        <v>30</v>
+      </c>
+      <c r="I5" s="6">
+        <f t="shared" si="0"/>
+        <v>750</v>
+      </c>
+      <c r="J5" t="s">
+        <v>616</v>
+      </c>
+      <c r="K5" t="s">
+        <v>22</v>
+      </c>
+      <c r="L5" t="s">
+        <v>597</v>
+      </c>
+      <c r="Q5">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="6" spans="1:17" x14ac:dyDescent="0.25">
+      <c r="B6" t="s">
+        <v>16</v>
+      </c>
+      <c r="C6" t="s">
+        <v>623</v>
+      </c>
+      <c r="D6" t="s">
+        <v>624</v>
+      </c>
+      <c r="E6" t="s">
+        <v>625</v>
+      </c>
+      <c r="F6" t="s">
+        <v>20</v>
+      </c>
+      <c r="G6" s="6">
+        <v>2500</v>
+      </c>
+      <c r="H6" s="6">
+        <v>35</v>
+      </c>
+      <c r="I6" s="6">
+        <f t="shared" si="0"/>
+        <v>2465</v>
+      </c>
+      <c r="J6" t="s">
+        <v>616</v>
+      </c>
+      <c r="K6" t="s">
+        <v>22</v>
+      </c>
+      <c r="L6" t="s">
+        <v>597</v>
+      </c>
+      <c r="M6" t="s">
+        <v>380</v>
+      </c>
+      <c r="Q6">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="7" spans="1:17" x14ac:dyDescent="0.25">
+      <c r="B7" t="s">
+        <v>16</v>
+      </c>
+      <c r="C7" t="s">
+        <v>629</v>
+      </c>
+      <c r="D7" t="s">
+        <v>630</v>
+      </c>
+      <c r="E7" t="s">
+        <v>631</v>
+      </c>
+      <c r="F7" s="6">
+        <v>6</v>
+      </c>
+      <c r="G7" s="6">
+        <v>845</v>
+      </c>
+      <c r="H7" s="6">
+        <v>25</v>
+      </c>
+      <c r="I7" s="6">
+        <f t="shared" si="0"/>
+        <v>820</v>
+      </c>
+      <c r="J7" t="s">
+        <v>616</v>
+      </c>
+      <c r="K7" t="s">
+        <v>22</v>
+      </c>
+      <c r="L7" t="s">
+        <v>597</v>
+      </c>
+      <c r="Q7">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="8" spans="1:17" x14ac:dyDescent="0.25">
+      <c r="B8" t="s">
+        <v>16</v>
+      </c>
+      <c r="C8" t="s">
+        <v>638</v>
+      </c>
+      <c r="D8" t="s">
+        <v>639</v>
+      </c>
+      <c r="E8" t="s">
+        <v>640</v>
+      </c>
+      <c r="F8" s="6">
+        <v>8</v>
+      </c>
+      <c r="G8" s="6">
+        <v>620</v>
+      </c>
+      <c r="H8" s="6">
+        <v>30</v>
+      </c>
+      <c r="I8" s="6">
+        <f t="shared" si="0"/>
+        <v>590</v>
+      </c>
+      <c r="J8" t="s">
+        <v>616</v>
+      </c>
+      <c r="K8" t="s">
+        <v>22</v>
+      </c>
+      <c r="L8" t="s">
+        <v>597</v>
+      </c>
+      <c r="Q8">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="9" spans="1:17" x14ac:dyDescent="0.25">
+      <c r="B9" t="s">
+        <v>16</v>
+      </c>
+      <c r="C9" t="s">
+        <v>24</v>
+      </c>
+      <c r="D9" t="s">
+        <v>641</v>
+      </c>
+      <c r="E9" t="s">
+        <v>26</v>
+      </c>
+      <c r="F9" s="6">
+        <v>7</v>
+      </c>
+      <c r="G9" s="6">
+        <v>820</v>
+      </c>
+      <c r="H9" s="6">
+        <v>30</v>
+      </c>
+      <c r="I9" s="6">
+        <f t="shared" si="0"/>
+        <v>790</v>
+      </c>
+      <c r="J9" t="s">
+        <v>616</v>
+      </c>
+      <c r="K9" t="s">
+        <v>22</v>
+      </c>
+      <c r="L9" t="s">
+        <v>597</v>
+      </c>
+      <c r="Q9">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="10" spans="1:17" x14ac:dyDescent="0.25">
+      <c r="A10" t="s">
+        <v>83</v>
+      </c>
+      <c r="B10" t="s">
+        <v>16</v>
+      </c>
+      <c r="C10" t="s">
+        <v>651</v>
+      </c>
+      <c r="E10" t="s">
+        <v>652</v>
+      </c>
+      <c r="F10" s="6">
+        <v>6</v>
+      </c>
+      <c r="G10" s="6">
+        <v>1110</v>
+      </c>
+      <c r="H10" s="6">
+        <v>30</v>
+      </c>
+      <c r="I10" s="6">
+        <f t="shared" si="0"/>
+        <v>1080</v>
+      </c>
+      <c r="J10" t="s">
+        <v>616</v>
+      </c>
+      <c r="K10" t="s">
+        <v>22</v>
+      </c>
+      <c r="L10" t="s">
+        <v>597</v>
+      </c>
+      <c r="Q10">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="11" spans="1:17" x14ac:dyDescent="0.25">
+      <c r="A11" t="s">
+        <v>83</v>
+      </c>
+      <c r="B11" t="s">
+        <v>16</v>
+      </c>
+      <c r="C11" t="s">
+        <v>655</v>
+      </c>
+      <c r="E11" t="s">
+        <v>656</v>
+      </c>
+      <c r="F11" t="s">
+        <v>259</v>
+      </c>
+      <c r="G11" s="6">
+        <v>45</v>
+      </c>
+      <c r="H11" s="6">
+        <v>45</v>
+      </c>
+      <c r="I11" s="6">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+      <c r="J11" t="s">
+        <v>616</v>
+      </c>
+      <c r="K11" t="s">
+        <v>22</v>
+      </c>
+      <c r="L11" t="s">
+        <v>597</v>
+      </c>
+      <c r="Q11">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="12" spans="1:17" x14ac:dyDescent="0.25">
+      <c r="B12" t="s">
+        <v>16</v>
+      </c>
+      <c r="C12" t="s">
+        <v>594</v>
+      </c>
+      <c r="D12" t="s">
+        <v>595</v>
+      </c>
+      <c r="E12" t="s">
+        <v>596</v>
+      </c>
+      <c r="F12" s="6">
+        <v>2</v>
+      </c>
+      <c r="G12" s="6">
+        <v>850</v>
+      </c>
+      <c r="H12" s="6">
+        <v>30</v>
+      </c>
+      <c r="I12" s="6">
+        <f t="shared" si="0"/>
+        <v>820</v>
+      </c>
+      <c r="J12" t="s">
+        <v>22</v>
+      </c>
+      <c r="K12" t="s">
+        <v>22</v>
+      </c>
+      <c r="L12" t="s">
+        <v>597</v>
+      </c>
+      <c r="Q12">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="13" spans="1:17" x14ac:dyDescent="0.25">
+      <c r="B13" t="s">
+        <v>16</v>
+      </c>
+      <c r="C13" t="s">
+        <v>604</v>
+      </c>
+      <c r="D13" t="s">
+        <v>605</v>
+      </c>
+      <c r="E13" t="s">
+        <v>606</v>
+      </c>
+      <c r="F13" t="s">
+        <v>153</v>
+      </c>
+      <c r="G13" s="6">
+        <v>1840</v>
+      </c>
+      <c r="H13" s="6">
+        <v>30</v>
+      </c>
+      <c r="I13" s="6">
+        <f t="shared" si="0"/>
+        <v>1810</v>
+      </c>
+      <c r="J13" t="s">
+        <v>22</v>
+      </c>
+      <c r="K13" t="s">
+        <v>22</v>
+      </c>
+      <c r="L13" t="s">
+        <v>597</v>
+      </c>
+      <c r="Q13">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="14" spans="1:17" x14ac:dyDescent="0.25">
+      <c r="B14" t="s">
+        <v>16</v>
+      </c>
+      <c r="C14" t="s">
+        <v>607</v>
+      </c>
+      <c r="D14" t="s">
+        <v>608</v>
+      </c>
+      <c r="E14" t="s">
+        <v>609</v>
+      </c>
+      <c r="F14" t="s">
+        <v>36</v>
+      </c>
+      <c r="G14" s="6">
+        <v>815</v>
+      </c>
+      <c r="H14" s="6">
+        <v>25</v>
+      </c>
+      <c r="I14" s="6">
+        <f t="shared" si="0"/>
+        <v>790</v>
+      </c>
+      <c r="J14" t="s">
+        <v>22</v>
+      </c>
+      <c r="K14" t="s">
+        <v>22</v>
+      </c>
+      <c r="L14" t="s">
+        <v>597</v>
+      </c>
+      <c r="Q14">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="15" spans="1:17" x14ac:dyDescent="0.25">
+      <c r="B15" t="s">
+        <v>16</v>
+      </c>
+      <c r="C15" t="s">
+        <v>610</v>
+      </c>
+      <c r="D15" t="s">
+        <v>611</v>
+      </c>
+      <c r="E15" t="s">
+        <v>612</v>
+      </c>
+      <c r="F15" t="s">
+        <v>44</v>
+      </c>
+      <c r="G15" s="6">
+        <v>815</v>
+      </c>
+      <c r="H15" s="6">
+        <v>25</v>
+      </c>
+      <c r="I15" s="6">
+        <f t="shared" si="0"/>
+        <v>790</v>
+      </c>
+      <c r="J15" t="s">
+        <v>22</v>
+      </c>
+      <c r="K15" t="s">
+        <v>22</v>
+      </c>
+      <c r="L15" t="s">
+        <v>597</v>
+      </c>
+      <c r="Q15">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="16" spans="1:17" x14ac:dyDescent="0.25">
+      <c r="B16" t="s">
+        <v>16</v>
+      </c>
+      <c r="C16" t="s">
+        <v>626</v>
+      </c>
+      <c r="D16" t="s">
+        <v>627</v>
+      </c>
+      <c r="E16" t="s">
+        <v>628</v>
+      </c>
+      <c r="F16" s="6">
+        <v>12</v>
+      </c>
+      <c r="G16" s="6">
+        <v>0</v>
+      </c>
+      <c r="H16" s="6">
+        <v>30</v>
+      </c>
+      <c r="I16" s="6">
+        <f>-H16</f>
+        <v>-30</v>
+      </c>
+      <c r="J16" t="s">
+        <v>22</v>
+      </c>
+      <c r="K16" t="s">
+        <v>22</v>
+      </c>
+      <c r="L16" t="s">
+        <v>597</v>
+      </c>
+      <c r="Q16">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="17" spans="1:17" x14ac:dyDescent="0.25">
+      <c r="B17" t="s">
+        <v>16</v>
+      </c>
+      <c r="C17" t="s">
+        <v>645</v>
+      </c>
+      <c r="D17" t="s">
+        <v>646</v>
+      </c>
+      <c r="E17" t="s">
+        <v>647</v>
+      </c>
+      <c r="F17" t="s">
+        <v>153</v>
+      </c>
+      <c r="G17" s="6">
+        <v>0</v>
+      </c>
+      <c r="H17" s="6">
+        <v>30</v>
+      </c>
+      <c r="I17" s="6">
+        <f>-H17</f>
+        <v>-30</v>
+      </c>
+      <c r="J17" t="s">
+        <v>22</v>
+      </c>
+      <c r="K17" t="s">
+        <v>22</v>
+      </c>
+      <c r="L17" t="s">
+        <v>597</v>
+      </c>
+      <c r="Q17">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="18" spans="1:17" x14ac:dyDescent="0.25">
+      <c r="B18" t="s">
+        <v>16</v>
+      </c>
+      <c r="C18" t="s">
+        <v>648</v>
+      </c>
+      <c r="D18" t="s">
+        <v>649</v>
+      </c>
+      <c r="E18" t="s">
+        <v>650</v>
+      </c>
+      <c r="F18" t="s">
+        <v>44</v>
+      </c>
+      <c r="G18" s="6">
+        <v>695</v>
+      </c>
+      <c r="H18" s="6">
+        <v>25</v>
+      </c>
+      <c r="I18" s="6">
+        <f>G18-H18</f>
+        <v>670</v>
+      </c>
+      <c r="J18" t="s">
+        <v>22</v>
+      </c>
+      <c r="K18" t="s">
+        <v>22</v>
+      </c>
+      <c r="L18" t="s">
+        <v>597</v>
+      </c>
+      <c r="Q18">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="19" spans="1:17" x14ac:dyDescent="0.25">
+      <c r="A19" t="s">
+        <v>83</v>
+      </c>
+      <c r="B19" t="s">
+        <v>16</v>
+      </c>
+      <c r="C19" t="s">
+        <v>657</v>
+      </c>
+      <c r="E19" t="s">
+        <v>658</v>
+      </c>
+      <c r="F19" t="s">
+        <v>44</v>
+      </c>
+      <c r="G19" s="6">
+        <v>4895</v>
+      </c>
+      <c r="H19" s="6">
+        <v>35</v>
+      </c>
+      <c r="I19" s="6">
+        <f>G19-H19</f>
+        <v>4860</v>
+      </c>
+      <c r="J19" t="s">
+        <v>22</v>
+      </c>
+      <c r="K19" t="s">
+        <v>22</v>
+      </c>
+      <c r="L19" t="s">
+        <v>597</v>
+      </c>
+      <c r="Q19">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="20" spans="1:17" x14ac:dyDescent="0.25">
+      <c r="A20" t="s">
+        <v>83</v>
+      </c>
+      <c r="B20" t="s">
+        <v>16</v>
+      </c>
+      <c r="C20" t="s">
+        <v>659</v>
+      </c>
+      <c r="E20" t="s">
+        <v>660</v>
+      </c>
+      <c r="F20" s="6">
+        <v>12</v>
+      </c>
+      <c r="G20" s="6">
+        <v>0</v>
+      </c>
+      <c r="H20" s="6">
+        <v>35</v>
+      </c>
+      <c r="I20" s="6">
+        <f>-H20</f>
+        <v>-35</v>
+      </c>
+      <c r="J20" t="s">
+        <v>22</v>
+      </c>
+      <c r="K20" t="s">
+        <v>22</v>
+      </c>
+      <c r="L20" t="s">
+        <v>597</v>
+      </c>
+      <c r="Q20">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="21" spans="1:17" x14ac:dyDescent="0.25">
+      <c r="A21" t="s">
+        <v>83</v>
+      </c>
+      <c r="B21" t="s">
+        <v>16</v>
+      </c>
+      <c r="C21" t="s">
+        <v>661</v>
+      </c>
+      <c r="E21" t="s">
+        <v>425</v>
+      </c>
+      <c r="F21" s="6">
+        <v>12</v>
+      </c>
+      <c r="G21" s="6">
+        <v>0</v>
+      </c>
+      <c r="H21" s="6">
+        <v>35</v>
+      </c>
+      <c r="I21" s="6">
+        <f>-H21</f>
+        <v>-35</v>
+      </c>
+      <c r="J21" t="s">
+        <v>22</v>
+      </c>
+      <c r="K21" t="s">
+        <v>22</v>
+      </c>
+      <c r="L21" t="s">
+        <v>597</v>
+      </c>
+      <c r="Q21">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="22" spans="1:17" x14ac:dyDescent="0.25">
+      <c r="B22" t="s">
+        <v>16</v>
+      </c>
+      <c r="C22" t="s">
+        <v>598</v>
+      </c>
+      <c r="D22" t="s">
+        <v>599</v>
+      </c>
+      <c r="E22" t="s">
+        <v>600</v>
+      </c>
+      <c r="F22" s="6">
+        <v>1</v>
+      </c>
+      <c r="G22" s="6">
+        <v>745</v>
+      </c>
+      <c r="H22" s="6">
+        <v>25</v>
+      </c>
+      <c r="I22" s="6">
+        <f t="shared" ref="I22:I27" si="1">G22-H22</f>
+        <v>720</v>
+      </c>
+      <c r="J22" t="s">
+        <v>165</v>
+      </c>
+      <c r="K22" t="s">
+        <v>22</v>
+      </c>
+      <c r="L22" t="s">
+        <v>597</v>
+      </c>
+      <c r="Q22">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="23" spans="1:17" x14ac:dyDescent="0.25">
+      <c r="B23" t="s">
+        <v>16</v>
+      </c>
+      <c r="C23" t="s">
+        <v>601</v>
+      </c>
+      <c r="D23" t="s">
+        <v>602</v>
+      </c>
+      <c r="E23" t="s">
+        <v>603</v>
+      </c>
+      <c r="F23" s="6">
+        <v>3</v>
+      </c>
+      <c r="G23" s="6">
+        <v>1025</v>
+      </c>
+      <c r="H23" s="6">
+        <v>25</v>
+      </c>
+      <c r="I23" s="6">
+        <f t="shared" si="1"/>
+        <v>1000</v>
+      </c>
+      <c r="J23" t="s">
+        <v>165</v>
+      </c>
+      <c r="K23" t="s">
+        <v>22</v>
+      </c>
+      <c r="L23" t="s">
+        <v>597</v>
+      </c>
+      <c r="Q23">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="24" spans="1:17" x14ac:dyDescent="0.25">
+      <c r="B24" t="s">
+        <v>16</v>
+      </c>
+      <c r="C24" t="s">
+        <v>632</v>
+      </c>
+      <c r="D24" t="s">
+        <v>633</v>
+      </c>
+      <c r="E24" t="s">
+        <v>634</v>
+      </c>
+      <c r="F24" t="s">
+        <v>86</v>
+      </c>
+      <c r="G24" s="6">
+        <v>115</v>
+      </c>
+      <c r="H24" s="6">
+        <v>25</v>
+      </c>
+      <c r="I24" s="6">
+        <f t="shared" si="1"/>
+        <v>90</v>
+      </c>
+      <c r="J24" t="s">
+        <v>165</v>
+      </c>
+      <c r="K24" t="s">
+        <v>22</v>
+      </c>
+      <c r="L24" t="s">
+        <v>597</v>
+      </c>
+      <c r="Q24">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="25" spans="1:17" x14ac:dyDescent="0.25">
+      <c r="B25" t="s">
+        <v>16</v>
+      </c>
+      <c r="C25" t="s">
+        <v>635</v>
+      </c>
+      <c r="D25" t="s">
+        <v>636</v>
+      </c>
+      <c r="E25" t="s">
+        <v>637</v>
+      </c>
+      <c r="F25" t="s">
+        <v>86</v>
+      </c>
+      <c r="G25" s="6">
+        <v>1325</v>
+      </c>
+      <c r="H25" s="6">
+        <v>25</v>
+      </c>
+      <c r="I25" s="6">
+        <f t="shared" si="1"/>
+        <v>1300</v>
+      </c>
+      <c r="J25" t="s">
+        <v>165</v>
+      </c>
+      <c r="K25" t="s">
+        <v>22</v>
+      </c>
+      <c r="L25" t="s">
+        <v>597</v>
+      </c>
+      <c r="Q25">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="26" spans="1:17" x14ac:dyDescent="0.25">
+      <c r="A26" t="s">
+        <v>83</v>
+      </c>
+      <c r="B26" t="s">
+        <v>16</v>
+      </c>
+      <c r="C26" t="s">
+        <v>653</v>
+      </c>
+      <c r="E26" t="s">
+        <v>654</v>
+      </c>
+      <c r="F26" s="6">
+        <v>5</v>
+      </c>
+      <c r="G26" s="6">
+        <v>30</v>
+      </c>
+      <c r="H26" s="6">
+        <v>30</v>
+      </c>
+      <c r="I26" s="6">
+        <f t="shared" ref="I26" si="2">G26-H26</f>
+        <v>0</v>
+      </c>
+      <c r="J26" t="s">
+        <v>165</v>
+      </c>
+      <c r="K26" t="s">
+        <v>22</v>
+      </c>
+      <c r="L26" t="s">
+        <v>597</v>
+      </c>
+      <c r="Q26">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="27" spans="1:17" x14ac:dyDescent="0.25">
+      <c r="B27" t="s">
+        <v>16</v>
+      </c>
+      <c r="C27" t="s">
+        <v>642</v>
+      </c>
+      <c r="D27" t="s">
+        <v>643</v>
+      </c>
+      <c r="E27" t="s">
+        <v>644</v>
+      </c>
+      <c r="F27" t="s">
+        <v>86</v>
+      </c>
+      <c r="G27" s="6">
+        <v>765</v>
+      </c>
+      <c r="H27" s="6">
+        <v>25</v>
+      </c>
+      <c r="I27" s="6">
+        <f t="shared" si="1"/>
+        <v>740</v>
+      </c>
+      <c r="J27" t="s">
+        <v>165</v>
+      </c>
+      <c r="K27" t="s">
+        <v>22</v>
+      </c>
+      <c r="L27" s="16" t="s">
+        <v>597</v>
+      </c>
+      <c r="Q27">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="28" spans="1:17" s="2" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="B28" s="2" t="s">
+        <v>16</v>
+      </c>
+      <c r="C28" s="2" t="s">
+        <v>233</v>
+      </c>
+      <c r="D28" s="2" t="s">
+        <v>234</v>
+      </c>
+      <c r="E28" s="2" t="s">
+        <v>235</v>
+      </c>
+      <c r="F28" s="12" t="s">
+        <v>128</v>
+      </c>
+      <c r="G28" s="12">
+        <v>695</v>
+      </c>
+      <c r="H28" s="12">
+        <v>0</v>
+      </c>
+      <c r="I28" s="12">
+        <f>G28-H28</f>
+        <v>695</v>
+      </c>
+      <c r="J28" s="14" t="s">
+        <v>446</v>
+      </c>
+      <c r="K28" s="2" t="s">
+        <v>22</v>
+      </c>
+      <c r="L28" s="17" t="s">
+        <v>182</v>
+      </c>
+      <c r="M28" s="14"/>
+      <c r="N28" s="14" t="s">
+        <v>448</v>
+      </c>
+      <c r="O28" s="14" t="s">
+        <v>448</v>
+      </c>
+      <c r="P28" s="14" t="s">
+        <v>449</v>
+      </c>
+      <c r="Q28" s="15">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="29" spans="1:17" s="2" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="B29" s="2" t="s">
+        <v>16</v>
+      </c>
+      <c r="C29" s="2" t="s">
+        <v>571</v>
+      </c>
+      <c r="D29" s="2" t="s">
+        <v>572</v>
+      </c>
+      <c r="E29" s="2" t="s">
+        <v>573</v>
+      </c>
+      <c r="F29" s="12">
+        <v>2</v>
+      </c>
+      <c r="G29" s="12">
+        <v>1020</v>
+      </c>
+      <c r="H29" s="12">
+        <v>0</v>
+      </c>
+      <c r="I29" s="12">
+        <f>G29-H29</f>
+        <v>1020</v>
+      </c>
+      <c r="J29" s="14" t="s">
+        <v>446</v>
+      </c>
+      <c r="K29" s="2" t="s">
+        <v>22</v>
+      </c>
+      <c r="L29" s="2" t="s">
+        <v>455</v>
+      </c>
+      <c r="M29" s="14"/>
+      <c r="N29" s="14" t="s">
+        <v>448</v>
+      </c>
+      <c r="O29" s="14" t="s">
+        <v>448</v>
+      </c>
+      <c r="P29" s="14" t="s">
+        <v>449</v>
+      </c>
+      <c r="Q29" s="15">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="31" spans="1:17" x14ac:dyDescent="0.25">
+      <c r="D31" s="1">
+        <f>COUNTA(D3:D29)</f>
+        <v>21</v>
+      </c>
+      <c r="G31" s="1">
+        <f t="shared" ref="G31:Q31" si="3">SUBTOTAL(9,G3:G29)</f>
+        <v>24205</v>
+      </c>
+      <c r="H31" s="1">
+        <f t="shared" si="3"/>
+        <v>735</v>
+      </c>
+      <c r="I31" s="1">
+        <f t="shared" si="3"/>
+        <v>23470</v>
+      </c>
+      <c r="J31" s="1">
+        <f t="shared" si="3"/>
+        <v>0</v>
+      </c>
+      <c r="K31" s="1">
+        <f t="shared" si="3"/>
+        <v>0</v>
+      </c>
+      <c r="L31" s="1">
+        <f t="shared" si="3"/>
+        <v>0</v>
+      </c>
+      <c r="M31" s="1">
+        <f t="shared" si="3"/>
+        <v>0</v>
+      </c>
+      <c r="N31" s="1">
+        <f t="shared" si="3"/>
+        <v>0</v>
+      </c>
+      <c r="O31" s="1">
+        <f t="shared" si="3"/>
+        <v>0</v>
+      </c>
+      <c r="P31" s="1">
+        <f t="shared" si="3"/>
+        <v>0</v>
+      </c>
+      <c r="Q31" s="1">
+        <f t="shared" si="3"/>
+        <v>27</v>
+      </c>
+    </row>
+    <row r="32" spans="1:17" x14ac:dyDescent="0.25">
+      <c r="H32">
+        <f>-6*17</f>
+        <v>-102</v>
+      </c>
+    </row>
+    <row r="33" spans="1:16" x14ac:dyDescent="0.25">
+      <c r="A33" s="1" t="s">
+        <v>16</v>
+      </c>
+      <c r="C33" s="20" t="s">
+        <v>89</v>
+      </c>
+      <c r="D33" s="20"/>
+      <c r="E33" s="4" t="s">
+        <v>90</v>
+      </c>
+      <c r="H33">
+        <f>-2*25</f>
+        <v>-50</v>
+      </c>
+      <c r="K33" s="7" t="s">
+        <v>22</v>
+      </c>
+      <c r="L33" s="7" t="s">
+        <v>91</v>
+      </c>
+      <c r="M33" s="7" t="s">
+        <v>90</v>
+      </c>
+      <c r="O33" s="4" t="s">
+        <v>92</v>
+      </c>
+    </row>
+    <row r="34" spans="1:16" x14ac:dyDescent="0.25">
+      <c r="A34" t="s">
+        <v>597</v>
+      </c>
+      <c r="B34" s="3" t="s">
+        <v>93</v>
+      </c>
+      <c r="C34" s="21">
+        <f>SUMIFS(I$3:I$29,B$3:B$29,A$33,L$3:L$29,A$34)</f>
+        <v>21755</v>
+      </c>
+      <c r="D34" s="21"/>
+      <c r="E34" s="3">
+        <f>SUMIFS(Q$3:Q$29,B$3:B$29,A$33,L$3:L$29,A$34)</f>
+        <v>25</v>
+      </c>
+      <c r="F34" t="s">
+        <v>94</v>
+      </c>
+      <c r="H34">
+        <f>-1*30</f>
+        <v>-30</v>
+      </c>
+      <c r="K34" t="s">
+        <v>95</v>
+      </c>
+      <c r="L34">
+        <f>SUMIFS(G$3:G$29,J$3:J$29,K$33)</f>
+        <v>9910</v>
+      </c>
+      <c r="M34">
+        <f>SUMIFS(Q$3:Q$29,J$3:J$29,K$33)</f>
+        <v>10</v>
+      </c>
+      <c r="O34" t="s">
+        <v>22</v>
+      </c>
+      <c r="P34">
+        <f>L39</f>
+        <v>8590</v>
+      </c>
+    </row>
+    <row r="35" spans="1:16" x14ac:dyDescent="0.25">
+      <c r="B35" s="2" t="s">
+        <v>97</v>
+      </c>
+      <c r="C35" s="22">
+        <v>0</v>
+      </c>
+      <c r="D35" s="22"/>
+      <c r="K35" t="s">
+        <v>98</v>
+      </c>
+      <c r="L35">
+        <f>-SUMIFS(H$3:H$29,J$3:J$29,K$33)+M35*5</f>
+        <v>-250</v>
+      </c>
+      <c r="M35">
+        <f>SUMIFS(Q$3:Q$29,J$3:J$29,K$33)-COUNTIFS(J$3:J$29,K$33,M$3:M$29,"*gộp*")</f>
+        <v>10</v>
+      </c>
+      <c r="O35" t="s">
+        <v>165</v>
+      </c>
+      <c r="P35">
+        <f>L47</f>
+        <v>3880</v>
+      </c>
+    </row>
+    <row r="36" spans="1:16" x14ac:dyDescent="0.25">
+      <c r="B36" s="2" t="s">
+        <v>99</v>
+      </c>
+      <c r="C36" s="22">
+        <f>-SUMIFS(I$3:I$29,B$3:B$29,A$33,P$3:P$29,"xx",N$3:N$29,"x")</f>
+        <v>-1715</v>
+      </c>
+      <c r="D36" s="22"/>
+      <c r="E36" s="2">
+        <f>SUMIFS(Q$3:Q$29,B$3:B$29,A$33,P$3:P$29,"xx",N$3:N$29,"x")</f>
+        <v>2</v>
+      </c>
+      <c r="K36" t="s">
+        <v>100</v>
+      </c>
+      <c r="L36">
+        <f>-M36*2</f>
+        <v>-50</v>
+      </c>
+      <c r="M36">
+        <f>Q31-(COUNTIFS(M$3:M$29,"*gộp*")/2)-COUNTIFS(P$3:P$29,"*xx*")</f>
+        <v>25</v>
+      </c>
+      <c r="O36" t="s">
+        <v>662</v>
+      </c>
+      <c r="P36">
+        <f>L55</f>
+        <v>7698</v>
+      </c>
+    </row>
+    <row r="37" spans="1:16" x14ac:dyDescent="0.25">
+      <c r="B37" s="4" t="s">
+        <v>101</v>
+      </c>
+      <c r="C37" s="20">
+        <f>SUBTOTAL(9,C34:C36)</f>
+        <v>20040</v>
+      </c>
+      <c r="D37" s="20"/>
+      <c r="E37">
+        <f>E34</f>
+        <v>25</v>
+      </c>
+      <c r="K37" s="2" t="s">
+        <v>102</v>
+      </c>
+      <c r="O37" t="s">
+        <v>103</v>
+      </c>
+      <c r="P37">
+        <f>-C41</f>
+        <v>-20040</v>
+      </c>
+    </row>
+    <row r="38" spans="1:16" x14ac:dyDescent="0.25">
+      <c r="B38" s="2" t="s">
+        <v>104</v>
+      </c>
+      <c r="C38" s="18"/>
+      <c r="D38" s="18"/>
+      <c r="K38" s="2" t="s">
+        <v>105</v>
+      </c>
+      <c r="L38" s="2">
+        <v>-1020</v>
+      </c>
+      <c r="O38" s="4" t="s">
+        <v>106</v>
+      </c>
+      <c r="P38" s="4">
+        <f>SUBTOTAL(9,P34:P37)</f>
+        <v>128</v>
+      </c>
+    </row>
+    <row r="39" spans="1:16" x14ac:dyDescent="0.25">
+      <c r="B39" s="8" t="s">
+        <v>107</v>
+      </c>
+      <c r="C39" s="18"/>
+      <c r="D39" s="18"/>
+      <c r="L39" s="9">
+        <f>SUBTOTAL(9,L34:L38)</f>
+        <v>8590</v>
+      </c>
+      <c r="M39" s="9">
+        <f>M34</f>
+        <v>10</v>
+      </c>
+    </row>
+    <row r="41" spans="1:16" x14ac:dyDescent="0.25">
+      <c r="B41" s="1" t="s">
+        <v>108</v>
+      </c>
+      <c r="C41" s="19">
+        <f>C37+C38+C39</f>
+        <v>20040</v>
+      </c>
+      <c r="D41" s="19"/>
+      <c r="E41" s="1" t="s">
+        <v>109</v>
+      </c>
+      <c r="K41" s="7" t="s">
+        <v>165</v>
+      </c>
+      <c r="L41" s="7" t="s">
+        <v>91</v>
+      </c>
+      <c r="M41" s="7" t="s">
+        <v>90</v>
+      </c>
+    </row>
+    <row r="42" spans="1:16" x14ac:dyDescent="0.25">
+      <c r="K42" t="s">
+        <v>95</v>
+      </c>
+      <c r="L42">
+        <f>SUMIFS(G$3:G$29,J$3:J$29,K$41)</f>
+        <v>4005</v>
+      </c>
+      <c r="M42">
+        <f>SUMIFS(Q$3:Q$29,J$3:J$29,K$41)</f>
+        <v>6</v>
+      </c>
+    </row>
+    <row r="43" spans="1:16" x14ac:dyDescent="0.25">
+      <c r="K43" t="s">
+        <v>98</v>
+      </c>
+      <c r="L43">
+        <f>-SUMIFS(H$3:H$29,J$3:J$29,K$41)+M43*5</f>
+        <v>-125</v>
+      </c>
+      <c r="M43">
+        <f>SUMIFS(Q$3:Q$29,J$3:J$29,K$41)-COUNTIFS(J$3:J$29,K$41,M$3:M$29,"*gộp*")</f>
+        <v>6</v>
+      </c>
+    </row>
+    <row r="44" spans="1:16" x14ac:dyDescent="0.25">
+      <c r="K44" t="s">
+        <v>100</v>
+      </c>
+    </row>
+    <row r="45" spans="1:16" x14ac:dyDescent="0.25">
+      <c r="K45" s="2" t="s">
+        <v>102</v>
+      </c>
+    </row>
+    <row r="46" spans="1:16" x14ac:dyDescent="0.25">
+      <c r="K46" s="2" t="s">
+        <v>105</v>
+      </c>
+    </row>
+    <row r="47" spans="1:16" x14ac:dyDescent="0.25">
+      <c r="L47" s="9">
+        <f>SUBTOTAL(9,L42:L46)</f>
+        <v>3880</v>
+      </c>
+      <c r="M47" s="9">
+        <f>M42</f>
+        <v>6</v>
+      </c>
+    </row>
+    <row r="49" spans="11:13" x14ac:dyDescent="0.25">
+      <c r="K49" s="7" t="s">
+        <v>616</v>
+      </c>
+      <c r="L49" s="7" t="s">
+        <v>91</v>
+      </c>
+      <c r="M49" s="7" t="s">
+        <v>90</v>
+      </c>
+    </row>
+    <row r="50" spans="11:13" x14ac:dyDescent="0.25">
+      <c r="K50" t="s">
+        <v>95</v>
+      </c>
+      <c r="L50">
+        <f>SUMIFS(G$3:G$29,J$3:J$29,K$49)</f>
+        <v>8575</v>
+      </c>
+      <c r="M50">
+        <f>SUMIFS(Q$3:Q$29,J$3:J$29,K$49)</f>
+        <v>9</v>
+      </c>
+    </row>
+    <row r="51" spans="11:13" x14ac:dyDescent="0.25">
+      <c r="K51" t="s">
+        <v>98</v>
+      </c>
+      <c r="L51">
+        <f>SUM(H32:H34)</f>
+        <v>-182</v>
+      </c>
+      <c r="M51">
+        <f>SUMIFS(Q$3:Q$29,J$3:J$29,K$49)</f>
+        <v>9</v>
+      </c>
+    </row>
+    <row r="52" spans="11:13" x14ac:dyDescent="0.25">
+      <c r="K52" t="s">
+        <v>100</v>
+      </c>
+    </row>
+    <row r="53" spans="11:13" x14ac:dyDescent="0.25">
+      <c r="K53" s="2" t="s">
+        <v>102</v>
+      </c>
+    </row>
+    <row r="54" spans="11:13" x14ac:dyDescent="0.25">
+      <c r="K54" s="2" t="s">
+        <v>105</v>
+      </c>
+      <c r="L54" s="2">
+        <v>-695</v>
+      </c>
+    </row>
+    <row r="55" spans="11:13" x14ac:dyDescent="0.25">
+      <c r="L55" s="9">
+        <f>SUBTOTAL(9,L50:L54)</f>
+        <v>7698</v>
+      </c>
+      <c r="M55" s="9">
+        <f>M50</f>
+        <v>9</v>
+      </c>
+    </row>
+  </sheetData>
+  <autoFilter ref="A2:P29" xr:uid="{00000000-0009-0000-0000-000005000000}">
+    <sortState xmlns:xlrd2="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata2" ref="A3:P29">
+      <sortCondition ref="J2:J29"/>
+    </sortState>
+  </autoFilter>
+  <mergeCells count="8">
+    <mergeCell ref="C38:D38"/>
+    <mergeCell ref="C39:D39"/>
+    <mergeCell ref="C41:D41"/>
+    <mergeCell ref="C33:D33"/>
+    <mergeCell ref="C34:D34"/>
+    <mergeCell ref="C35:D35"/>
+    <mergeCell ref="C36:D36"/>
+    <mergeCell ref="C37:D37"/>
+  </mergeCells>
+  <pageMargins left="0.75" right="0.75" top="0.75" bottom="0.5" header="0.5" footer="0.75"/>
+  <pageSetup paperSize="9" orientation="portrait" r:id="rId1"/>
+</worksheet>
 </file>
--- a/data/Apr/InternalDailyReport.xlsx
+++ b/data/Apr/InternalDailyReport.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\Work\Freelance\TextInputter\data\Apr\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{B474649D-7D99-4DA7-A7CB-C8F5FA57C8D2}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{E8714206-4EC6-4B27-809B-E512127A59AD}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" firstSheet="10" activeTab="23" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" firstSheet="11" activeTab="25" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="01-04" sheetId="2" r:id="rId1"/>
@@ -37,7 +37,8 @@
     <sheet name="25-04" sheetId="28" r:id="rId22"/>
     <sheet name="27-04" sheetId="29" r:id="rId23"/>
     <sheet name="28-04" sheetId="30" r:id="rId24"/>
-    <sheet name="Sheet1" sheetId="19" r:id="rId25"/>
+    <sheet name="29-04" sheetId="31" r:id="rId25"/>
+    <sheet name="Sheet1" sheetId="19" r:id="rId26"/>
   </sheets>
   <definedNames>
     <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'01-04'!$A$2:$P$23</definedName>
@@ -64,7 +65,8 @@
     <definedName name="_xlnm._FilterDatabase" localSheetId="21" hidden="1">'25-04'!$A$2:$P$53</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="22" hidden="1">'27-04'!$A$2:$P$125</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="23" hidden="1">'28-04'!$A$2:$P$49</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="24" hidden="1">Sheet1!$A$2:$E$28</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="24" hidden="1">'29-04'!$A$2:$P$60</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="25" hidden="1">Sheet1!$A$2:$E$27</definedName>
   </definedNames>
   <calcPr calcId="191029"/>
   <extLst>
@@ -106,7 +108,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="10900" uniqueCount="3106">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="11399" uniqueCount="3251">
   <si>
     <t>Tình trạng TT</t>
   </si>
@@ -9090,6 +9092,312 @@
     <t>đơn thiếu ngày 13.4</t>
   </si>
   <si>
+    <t>THƯƠNG 1994</t>
+  </si>
+  <si>
+    <t>Tòa S501, Vinhome grand park, long thạnh mỹ</t>
+  </si>
+  <si>
+    <t>28-04-2026</t>
+  </si>
+  <si>
+    <t>HD016989</t>
+  </si>
+  <si>
+    <t>AT 28-04</t>
+  </si>
+  <si>
+    <t>chi - fb Mi Na</t>
+  </si>
+  <si>
+    <t>HD017060</t>
+  </si>
+  <si>
+    <t>1619/29 phạm thế hiển phường 6</t>
+  </si>
+  <si>
+    <t>Phương Phan</t>
+  </si>
+  <si>
+    <t>HD017091</t>
+  </si>
+  <si>
+    <t>D4/10 ấp 46, Tân Vĩnh Lộc</t>
+  </si>
+  <si>
+    <t>HD016592</t>
+  </si>
+  <si>
+    <t>Phạm Mỹ Tiên</t>
+  </si>
+  <si>
+    <t>HD017135</t>
+  </si>
+  <si>
+    <t>10/14 âu duong lân p3</t>
+  </si>
+  <si>
+    <t>Thảo Susi</t>
+  </si>
+  <si>
+    <t>HD016982</t>
+  </si>
+  <si>
+    <t>10/16 đường số 8 phường Bình Hưng Hòa</t>
+  </si>
+  <si>
+    <t>Trang Nabie</t>
+  </si>
+  <si>
+    <t>HD016850</t>
+  </si>
+  <si>
+    <t>V6, Sunrise city south tower 23 nguyễn hữu thọ, phường tân hưng</t>
+  </si>
+  <si>
+    <t>HD017081</t>
+  </si>
+  <si>
+    <t>HD017133</t>
+  </si>
+  <si>
+    <t>Vũ Thùy Dương</t>
+  </si>
+  <si>
+    <t>HD016977</t>
+  </si>
+  <si>
+    <t>96/50/5 đường phạm đăng giảng, bình hưng hòa</t>
+  </si>
+  <si>
+    <t>Bé Bờm</t>
+  </si>
+  <si>
+    <t>HD017078</t>
+  </si>
+  <si>
+    <t>167/10 Đào Sư Tích, Phước Kiển</t>
+  </si>
+  <si>
+    <t>Trần Minh Thông</t>
+  </si>
+  <si>
+    <t>H0017097</t>
+  </si>
+  <si>
+    <t>1707 Phạm thế hiển phường bình đông</t>
+  </si>
+  <si>
+    <t>đơn chuyển AT 28-04</t>
+  </si>
+  <si>
+    <t>NGUYỄN MINH DUY</t>
+  </si>
+  <si>
+    <t>90/35 Trần Văn Ơn, Phường Tân Sơn Nhì</t>
+  </si>
+  <si>
+    <t>HƯƠNG TRẦN</t>
+  </si>
+  <si>
+    <t>261/26c chu văn an p12</t>
+  </si>
+  <si>
+    <t>Vy Nhật Hà note kh gọi được thì nhắn zalo</t>
+  </si>
+  <si>
+    <t>HD016775</t>
+  </si>
+  <si>
+    <t>Landmark 1 vinhome central park p thạnh mỹ tây</t>
+  </si>
+  <si>
+    <t>Thiên Thiên</t>
+  </si>
+  <si>
+    <t>HD017084</t>
+  </si>
+  <si>
+    <t>20 đường số 6, linh chiểu</t>
+  </si>
+  <si>
+    <t>Sunwah White House fb Mzzton</t>
+  </si>
+  <si>
+    <t>HD017045</t>
+  </si>
+  <si>
+    <t>90 nguyễn hữu cảnh thạnh mỹ tây</t>
+  </si>
+  <si>
+    <t>Diệu Quyên</t>
+  </si>
+  <si>
+    <t>HD017101</t>
+  </si>
+  <si>
+    <t>242/20 phạm văn bạch p15</t>
+  </si>
+  <si>
+    <t>(Anna Hanh )</t>
+  </si>
+  <si>
+    <t>HD016907</t>
+  </si>
+  <si>
+    <t>188 Nguyễn Văn Công, P.3</t>
+  </si>
+  <si>
+    <t>HD017134</t>
+  </si>
+  <si>
+    <t>Diễm</t>
+  </si>
+  <si>
+    <t>HD016967</t>
+  </si>
+  <si>
+    <t>22/31/4 đường số 21, Phường 8 (phường Thông Tây Hội mới)</t>
+  </si>
+  <si>
+    <t>Nick Loan</t>
+  </si>
+  <si>
+    <t>HD016998</t>
+  </si>
+  <si>
+    <t>536/43/40 âu cơ p. bảy hiền</t>
+  </si>
+  <si>
+    <t>Khánh Vy Đỗ</t>
+  </si>
+  <si>
+    <t>HD017102</t>
+  </si>
+  <si>
+    <t>24 đường số 6 - tam phú</t>
+  </si>
+  <si>
+    <t>BN182</t>
+  </si>
+  <si>
+    <t>HD017028</t>
+  </si>
+  <si>
+    <t>Truc Trieu</t>
+  </si>
+  <si>
+    <t>HD017106</t>
+  </si>
+  <si>
+    <t>Số nhà A6, Garden Home Thủ Đức, Đường số 3, QL13, Phường Hiệp Binh Phước</t>
+  </si>
+  <si>
+    <t>người nhận nana - fb Oanh Tống</t>
+  </si>
+  <si>
+    <t>HD016818</t>
+  </si>
+  <si>
+    <t>FANG FANG</t>
+  </si>
+  <si>
+    <t>A75/6B/2 Bạch Đằng, Phường 2</t>
+  </si>
+  <si>
+    <t>Thanh Thanh Tô</t>
+  </si>
+  <si>
+    <t>HD017096</t>
+  </si>
+  <si>
+    <t>2/16 tân lập p8</t>
+  </si>
+  <si>
+    <t>Lê Thảo</t>
+  </si>
+  <si>
+    <t>HD016900</t>
+  </si>
+  <si>
+    <t>3 Đặng Dung, P Tân Định</t>
+  </si>
+  <si>
+    <t>huyền nguyễn</t>
+  </si>
+  <si>
+    <t>HD016308</t>
+  </si>
+  <si>
+    <t>thảo fb Nguyễn Bình Phương Trinh</t>
+  </si>
+  <si>
+    <t>HD016407</t>
+  </si>
+  <si>
+    <t>232/111 Vĩnh Khánh f8</t>
+  </si>
+  <si>
+    <t>HD016824</t>
+  </si>
+  <si>
+    <t>485 nguyễn đình chiểu</t>
+  </si>
+  <si>
+    <t>Lynn Pham</t>
+  </si>
+  <si>
+    <t>HD017066</t>
+  </si>
+  <si>
+    <t>2/11 thiên phước phường 9</t>
+  </si>
+  <si>
+    <t>Thanh Vy</t>
+  </si>
+  <si>
+    <t>HD017042</t>
+  </si>
+  <si>
+    <t>167 sư vạn hạnh p3</t>
+  </si>
+  <si>
+    <t>GIA HUY nhận hộ ELIS NGUYỄN ( singapore)</t>
+  </si>
+  <si>
+    <t>HD017110</t>
+  </si>
+  <si>
+    <t>HD016826</t>
+  </si>
+  <si>
+    <t>Lê Ngọc Anh</t>
+  </si>
+  <si>
+    <t>HD016990</t>
+  </si>
+  <si>
+    <t>220/18 Hồ Văn Huê, P.9</t>
+  </si>
+  <si>
+    <t>HD016798</t>
+  </si>
+  <si>
+    <t>HD016728</t>
+  </si>
+  <si>
+    <t>Duyên Huỳnh</t>
+  </si>
+  <si>
+    <t>HD016794</t>
+  </si>
+  <si>
+    <t>Cc tôn thất thuyết phường 1</t>
+  </si>
+  <si>
+    <t>at 28-04</t>
+  </si>
+  <si>
     <t>THÁNG 4</t>
   </si>
   <si>
@@ -9120,310 +9428,439 @@
     <t>Lợi nhuận</t>
   </si>
   <si>
-    <t>NGUYỄN MINH DUY</t>
-  </si>
-  <si>
-    <t>90/35 Trần Văn Ơn, Phường Tân Sơn Nhì</t>
-  </si>
-  <si>
-    <t>28-04-2026</t>
-  </si>
-  <si>
-    <t>THƯƠNG 1994</t>
-  </si>
-  <si>
-    <t>Tòa S501, Vinhome grand park, long thạnh mỹ</t>
-  </si>
-  <si>
-    <t>FANG FANG</t>
-  </si>
-  <si>
-    <t>A75/6B/2 Bạch Đằng, Phường 2</t>
-  </si>
-  <si>
-    <t>HƯƠNG TRẦN</t>
-  </si>
-  <si>
-    <t>261/26c chu văn an p12</t>
-  </si>
-  <si>
-    <t>Thanh Thanh Tô</t>
-  </si>
-  <si>
-    <t>HD017096</t>
-  </si>
-  <si>
-    <t>2/16 tân lập p8</t>
-  </si>
-  <si>
-    <t>HD016989</t>
-  </si>
-  <si>
-    <t>AT 28-04</t>
-  </si>
-  <si>
-    <t>Lê Thảo</t>
-  </si>
-  <si>
-    <t>HD016900</t>
-  </si>
-  <si>
-    <t>3 Đặng Dung, P Tân Định</t>
-  </si>
-  <si>
-    <t>Vy Nhật Hà note kh gọi được thì nhắn zalo</t>
-  </si>
-  <si>
-    <t>HD016775</t>
-  </si>
-  <si>
-    <t>Landmark 1 vinhome central park p thạnh mỹ tây</t>
-  </si>
-  <si>
-    <t>chi - fb Mi Na</t>
-  </si>
-  <si>
-    <t>HD017060</t>
-  </si>
-  <si>
-    <t>1619/29 phạm thế hiển phường 6</t>
-  </si>
-  <si>
-    <t>Phương Phan</t>
-  </si>
-  <si>
-    <t>HD017091</t>
-  </si>
-  <si>
-    <t>D4/10 ấp 46, Tân Vĩnh Lộc</t>
-  </si>
-  <si>
-    <t>Thiên Thiên</t>
-  </si>
-  <si>
-    <t>HD017084</t>
-  </si>
-  <si>
-    <t>20 đường số 6, linh chiểu</t>
-  </si>
-  <si>
-    <t>huyền nguyễn</t>
-  </si>
-  <si>
-    <t>HD016308</t>
-  </si>
-  <si>
-    <t>Sunwah White House fb Mzzton</t>
-  </si>
-  <si>
-    <t>HD017045</t>
-  </si>
-  <si>
-    <t>90 nguyễn hữu cảnh thạnh mỹ tây</t>
-  </si>
-  <si>
-    <t>Diệu Quyên</t>
-  </si>
-  <si>
-    <t>HD017101</t>
-  </si>
-  <si>
-    <t>242/20 phạm văn bạch p15</t>
-  </si>
-  <si>
-    <t>(Anna Hanh )</t>
-  </si>
-  <si>
-    <t>HD016907</t>
-  </si>
-  <si>
-    <t>188 Nguyễn Văn Công, P.3</t>
-  </si>
-  <si>
-    <t>HD017134</t>
-  </si>
-  <si>
-    <t>Diễm</t>
-  </si>
-  <si>
-    <t>HD016967</t>
-  </si>
-  <si>
-    <t>22/31/4 đường số 21, Phường 8 (phường Thông Tây Hội mới)</t>
-  </si>
-  <si>
-    <t>HD016592</t>
-  </si>
-  <si>
-    <t>Phạm Mỹ Tiên</t>
-  </si>
-  <si>
-    <t>HD017135</t>
-  </si>
-  <si>
-    <t>10/14 âu duong lân p3</t>
-  </si>
-  <si>
-    <t>thảo fb Nguyễn Bình Phương Trinh</t>
-  </si>
-  <si>
-    <t>HD016407</t>
-  </si>
-  <si>
-    <t>232/111 Vĩnh Khánh f8</t>
-  </si>
-  <si>
-    <t>Nick Loan</t>
-  </si>
-  <si>
-    <t>HD016998</t>
-  </si>
-  <si>
-    <t>536/43/40 âu cơ p. bảy hiền</t>
-  </si>
-  <si>
-    <t>HD016824</t>
-  </si>
-  <si>
-    <t>485 nguyễn đình chiểu</t>
-  </si>
-  <si>
-    <t>Khánh Vy Đỗ</t>
-  </si>
-  <si>
-    <t>HD017102</t>
-  </si>
-  <si>
-    <t>24 đường số 6 - tam phú</t>
-  </si>
-  <si>
-    <t>Thảo Susi</t>
-  </si>
-  <si>
-    <t>HD016982</t>
-  </si>
-  <si>
-    <t>10/16 đường số 8 phường Bình Hưng Hòa</t>
-  </si>
-  <si>
-    <t>Lynn Pham</t>
-  </si>
-  <si>
-    <t>HD017066</t>
-  </si>
-  <si>
-    <t>2/11 thiên phước phường 9</t>
-  </si>
-  <si>
-    <t>Thanh Vy</t>
-  </si>
-  <si>
-    <t>HD017042</t>
-  </si>
-  <si>
-    <t>167 sư vạn hạnh p3</t>
-  </si>
-  <si>
-    <t>GIA HUY nhận hộ ELIS NGUYỄN ( singapore)</t>
-  </si>
-  <si>
-    <t>HD017110</t>
-  </si>
-  <si>
-    <t>Trang Nabie</t>
-  </si>
-  <si>
-    <t>HD016850</t>
-  </si>
-  <si>
-    <t>V6, Sunrise city south tower 23 nguyễn hữu thọ, phường tân hưng</t>
-  </si>
-  <si>
-    <t>HD016826</t>
-  </si>
-  <si>
-    <t>Lê Ngọc Anh</t>
-  </si>
-  <si>
-    <t>HD016990</t>
-  </si>
-  <si>
-    <t>220/18 Hồ Văn Huê, P.9</t>
-  </si>
-  <si>
-    <t>HD017081</t>
-  </si>
-  <si>
-    <t>HD017133</t>
-  </si>
-  <si>
-    <t>BN182</t>
-  </si>
-  <si>
-    <t>HD017028</t>
-  </si>
-  <si>
-    <t>HD016798</t>
-  </si>
-  <si>
-    <t>Truc Trieu</t>
-  </si>
-  <si>
-    <t>HD017106</t>
-  </si>
-  <si>
-    <t>Số nhà A6, Garden Home Thủ Đức, Đường số 3, QL13, Phường Hiệp Binh Phước</t>
-  </si>
-  <si>
-    <t>người nhận nana - fb Oanh Tống</t>
-  </si>
-  <si>
-    <t>HD016818</t>
-  </si>
-  <si>
-    <t>HD016728</t>
-  </si>
-  <si>
-    <t>Vũ Thùy Dương</t>
-  </si>
-  <si>
-    <t>HD016977</t>
-  </si>
-  <si>
-    <t>96/50/5 đường phạm đăng giảng, bình hưng hòa</t>
-  </si>
-  <si>
-    <t>Duyên Huỳnh</t>
-  </si>
-  <si>
-    <t>HD016794</t>
-  </si>
-  <si>
-    <t>Cc tôn thất thuyết phường 1</t>
-  </si>
-  <si>
-    <t>Bé Bờm</t>
-  </si>
-  <si>
-    <t>HD017078</t>
-  </si>
-  <si>
-    <t>167/10 Đào Sư Tích, Phước Kiển</t>
-  </si>
-  <si>
-    <t>Trần Minh Thông</t>
-  </si>
-  <si>
-    <t>H0017097</t>
-  </si>
-  <si>
-    <t>1707 Phạm thế hiển phường bình đông</t>
-  </si>
-  <si>
-    <t>đơn chuyển AT 28-04</t>
-  </si>
-  <si>
-    <t>at 28-04</t>
+    <t>HD017294</t>
+  </si>
+  <si>
+    <t>29-04-2026</t>
+  </si>
+  <si>
+    <t>Phương Như</t>
+  </si>
+  <si>
+    <t>HD017191</t>
+  </si>
+  <si>
+    <t>10 đường số 2 binh thuận tân thuận</t>
+  </si>
+  <si>
+    <t>AT 29-04</t>
+  </si>
+  <si>
+    <t>Như Ý Nguyễn</t>
+  </si>
+  <si>
+    <t>HD017549</t>
+  </si>
+  <si>
+    <t>4 đào trí phường phú thuận</t>
+  </si>
+  <si>
+    <t>Cindy Nguyễn</t>
+  </si>
+  <si>
+    <t>HD017482</t>
+  </si>
+  <si>
+    <t>12/7 đường P - Khu phố Mỹ Tú 2 - P. Tân Hưng</t>
+  </si>
+  <si>
+    <t>Võ Ngọc Đan Thanh</t>
+  </si>
+  <si>
+    <t>HD017534</t>
+  </si>
+  <si>
+    <t>300 Khuông Việt, phường Phú Trung</t>
+  </si>
+  <si>
+    <t>HD017550</t>
+  </si>
+  <si>
+    <t>HD017199</t>
+  </si>
+  <si>
+    <t>Toà Landmark 2</t>
+  </si>
+  <si>
+    <t>HD017210</t>
+  </si>
+  <si>
+    <t>9 tiên lân 17, bà điểm Phòng 306</t>
+  </si>
+  <si>
+    <t>Chanboramey 015738168</t>
+  </si>
+  <si>
+    <t>HD016946</t>
+  </si>
+  <si>
+    <t>157 nguyễn du</t>
+  </si>
+  <si>
+    <t>thanh (NHẬN HÀNG CHO TRÀ LY)</t>
+  </si>
+  <si>
+    <t>HD017493</t>
+  </si>
+  <si>
+    <t>404 VÕ VĂN TẦN</t>
+  </si>
+  <si>
+    <t>HD017437</t>
+  </si>
+  <si>
+    <t>HD017518</t>
+  </si>
+  <si>
+    <t>212 b/d11 nguyen trai</t>
+  </si>
+  <si>
+    <t>Nguyễn Thu Hoa</t>
+  </si>
+  <si>
+    <t>HD017198</t>
+  </si>
+  <si>
+    <t>190C mai xuân thưởng.p2</t>
+  </si>
+  <si>
+    <t>HD017515</t>
+  </si>
+  <si>
+    <t>Lan Anh Nguyễn</t>
+  </si>
+  <si>
+    <t>HD017489</t>
+  </si>
+  <si>
+    <t>70 đường số 1 KDC nam long</t>
+  </si>
+  <si>
+    <t>smail- huyền trang</t>
+  </si>
+  <si>
+    <t>HD017006</t>
+  </si>
+  <si>
+    <t>124 đường 24b p.bình trị Đông b</t>
+  </si>
+  <si>
+    <t>Minh Nguyễn</t>
+  </si>
+  <si>
+    <t>HD017439</t>
+  </si>
+  <si>
+    <t>175/87/8/4 đường 2 tăng Nhơn Phú b</t>
+  </si>
+  <si>
+    <t>Hoa Hoa</t>
+  </si>
+  <si>
+    <t>HD017317</t>
+  </si>
+  <si>
+    <t>Chung cư topaz elite tạ quang bửu p4 Sảnh Dragon 1B</t>
+  </si>
+  <si>
+    <t>Thuý Stella</t>
+  </si>
+  <si>
+    <t>HD017442</t>
+  </si>
+  <si>
+    <t>68/25 trần quang khải p tân định</t>
+  </si>
+  <si>
+    <t>Tran Kim</t>
+  </si>
+  <si>
+    <t>HD017537</t>
+  </si>
+  <si>
+    <t>77A Đường số 9, p.Khánh hội</t>
+  </si>
+  <si>
+    <t>Chân Chân</t>
+  </si>
+  <si>
+    <t>HD017536</t>
+  </si>
+  <si>
+    <t>69/15 Võ Thị Liễu, An Phú Đông</t>
+  </si>
+  <si>
+    <t>Bé Ty - fb Anh Lan</t>
+  </si>
+  <si>
+    <t>HD017415</t>
+  </si>
+  <si>
+    <t>532/3/6 Kinh Dương Vương, Phường An Lạc</t>
+  </si>
+  <si>
+    <t>Lucia Nguyễn</t>
+  </si>
+  <si>
+    <t>HD017190</t>
+  </si>
+  <si>
+    <t>Block E eco green nguyễn văn linh</t>
+  </si>
+  <si>
+    <t>Chí Đinh</t>
+  </si>
+  <si>
+    <t>HD017543</t>
+  </si>
+  <si>
+    <t>hẻm 191 cống quỳnh, nhà trọ an house</t>
+  </si>
+  <si>
+    <t>Diệu Linh</t>
+  </si>
+  <si>
+    <t>HD017206</t>
+  </si>
+  <si>
+    <t>103 đường số 6, phường Bình Hưng Hòa</t>
+  </si>
+  <si>
+    <t>Minh Hải ( Thanh Phan )</t>
+  </si>
+  <si>
+    <t>HD017443</t>
+  </si>
+  <si>
+    <t>Lê Tố Quyên</t>
+  </si>
+  <si>
+    <t>HD017197</t>
+  </si>
+  <si>
+    <t>149/1 +3 Nơ Trang Long p12</t>
+  </si>
+  <si>
+    <t>_____lay_____</t>
+  </si>
+  <si>
+    <t>HD017179</t>
+  </si>
+  <si>
+    <t>164/22 Vo Thi Sau, D.3</t>
+  </si>
+  <si>
+    <t>Loan Đặng</t>
+  </si>
+  <si>
+    <t>HD017570</t>
+  </si>
+  <si>
+    <t>45 Lê Anh Xuân Bến Thành</t>
+  </si>
+  <si>
+    <t>HD016638</t>
+  </si>
+  <si>
+    <t>Kim Phụng (inst -suicao20_12)</t>
+  </si>
+  <si>
+    <t>HD017491</t>
+  </si>
+  <si>
+    <t>5 Lê Quý Đôn phường Võ Thị Sáu</t>
+  </si>
+  <si>
+    <t>HD017278</t>
+  </si>
+  <si>
+    <t>39 hồ hảo hớn, P. cô giang</t>
+  </si>
+  <si>
+    <t>HD017481</t>
+  </si>
+  <si>
+    <t>Anh Lee</t>
+  </si>
+  <si>
+    <t>HD017305</t>
+  </si>
+  <si>
+    <t>89 lê thị chợ p. phú thuận</t>
+  </si>
+  <si>
+    <t>Thư Mon</t>
+  </si>
+  <si>
+    <t>HD017416</t>
+  </si>
+  <si>
+    <t>Chung cư sài gòn mia, đường 9a, kdc trung sơn, bình hưng</t>
+  </si>
+  <si>
+    <t>HD017205</t>
+  </si>
+  <si>
+    <t>Jemial Vo</t>
+  </si>
+  <si>
+    <t>HD017495</t>
+  </si>
+  <si>
+    <t>438 phan văn trị, p. hạnh thông</t>
+  </si>
+  <si>
+    <t>Trịnh Thảo Như</t>
+  </si>
+  <si>
+    <t>HD017282</t>
+  </si>
+  <si>
+    <t>7a/5/42 thành thái p14</t>
+  </si>
+  <si>
+    <t>Yến Nhi ( chị thảo )</t>
+  </si>
+  <si>
+    <t>HD017513</t>
+  </si>
+  <si>
+    <t>406/8 Cộng Hoà, phường 13</t>
+  </si>
+  <si>
+    <t>An Nghi</t>
+  </si>
+  <si>
+    <t>HD017459</t>
+  </si>
+  <si>
+    <t>007 Lô B, Đường C6, Cc Tây Thạnh, P. Tây Thạnh</t>
+  </si>
+  <si>
+    <t>HD017005</t>
+  </si>
+  <si>
+    <t>Gia Trân fb Hà Võ</t>
+  </si>
+  <si>
+    <t>HD017164</t>
+  </si>
+  <si>
+    <t>73 hoa sữa phường 7 cầu kiệu</t>
+  </si>
+  <si>
+    <t>Nhung SaLin</t>
+  </si>
+  <si>
+    <t>HD017163</t>
+  </si>
+  <si>
+    <t>19a Trần Quang diệu p13</t>
+  </si>
+  <si>
+    <t>HD017297</t>
+  </si>
+  <si>
+    <t>hương</t>
+  </si>
+  <si>
+    <t>HD017535</t>
+  </si>
+  <si>
+    <t>97 đường 24A - bình trị đông B</t>
+  </si>
+  <si>
+    <t>Thúy Linh</t>
+  </si>
+  <si>
+    <t>HD017173</t>
+  </si>
+  <si>
+    <t>132 bến Vân đồn p6</t>
+  </si>
+  <si>
+    <t>Thiên Trang</t>
+  </si>
+  <si>
+    <t>HD017325</t>
+  </si>
+  <si>
+    <t>221 trần bình trọng p2</t>
+  </si>
+  <si>
+    <t>Lương Thúy</t>
+  </si>
+  <si>
+    <t>HD017209</t>
+  </si>
+  <si>
+    <t>549/3 lê văn thọ</t>
+  </si>
+  <si>
+    <t>Keo Kimyou</t>
+  </si>
+  <si>
+    <t>HD017479</t>
+  </si>
+  <si>
+    <t>(HLH express): Tổng kho Sài Gòn 9, Lô G2, Đường K1, KCN Cát Lái</t>
+  </si>
+  <si>
+    <t>Cô Ngọc ( gửi Châu)</t>
+  </si>
+  <si>
+    <t>HD017166</t>
+  </si>
+  <si>
+    <t>481/11 Đoàn Văn Bơ, phường Xóm Chiếu</t>
+  </si>
+  <si>
+    <t>HD017180</t>
+  </si>
+  <si>
+    <t>Hằng</t>
+  </si>
+  <si>
+    <t>HD017480</t>
+  </si>
+  <si>
+    <t>Block A2 Topaz City, số 39 đường Cao Lỗ, P4</t>
+  </si>
+  <si>
+    <t>Natalie Nguyen</t>
+  </si>
+  <si>
+    <t>HD017387</t>
+  </si>
+  <si>
+    <t>239/64 Trần Văn Đang, phường 11</t>
+  </si>
+  <si>
+    <t>Minh Nguyệt + Lin Xiao + Hàng Aỉ</t>
+  </si>
+  <si>
+    <t>HD017572</t>
+  </si>
+  <si>
+    <t>C16-17 lô C1, đường DD5, phường Đông Hưng Thuận</t>
+  </si>
+  <si>
+    <t>016701721-010535777</t>
+  </si>
+  <si>
+    <t>SUMO</t>
+  </si>
+  <si>
+    <t>487 le van sy f12</t>
+  </si>
+  <si>
+    <t>CHỊ MYMY</t>
+  </si>
+  <si>
+    <t>128/25 nguyễn lâm p3</t>
+  </si>
+  <si>
+    <t>at 29-04</t>
   </si>
 </sst>
 </file>
@@ -9627,14 +10064,14 @@
     <xf numFmtId="0" fontId="0" fillId="10" borderId="1" xfId="0" applyFill="1" applyBorder="1"/>
     <xf numFmtId="3" fontId="0" fillId="10" borderId="1" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="10" borderId="0" xfId="0" applyFill="1"/>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="3" fontId="5" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="3" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="0" fillId="3" borderId="0" xfId="0" applyFill="1"/>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="3" fontId="0" fillId="3" borderId="0" xfId="0" applyNumberFormat="1" applyFill="1"/>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="3" fontId="5" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
   </cellXfs>
   <cellStyles count="2">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -10903,10 +11340,10 @@
       <c r="A27" s="1" t="s">
         <v>16</v>
       </c>
-      <c r="C27" s="45" t="s">
+      <c r="C27" s="47" t="s">
         <v>89</v>
       </c>
-      <c r="D27" s="45"/>
+      <c r="D27" s="47"/>
       <c r="E27" s="4" t="s">
         <v>90</v>
       </c>
@@ -10934,11 +11371,11 @@
       <c r="B28" s="3" t="s">
         <v>93</v>
       </c>
-      <c r="C28" s="46">
+      <c r="C28" s="48">
         <f>SUMIFS(I$3:I$23,B$3:B$23,A$27,L$3:L$23,A$28)</f>
         <v>11295</v>
       </c>
-      <c r="D28" s="46"/>
+      <c r="D28" s="48"/>
       <c r="E28" s="3">
         <f>SUMIFS(Q$3:Q$23,B$3:B$23,A$27,L$3:L$23,A$28)</f>
         <v>21</v>
@@ -10969,10 +11406,10 @@
       <c r="B29" s="2" t="s">
         <v>97</v>
       </c>
-      <c r="C29" s="47">
+      <c r="C29" s="49">
         <v>0</v>
       </c>
-      <c r="D29" s="47"/>
+      <c r="D29" s="49"/>
       <c r="K29" t="s">
         <v>98</v>
       </c>
@@ -10996,11 +11433,11 @@
       <c r="B30" s="2" t="s">
         <v>99</v>
       </c>
-      <c r="C30" s="47">
+      <c r="C30" s="49">
         <f>-SUMIFS(I$3:I$23,B$3:B$23,A$27,P$3:P$23,"xx",N$3:N$23,"x")</f>
         <v>0</v>
       </c>
-      <c r="D30" s="47"/>
+      <c r="D30" s="49"/>
       <c r="E30" s="2">
         <f>SUMIFS(Q$3:Q$23,B$3:B$23,A$27,P$3:P$23,"xx",N$3:N$23,"x")</f>
         <v>0</v>
@@ -11020,11 +11457,11 @@
       <c r="B31" s="4" t="s">
         <v>101</v>
       </c>
-      <c r="C31" s="45">
+      <c r="C31" s="47">
         <f>SUBTOTAL(9,C28:C30)</f>
         <v>11295</v>
       </c>
-      <c r="D31" s="45"/>
+      <c r="D31" s="47"/>
       <c r="E31">
         <f>E28</f>
         <v>21</v>
@@ -11044,8 +11481,8 @@
       <c r="B32" s="2" t="s">
         <v>104</v>
       </c>
-      <c r="C32" s="43"/>
-      <c r="D32" s="43"/>
+      <c r="C32" s="45"/>
+      <c r="D32" s="45"/>
       <c r="K32" s="2" t="s">
         <v>105</v>
       </c>
@@ -11061,8 +11498,8 @@
       <c r="B33" s="8" t="s">
         <v>107</v>
       </c>
-      <c r="C33" s="43"/>
-      <c r="D33" s="43"/>
+      <c r="C33" s="45"/>
+      <c r="D33" s="45"/>
       <c r="L33" s="9">
         <f>SUBTOTAL(9,L28:L32)</f>
         <v>7314</v>
@@ -11076,11 +11513,11 @@
       <c r="B35" s="1" t="s">
         <v>108</v>
       </c>
-      <c r="C35" s="44">
+      <c r="C35" s="46">
         <f>C31+C32+C33</f>
         <v>11295</v>
       </c>
-      <c r="D35" s="44"/>
+      <c r="D35" s="46"/>
       <c r="E35" s="1" t="s">
         <v>109</v>
       </c>
@@ -13181,10 +13618,10 @@
       <c r="A47" s="1" t="s">
         <v>16</v>
       </c>
-      <c r="C47" s="45" t="s">
+      <c r="C47" s="47" t="s">
         <v>89</v>
       </c>
-      <c r="D47" s="45"/>
+      <c r="D47" s="47"/>
       <c r="E47" s="4" t="s">
         <v>90</v>
       </c>
@@ -13212,11 +13649,11 @@
       <c r="B48" s="3" t="s">
         <v>93</v>
       </c>
-      <c r="C48" s="46">
+      <c r="C48" s="48">
         <f>SUMIFS(I$3:I$43,B$3:B$43,A$47,L$3:L$43,A$48)</f>
         <v>28800</v>
       </c>
-      <c r="D48" s="46"/>
+      <c r="D48" s="48"/>
       <c r="E48" s="3">
         <f>SUMIFS(Q$3:Q$43,B$3:B$43,A$47,L$3:L$43,A$48)</f>
         <v>41</v>
@@ -13251,10 +13688,10 @@
       <c r="B49" s="2" t="s">
         <v>97</v>
       </c>
-      <c r="C49" s="47">
+      <c r="C49" s="49">
         <v>0</v>
       </c>
-      <c r="D49" s="47"/>
+      <c r="D49" s="49"/>
       <c r="K49" t="s">
         <v>98</v>
       </c>
@@ -13278,11 +13715,11 @@
       <c r="B50" s="2" t="s">
         <v>99</v>
       </c>
-      <c r="C50" s="47">
+      <c r="C50" s="49">
         <f>-SUMIFS(I$3:I$43,B$3:B$43,A$47,P$3:P$43,"xx",N$3:N$43,"x")</f>
         <v>0</v>
       </c>
-      <c r="D50" s="47"/>
+      <c r="D50" s="49"/>
       <c r="E50" s="2">
         <f>SUMIFS(Q$3:Q$43,B$3:B$43,A$47,P$3:P$43,"xx",N$3:N$43,"x")</f>
         <v>0</v>
@@ -13310,11 +13747,11 @@
       <c r="B51" s="4" t="s">
         <v>101</v>
       </c>
-      <c r="C51" s="45">
+      <c r="C51" s="47">
         <f>SUBTOTAL(9,C48:C50)</f>
         <v>28800</v>
       </c>
-      <c r="D51" s="45"/>
+      <c r="D51" s="47"/>
       <c r="E51">
         <f>E48</f>
         <v>41</v>
@@ -13334,8 +13771,8 @@
       <c r="B52" s="2" t="s">
         <v>104</v>
       </c>
-      <c r="C52" s="43"/>
-      <c r="D52" s="43"/>
+      <c r="C52" s="45"/>
+      <c r="D52" s="45"/>
       <c r="K52" s="2" t="s">
         <v>105</v>
       </c>
@@ -13351,8 +13788,8 @@
       <c r="B53" s="8" t="s">
         <v>107</v>
       </c>
-      <c r="C53" s="43"/>
-      <c r="D53" s="43"/>
+      <c r="C53" s="45"/>
+      <c r="D53" s="45"/>
       <c r="L53" s="9">
         <f>SUBTOTAL(9,L48:L52)</f>
         <v>3498</v>
@@ -13373,11 +13810,11 @@
       <c r="B55" s="1" t="s">
         <v>108</v>
       </c>
-      <c r="C55" s="44">
+      <c r="C55" s="46">
         <f>C51+C52+C53</f>
         <v>28800</v>
       </c>
-      <c r="D55" s="44"/>
+      <c r="D55" s="46"/>
       <c r="E55" s="1" t="s">
         <v>109</v>
       </c>
@@ -16562,10 +16999,10 @@
       <c r="A70" s="1" t="s">
         <v>16</v>
       </c>
-      <c r="C70" s="45" t="s">
+      <c r="C70" s="47" t="s">
         <v>89</v>
       </c>
-      <c r="D70" s="45"/>
+      <c r="D70" s="47"/>
       <c r="E70" s="4" t="s">
         <v>90</v>
       </c>
@@ -16593,11 +17030,11 @@
       <c r="B71" s="3" t="s">
         <v>93</v>
       </c>
-      <c r="C71" s="46">
+      <c r="C71" s="48">
         <f>SUMIFS(I$3:I$66,B$3:B$66,A$70,L$3:L$66,A$71)</f>
         <v>40275</v>
       </c>
-      <c r="D71" s="46"/>
+      <c r="D71" s="48"/>
       <c r="E71" s="3">
         <f>SUMIFS(Q$3:Q$66,B$3:B$66,A$70,L$3:L$66,A$71)</f>
         <v>63</v>
@@ -16632,10 +17069,10 @@
       <c r="B72" s="2" t="s">
         <v>97</v>
       </c>
-      <c r="C72" s="47">
+      <c r="C72" s="49">
         <v>0</v>
       </c>
-      <c r="D72" s="47"/>
+      <c r="D72" s="49"/>
       <c r="K72" t="s">
         <v>98</v>
       </c>
@@ -16659,11 +17096,11 @@
       <c r="B73" s="2" t="s">
         <v>99</v>
       </c>
-      <c r="C73" s="47">
+      <c r="C73" s="49">
         <f>-SUMIFS(I$3:I$66,B$3:B$66,A$70,P$3:P$66,"xx",N$3:N$66,"x")</f>
         <v>-790</v>
       </c>
-      <c r="D73" s="47"/>
+      <c r="D73" s="49"/>
       <c r="E73" s="2">
         <f>SUMIFS(Q$3:Q$66,B$3:B$66,A$70,P$3:P$66,"xx",N$3:N$66,"x")</f>
         <v>1</v>
@@ -16683,11 +17120,11 @@
       <c r="B74" s="4" t="s">
         <v>101</v>
       </c>
-      <c r="C74" s="45">
+      <c r="C74" s="47">
         <f>SUBTOTAL(9,C71:C73)</f>
         <v>39485</v>
       </c>
-      <c r="D74" s="45"/>
+      <c r="D74" s="47"/>
       <c r="E74">
         <f>E71</f>
         <v>63</v>
@@ -16707,8 +17144,8 @@
       <c r="B75" s="2" t="s">
         <v>104</v>
       </c>
-      <c r="C75" s="43"/>
-      <c r="D75" s="43"/>
+      <c r="C75" s="45"/>
+      <c r="D75" s="45"/>
       <c r="K75" s="2" t="s">
         <v>105</v>
       </c>
@@ -16724,8 +17161,8 @@
       <c r="B76" s="8" t="s">
         <v>107</v>
       </c>
-      <c r="C76" s="43"/>
-      <c r="D76" s="43"/>
+      <c r="C76" s="45"/>
+      <c r="D76" s="45"/>
       <c r="L76" s="9">
         <f>SUBTOTAL(9,L71:L75)</f>
         <v>15833</v>
@@ -16754,11 +17191,11 @@
       <c r="B78" s="1" t="s">
         <v>108</v>
       </c>
-      <c r="C78" s="44">
+      <c r="C78" s="46">
         <f>C74+C75+C76</f>
         <v>39485</v>
       </c>
-      <c r="D78" s="44"/>
+      <c r="D78" s="46"/>
       <c r="E78" s="1" t="s">
         <v>109</v>
       </c>
@@ -18210,10 +18647,10 @@
       <c r="A30" s="1" t="s">
         <v>16</v>
       </c>
-      <c r="C30" s="45" t="s">
+      <c r="C30" s="47" t="s">
         <v>89</v>
       </c>
-      <c r="D30" s="45"/>
+      <c r="D30" s="47"/>
       <c r="E30" s="4" t="s">
         <v>90</v>
       </c>
@@ -18241,11 +18678,11 @@
       <c r="B31" s="3" t="s">
         <v>93</v>
       </c>
-      <c r="C31" s="46">
+      <c r="C31" s="48">
         <f>SUMIFS(I$3:I$26,B$3:B$26,A$30,L$3:L$26,A$31)</f>
         <v>10860</v>
       </c>
-      <c r="D31" s="46"/>
+      <c r="D31" s="48"/>
       <c r="E31" s="3">
         <f>SUMIFS(Q$3:Q$26,B$3:B$26,A$30,L$3:L$26,A$31)</f>
         <v>20</v>
@@ -18280,10 +18717,10 @@
       <c r="B32" s="2" t="s">
         <v>97</v>
       </c>
-      <c r="C32" s="47">
+      <c r="C32" s="49">
         <v>0</v>
       </c>
-      <c r="D32" s="47"/>
+      <c r="D32" s="49"/>
       <c r="K32" t="s">
         <v>98</v>
       </c>
@@ -18307,11 +18744,11 @@
       <c r="B33" s="2" t="s">
         <v>99</v>
       </c>
-      <c r="C33" s="47">
+      <c r="C33" s="49">
         <f>-SUMIFS(I$3:I$26,B$3:B$26,A$30,P$3:P$26,"xx",N$3:N$26,"x")</f>
         <v>-2910</v>
       </c>
-      <c r="D33" s="47"/>
+      <c r="D33" s="49"/>
       <c r="E33" s="2">
         <f>SUMIFS(Q$3:Q$26,B$3:B$26,A$30,P$3:P$26,"xx",N$3:N$26,"x")</f>
         <v>4</v>
@@ -18331,11 +18768,11 @@
       <c r="B34" s="4" t="s">
         <v>101</v>
       </c>
-      <c r="C34" s="45">
+      <c r="C34" s="47">
         <f>SUBTOTAL(9,C31:C33)</f>
         <v>7950</v>
       </c>
-      <c r="D34" s="45"/>
+      <c r="D34" s="47"/>
       <c r="E34">
         <f>E31</f>
         <v>20</v>
@@ -18361,8 +18798,8 @@
       <c r="B35" s="2" t="s">
         <v>104</v>
       </c>
-      <c r="C35" s="43"/>
-      <c r="D35" s="43"/>
+      <c r="C35" s="45"/>
+      <c r="D35" s="45"/>
       <c r="K35" s="2" t="s">
         <v>105</v>
       </c>
@@ -18378,8 +18815,8 @@
       <c r="B36" s="8" t="s">
         <v>107</v>
       </c>
-      <c r="C36" s="43"/>
-      <c r="D36" s="43"/>
+      <c r="C36" s="45"/>
+      <c r="D36" s="45"/>
       <c r="L36" s="9">
         <f>SUBTOTAL(9,L31:L35)</f>
         <v>-328</v>
@@ -18400,11 +18837,11 @@
       <c r="B38" s="1" t="s">
         <v>108</v>
       </c>
-      <c r="C38" s="44">
+      <c r="C38" s="46">
         <f>C34+C35+C36</f>
         <v>7950</v>
       </c>
-      <c r="D38" s="44"/>
+      <c r="D38" s="46"/>
       <c r="E38" s="1" t="s">
         <v>109</v>
       </c>
@@ -20215,10 +20652,10 @@
       <c r="A39" s="1" t="s">
         <v>16</v>
       </c>
-      <c r="C39" s="45" t="s">
+      <c r="C39" s="47" t="s">
         <v>89</v>
       </c>
-      <c r="D39" s="45"/>
+      <c r="D39" s="47"/>
       <c r="E39" s="4" t="s">
         <v>90</v>
       </c>
@@ -20246,11 +20683,11 @@
       <c r="B40" s="3" t="s">
         <v>93</v>
       </c>
-      <c r="C40" s="46">
+      <c r="C40" s="48">
         <f>SUMIFS(I$3:I$35,B$3:B$35,A$39,L$3:L$35,A$40)</f>
         <v>22860</v>
       </c>
-      <c r="D40" s="46"/>
+      <c r="D40" s="48"/>
       <c r="E40" s="3">
         <f>SUMIFS(Q$3:Q$35,B$3:B$35,A$39,L$3:L$35,A$40)</f>
         <v>32</v>
@@ -20285,10 +20722,10 @@
       <c r="B41" s="2" t="s">
         <v>97</v>
       </c>
-      <c r="C41" s="47">
+      <c r="C41" s="49">
         <v>0</v>
       </c>
-      <c r="D41" s="47"/>
+      <c r="D41" s="49"/>
       <c r="K41" t="s">
         <v>98</v>
       </c>
@@ -20312,11 +20749,11 @@
       <c r="B42" s="2" t="s">
         <v>99</v>
       </c>
-      <c r="C42" s="47">
+      <c r="C42" s="49">
         <f>-SUMIFS(I$3:I$35,B$3:B$35,A$39,P$3:P$35,"xx",N$3:N$35,"x")</f>
         <v>-870</v>
       </c>
-      <c r="D42" s="47"/>
+      <c r="D42" s="49"/>
       <c r="E42" s="2">
         <f>SUMIFS(Q$3:Q$35,B$3:B$35,A$39,P$3:P$35,"xx",N$3:N$35,"x")</f>
         <v>1</v>
@@ -20336,11 +20773,11 @@
       <c r="B43" s="4" t="s">
         <v>101</v>
       </c>
-      <c r="C43" s="45">
+      <c r="C43" s="47">
         <f>SUBTOTAL(9,C40:C42)</f>
         <v>21990</v>
       </c>
-      <c r="D43" s="45"/>
+      <c r="D43" s="47"/>
       <c r="E43">
         <f>E40</f>
         <v>32</v>
@@ -20360,8 +20797,8 @@
       <c r="B44" s="2" t="s">
         <v>104</v>
       </c>
-      <c r="C44" s="43"/>
-      <c r="D44" s="43"/>
+      <c r="C44" s="45"/>
+      <c r="D44" s="45"/>
       <c r="K44" s="2" t="s">
         <v>105</v>
       </c>
@@ -20377,8 +20814,8 @@
       <c r="B45" s="8" t="s">
         <v>107</v>
       </c>
-      <c r="C45" s="43"/>
-      <c r="D45" s="43"/>
+      <c r="C45" s="45"/>
+      <c r="D45" s="45"/>
       <c r="L45" s="9">
         <f>SUBTOTAL(9,L40:L44)</f>
         <v>5050</v>
@@ -20399,11 +20836,11 @@
       <c r="B47" s="1" t="s">
         <v>108</v>
       </c>
-      <c r="C47" s="44">
+      <c r="C47" s="46">
         <f>C43+C44+C45</f>
         <v>21990</v>
       </c>
-      <c r="D47" s="44"/>
+      <c r="D47" s="46"/>
       <c r="E47" s="1" t="s">
         <v>109</v>
       </c>
@@ -22979,10 +23416,10 @@
       <c r="A56" s="1" t="s">
         <v>16</v>
       </c>
-      <c r="C56" s="45" t="s">
+      <c r="C56" s="47" t="s">
         <v>89</v>
       </c>
-      <c r="D56" s="45"/>
+      <c r="D56" s="47"/>
       <c r="E56" s="4" t="s">
         <v>90</v>
       </c>
@@ -23010,11 +23447,11 @@
       <c r="B57" s="3" t="s">
         <v>93</v>
       </c>
-      <c r="C57" s="46">
+      <c r="C57" s="48">
         <f>SUMIFS(I$3:I$52,B$3:B$52,A$56,L$3:L$52,A$57)</f>
         <v>28155</v>
       </c>
-      <c r="D57" s="46"/>
+      <c r="D57" s="48"/>
       <c r="E57" s="3">
         <f>SUMIFS(Q$3:Q$52,B$3:B$52,A$56,L$3:L$52,A$57)</f>
         <v>49</v>
@@ -23045,10 +23482,10 @@
       <c r="B58" s="2" t="s">
         <v>97</v>
       </c>
-      <c r="C58" s="47">
+      <c r="C58" s="49">
         <v>0</v>
       </c>
-      <c r="D58" s="47"/>
+      <c r="D58" s="49"/>
       <c r="K58" t="s">
         <v>98</v>
       </c>
@@ -23072,11 +23509,11 @@
       <c r="B59" s="2" t="s">
         <v>99</v>
       </c>
-      <c r="C59" s="47">
+      <c r="C59" s="49">
         <f>-SUMIFS(I$3:I$52,B$3:B$52,A$56,P$3:P$52,"xx",N$3:N$52,"x")</f>
         <v>-3155</v>
       </c>
-      <c r="D59" s="47"/>
+      <c r="D59" s="49"/>
       <c r="E59" s="2">
         <f>SUMIFS(Q$3:Q$52,B$3:B$52,A$56,P$3:P$52,"xx",N$3:N$52,"x")</f>
         <v>2</v>
@@ -23096,11 +23533,11 @@
       <c r="B60" s="4" t="s">
         <v>101</v>
       </c>
-      <c r="C60" s="45">
+      <c r="C60" s="47">
         <f>SUBTOTAL(9,C57:C59)</f>
         <v>25000</v>
       </c>
-      <c r="D60" s="45"/>
+      <c r="D60" s="47"/>
       <c r="E60">
         <f>E57</f>
         <v>49</v>
@@ -23120,8 +23557,8 @@
       <c r="B61" s="2" t="s">
         <v>104</v>
       </c>
-      <c r="C61" s="43"/>
-      <c r="D61" s="43"/>
+      <c r="C61" s="45"/>
+      <c r="D61" s="45"/>
       <c r="K61" s="2" t="s">
         <v>105</v>
       </c>
@@ -23137,8 +23574,8 @@
       <c r="B62" s="8" t="s">
         <v>107</v>
       </c>
-      <c r="C62" s="43"/>
-      <c r="D62" s="43"/>
+      <c r="C62" s="45"/>
+      <c r="D62" s="45"/>
       <c r="L62" s="9">
         <f>SUBTOTAL(9,L57:L61)</f>
         <v>7146</v>
@@ -23159,11 +23596,11 @@
       <c r="B64" s="1" t="s">
         <v>108</v>
       </c>
-      <c r="C64" s="44">
+      <c r="C64" s="46">
         <f>C60+C61+C62</f>
         <v>25000</v>
       </c>
-      <c r="D64" s="44"/>
+      <c r="D64" s="46"/>
       <c r="E64" s="1" t="s">
         <v>109</v>
       </c>
@@ -25772,10 +26209,10 @@
       <c r="A57" s="1" t="s">
         <v>16</v>
       </c>
-      <c r="C57" s="45" t="s">
+      <c r="C57" s="47" t="s">
         <v>89</v>
       </c>
-      <c r="D57" s="45"/>
+      <c r="D57" s="47"/>
       <c r="E57" s="4" t="s">
         <v>90</v>
       </c>
@@ -25803,11 +26240,11 @@
       <c r="B58" s="3" t="s">
         <v>93</v>
       </c>
-      <c r="C58" s="46">
+      <c r="C58" s="48">
         <f>SUMIFS(I$3:I$53,B$3:B$53,A$57,L$3:L$53,A$58)</f>
         <v>30480</v>
       </c>
-      <c r="D58" s="46"/>
+      <c r="D58" s="48"/>
       <c r="E58" s="3">
         <f>SUMIFS(Q$3:Q$53,B$3:B$53,A$57,L$3:L$53,A$58)</f>
         <v>51</v>
@@ -25842,10 +26279,10 @@
       <c r="B59" s="2" t="s">
         <v>97</v>
       </c>
-      <c r="C59" s="47">
+      <c r="C59" s="49">
         <v>0</v>
       </c>
-      <c r="D59" s="47"/>
+      <c r="D59" s="49"/>
       <c r="K59" t="s">
         <v>98</v>
       </c>
@@ -25869,11 +26306,11 @@
       <c r="B60" s="2" t="s">
         <v>99</v>
       </c>
-      <c r="C60" s="47">
+      <c r="C60" s="49">
         <f>-SUMIFS(I$3:I$53,B$3:B$53,A$57,P$3:P$53,"xx",N$3:N$53,"x")</f>
         <v>0</v>
       </c>
-      <c r="D60" s="47"/>
+      <c r="D60" s="49"/>
       <c r="E60" s="2">
         <f>SUMIFS(Q$3:Q$53,B$3:B$53,A$57,P$3:P$53,"xx",N$3:N$53,"x")</f>
         <v>0</v>
@@ -25893,11 +26330,11 @@
       <c r="B61" s="4" t="s">
         <v>101</v>
       </c>
-      <c r="C61" s="45">
+      <c r="C61" s="47">
         <f>SUBTOTAL(9,C58:C60)</f>
         <v>30480</v>
       </c>
-      <c r="D61" s="45"/>
+      <c r="D61" s="47"/>
       <c r="E61">
         <f>E58</f>
         <v>51</v>
@@ -25917,8 +26354,8 @@
       <c r="B62" s="2" t="s">
         <v>104</v>
       </c>
-      <c r="C62" s="43"/>
-      <c r="D62" s="43"/>
+      <c r="C62" s="45"/>
+      <c r="D62" s="45"/>
       <c r="K62" s="2" t="s">
         <v>105</v>
       </c>
@@ -25934,8 +26371,8 @@
       <c r="B63" s="8" t="s">
         <v>107</v>
       </c>
-      <c r="C63" s="43"/>
-      <c r="D63" s="43"/>
+      <c r="C63" s="45"/>
+      <c r="D63" s="45"/>
       <c r="L63" s="9">
         <f>SUBTOTAL(9,L58:L62)</f>
         <v>13705</v>
@@ -25956,11 +26393,11 @@
       <c r="B65" s="1" t="s">
         <v>108</v>
       </c>
-      <c r="C65" s="44">
+      <c r="C65" s="46">
         <f>C61+C62+C63</f>
         <v>30480</v>
       </c>
-      <c r="D65" s="44"/>
+      <c r="D65" s="46"/>
       <c r="E65" s="1" t="s">
         <v>109</v>
       </c>
@@ -27928,10 +28365,10 @@
       <c r="A42" s="1" t="s">
         <v>16</v>
       </c>
-      <c r="C42" s="45" t="s">
+      <c r="C42" s="47" t="s">
         <v>89</v>
       </c>
-      <c r="D42" s="45"/>
+      <c r="D42" s="47"/>
       <c r="E42" s="4" t="s">
         <v>90</v>
       </c>
@@ -27959,11 +28396,11 @@
       <c r="B43" s="3" t="s">
         <v>93</v>
       </c>
-      <c r="C43" s="46">
+      <c r="C43" s="48">
         <f>SUMIFS(I$3:I$38,B$3:B$38,A$42,L$3:L$38,A$43)</f>
         <v>16055</v>
       </c>
-      <c r="D43" s="46"/>
+      <c r="D43" s="48"/>
       <c r="E43" s="3">
         <f>SUMIFS(Q$3:Q$38,B$3:B$38,A$42,L$3:L$38,A$43)</f>
         <v>33</v>
@@ -27994,10 +28431,10 @@
       <c r="B44" s="2" t="s">
         <v>97</v>
       </c>
-      <c r="C44" s="47">
+      <c r="C44" s="49">
         <v>0</v>
       </c>
-      <c r="D44" s="47"/>
+      <c r="D44" s="49"/>
       <c r="K44" t="s">
         <v>98</v>
       </c>
@@ -28021,11 +28458,11 @@
       <c r="B45" s="2" t="s">
         <v>99</v>
       </c>
-      <c r="C45" s="47">
+      <c r="C45" s="49">
         <f>-SUMIFS(I$3:I$38,B$3:B$38,A$42,P$3:P$38,"xx",N$3:N$38,"x")</f>
         <v>-3310</v>
       </c>
-      <c r="D45" s="47"/>
+      <c r="D45" s="49"/>
       <c r="E45" s="2">
         <f>SUMIFS(Q$3:Q$38,B$3:B$38,A$42,P$3:P$38,"xx",N$3:N$38,"x")</f>
         <v>4</v>
@@ -28045,11 +28482,11 @@
       <c r="B46" s="4" t="s">
         <v>101</v>
       </c>
-      <c r="C46" s="45">
+      <c r="C46" s="47">
         <f>SUBTOTAL(9,C43:C45)</f>
         <v>12745</v>
       </c>
-      <c r="D46" s="45"/>
+      <c r="D46" s="47"/>
       <c r="E46">
         <f>E43</f>
         <v>33</v>
@@ -28069,8 +28506,8 @@
       <c r="B47" s="2" t="s">
         <v>104</v>
       </c>
-      <c r="C47" s="43"/>
-      <c r="D47" s="43"/>
+      <c r="C47" s="45"/>
+      <c r="D47" s="45"/>
       <c r="K47" s="2" t="s">
         <v>105</v>
       </c>
@@ -28092,8 +28529,8 @@
       <c r="B48" s="8" t="s">
         <v>107</v>
       </c>
-      <c r="C48" s="43"/>
-      <c r="D48" s="43"/>
+      <c r="C48" s="45"/>
+      <c r="D48" s="45"/>
       <c r="L48" s="9">
         <f>SUBTOTAL(9,L43:L47)</f>
         <v>840</v>
@@ -28114,11 +28551,11 @@
       <c r="B50" s="1" t="s">
         <v>108</v>
       </c>
-      <c r="C50" s="44">
+      <c r="C50" s="46">
         <f>C46+C47+C48</f>
         <v>12745</v>
       </c>
-      <c r="D50" s="44"/>
+      <c r="D50" s="46"/>
       <c r="E50" s="1" t="s">
         <v>109</v>
       </c>
@@ -32693,10 +33130,10 @@
       <c r="A101" s="1" t="s">
         <v>16</v>
       </c>
-      <c r="C101" s="45" t="s">
+      <c r="C101" s="47" t="s">
         <v>89</v>
       </c>
-      <c r="D101" s="45"/>
+      <c r="D101" s="47"/>
       <c r="E101" s="4" t="s">
         <v>90</v>
       </c>
@@ -32724,11 +33161,11 @@
       <c r="B102" s="3" t="s">
         <v>93</v>
       </c>
-      <c r="C102" s="46">
+      <c r="C102" s="48">
         <f>SUMIFS(I$3:I$97,B$3:B$97,A$101,L$3:L$97,A$102)</f>
         <v>56435</v>
       </c>
-      <c r="D102" s="46"/>
+      <c r="D102" s="48"/>
       <c r="E102" s="3">
         <f>SUMIFS(Q$3:Q$97,B$3:B$97,A$101,L$3:L$97,A$102)</f>
         <v>95</v>
@@ -32763,10 +33200,10 @@
       <c r="B103" s="2" t="s">
         <v>97</v>
       </c>
-      <c r="C103" s="47">
+      <c r="C103" s="49">
         <v>0</v>
       </c>
-      <c r="D103" s="47"/>
+      <c r="D103" s="49"/>
       <c r="K103" t="s">
         <v>98</v>
       </c>
@@ -32790,11 +33227,11 @@
       <c r="B104" s="2" t="s">
         <v>99</v>
       </c>
-      <c r="C104" s="47">
+      <c r="C104" s="49">
         <f>-SUMIFS(I$3:I$97,B$3:B$97,A$101,P$3:P$97,"xx",N$3:N$97,"x")</f>
         <v>-2780</v>
       </c>
-      <c r="D104" s="47"/>
+      <c r="D104" s="49"/>
       <c r="E104" s="2">
         <f>SUMIFS(Q$3:Q$97,B$3:B$97,A$101,P$3:P$97,"xx",N$3:N$97,"x")</f>
         <v>3</v>
@@ -32814,11 +33251,11 @@
       <c r="B105" s="4" t="s">
         <v>101</v>
       </c>
-      <c r="C105" s="45">
+      <c r="C105" s="47">
         <f>SUBTOTAL(9,C102:C104)</f>
         <v>53655</v>
       </c>
-      <c r="D105" s="45"/>
+      <c r="D105" s="47"/>
       <c r="E105">
         <f>E102</f>
         <v>95</v>
@@ -32838,8 +33275,8 @@
       <c r="B106" s="2" t="s">
         <v>104</v>
       </c>
-      <c r="C106" s="43"/>
-      <c r="D106" s="43"/>
+      <c r="C106" s="45"/>
+      <c r="D106" s="45"/>
       <c r="K106" s="2" t="s">
         <v>105</v>
       </c>
@@ -32855,8 +33292,8 @@
       <c r="B107" s="8" t="s">
         <v>107</v>
       </c>
-      <c r="C107" s="43"/>
-      <c r="D107" s="43"/>
+      <c r="C107" s="45"/>
+      <c r="D107" s="45"/>
       <c r="L107" s="9">
         <f>SUBTOTAL(9,L102:L106)</f>
         <v>8245</v>
@@ -32877,11 +33314,11 @@
       <c r="B109" s="1" t="s">
         <v>108</v>
       </c>
-      <c r="C109" s="44">
+      <c r="C109" s="46">
         <f>C105+C106+C107</f>
         <v>53655</v>
       </c>
-      <c r="D109" s="44"/>
+      <c r="D109" s="46"/>
       <c r="E109" s="1" t="s">
         <v>109</v>
       </c>
@@ -36010,10 +36447,10 @@
       <c r="A68" s="1" t="s">
         <v>16</v>
       </c>
-      <c r="C68" s="45" t="s">
+      <c r="C68" s="47" t="s">
         <v>89</v>
       </c>
-      <c r="D68" s="45"/>
+      <c r="D68" s="47"/>
       <c r="E68" s="4" t="s">
         <v>90</v>
       </c>
@@ -36041,11 +36478,11 @@
       <c r="B69" s="3" t="s">
         <v>93</v>
       </c>
-      <c r="C69" s="46">
+      <c r="C69" s="48">
         <f>SUMIFS(I$3:I$64,B$3:B$64,A$68,L$3:L$64,A$69)</f>
         <v>47670</v>
       </c>
-      <c r="D69" s="46"/>
+      <c r="D69" s="48"/>
       <c r="E69" s="3">
         <f>SUMIFS(Q$3:Q$64,B$3:B$64,A$68,L$3:L$64,A$69)</f>
         <v>58</v>
@@ -36080,10 +36517,10 @@
       <c r="B70" s="2" t="s">
         <v>97</v>
       </c>
-      <c r="C70" s="47">
+      <c r="C70" s="49">
         <v>0</v>
       </c>
-      <c r="D70" s="47"/>
+      <c r="D70" s="49"/>
       <c r="K70" t="s">
         <v>98</v>
       </c>
@@ -36107,11 +36544,11 @@
       <c r="B71" s="2" t="s">
         <v>99</v>
       </c>
-      <c r="C71" s="47">
+      <c r="C71" s="49">
         <f>-SUMIFS(I$3:I$64,B$3:B$64,A$68,P$3:P$64,"xx",N$3:N$64,"x")</f>
         <v>-5360</v>
       </c>
-      <c r="D71" s="47"/>
+      <c r="D71" s="49"/>
       <c r="E71" s="2">
         <f>SUMIFS(Q$3:Q$64,B$3:B$64,A$68,P$3:P$64,"xx",N$3:N$64,"x")</f>
         <v>5</v>
@@ -36131,11 +36568,11 @@
       <c r="B72" s="4" t="s">
         <v>101</v>
       </c>
-      <c r="C72" s="45">
+      <c r="C72" s="47">
         <f>SUBTOTAL(9,C69:C71)</f>
         <v>42310</v>
       </c>
-      <c r="D72" s="45"/>
+      <c r="D72" s="47"/>
       <c r="E72">
         <f>E69</f>
         <v>58</v>
@@ -36155,8 +36592,8 @@
       <c r="B73" s="2" t="s">
         <v>104</v>
       </c>
-      <c r="C73" s="43"/>
-      <c r="D73" s="43"/>
+      <c r="C73" s="45"/>
+      <c r="D73" s="45"/>
       <c r="K73" s="2" t="s">
         <v>105</v>
       </c>
@@ -36172,8 +36609,8 @@
       <c r="B74" s="8" t="s">
         <v>107</v>
       </c>
-      <c r="C74" s="43"/>
-      <c r="D74" s="43"/>
+      <c r="C74" s="45"/>
+      <c r="D74" s="45"/>
       <c r="L74" s="9">
         <f>SUBTOTAL(9,L69:L73)</f>
         <v>6850</v>
@@ -36194,11 +36631,11 @@
       <c r="B76" s="1" t="s">
         <v>108</v>
       </c>
-      <c r="C76" s="44">
+      <c r="C76" s="46">
         <f>C72+C73+C74</f>
         <v>42310</v>
       </c>
-      <c r="D76" s="44"/>
+      <c r="D76" s="46"/>
       <c r="E76" s="1" t="s">
         <v>109</v>
       </c>
@@ -38951,10 +39388,10 @@
       <c r="A60" s="1" t="s">
         <v>16</v>
       </c>
-      <c r="C60" s="45" t="s">
+      <c r="C60" s="47" t="s">
         <v>89</v>
       </c>
-      <c r="D60" s="45"/>
+      <c r="D60" s="47"/>
       <c r="E60" s="4" t="s">
         <v>90</v>
       </c>
@@ -38982,11 +39419,11 @@
       <c r="B61" s="3" t="s">
         <v>93</v>
       </c>
-      <c r="C61" s="46">
+      <c r="C61" s="48">
         <f>SUMIFS(I$3:I$56,B$3:B$56,A$60,L$3:L$56,A$61)</f>
         <v>50515</v>
       </c>
-      <c r="D61" s="46"/>
+      <c r="D61" s="48"/>
       <c r="E61" s="3">
         <f>SUMIFS(Q$3:Q$56,B$3:B$56,A$60,L$3:L$56,A$61)</f>
         <v>54</v>
@@ -39021,10 +39458,10 @@
       <c r="B62" s="2" t="s">
         <v>97</v>
       </c>
-      <c r="C62" s="47">
+      <c r="C62" s="49">
         <v>0</v>
       </c>
-      <c r="D62" s="47"/>
+      <c r="D62" s="49"/>
       <c r="K62" t="s">
         <v>98</v>
       </c>
@@ -39048,11 +39485,11 @@
       <c r="B63" s="2" t="s">
         <v>99</v>
       </c>
-      <c r="C63" s="47">
+      <c r="C63" s="49">
         <f>-SUMIFS(I$3:I$56,B$3:B$56,A$60,P$3:P$56,"xx",N$3:N$56,"x")</f>
         <v>0</v>
       </c>
-      <c r="D63" s="47"/>
+      <c r="D63" s="49"/>
       <c r="E63" s="2">
         <f>SUMIFS(Q$3:Q$56,B$3:B$56,A$60,P$3:P$56,"xx",N$3:N$56,"x")</f>
         <v>0</v>
@@ -39080,11 +39517,11 @@
       <c r="B64" s="4" t="s">
         <v>101</v>
       </c>
-      <c r="C64" s="45">
+      <c r="C64" s="47">
         <f>SUBTOTAL(9,C61:C63)</f>
         <v>50515</v>
       </c>
-      <c r="D64" s="45"/>
+      <c r="D64" s="47"/>
       <c r="E64">
         <f>E61</f>
         <v>54</v>
@@ -39104,8 +39541,8 @@
       <c r="B65" s="2" t="s">
         <v>104</v>
       </c>
-      <c r="C65" s="43"/>
-      <c r="D65" s="43"/>
+      <c r="C65" s="45"/>
+      <c r="D65" s="45"/>
       <c r="I65">
         <v>33514</v>
       </c>
@@ -39124,8 +39561,8 @@
       <c r="B66" s="8" t="s">
         <v>107</v>
       </c>
-      <c r="C66" s="43"/>
-      <c r="D66" s="43"/>
+      <c r="C66" s="45"/>
+      <c r="D66" s="45"/>
       <c r="I66">
         <v>33379</v>
       </c>
@@ -39158,11 +39595,11 @@
       <c r="B68" s="1" t="s">
         <v>108</v>
       </c>
-      <c r="C68" s="44">
+      <c r="C68" s="46">
         <f>C64+C65+C66</f>
         <v>50515</v>
       </c>
-      <c r="D68" s="44"/>
+      <c r="D68" s="46"/>
       <c r="E68" s="1" t="s">
         <v>109</v>
       </c>
@@ -40371,10 +40808,10 @@
       <c r="A28" s="1" t="s">
         <v>16</v>
       </c>
-      <c r="C28" s="45" t="s">
+      <c r="C28" s="47" t="s">
         <v>89</v>
       </c>
-      <c r="D28" s="45"/>
+      <c r="D28" s="47"/>
       <c r="E28" s="4" t="s">
         <v>90</v>
       </c>
@@ -40402,11 +40839,11 @@
       <c r="B29" s="3" t="s">
         <v>93</v>
       </c>
-      <c r="C29" s="46">
+      <c r="C29" s="48">
         <f>SUMIFS(I$3:I$24,B$3:B$24,A$28,L$3:L$24,A$29)</f>
         <v>7205</v>
       </c>
-      <c r="D29" s="46"/>
+      <c r="D29" s="48"/>
       <c r="E29" s="3">
         <f>SUMIFS(Q$3:Q$24,B$3:B$24,A$28,L$3:L$24,A$29)</f>
         <v>22</v>
@@ -40441,10 +40878,10 @@
       <c r="B30" s="2" t="s">
         <v>97</v>
       </c>
-      <c r="C30" s="47">
+      <c r="C30" s="49">
         <v>0</v>
       </c>
-      <c r="D30" s="47"/>
+      <c r="D30" s="49"/>
       <c r="K30" t="s">
         <v>98</v>
       </c>
@@ -40468,11 +40905,11 @@
       <c r="B31" s="2" t="s">
         <v>99</v>
       </c>
-      <c r="C31" s="47">
+      <c r="C31" s="49">
         <f>-SUMIFS(I$3:I$24,B$3:B$24,A$28,P$3:P$24,"xx",N$3:N$24,"x")</f>
         <v>0</v>
       </c>
-      <c r="D31" s="47"/>
+      <c r="D31" s="49"/>
       <c r="E31" s="2">
         <f>SUMIFS(Q$3:Q$24,B$3:B$24,A$28,P$3:P$24,"xx",N$3:N$24,"x")</f>
         <v>0</v>
@@ -40500,11 +40937,11 @@
       <c r="B32" s="4" t="s">
         <v>101</v>
       </c>
-      <c r="C32" s="45">
+      <c r="C32" s="47">
         <f>SUBTOTAL(9,C29:C31)</f>
         <v>7205</v>
       </c>
-      <c r="D32" s="45"/>
+      <c r="D32" s="47"/>
       <c r="E32">
         <f>E29</f>
         <v>22</v>
@@ -40524,8 +40961,8 @@
       <c r="B33" s="2" t="s">
         <v>104</v>
       </c>
-      <c r="C33" s="43"/>
-      <c r="D33" s="43"/>
+      <c r="C33" s="45"/>
+      <c r="D33" s="45"/>
       <c r="K33" s="2" t="s">
         <v>105</v>
       </c>
@@ -40541,8 +40978,8 @@
       <c r="B34" s="8" t="s">
         <v>107</v>
       </c>
-      <c r="C34" s="43"/>
-      <c r="D34" s="43"/>
+      <c r="C34" s="45"/>
+      <c r="D34" s="45"/>
       <c r="L34" s="9">
         <f>SUBTOTAL(9,L29:L33)</f>
         <v>2296</v>
@@ -40556,11 +40993,11 @@
       <c r="B36" s="1" t="s">
         <v>108</v>
       </c>
-      <c r="C36" s="44">
+      <c r="C36" s="46">
         <f>C32+C33+C34</f>
         <v>7205</v>
       </c>
-      <c r="D36" s="44"/>
+      <c r="D36" s="46"/>
       <c r="E36" s="1" t="s">
         <v>109</v>
       </c>
@@ -43449,10 +43886,10 @@
       <c r="A65" s="1" t="s">
         <v>16</v>
       </c>
-      <c r="C65" s="45" t="s">
+      <c r="C65" s="47" t="s">
         <v>89</v>
       </c>
-      <c r="D65" s="45"/>
+      <c r="D65" s="47"/>
       <c r="E65" s="4" t="s">
         <v>90</v>
       </c>
@@ -43480,11 +43917,11 @@
       <c r="B66" s="3" t="s">
         <v>93</v>
       </c>
-      <c r="C66" s="46">
+      <c r="C66" s="48">
         <f>SUMIFS(I$3:I$61,B$3:B$61,A$65,L$3:L$61,A$66)</f>
         <v>34740</v>
       </c>
-      <c r="D66" s="46"/>
+      <c r="D66" s="48"/>
       <c r="E66" s="3">
         <f>SUMIFS(Q$3:Q$61,B$3:B$61,A$65,L$3:L$61,A$66)</f>
         <v>59</v>
@@ -43519,10 +43956,10 @@
       <c r="B67" s="2" t="s">
         <v>97</v>
       </c>
-      <c r="C67" s="47">
+      <c r="C67" s="49">
         <v>0</v>
       </c>
-      <c r="D67" s="47"/>
+      <c r="D67" s="49"/>
       <c r="K67" t="s">
         <v>98</v>
       </c>
@@ -43546,11 +43983,11 @@
       <c r="B68" s="2" t="s">
         <v>99</v>
       </c>
-      <c r="C68" s="47">
+      <c r="C68" s="49">
         <f>-SUMIFS(I$3:I$61,B$3:B$61,A$65,P$3:P$61,"xx",N$3:N$61,"x")</f>
         <v>0</v>
       </c>
-      <c r="D68" s="47"/>
+      <c r="D68" s="49"/>
       <c r="E68" s="2">
         <f>SUMIFS(Q$3:Q$61,B$3:B$61,A$65,P$3:P$61,"xx",N$3:N$61,"x")</f>
         <v>0</v>
@@ -43570,11 +44007,11 @@
       <c r="B69" s="4" t="s">
         <v>101</v>
       </c>
-      <c r="C69" s="45">
+      <c r="C69" s="47">
         <f>SUBTOTAL(9,C66:C68)</f>
         <v>34740</v>
       </c>
-      <c r="D69" s="45"/>
+      <c r="D69" s="47"/>
       <c r="E69">
         <f>E66</f>
         <v>59</v>
@@ -43594,8 +44031,8 @@
       <c r="B70" s="2" t="s">
         <v>104</v>
       </c>
-      <c r="C70" s="43"/>
-      <c r="D70" s="43"/>
+      <c r="C70" s="45"/>
+      <c r="D70" s="45"/>
       <c r="K70" s="2" t="s">
         <v>105</v>
       </c>
@@ -43611,8 +44048,8 @@
       <c r="B71" s="8" t="s">
         <v>107</v>
       </c>
-      <c r="C71" s="43"/>
-      <c r="D71" s="43"/>
+      <c r="C71" s="45"/>
+      <c r="D71" s="45"/>
       <c r="L71" s="9">
         <f>SUBTOTAL(9,L66:L70)</f>
         <v>26296</v>
@@ -43633,11 +44070,11 @@
       <c r="B73" s="1" t="s">
         <v>108</v>
       </c>
-      <c r="C73" s="44">
+      <c r="C73" s="46">
         <f>C69+C70+C71</f>
         <v>34740</v>
       </c>
-      <c r="D73" s="44"/>
+      <c r="D73" s="46"/>
       <c r="E73" s="1" t="s">
         <v>109</v>
       </c>
@@ -46824,10 +47261,10 @@
       <c r="A70" s="1" t="s">
         <v>16</v>
       </c>
-      <c r="C70" s="45" t="s">
+      <c r="C70" s="47" t="s">
         <v>89</v>
       </c>
-      <c r="D70" s="45"/>
+      <c r="D70" s="47"/>
       <c r="E70" s="4" t="s">
         <v>90</v>
       </c>
@@ -46855,11 +47292,11 @@
       <c r="B71" s="3" t="s">
         <v>93</v>
       </c>
-      <c r="C71" s="46">
+      <c r="C71" s="48">
         <f>SUMIFS(I$3:I$66,B$3:B$66,A$70,L$3:L$66,A$71)</f>
         <v>50540</v>
       </c>
-      <c r="D71" s="46"/>
+      <c r="D71" s="48"/>
       <c r="E71" s="3">
         <f>SUMIFS(Q$3:Q$66,B$3:B$66,A$70,L$3:L$66,A$71)</f>
         <v>64</v>
@@ -46893,10 +47330,10 @@
       <c r="B72" s="2" t="s">
         <v>97</v>
       </c>
-      <c r="C72" s="47">
+      <c r="C72" s="49">
         <v>0</v>
       </c>
-      <c r="D72" s="47"/>
+      <c r="D72" s="49"/>
       <c r="K72" t="s">
         <v>98</v>
       </c>
@@ -46919,11 +47356,11 @@
       <c r="B73" s="2" t="s">
         <v>99</v>
       </c>
-      <c r="C73" s="47">
+      <c r="C73" s="49">
         <f>-SUMIFS(I$3:I$66,B$3:B$66,A$70,P$3:P$66,"xx",N$3:N$66,"x")</f>
         <v>0</v>
       </c>
-      <c r="D73" s="47"/>
+      <c r="D73" s="49"/>
       <c r="E73" s="2">
         <f>SUMIFS(Q$3:Q$66,B$3:B$66,A$70,P$3:P$66,"xx",N$3:N$66,"x")</f>
         <v>0</v>
@@ -46946,11 +47383,11 @@
       <c r="B74" s="4" t="s">
         <v>101</v>
       </c>
-      <c r="C74" s="45">
+      <c r="C74" s="47">
         <f>SUBTOTAL(9,C71:C73)</f>
         <v>50540</v>
       </c>
-      <c r="D74" s="45"/>
+      <c r="D74" s="47"/>
       <c r="E74">
         <f>E71</f>
         <v>64</v>
@@ -46973,8 +47410,8 @@
       <c r="B75" s="2" t="s">
         <v>104</v>
       </c>
-      <c r="C75" s="43"/>
-      <c r="D75" s="43"/>
+      <c r="C75" s="45"/>
+      <c r="D75" s="45"/>
       <c r="G75" s="10" t="s">
         <v>2580</v>
       </c>
@@ -46997,8 +47434,8 @@
       <c r="B76" s="8" t="s">
         <v>107</v>
       </c>
-      <c r="C76" s="43"/>
-      <c r="D76" s="43"/>
+      <c r="C76" s="45"/>
+      <c r="D76" s="45"/>
       <c r="L76" s="9">
         <f>SUBTOTAL(9,L71:L75)</f>
         <v>24613</v>
@@ -47012,11 +47449,11 @@
       <c r="B78" s="1" t="s">
         <v>108</v>
       </c>
-      <c r="C78" s="44">
+      <c r="C78" s="46">
         <f>C74+C75+C76</f>
         <v>50540</v>
       </c>
-      <c r="D78" s="44"/>
+      <c r="D78" s="46"/>
       <c r="E78" s="1" t="s">
         <v>109</v>
       </c>
@@ -49582,10 +50019,10 @@
       <c r="A57" s="1" t="s">
         <v>16</v>
       </c>
-      <c r="C57" s="45" t="s">
+      <c r="C57" s="47" t="s">
         <v>89</v>
       </c>
-      <c r="D57" s="45"/>
+      <c r="D57" s="47"/>
       <c r="E57" s="4" t="s">
         <v>90</v>
       </c>
@@ -49613,11 +50050,11 @@
       <c r="B58" s="3" t="s">
         <v>93</v>
       </c>
-      <c r="C58" s="46">
+      <c r="C58" s="48">
         <f>SUMIFS(I$3:I$53,B$3:B$53,A$57,L$3:L$53,A$58)</f>
         <v>33955</v>
       </c>
-      <c r="D58" s="46"/>
+      <c r="D58" s="48"/>
       <c r="E58" s="3">
         <f>SUMIFS(Q$3:Q$53,B$3:B$53,A$57,L$3:L$53,A$58)</f>
         <v>50</v>
@@ -49652,10 +50089,10 @@
       <c r="B59" s="2" t="s">
         <v>97</v>
       </c>
-      <c r="C59" s="47">
+      <c r="C59" s="49">
         <v>0</v>
       </c>
-      <c r="D59" s="47"/>
+      <c r="D59" s="49"/>
       <c r="K59" t="s">
         <v>98</v>
       </c>
@@ -49679,11 +50116,11 @@
       <c r="B60" s="2" t="s">
         <v>99</v>
       </c>
-      <c r="C60" s="47">
+      <c r="C60" s="49">
         <f>-SUMIFS(I$3:I$53,B$3:B$53,A$57,P$3:P$53,"xx",N$3:N$53,"x")</f>
         <v>-765</v>
       </c>
-      <c r="D60" s="47"/>
+      <c r="D60" s="49"/>
       <c r="E60" s="2">
         <f>SUMIFS(Q$3:Q$53,B$3:B$53,A$57,P$3:P$53,"xx",N$3:N$53,"x")</f>
         <v>1</v>
@@ -49703,11 +50140,11 @@
       <c r="B61" s="4" t="s">
         <v>101</v>
       </c>
-      <c r="C61" s="45">
+      <c r="C61" s="47">
         <f>SUBTOTAL(9,C58:C60)</f>
         <v>33190</v>
       </c>
-      <c r="D61" s="45"/>
+      <c r="D61" s="47"/>
       <c r="E61">
         <f>E58</f>
         <v>50</v>
@@ -49729,8 +50166,8 @@
       <c r="B62" s="2" t="s">
         <v>104</v>
       </c>
-      <c r="C62" s="43"/>
-      <c r="D62" s="43"/>
+      <c r="C62" s="45"/>
+      <c r="D62" s="45"/>
       <c r="K62" s="2" t="s">
         <v>105</v>
       </c>
@@ -49746,8 +50183,8 @@
       <c r="B63" s="8" t="s">
         <v>107</v>
       </c>
-      <c r="C63" s="43"/>
-      <c r="D63" s="43"/>
+      <c r="C63" s="45"/>
+      <c r="D63" s="45"/>
       <c r="L63" s="9">
         <f>SUBTOTAL(9,L58:L62)</f>
         <v>19225</v>
@@ -49761,11 +50198,11 @@
       <c r="B65" s="1" t="s">
         <v>108</v>
       </c>
-      <c r="C65" s="44">
+      <c r="C65" s="46">
         <f>C61+C62+C63</f>
         <v>33190</v>
       </c>
-      <c r="D65" s="44"/>
+      <c r="D65" s="46"/>
       <c r="E65" s="1" t="s">
         <v>109</v>
       </c>
@@ -53505,14 +53942,14 @@
         <v>88</v>
       </c>
       <c r="G81" s="19">
-        <v>2910</v>
+        <v>0</v>
       </c>
       <c r="H81" s="19">
-        <v>30</v>
+        <v>25</v>
       </c>
       <c r="I81" s="19">
         <f>G81-H81</f>
-        <v>2880</v>
+        <v>-25</v>
       </c>
       <c r="J81" s="18" t="s">
         <v>165</v>
@@ -55530,15 +55967,15 @@
       </c>
       <c r="G127" s="1">
         <f t="shared" ref="G127:Q127" si="8">SUBTOTAL(9,G3:G125)</f>
-        <v>96660</v>
+        <v>93750</v>
       </c>
       <c r="H127" s="1">
         <f t="shared" si="8"/>
-        <v>3130</v>
+        <v>3125</v>
       </c>
       <c r="I127" s="1">
         <f t="shared" si="8"/>
-        <v>93530</v>
+        <v>90625</v>
       </c>
       <c r="J127" s="1">
         <f t="shared" si="8"/>
@@ -55587,10 +56024,10 @@
       <c r="A129" s="1" t="s">
         <v>16</v>
       </c>
-      <c r="C129" s="45" t="s">
+      <c r="C129" s="47" t="s">
         <v>89</v>
       </c>
-      <c r="D129" s="45"/>
+      <c r="D129" s="47"/>
       <c r="E129" s="4" t="s">
         <v>90</v>
       </c>
@@ -55621,11 +56058,11 @@
       <c r="B130" s="3" t="s">
         <v>93</v>
       </c>
-      <c r="C130" s="46">
+      <c r="C130" s="48">
         <f>SUMIFS(I$3:I$125,B$3:B$125,A$129,L$3:L$125,A$130)</f>
-        <v>91420</v>
-      </c>
-      <c r="D130" s="46"/>
+        <v>88515</v>
+      </c>
+      <c r="D130" s="48"/>
       <c r="E130" s="3">
         <f>SUMIFS(Q$3:Q$125,B$3:B$125,A$129,L$3:L$125,A$130)</f>
         <v>120</v>
@@ -55642,7 +56079,7 @@
       </c>
       <c r="L130">
         <f>SUMIFS(G$3:G$125,J$3:J$125,K$129)</f>
-        <v>28550</v>
+        <v>25640</v>
       </c>
       <c r="M130">
         <f>SUMIFS(Q$3:Q$125,J$3:J$125,K$129)-INT(COUNTIFS(J$3:J$125,K$129,M$3:M$125,"*gộp*")/2)</f>
@@ -55653,23 +56090,23 @@
       </c>
       <c r="P130">
         <f>L135</f>
-        <v>27810</v>
+        <v>24905</v>
       </c>
     </row>
     <row r="131" spans="1:16" x14ac:dyDescent="0.25">
       <c r="B131" s="2" t="s">
         <v>97</v>
       </c>
-      <c r="C131" s="47">
+      <c r="C131" s="49">
         <v>0</v>
       </c>
-      <c r="D131" s="47"/>
+      <c r="D131" s="49"/>
       <c r="K131" t="s">
         <v>98</v>
       </c>
       <c r="L131">
         <f>-SUMIFS(H$3:H$125,J$3:J$125,K$129)+M131*5</f>
-        <v>-740</v>
+        <v>-735</v>
       </c>
       <c r="M131">
         <f>SUMIFS(Q$3:Q$125,J$3:J$125,K$129)-INT(COUNTIFS(J$3:J$125,K$129,M$3:M$125,"*gộp*")/2)</f>
@@ -55680,18 +56117,18 @@
       </c>
       <c r="P131">
         <f>L143</f>
-        <v>28028</v>
+        <v>28018</v>
       </c>
     </row>
     <row r="132" spans="1:16" x14ac:dyDescent="0.25">
       <c r="B132" s="2" t="s">
         <v>99</v>
       </c>
-      <c r="C132" s="47">
+      <c r="C132" s="49">
         <f>-SUMIFS(I$3:I$125,B$3:B$125,A$129,P$3:P$125,"xx",N$3:N$125,"x")</f>
         <v>-5870</v>
       </c>
-      <c r="D132" s="47"/>
+      <c r="D132" s="49"/>
       <c r="E132" s="2">
         <f>SUMIFS(Q$3:Q$125,B$3:B$125,A$129,P$3:P$125,"xx",N$3:N$125,"x")</f>
         <v>7</v>
@@ -55711,11 +56148,11 @@
       <c r="B133" s="4" t="s">
         <v>101</v>
       </c>
-      <c r="C133" s="45">
+      <c r="C133" s="47">
         <f>SUBTOTAL(9,C130:C132)</f>
-        <v>85550</v>
-      </c>
-      <c r="D133" s="45"/>
+        <v>82645</v>
+      </c>
+      <c r="D133" s="47"/>
       <c r="E133">
         <f>E130</f>
         <v>120</v>
@@ -55735,8 +56172,8 @@
       <c r="B134" s="2" t="s">
         <v>104</v>
       </c>
-      <c r="C134" s="43"/>
-      <c r="D134" s="43"/>
+      <c r="C134" s="45"/>
+      <c r="D134" s="45"/>
       <c r="K134" s="2" t="s">
         <v>105</v>
       </c>
@@ -55745,20 +56182,20 @@
       </c>
       <c r="P134">
         <f>-C137</f>
-        <v>-86340</v>
+        <v>-83435</v>
       </c>
     </row>
     <row r="135" spans="1:16" x14ac:dyDescent="0.25">
       <c r="B135" s="8" t="s">
         <v>107</v>
       </c>
-      <c r="C135" s="43">
+      <c r="C135" s="45">
         <v>790</v>
       </c>
-      <c r="D135" s="43"/>
+      <c r="D135" s="45"/>
       <c r="L135" s="9">
         <f>SUBTOTAL(9,L130:L134)</f>
-        <v>27810</v>
+        <v>24905</v>
       </c>
       <c r="M135" s="9">
         <f>M130</f>
@@ -55767,9 +56204,7 @@
       <c r="O135" s="30" t="s">
         <v>2993</v>
       </c>
-      <c r="P135" s="30">
-        <v>790</v>
-      </c>
+      <c r="P135" s="30"/>
     </row>
     <row r="136" spans="1:16" x14ac:dyDescent="0.25">
       <c r="O136" s="4" t="s">
@@ -55777,18 +56212,18 @@
       </c>
       <c r="P136" s="4">
         <f>SUBTOTAL(9,P130:P135)</f>
-        <v>317</v>
+        <v>-483</v>
       </c>
     </row>
     <row r="137" spans="1:16" x14ac:dyDescent="0.25">
       <c r="B137" s="1" t="s">
         <v>108</v>
       </c>
-      <c r="C137" s="44">
+      <c r="C137" s="46">
         <f>C133+C134+C135</f>
-        <v>86340</v>
-      </c>
-      <c r="D137" s="44"/>
+        <v>83435</v>
+      </c>
+      <c r="D137" s="46"/>
       <c r="E137" s="1" t="s">
         <v>109</v>
       </c>
@@ -55811,7 +56246,8 @@
         <v>28870</v>
       </c>
       <c r="M138">
-        <v>30</v>
+        <f>SUMIFS(Q$3:Q$125,J$3:J$125,K$137)-INT(COUNTIFS(J$3:J$125,K$137,M$3:M$125,"*gộp*")/2)</f>
+        <v>28</v>
       </c>
     </row>
     <row r="139" spans="1:16" x14ac:dyDescent="0.25">
@@ -55820,10 +56256,11 @@
       </c>
       <c r="L139">
         <f>-SUMIFS(H$3:H$125,J$3:J$125,K$137)+M139*5</f>
-        <v>-630</v>
+        <v>-640</v>
       </c>
       <c r="M139">
-        <v>30</v>
+        <f>SUMIFS(Q$3:Q$125,J$3:J$125,K$137)-INT(COUNTIFS(J$3:J$125,K$137,M$3:M$125,"*gộp*")/2)</f>
+        <v>28</v>
       </c>
     </row>
     <row r="140" spans="1:16" x14ac:dyDescent="0.25">
@@ -55852,11 +56289,11 @@
     <row r="143" spans="1:16" x14ac:dyDescent="0.25">
       <c r="L143" s="9">
         <f>SUBTOTAL(9,L138:L142)</f>
-        <v>28028</v>
+        <v>28018</v>
       </c>
       <c r="M143" s="9">
         <f>M138</f>
-        <v>30</v>
+        <v>28</v>
       </c>
     </row>
     <row r="145" spans="11:13" x14ac:dyDescent="0.25">
@@ -55879,7 +56316,8 @@
         <v>28155</v>
       </c>
       <c r="M146">
-        <v>40</v>
+        <f>SUMIFS(Q$3:Q$125,J$3:J$125,K$145)-INT(COUNTIFS(J$3:J$125,K$145,M$3:M$125,"*gộp*")/2)</f>
+        <v>38</v>
       </c>
     </row>
     <row r="147" spans="11:13" x14ac:dyDescent="0.25">
@@ -55891,7 +56329,8 @@
         <v>-904</v>
       </c>
       <c r="M147">
-        <v>40</v>
+        <f>SUMIFS(Q$3:Q$125,J$3:J$125,K$145)-INT(COUNTIFS(J$3:J$125,K$145,M$3:M$125,"*gộp*")/2)</f>
+        <v>38</v>
       </c>
     </row>
     <row r="148" spans="11:13" x14ac:dyDescent="0.25">
@@ -55922,7 +56361,7 @@
       </c>
       <c r="M151" s="9">
         <f>M146</f>
-        <v>40</v>
+        <v>38</v>
       </c>
     </row>
     <row r="153" spans="11:13" x14ac:dyDescent="0.25">
@@ -56089,11 +56528,11 @@
         <v>16</v>
       </c>
       <c r="C3" s="18" t="s">
-        <v>3007</v>
+        <v>2994</v>
       </c>
       <c r="D3" s="18"/>
       <c r="E3" s="18" t="s">
-        <v>3008</v>
+        <v>2995</v>
       </c>
       <c r="F3" s="18" t="s">
         <v>2698</v>
@@ -56115,7 +56554,7 @@
         <v>21</v>
       </c>
       <c r="L3" s="18" t="s">
-        <v>3006</v>
+        <v>2996</v>
       </c>
       <c r="M3" s="18"/>
       <c r="N3" s="18"/>
@@ -56134,7 +56573,7 @@
         <v>37</v>
       </c>
       <c r="D4" s="18" t="s">
-        <v>3016</v>
+        <v>2997</v>
       </c>
       <c r="E4" s="18" t="s">
         <v>39</v>
@@ -56153,13 +56592,13 @@
         <v>880</v>
       </c>
       <c r="J4" s="18" t="s">
-        <v>3017</v>
+        <v>2998</v>
       </c>
       <c r="K4" s="18" t="s">
         <v>21</v>
       </c>
       <c r="L4" s="18" t="s">
-        <v>3006</v>
+        <v>2996</v>
       </c>
       <c r="M4" s="18"/>
       <c r="N4" s="18"/>
@@ -56175,13 +56614,13 @@
         <v>16</v>
       </c>
       <c r="C5" s="18" t="s">
-        <v>3024</v>
+        <v>2999</v>
       </c>
       <c r="D5" s="18" t="s">
-        <v>3025</v>
+        <v>3000</v>
       </c>
       <c r="E5" s="18" t="s">
-        <v>3026</v>
+        <v>3001</v>
       </c>
       <c r="F5" s="19">
         <v>8</v>
@@ -56197,13 +56636,13 @@
         <v>1550</v>
       </c>
       <c r="J5" s="18" t="s">
-        <v>3017</v>
+        <v>2998</v>
       </c>
       <c r="K5" s="18" t="s">
         <v>21</v>
       </c>
       <c r="L5" s="18" t="s">
-        <v>3006</v>
+        <v>2996</v>
       </c>
       <c r="M5" s="18"/>
       <c r="N5" s="18"/>
@@ -56219,13 +56658,13 @@
         <v>16</v>
       </c>
       <c r="C6" s="18" t="s">
-        <v>3027</v>
+        <v>3002</v>
       </c>
       <c r="D6" s="18" t="s">
-        <v>3028</v>
+        <v>3003</v>
       </c>
       <c r="E6" s="18" t="s">
-        <v>3029</v>
+        <v>3004</v>
       </c>
       <c r="F6" s="18" t="s">
         <v>128</v>
@@ -56241,13 +56680,13 @@
         <v>790</v>
       </c>
       <c r="J6" s="18" t="s">
-        <v>3017</v>
+        <v>2998</v>
       </c>
       <c r="K6" s="18" t="s">
         <v>21</v>
       </c>
       <c r="L6" s="18" t="s">
-        <v>3006</v>
+        <v>2996</v>
       </c>
       <c r="M6" s="18"/>
       <c r="N6" s="18"/>
@@ -56266,7 +56705,7 @@
         <v>2331</v>
       </c>
       <c r="D7" s="40" t="s">
-        <v>3048</v>
+        <v>3005</v>
       </c>
       <c r="E7" s="40" t="s">
         <v>2333</v>
@@ -56285,13 +56724,13 @@
         <v>100</v>
       </c>
       <c r="J7" s="40" t="s">
-        <v>3017</v>
+        <v>2998</v>
       </c>
       <c r="K7" s="40" t="s">
         <v>21</v>
       </c>
       <c r="L7" s="40" t="s">
-        <v>3006</v>
+        <v>2996</v>
       </c>
       <c r="M7" s="40" t="s">
         <v>49</v>
@@ -56309,13 +56748,13 @@
         <v>16</v>
       </c>
       <c r="C8" s="18" t="s">
-        <v>3049</v>
+        <v>3006</v>
       </c>
       <c r="D8" s="18" t="s">
-        <v>3050</v>
+        <v>3007</v>
       </c>
       <c r="E8" s="18" t="s">
-        <v>3051</v>
+        <v>3008</v>
       </c>
       <c r="F8" s="19">
         <v>8</v>
@@ -56331,13 +56770,13 @@
         <v>1910</v>
       </c>
       <c r="J8" s="18" t="s">
-        <v>3017</v>
+        <v>2998</v>
       </c>
       <c r="K8" s="18" t="s">
         <v>21</v>
       </c>
       <c r="L8" s="18" t="s">
-        <v>3006</v>
+        <v>2996</v>
       </c>
       <c r="M8" s="18"/>
       <c r="N8" s="18"/>
@@ -56353,13 +56792,13 @@
         <v>16</v>
       </c>
       <c r="C9" s="18" t="s">
-        <v>3063</v>
+        <v>3009</v>
       </c>
       <c r="D9" s="18" t="s">
-        <v>3064</v>
+        <v>3010</v>
       </c>
       <c r="E9" s="18" t="s">
-        <v>3065</v>
+        <v>3011</v>
       </c>
       <c r="F9" s="18" t="s">
         <v>26</v>
@@ -56375,13 +56814,13 @@
         <v>1120</v>
       </c>
       <c r="J9" s="18" t="s">
-        <v>3017</v>
+        <v>2998</v>
       </c>
       <c r="K9" s="18" t="s">
         <v>21</v>
       </c>
       <c r="L9" s="18" t="s">
-        <v>3006</v>
+        <v>2996</v>
       </c>
       <c r="M9" s="18"/>
       <c r="N9" s="18"/>
@@ -56397,13 +56836,13 @@
         <v>16</v>
       </c>
       <c r="C10" s="18" t="s">
-        <v>3074</v>
+        <v>3012</v>
       </c>
       <c r="D10" s="18" t="s">
-        <v>3075</v>
+        <v>3013</v>
       </c>
       <c r="E10" s="18" t="s">
-        <v>3076</v>
+        <v>3014</v>
       </c>
       <c r="F10" s="19">
         <v>7</v>
@@ -56419,13 +56858,13 @@
         <v>540</v>
       </c>
       <c r="J10" s="18" t="s">
-        <v>3017</v>
+        <v>2998</v>
       </c>
       <c r="K10" s="18" t="s">
         <v>21</v>
       </c>
       <c r="L10" s="18" t="s">
-        <v>3006</v>
+        <v>2996</v>
       </c>
       <c r="M10" s="18"/>
       <c r="N10" s="18"/>
@@ -56444,7 +56883,7 @@
         <v>196</v>
       </c>
       <c r="D11" s="18" t="s">
-        <v>3081</v>
+        <v>3015</v>
       </c>
       <c r="E11" s="18" t="s">
         <v>198</v>
@@ -56463,13 +56902,13 @@
         <v>770</v>
       </c>
       <c r="J11" s="18" t="s">
-        <v>3017</v>
+        <v>2998</v>
       </c>
       <c r="K11" s="18" t="s">
         <v>21</v>
       </c>
       <c r="L11" s="18" t="s">
-        <v>3006</v>
+        <v>2996</v>
       </c>
       <c r="M11" s="18"/>
       <c r="N11" s="18"/>
@@ -56488,7 +56927,7 @@
         <v>1159</v>
       </c>
       <c r="D12" s="18" t="s">
-        <v>3082</v>
+        <v>3016</v>
       </c>
       <c r="E12" s="18" t="s">
         <v>1161</v>
@@ -56507,13 +56946,13 @@
         <v>-30</v>
       </c>
       <c r="J12" s="18" t="s">
-        <v>3017</v>
+        <v>2998</v>
       </c>
       <c r="K12" s="18" t="s">
         <v>21</v>
       </c>
       <c r="L12" s="18" t="s">
-        <v>3006</v>
+        <v>2996</v>
       </c>
       <c r="M12" s="18"/>
       <c r="N12" s="18"/>
@@ -56529,13 +56968,13 @@
         <v>16</v>
       </c>
       <c r="C13" s="18" t="s">
-        <v>3092</v>
+        <v>3017</v>
       </c>
       <c r="D13" s="18" t="s">
-        <v>3093</v>
+        <v>3018</v>
       </c>
       <c r="E13" s="18" t="s">
-        <v>3094</v>
+        <v>3019</v>
       </c>
       <c r="F13" s="18" t="s">
         <v>26</v>
@@ -56551,13 +56990,13 @@
         <v>-30</v>
       </c>
       <c r="J13" s="18" t="s">
-        <v>3017</v>
+        <v>2998</v>
       </c>
       <c r="K13" s="18" t="s">
         <v>21</v>
       </c>
       <c r="L13" s="18" t="s">
-        <v>3006</v>
+        <v>2996</v>
       </c>
       <c r="M13" s="18"/>
       <c r="N13" s="18"/>
@@ -56573,13 +57012,13 @@
         <v>16</v>
       </c>
       <c r="C14" s="18" t="s">
-        <v>3098</v>
+        <v>3020</v>
       </c>
       <c r="D14" s="18" t="s">
-        <v>3099</v>
+        <v>3021</v>
       </c>
       <c r="E14" s="18" t="s">
-        <v>3100</v>
+        <v>3022</v>
       </c>
       <c r="F14" s="18" t="s">
         <v>113</v>
@@ -56595,13 +57034,13 @@
         <v>900</v>
       </c>
       <c r="J14" s="18" t="s">
-        <v>3017</v>
+        <v>2998</v>
       </c>
       <c r="K14" s="18" t="s">
         <v>21</v>
       </c>
       <c r="L14" s="18" t="s">
-        <v>3006</v>
+        <v>2996</v>
       </c>
       <c r="M14" s="18"/>
       <c r="N14" s="18"/>
@@ -56617,13 +57056,13 @@
         <v>16</v>
       </c>
       <c r="C15" s="18" t="s">
-        <v>3101</v>
+        <v>3023</v>
       </c>
       <c r="D15" s="18" t="s">
-        <v>3102</v>
+        <v>3024</v>
       </c>
       <c r="E15" s="18" t="s">
-        <v>3103</v>
+        <v>3025</v>
       </c>
       <c r="F15" s="19">
         <v>8</v>
@@ -56639,13 +57078,13 @@
         <v>720</v>
       </c>
       <c r="J15" s="18" t="s">
-        <v>3017</v>
+        <v>2998</v>
       </c>
       <c r="K15" s="18" t="s">
         <v>21</v>
       </c>
       <c r="L15" s="18" t="s">
-        <v>3006</v>
+        <v>2996</v>
       </c>
       <c r="M15" s="18"/>
       <c r="N15" s="18"/>
@@ -56656,48 +57095,48 @@
       </c>
     </row>
     <row r="16" spans="1:17" s="10" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A16" s="49"/>
-      <c r="B16" s="49" t="s">
-        <v>16</v>
-      </c>
-      <c r="C16" s="49" t="s">
+      <c r="A16" s="43"/>
+      <c r="B16" s="43" t="s">
+        <v>16</v>
+      </c>
+      <c r="C16" s="43" t="s">
         <v>2246</v>
       </c>
-      <c r="D16" s="49" t="s">
+      <c r="D16" s="43" t="s">
         <v>2247</v>
       </c>
-      <c r="E16" s="49" t="s">
+      <c r="E16" s="43" t="s">
         <v>2248</v>
       </c>
-      <c r="F16" s="50">
-        <v>1</v>
-      </c>
-      <c r="G16" s="50">
+      <c r="F16" s="44">
+        <v>1</v>
+      </c>
+      <c r="G16" s="44">
         <v>480</v>
       </c>
-      <c r="H16" s="50">
+      <c r="H16" s="44">
         <v>30</v>
       </c>
-      <c r="I16" s="50">
+      <c r="I16" s="44">
         <f t="shared" si="1"/>
         <v>450</v>
       </c>
-      <c r="J16" s="49" t="s">
-        <v>3017</v>
-      </c>
-      <c r="K16" s="49" t="s">
-        <v>21</v>
-      </c>
-      <c r="L16" s="49" t="s">
+      <c r="J16" s="43" t="s">
+        <v>2998</v>
+      </c>
+      <c r="K16" s="43" t="s">
+        <v>21</v>
+      </c>
+      <c r="L16" s="43" t="s">
         <v>2165</v>
       </c>
-      <c r="M16" s="49" t="s">
-        <v>3104</v>
-      </c>
-      <c r="N16" s="49"/>
-      <c r="O16" s="49"/>
-      <c r="P16" s="49"/>
-      <c r="Q16" s="49">
+      <c r="M16" s="43" t="s">
+        <v>3026</v>
+      </c>
+      <c r="N16" s="43"/>
+      <c r="O16" s="43"/>
+      <c r="P16" s="43"/>
+      <c r="Q16" s="43">
         <v>1</v>
       </c>
     </row>
@@ -56709,11 +57148,11 @@
         <v>16</v>
       </c>
       <c r="C17" s="18" t="s">
-        <v>3004</v>
+        <v>3027</v>
       </c>
       <c r="D17" s="18"/>
       <c r="E17" s="18" t="s">
-        <v>3005</v>
+        <v>3028</v>
       </c>
       <c r="F17" s="18" t="s">
         <v>217</v>
@@ -56735,7 +57174,7 @@
         <v>21</v>
       </c>
       <c r="L17" s="18" t="s">
-        <v>3006</v>
+        <v>2996</v>
       </c>
       <c r="M17" s="18"/>
       <c r="N17" s="18"/>
@@ -56779,7 +57218,7 @@
         <v>21</v>
       </c>
       <c r="L18" s="18" t="s">
-        <v>3006</v>
+        <v>2996</v>
       </c>
       <c r="M18" s="18"/>
       <c r="N18" s="18"/>
@@ -56823,7 +57262,7 @@
         <v>21</v>
       </c>
       <c r="L19" s="18" t="s">
-        <v>3006</v>
+        <v>2996</v>
       </c>
       <c r="M19" s="18"/>
       <c r="N19" s="18"/>
@@ -56841,11 +57280,11 @@
         <v>16</v>
       </c>
       <c r="C20" s="18" t="s">
-        <v>3011</v>
+        <v>3029</v>
       </c>
       <c r="D20" s="18"/>
       <c r="E20" s="18" t="s">
-        <v>3012</v>
+        <v>3030</v>
       </c>
       <c r="F20" s="18" t="s">
         <v>68</v>
@@ -56867,7 +57306,7 @@
         <v>21</v>
       </c>
       <c r="L20" s="18" t="s">
-        <v>3006</v>
+        <v>2996</v>
       </c>
       <c r="M20" s="18"/>
       <c r="N20" s="18"/>
@@ -56883,13 +57322,13 @@
         <v>16</v>
       </c>
       <c r="C21" s="18" t="s">
-        <v>3021</v>
+        <v>3031</v>
       </c>
       <c r="D21" s="18" t="s">
-        <v>3022</v>
+        <v>3032</v>
       </c>
       <c r="E21" s="18" t="s">
-        <v>3023</v>
+        <v>3033</v>
       </c>
       <c r="F21" s="18" t="s">
         <v>68</v>
@@ -56911,7 +57350,7 @@
         <v>21</v>
       </c>
       <c r="L21" s="18" t="s">
-        <v>3006</v>
+        <v>2996</v>
       </c>
       <c r="M21" s="18"/>
       <c r="N21" s="18"/>
@@ -56927,13 +57366,13 @@
         <v>16</v>
       </c>
       <c r="C22" s="18" t="s">
-        <v>3030</v>
+        <v>3034</v>
       </c>
       <c r="D22" s="18" t="s">
-        <v>3031</v>
+        <v>3035</v>
       </c>
       <c r="E22" s="18" t="s">
-        <v>3032</v>
+        <v>3036</v>
       </c>
       <c r="F22" s="18" t="s">
         <v>153</v>
@@ -56955,7 +57394,7 @@
         <v>21</v>
       </c>
       <c r="L22" s="18" t="s">
-        <v>3006</v>
+        <v>2996</v>
       </c>
       <c r="M22" s="18"/>
       <c r="N22" s="18"/>
@@ -56971,13 +57410,13 @@
         <v>16</v>
       </c>
       <c r="C23" s="18" t="s">
-        <v>3035</v>
+        <v>3037</v>
       </c>
       <c r="D23" s="18" t="s">
-        <v>3036</v>
+        <v>3038</v>
       </c>
       <c r="E23" s="18" t="s">
-        <v>3037</v>
+        <v>3039</v>
       </c>
       <c r="F23" s="18" t="s">
         <v>68</v>
@@ -56999,7 +57438,7 @@
         <v>21</v>
       </c>
       <c r="L23" s="18" t="s">
-        <v>3006</v>
+        <v>2996</v>
       </c>
       <c r="M23" s="18"/>
       <c r="N23" s="18"/>
@@ -57015,13 +57454,13 @@
         <v>16</v>
       </c>
       <c r="C24" s="18" t="s">
-        <v>3038</v>
+        <v>3040</v>
       </c>
       <c r="D24" s="18" t="s">
-        <v>3039</v>
+        <v>3041</v>
       </c>
       <c r="E24" s="18" t="s">
-        <v>3040</v>
+        <v>3042</v>
       </c>
       <c r="F24" s="18" t="s">
         <v>88</v>
@@ -57043,7 +57482,7 @@
         <v>21</v>
       </c>
       <c r="L24" s="18" t="s">
-        <v>3006</v>
+        <v>2996</v>
       </c>
       <c r="M24" s="18"/>
       <c r="N24" s="18"/>
@@ -57059,13 +57498,13 @@
         <v>16</v>
       </c>
       <c r="C25" s="40" t="s">
-        <v>3041</v>
+        <v>3043</v>
       </c>
       <c r="D25" s="40" t="s">
-        <v>3042</v>
+        <v>3044</v>
       </c>
       <c r="E25" s="40" t="s">
-        <v>3043</v>
+        <v>3045</v>
       </c>
       <c r="F25" s="40" t="s">
         <v>72</v>
@@ -57087,7 +57526,7 @@
         <v>21</v>
       </c>
       <c r="L25" s="40" t="s">
-        <v>3006</v>
+        <v>2996</v>
       </c>
       <c r="M25" s="40" t="s">
         <v>49</v>
@@ -57108,7 +57547,7 @@
         <v>726</v>
       </c>
       <c r="D26" s="18" t="s">
-        <v>3044</v>
+        <v>3046</v>
       </c>
       <c r="E26" s="18" t="s">
         <v>728</v>
@@ -57133,7 +57572,7 @@
         <v>21</v>
       </c>
       <c r="L26" s="18" t="s">
-        <v>3006</v>
+        <v>2996</v>
       </c>
       <c r="M26" s="18"/>
       <c r="N26" s="18"/>
@@ -57149,13 +57588,13 @@
         <v>16</v>
       </c>
       <c r="C27" s="18" t="s">
-        <v>3045</v>
+        <v>3047</v>
       </c>
       <c r="D27" s="18" t="s">
-        <v>3046</v>
+        <v>3048</v>
       </c>
       <c r="E27" s="18" t="s">
-        <v>3047</v>
+        <v>3049</v>
       </c>
       <c r="F27" s="18" t="s">
         <v>72</v>
@@ -57177,7 +57616,7 @@
         <v>21</v>
       </c>
       <c r="L27" s="18" t="s">
-        <v>3006</v>
+        <v>2996</v>
       </c>
       <c r="M27" s="18"/>
       <c r="N27" s="18"/>
@@ -57193,13 +57632,13 @@
         <v>16</v>
       </c>
       <c r="C28" s="18" t="s">
-        <v>3055</v>
+        <v>3050</v>
       </c>
       <c r="D28" s="18" t="s">
-        <v>3056</v>
+        <v>3051</v>
       </c>
       <c r="E28" s="18" t="s">
-        <v>3057</v>
+        <v>3052</v>
       </c>
       <c r="F28" s="18" t="s">
         <v>88</v>
@@ -57221,7 +57660,7 @@
         <v>21</v>
       </c>
       <c r="L28" s="18" t="s">
-        <v>3006</v>
+        <v>2996</v>
       </c>
       <c r="M28" s="18"/>
       <c r="N28" s="18"/>
@@ -57237,13 +57676,13 @@
         <v>16</v>
       </c>
       <c r="C29" s="18" t="s">
-        <v>3060</v>
+        <v>3053</v>
       </c>
       <c r="D29" s="18" t="s">
-        <v>3061</v>
+        <v>3054</v>
       </c>
       <c r="E29" s="18" t="s">
-        <v>3062</v>
+        <v>3055</v>
       </c>
       <c r="F29" s="18" t="s">
         <v>153</v>
@@ -57265,7 +57704,7 @@
         <v>21</v>
       </c>
       <c r="L29" s="18" t="s">
-        <v>3006</v>
+        <v>2996</v>
       </c>
       <c r="M29" s="18"/>
       <c r="N29" s="18"/>
@@ -57281,10 +57720,10 @@
         <v>16</v>
       </c>
       <c r="C30" s="18" t="s">
-        <v>3083</v>
+        <v>3056</v>
       </c>
       <c r="D30" s="18" t="s">
-        <v>3084</v>
+        <v>3057</v>
       </c>
       <c r="E30" s="18" t="s">
         <v>2105</v>
@@ -57309,7 +57748,7 @@
         <v>21</v>
       </c>
       <c r="L30" s="18" t="s">
-        <v>3006</v>
+        <v>2996</v>
       </c>
       <c r="M30" s="18"/>
       <c r="N30" s="18"/>
@@ -57325,13 +57764,13 @@
         <v>16</v>
       </c>
       <c r="C31" s="18" t="s">
-        <v>3086</v>
+        <v>3058</v>
       </c>
       <c r="D31" s="18" t="s">
-        <v>3087</v>
+        <v>3059</v>
       </c>
       <c r="E31" s="18" t="s">
-        <v>3088</v>
+        <v>3060</v>
       </c>
       <c r="F31" s="18" t="s">
         <v>153</v>
@@ -57353,7 +57792,7 @@
         <v>21</v>
       </c>
       <c r="L31" s="18" t="s">
-        <v>3006</v>
+        <v>2996</v>
       </c>
       <c r="M31" s="18"/>
       <c r="N31" s="18"/>
@@ -57369,10 +57808,10 @@
         <v>16</v>
       </c>
       <c r="C32" s="18" t="s">
-        <v>3089</v>
+        <v>3061</v>
       </c>
       <c r="D32" s="18" t="s">
-        <v>3090</v>
+        <v>3062</v>
       </c>
       <c r="E32" s="18" t="s">
         <v>1417</v>
@@ -57397,7 +57836,7 @@
         <v>21</v>
       </c>
       <c r="L32" s="18" t="s">
-        <v>3006</v>
+        <v>2996</v>
       </c>
       <c r="M32" s="18"/>
       <c r="N32" s="18"/>
@@ -57441,7 +57880,7 @@
         <v>21</v>
       </c>
       <c r="L33" s="18" t="s">
-        <v>3006</v>
+        <v>2996</v>
       </c>
       <c r="M33" s="18"/>
       <c r="N33" s="18"/>
@@ -57485,7 +57924,7 @@
         <v>21</v>
       </c>
       <c r="L34" s="18" t="s">
-        <v>3006</v>
+        <v>2996</v>
       </c>
       <c r="M34" s="18"/>
       <c r="N34" s="18"/>
@@ -57503,11 +57942,11 @@
         <v>16</v>
       </c>
       <c r="C35" s="18" t="s">
-        <v>3009</v>
+        <v>3063</v>
       </c>
       <c r="D35" s="18"/>
       <c r="E35" s="18" t="s">
-        <v>3010</v>
+        <v>3064</v>
       </c>
       <c r="F35" s="18" t="s">
         <v>88</v>
@@ -57529,7 +57968,7 @@
         <v>21</v>
       </c>
       <c r="L35" s="18" t="s">
-        <v>3006</v>
+        <v>2996</v>
       </c>
       <c r="M35" s="18"/>
       <c r="N35" s="18"/>
@@ -57545,13 +57984,13 @@
         <v>16</v>
       </c>
       <c r="C36" s="18" t="s">
-        <v>3013</v>
+        <v>3065</v>
       </c>
       <c r="D36" s="18" t="s">
-        <v>3014</v>
+        <v>3066</v>
       </c>
       <c r="E36" s="18" t="s">
-        <v>3015</v>
+        <v>3067</v>
       </c>
       <c r="F36" s="18" t="s">
         <v>88</v>
@@ -57573,7 +58012,7 @@
         <v>21</v>
       </c>
       <c r="L36" s="18" t="s">
-        <v>3006</v>
+        <v>2996</v>
       </c>
       <c r="M36" s="18"/>
       <c r="N36" s="18"/>
@@ -57589,13 +58028,13 @@
         <v>16</v>
       </c>
       <c r="C37" s="18" t="s">
-        <v>3018</v>
+        <v>3068</v>
       </c>
       <c r="D37" s="18" t="s">
-        <v>3019</v>
+        <v>3069</v>
       </c>
       <c r="E37" s="18" t="s">
-        <v>3020</v>
+        <v>3070</v>
       </c>
       <c r="F37" s="19">
         <v>1</v>
@@ -57617,7 +58056,7 @@
         <v>21</v>
       </c>
       <c r="L37" s="18" t="s">
-        <v>3006</v>
+        <v>2996</v>
       </c>
       <c r="M37" s="18"/>
       <c r="N37" s="18"/>
@@ -57633,10 +58072,10 @@
         <v>16</v>
       </c>
       <c r="C38" s="18" t="s">
-        <v>3033</v>
+        <v>3071</v>
       </c>
       <c r="D38" s="18" t="s">
-        <v>3034</v>
+        <v>3072</v>
       </c>
       <c r="E38" s="18" t="s">
         <v>756</v>
@@ -57661,7 +58100,7 @@
         <v>21</v>
       </c>
       <c r="L38" s="18" t="s">
-        <v>3006</v>
+        <v>2996</v>
       </c>
       <c r="M38" s="25" t="s">
         <v>398</v>
@@ -57679,13 +58118,13 @@
         <v>16</v>
       </c>
       <c r="C39" s="18" t="s">
-        <v>3052</v>
+        <v>3073</v>
       </c>
       <c r="D39" s="18" t="s">
-        <v>3053</v>
+        <v>3074</v>
       </c>
       <c r="E39" s="18" t="s">
-        <v>3054</v>
+        <v>3075</v>
       </c>
       <c r="F39" s="19">
         <v>4</v>
@@ -57707,7 +58146,7 @@
         <v>21</v>
       </c>
       <c r="L39" s="18" t="s">
-        <v>3006</v>
+        <v>2996</v>
       </c>
       <c r="M39" s="18"/>
       <c r="N39" s="18"/>
@@ -57726,10 +58165,10 @@
         <v>1772</v>
       </c>
       <c r="D40" s="18" t="s">
-        <v>3058</v>
+        <v>3076</v>
       </c>
       <c r="E40" s="18" t="s">
-        <v>3059</v>
+        <v>3077</v>
       </c>
       <c r="F40" s="19">
         <v>3</v>
@@ -57751,7 +58190,7 @@
         <v>21</v>
       </c>
       <c r="L40" s="18" t="s">
-        <v>3006</v>
+        <v>2996</v>
       </c>
       <c r="M40" s="18"/>
       <c r="N40" s="18"/>
@@ -57767,13 +58206,13 @@
         <v>16</v>
       </c>
       <c r="C41" s="18" t="s">
-        <v>3066</v>
+        <v>3078</v>
       </c>
       <c r="D41" s="18" t="s">
-        <v>3067</v>
+        <v>3079</v>
       </c>
       <c r="E41" s="18" t="s">
-        <v>3068</v>
+        <v>3080</v>
       </c>
       <c r="F41" s="18" t="s">
         <v>88</v>
@@ -57795,7 +58234,7 @@
         <v>21</v>
       </c>
       <c r="L41" s="18" t="s">
-        <v>3006</v>
+        <v>2996</v>
       </c>
       <c r="M41" s="18"/>
       <c r="N41" s="18"/>
@@ -57811,13 +58250,13 @@
         <v>16</v>
       </c>
       <c r="C42" s="18" t="s">
-        <v>3069</v>
+        <v>3081</v>
       </c>
       <c r="D42" s="18" t="s">
-        <v>3070</v>
+        <v>3082</v>
       </c>
       <c r="E42" s="18" t="s">
-        <v>3071</v>
+        <v>3083</v>
       </c>
       <c r="F42" s="19">
         <v>10</v>
@@ -57839,7 +58278,7 @@
         <v>21</v>
       </c>
       <c r="L42" s="18" t="s">
-        <v>3006</v>
+        <v>2996</v>
       </c>
       <c r="M42" s="18"/>
       <c r="N42" s="18"/>
@@ -57855,10 +58294,10 @@
         <v>16</v>
       </c>
       <c r="C43" s="18" t="s">
-        <v>3072</v>
+        <v>3084</v>
       </c>
       <c r="D43" s="18" t="s">
-        <v>3073</v>
+        <v>3085</v>
       </c>
       <c r="E43" s="18" t="s">
         <v>2944</v>
@@ -57883,7 +58322,7 @@
         <v>21</v>
       </c>
       <c r="L43" s="18" t="s">
-        <v>3006</v>
+        <v>2996</v>
       </c>
       <c r="M43" s="18"/>
       <c r="N43" s="18"/>
@@ -57902,7 +58341,7 @@
         <v>1001</v>
       </c>
       <c r="D44" s="18" t="s">
-        <v>3077</v>
+        <v>3086</v>
       </c>
       <c r="E44" s="18" t="s">
         <v>1003</v>
@@ -57927,7 +58366,7 @@
         <v>21</v>
       </c>
       <c r="L44" s="18" t="s">
-        <v>3006</v>
+        <v>2996</v>
       </c>
       <c r="M44" s="18"/>
       <c r="N44" s="18"/>
@@ -57943,13 +58382,13 @@
         <v>16</v>
       </c>
       <c r="C45" s="18" t="s">
-        <v>3078</v>
+        <v>3087</v>
       </c>
       <c r="D45" s="18" t="s">
-        <v>3079</v>
+        <v>3088</v>
       </c>
       <c r="E45" s="18" t="s">
-        <v>3080</v>
+        <v>3089</v>
       </c>
       <c r="F45" s="18" t="s">
         <v>85</v>
@@ -57971,7 +58410,7 @@
         <v>21</v>
       </c>
       <c r="L45" s="18" t="s">
-        <v>3006</v>
+        <v>2996</v>
       </c>
       <c r="M45" s="18"/>
       <c r="N45" s="18"/>
@@ -57990,7 +58429,7 @@
         <v>997</v>
       </c>
       <c r="D46" s="18" t="s">
-        <v>3085</v>
+        <v>3090</v>
       </c>
       <c r="E46" s="18" t="s">
         <v>999</v>
@@ -58015,7 +58454,7 @@
         <v>21</v>
       </c>
       <c r="L46" s="18" t="s">
-        <v>3006</v>
+        <v>2996</v>
       </c>
       <c r="M46" s="18"/>
       <c r="N46" s="18"/>
@@ -58059,7 +58498,7 @@
         <v>21</v>
       </c>
       <c r="L47" s="18" t="s">
-        <v>3006</v>
+        <v>2996</v>
       </c>
       <c r="M47" s="18"/>
       <c r="N47" s="18"/>
@@ -58075,13 +58514,13 @@
         <v>16</v>
       </c>
       <c r="C48" s="18" t="s">
-        <v>3095</v>
+        <v>3092</v>
       </c>
       <c r="D48" s="18" t="s">
-        <v>3096</v>
+        <v>3093</v>
       </c>
       <c r="E48" s="18" t="s">
-        <v>3097</v>
+        <v>3094</v>
       </c>
       <c r="F48" s="19">
         <v>4</v>
@@ -58103,7 +58542,7 @@
         <v>21</v>
       </c>
       <c r="L48" s="18" t="s">
-        <v>3006</v>
+        <v>2996</v>
       </c>
       <c r="M48" s="18"/>
       <c r="N48" s="18"/>
@@ -58137,7 +58576,7 @@
         <v>0</v>
       </c>
       <c r="I49" s="21">
-        <f t="shared" ref="I49" si="2">G49-H49</f>
+        <f>G49-H49</f>
         <v>750</v>
       </c>
       <c r="J49" s="20" t="s">
@@ -58171,47 +58610,47 @@
         <v>39</v>
       </c>
       <c r="G51" s="1">
-        <f t="shared" ref="G51:Q51" si="3">SUBTOTAL(9,G3:G49)</f>
+        <f t="shared" ref="G51:Q51" si="2">SUBTOTAL(9,G3:G49)</f>
         <v>40921</v>
       </c>
       <c r="H51" s="1">
-        <f t="shared" si="3"/>
+        <f t="shared" si="2"/>
         <v>1280</v>
       </c>
       <c r="I51" s="1">
-        <f t="shared" si="3"/>
+        <f t="shared" si="2"/>
         <v>39641</v>
       </c>
       <c r="J51" s="1">
-        <f t="shared" si="3"/>
+        <f t="shared" si="2"/>
         <v>0</v>
       </c>
       <c r="K51" s="1">
-        <f t="shared" si="3"/>
+        <f t="shared" si="2"/>
         <v>0</v>
       </c>
       <c r="L51" s="1">
-        <f t="shared" si="3"/>
+        <f t="shared" si="2"/>
         <v>0</v>
       </c>
       <c r="M51" s="1">
-        <f t="shared" si="3"/>
+        <f t="shared" si="2"/>
         <v>0</v>
       </c>
       <c r="N51" s="1">
-        <f t="shared" si="3"/>
+        <f t="shared" si="2"/>
         <v>0</v>
       </c>
       <c r="O51" s="1">
-        <f t="shared" si="3"/>
+        <f t="shared" si="2"/>
         <v>0</v>
       </c>
       <c r="P51" s="1">
-        <f t="shared" si="3"/>
+        <f t="shared" si="2"/>
         <v>0</v>
       </c>
       <c r="Q51" s="1">
-        <f t="shared" si="3"/>
+        <f t="shared" si="2"/>
         <v>47</v>
       </c>
     </row>
@@ -58225,10 +58664,10 @@
       <c r="A53" s="1" t="s">
         <v>16</v>
       </c>
-      <c r="C53" s="45" t="s">
+      <c r="C53" s="47" t="s">
         <v>89</v>
       </c>
-      <c r="D53" s="45"/>
+      <c r="D53" s="47"/>
       <c r="E53" s="4" t="s">
         <v>90</v>
       </c>
@@ -58251,16 +58690,16 @@
     </row>
     <row r="54" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A54" t="s">
-        <v>3006</v>
+        <v>2996</v>
       </c>
       <c r="B54" s="3" t="s">
         <v>93</v>
       </c>
-      <c r="C54" s="46">
+      <c r="C54" s="48">
         <f>SUMIFS(I$3:I$49,B$3:B$49,A$53,L$3:L$49,A$54)</f>
         <v>38441</v>
       </c>
-      <c r="D54" s="46"/>
+      <c r="D54" s="48"/>
       <c r="E54" s="3">
         <f>SUMIFS(Q$3:Q$49,B$3:B$49,A$53,L$3:L$49,A$54)</f>
         <v>45</v>
@@ -58295,10 +58734,10 @@
       <c r="B55" s="2" t="s">
         <v>97</v>
       </c>
-      <c r="C55" s="47">
+      <c r="C55" s="49">
         <v>0</v>
       </c>
-      <c r="D55" s="47"/>
+      <c r="D55" s="49"/>
       <c r="K55" t="s">
         <v>98</v>
       </c>
@@ -58322,11 +58761,11 @@
       <c r="B56" s="2" t="s">
         <v>99</v>
       </c>
-      <c r="C56" s="47">
+      <c r="C56" s="49">
         <f>-SUMIFS(I$3:I$49,B$3:B$49,A$53,P$3:P$49,"xx",N$3:N$49,"x")</f>
         <v>-750</v>
       </c>
-      <c r="D56" s="47"/>
+      <c r="D56" s="49"/>
       <c r="E56" s="2">
         <f>SUMIFS(Q$3:Q$49,B$3:B$49,A$53,P$3:P$49,"xx",N$3:N$49,"x")</f>
         <v>1</v>
@@ -58354,11 +58793,11 @@
       <c r="B57" s="4" t="s">
         <v>101</v>
       </c>
-      <c r="C57" s="45">
+      <c r="C57" s="47">
         <f>SUBTOTAL(9,C54:C56)</f>
         <v>37691</v>
       </c>
-      <c r="D57" s="45"/>
+      <c r="D57" s="47"/>
       <c r="E57">
         <f>E54</f>
         <v>45</v>
@@ -58367,7 +58806,7 @@
         <v>102</v>
       </c>
       <c r="O57" t="s">
-        <v>3105</v>
+        <v>3095</v>
       </c>
       <c r="P57">
         <f>L84</f>
@@ -58378,8 +58817,8 @@
       <c r="B58" s="2" t="s">
         <v>104</v>
       </c>
-      <c r="C58" s="43"/>
-      <c r="D58" s="43"/>
+      <c r="C58" s="45"/>
+      <c r="D58" s="45"/>
       <c r="K58" s="2" t="s">
         <v>105</v>
       </c>
@@ -58401,8 +58840,8 @@
       <c r="B59" s="8" t="s">
         <v>107</v>
       </c>
-      <c r="C59" s="43"/>
-      <c r="D59" s="43"/>
+      <c r="C59" s="45"/>
+      <c r="D59" s="45"/>
       <c r="L59" s="9">
         <f>SUBTOTAL(9,L54:L58)</f>
         <v>18525</v>
@@ -58423,11 +58862,11 @@
       <c r="B61" s="1" t="s">
         <v>108</v>
       </c>
-      <c r="C61" s="44">
+      <c r="C61" s="46">
         <f>C57+C58+C59</f>
         <v>37691</v>
       </c>
-      <c r="D61" s="44"/>
+      <c r="D61" s="46"/>
       <c r="E61" s="1" t="s">
         <v>109</v>
       </c>
@@ -58458,10 +58897,10 @@
       <c r="A63" s="1" t="s">
         <v>16</v>
       </c>
-      <c r="C63" s="45" t="s">
+      <c r="C63" s="47" t="s">
         <v>89</v>
       </c>
-      <c r="D63" s="45"/>
+      <c r="D63" s="47"/>
       <c r="E63" s="4" t="s">
         <v>90</v>
       </c>
@@ -58484,11 +58923,11 @@
       <c r="B64" s="3" t="s">
         <v>93</v>
       </c>
-      <c r="C64" s="46">
+      <c r="C64" s="48">
         <f>SUMIFS(I$3:I$49,B$3:B$49,A$63,L$3:L$49,A$64)</f>
         <v>450</v>
       </c>
-      <c r="D64" s="46"/>
+      <c r="D64" s="48"/>
       <c r="E64" s="3">
         <f>SUMIFS(Q$3:Q$49,B$3:B$49,A$63,L$3:L$49,A$64)</f>
         <v>1</v>
@@ -58504,10 +58943,10 @@
       <c r="B65" s="2" t="s">
         <v>97</v>
       </c>
-      <c r="C65" s="47">
+      <c r="C65" s="49">
         <v>0</v>
       </c>
-      <c r="D65" s="47"/>
+      <c r="D65" s="49"/>
       <c r="K65" s="2" t="s">
         <v>102</v>
       </c>
@@ -58516,8 +58955,8 @@
       <c r="B66" s="2" t="s">
         <v>99</v>
       </c>
-      <c r="C66" s="47"/>
-      <c r="D66" s="47"/>
+      <c r="C66" s="49"/>
+      <c r="D66" s="49"/>
       <c r="E66" s="2"/>
       <c r="K66" s="2" t="s">
         <v>105</v>
@@ -58527,17 +58966,17 @@
       <c r="B67" s="4" t="s">
         <v>101</v>
       </c>
-      <c r="C67" s="45">
+      <c r="C67" s="47">
         <f>SUBTOTAL(9,C64:C66)</f>
         <v>450</v>
       </c>
-      <c r="D67" s="45"/>
+      <c r="D67" s="47"/>
       <c r="E67">
         <f>E64</f>
         <v>1</v>
       </c>
       <c r="K67" s="2" t="s">
-        <v>3104</v>
+        <v>3026</v>
       </c>
       <c r="L67" s="29">
         <v>-475</v>
@@ -58550,8 +58989,8 @@
       <c r="B68" s="2" t="s">
         <v>104</v>
       </c>
-      <c r="C68" s="43"/>
-      <c r="D68" s="43"/>
+      <c r="C68" s="45"/>
+      <c r="D68" s="45"/>
       <c r="L68" s="9">
         <f>SUBTOTAL(9,L62:L66)</f>
         <v>10016</v>
@@ -58565,8 +59004,8 @@
       <c r="B69" s="8" t="s">
         <v>107</v>
       </c>
-      <c r="C69" s="43"/>
-      <c r="D69" s="43"/>
+      <c r="C69" s="45"/>
+      <c r="D69" s="45"/>
     </row>
     <row r="70" spans="2:13" x14ac:dyDescent="0.25">
       <c r="K70" s="7" t="s">
@@ -58583,11 +59022,11 @@
       <c r="B71" s="1" t="s">
         <v>108</v>
       </c>
-      <c r="C71" s="44">
+      <c r="C71" s="46">
         <f>C67+C68+C69</f>
         <v>450</v>
       </c>
-      <c r="D71" s="44"/>
+      <c r="D71" s="46"/>
       <c r="E71" s="1" t="s">
         <v>109</v>
       </c>
@@ -58643,7 +59082,7 @@
     </row>
     <row r="78" spans="2:13" x14ac:dyDescent="0.25">
       <c r="K78" s="7" t="s">
-        <v>3017</v>
+        <v>2998</v>
       </c>
       <c r="L78" s="7" t="s">
         <v>91</v>
@@ -58704,39 +59143,3206 @@
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A2:P49" xr:uid="{00000000-0009-0000-0000-000018000000}">
+  <autoFilter ref="A2:P49" xr:uid="{00000000-0009-0000-0000-000017000000}">
     <sortState xmlns:xlrd2="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata2" ref="A3:P49">
       <sortCondition ref="J2:J49"/>
     </sortState>
   </autoFilter>
   <mergeCells count="16">
-    <mergeCell ref="C53:D53"/>
-    <mergeCell ref="C54:D54"/>
-    <mergeCell ref="C55:D55"/>
-    <mergeCell ref="C56:D56"/>
-    <mergeCell ref="C57:D57"/>
-    <mergeCell ref="C58:D58"/>
-    <mergeCell ref="C59:D59"/>
-    <mergeCell ref="C61:D61"/>
-    <mergeCell ref="C63:D63"/>
-    <mergeCell ref="C64:D64"/>
     <mergeCell ref="C71:D71"/>
     <mergeCell ref="C65:D65"/>
     <mergeCell ref="C66:D66"/>
     <mergeCell ref="C67:D67"/>
     <mergeCell ref="C68:D68"/>
     <mergeCell ref="C69:D69"/>
+    <mergeCell ref="C58:D58"/>
+    <mergeCell ref="C59:D59"/>
+    <mergeCell ref="C61:D61"/>
+    <mergeCell ref="C63:D63"/>
+    <mergeCell ref="C64:D64"/>
+    <mergeCell ref="C53:D53"/>
+    <mergeCell ref="C54:D54"/>
+    <mergeCell ref="C55:D55"/>
+    <mergeCell ref="C56:D56"/>
+    <mergeCell ref="C57:D57"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="0.75" bottom="0.5" header="0.5" footer="0.75"/>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet25.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-1900-000000000000}">
+  <dimension ref="A2:R94"/>
+  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <cols>
+    <col min="1" max="1" width="12.7109375" customWidth="1"/>
+    <col min="2" max="2" width="17.7109375" customWidth="1"/>
+    <col min="3" max="3" width="30.28515625" customWidth="1"/>
+    <col min="4" max="4" width="9.85546875" customWidth="1"/>
+    <col min="5" max="5" width="63.7109375" customWidth="1"/>
+    <col min="6" max="6" width="10.85546875" customWidth="1"/>
+    <col min="7" max="7" width="9.140625" customWidth="1"/>
+    <col min="8" max="8" width="9.5703125" customWidth="1"/>
+    <col min="9" max="9" width="10.5703125" customWidth="1"/>
+    <col min="10" max="10" width="9.7109375" customWidth="1"/>
+    <col min="11" max="11" width="10.85546875" customWidth="1"/>
+    <col min="12" max="12" width="10.42578125" customWidth="1"/>
+    <col min="13" max="13" width="13.85546875" customWidth="1"/>
+    <col min="14" max="14" width="9.7109375" customWidth="1"/>
+    <col min="15" max="15" width="10.42578125" customWidth="1"/>
+    <col min="16" max="16" width="7" bestFit="1" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="2" spans="1:18" x14ac:dyDescent="0.25">
+      <c r="A2" s="17" t="s">
+        <v>0</v>
+      </c>
+      <c r="B2" s="17" t="s">
+        <v>1</v>
+      </c>
+      <c r="C2" s="17" t="s">
+        <v>2</v>
+      </c>
+      <c r="D2" s="17" t="s">
+        <v>3</v>
+      </c>
+      <c r="E2" s="17" t="s">
+        <v>4</v>
+      </c>
+      <c r="F2" s="17" t="s">
+        <v>5</v>
+      </c>
+      <c r="G2" s="17" t="s">
+        <v>6</v>
+      </c>
+      <c r="H2" s="17" t="s">
+        <v>7</v>
+      </c>
+      <c r="I2" s="17" t="s">
+        <v>8</v>
+      </c>
+      <c r="J2" s="17" t="s">
+        <v>9</v>
+      </c>
+      <c r="K2" s="17" t="s">
+        <v>10</v>
+      </c>
+      <c r="L2" s="17" t="s">
+        <v>11</v>
+      </c>
+      <c r="M2" s="17" t="s">
+        <v>12</v>
+      </c>
+      <c r="N2" s="17" t="s">
+        <v>13</v>
+      </c>
+      <c r="O2" s="17" t="s">
+        <v>14</v>
+      </c>
+      <c r="P2" s="17" t="s">
+        <v>15</v>
+      </c>
+      <c r="Q2" s="18"/>
+    </row>
+    <row r="3" spans="1:18" x14ac:dyDescent="0.25">
+      <c r="A3" s="18"/>
+      <c r="B3" s="18" t="s">
+        <v>16</v>
+      </c>
+      <c r="C3" s="18" t="s">
+        <v>3145</v>
+      </c>
+      <c r="D3" s="18" t="s">
+        <v>3146</v>
+      </c>
+      <c r="E3" s="18" t="s">
+        <v>3147</v>
+      </c>
+      <c r="F3" s="19">
+        <v>9</v>
+      </c>
+      <c r="G3" s="19">
+        <v>820</v>
+      </c>
+      <c r="H3" s="19">
+        <v>30</v>
+      </c>
+      <c r="I3" s="19">
+        <f>G3-H3</f>
+        <v>790</v>
+      </c>
+      <c r="J3" s="18" t="s">
+        <v>20</v>
+      </c>
+      <c r="K3" s="18" t="s">
+        <v>21</v>
+      </c>
+      <c r="L3" s="18" t="s">
+        <v>3107</v>
+      </c>
+      <c r="M3" s="18"/>
+      <c r="N3" s="18"/>
+      <c r="O3" s="18"/>
+      <c r="P3" s="18"/>
+      <c r="Q3" s="18">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="4" spans="1:18" x14ac:dyDescent="0.25">
+      <c r="A4" s="18"/>
+      <c r="B4" s="18" t="s">
+        <v>16</v>
+      </c>
+      <c r="C4" s="18" t="s">
+        <v>3108</v>
+      </c>
+      <c r="D4" s="18" t="s">
+        <v>3109</v>
+      </c>
+      <c r="E4" s="18" t="s">
+        <v>3110</v>
+      </c>
+      <c r="F4" s="19">
+        <v>7</v>
+      </c>
+      <c r="G4" s="19">
+        <v>720</v>
+      </c>
+      <c r="H4" s="19">
+        <v>30</v>
+      </c>
+      <c r="I4" s="19">
+        <f>G4-H4</f>
+        <v>690</v>
+      </c>
+      <c r="J4" s="18" t="s">
+        <v>3111</v>
+      </c>
+      <c r="K4" s="18" t="s">
+        <v>21</v>
+      </c>
+      <c r="L4" s="18" t="s">
+        <v>3107</v>
+      </c>
+      <c r="M4" s="18"/>
+      <c r="N4" s="18"/>
+      <c r="O4" s="18"/>
+      <c r="P4" s="18"/>
+      <c r="Q4" s="18">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="5" spans="1:18" x14ac:dyDescent="0.25">
+      <c r="A5" s="18"/>
+      <c r="B5" s="18" t="s">
+        <v>16</v>
+      </c>
+      <c r="C5" s="18" t="s">
+        <v>3112</v>
+      </c>
+      <c r="D5" s="18" t="s">
+        <v>3113</v>
+      </c>
+      <c r="E5" s="18" t="s">
+        <v>3114</v>
+      </c>
+      <c r="F5" s="19">
+        <v>7</v>
+      </c>
+      <c r="G5" s="19">
+        <v>0</v>
+      </c>
+      <c r="H5" s="19">
+        <v>30</v>
+      </c>
+      <c r="I5" s="19">
+        <f>-H5</f>
+        <v>-30</v>
+      </c>
+      <c r="J5" s="18" t="s">
+        <v>3111</v>
+      </c>
+      <c r="K5" s="18" t="s">
+        <v>21</v>
+      </c>
+      <c r="L5" s="18" t="s">
+        <v>3107</v>
+      </c>
+      <c r="M5" s="18"/>
+      <c r="N5" s="18"/>
+      <c r="O5" s="18"/>
+      <c r="P5" s="18"/>
+      <c r="Q5" s="18">
+        <v>1</v>
+      </c>
+      <c r="R5" s="6">
+        <f>H5</f>
+        <v>30</v>
+      </c>
+    </row>
+    <row r="6" spans="1:18" x14ac:dyDescent="0.25">
+      <c r="A6" s="18"/>
+      <c r="B6" s="18" t="s">
+        <v>16</v>
+      </c>
+      <c r="C6" s="18" t="s">
+        <v>3115</v>
+      </c>
+      <c r="D6" s="18" t="s">
+        <v>3116</v>
+      </c>
+      <c r="E6" s="18" t="s">
+        <v>3117</v>
+      </c>
+      <c r="F6" s="19">
+        <v>7</v>
+      </c>
+      <c r="G6" s="19">
+        <v>1980</v>
+      </c>
+      <c r="H6" s="19">
+        <v>30</v>
+      </c>
+      <c r="I6" s="19">
+        <f>G6-H6</f>
+        <v>1950</v>
+      </c>
+      <c r="J6" s="18" t="s">
+        <v>3111</v>
+      </c>
+      <c r="K6" s="18" t="s">
+        <v>21</v>
+      </c>
+      <c r="L6" s="18" t="s">
+        <v>3107</v>
+      </c>
+      <c r="M6" s="18"/>
+      <c r="N6" s="18"/>
+      <c r="O6" s="18"/>
+      <c r="P6" s="18"/>
+      <c r="Q6" s="18">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="7" spans="1:18" x14ac:dyDescent="0.25">
+      <c r="A7" s="18"/>
+      <c r="B7" s="18" t="s">
+        <v>16</v>
+      </c>
+      <c r="C7" s="18" t="s">
+        <v>3118</v>
+      </c>
+      <c r="D7" s="18" t="s">
+        <v>3119</v>
+      </c>
+      <c r="E7" s="18" t="s">
+        <v>3120</v>
+      </c>
+      <c r="F7" s="18" t="s">
+        <v>217</v>
+      </c>
+      <c r="G7" s="19">
+        <v>945</v>
+      </c>
+      <c r="H7" s="19">
+        <v>25</v>
+      </c>
+      <c r="I7" s="19">
+        <f>G7-H7</f>
+        <v>920</v>
+      </c>
+      <c r="J7" s="18" t="s">
+        <v>3111</v>
+      </c>
+      <c r="K7" s="18" t="s">
+        <v>21</v>
+      </c>
+      <c r="L7" s="18" t="s">
+        <v>3107</v>
+      </c>
+      <c r="M7" s="18"/>
+      <c r="N7" s="18"/>
+      <c r="O7" s="18"/>
+      <c r="P7" s="18"/>
+      <c r="Q7" s="18">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="8" spans="1:18" x14ac:dyDescent="0.25">
+      <c r="A8" s="18"/>
+      <c r="B8" s="18" t="s">
+        <v>16</v>
+      </c>
+      <c r="C8" s="18" t="s">
+        <v>2244</v>
+      </c>
+      <c r="D8" s="18" t="s">
+        <v>3121</v>
+      </c>
+      <c r="E8" s="18" t="s">
+        <v>1016</v>
+      </c>
+      <c r="F8" s="18" t="s">
+        <v>88</v>
+      </c>
+      <c r="G8" s="19">
+        <v>0</v>
+      </c>
+      <c r="H8" s="19">
+        <v>25</v>
+      </c>
+      <c r="I8" s="19">
+        <f>-H8</f>
+        <v>-25</v>
+      </c>
+      <c r="J8" s="18" t="s">
+        <v>3111</v>
+      </c>
+      <c r="K8" s="18" t="s">
+        <v>21</v>
+      </c>
+      <c r="L8" s="18" t="s">
+        <v>3107</v>
+      </c>
+      <c r="M8" s="18"/>
+      <c r="N8" s="18"/>
+      <c r="O8" s="18"/>
+      <c r="P8" s="18"/>
+      <c r="Q8" s="18">
+        <v>1</v>
+      </c>
+      <c r="R8" s="6">
+        <f>H8</f>
+        <v>25</v>
+      </c>
+    </row>
+    <row r="9" spans="1:18" s="42" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A9" s="40"/>
+      <c r="B9" s="40" t="s">
+        <v>16</v>
+      </c>
+      <c r="C9" s="40" t="s">
+        <v>110</v>
+      </c>
+      <c r="D9" s="40" t="s">
+        <v>3124</v>
+      </c>
+      <c r="E9" s="40" t="s">
+        <v>3125</v>
+      </c>
+      <c r="F9" s="40" t="s">
+        <v>259</v>
+      </c>
+      <c r="G9" s="41">
+        <v>35</v>
+      </c>
+      <c r="H9" s="41">
+        <v>35</v>
+      </c>
+      <c r="I9" s="41">
+        <f t="shared" ref="I9:I25" si="0">G9-H9</f>
+        <v>0</v>
+      </c>
+      <c r="J9" s="40" t="s">
+        <v>3111</v>
+      </c>
+      <c r="K9" s="40" t="s">
+        <v>21</v>
+      </c>
+      <c r="L9" s="40" t="s">
+        <v>3107</v>
+      </c>
+      <c r="M9" s="40" t="s">
+        <v>49</v>
+      </c>
+      <c r="N9" s="40"/>
+      <c r="O9" s="40"/>
+      <c r="P9" s="40"/>
+      <c r="Q9" s="40">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="10" spans="1:18" x14ac:dyDescent="0.25">
+      <c r="A10" s="18"/>
+      <c r="B10" s="18" t="s">
+        <v>16</v>
+      </c>
+      <c r="C10" s="18" t="s">
+        <v>3135</v>
+      </c>
+      <c r="D10" s="18" t="s">
+        <v>3136</v>
+      </c>
+      <c r="E10" s="18" t="s">
+        <v>3137</v>
+      </c>
+      <c r="F10" s="19">
+        <v>6</v>
+      </c>
+      <c r="G10" s="19">
+        <v>1805</v>
+      </c>
+      <c r="H10" s="19">
+        <v>25</v>
+      </c>
+      <c r="I10" s="19">
+        <f t="shared" si="0"/>
+        <v>1780</v>
+      </c>
+      <c r="J10" s="18" t="s">
+        <v>3111</v>
+      </c>
+      <c r="K10" s="18" t="s">
+        <v>21</v>
+      </c>
+      <c r="L10" s="18" t="s">
+        <v>3107</v>
+      </c>
+      <c r="M10" s="18"/>
+      <c r="N10" s="18"/>
+      <c r="O10" s="18"/>
+      <c r="P10" s="18"/>
+      <c r="Q10" s="18">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="11" spans="1:18" x14ac:dyDescent="0.25">
+      <c r="A11" s="18"/>
+      <c r="B11" s="18" t="s">
+        <v>16</v>
+      </c>
+      <c r="C11" s="18" t="s">
+        <v>3139</v>
+      </c>
+      <c r="D11" s="18" t="s">
+        <v>3140</v>
+      </c>
+      <c r="E11" s="18" t="s">
+        <v>3141</v>
+      </c>
+      <c r="F11" s="19">
+        <v>7</v>
+      </c>
+      <c r="G11" s="19">
+        <v>830</v>
+      </c>
+      <c r="H11" s="19">
+        <v>30</v>
+      </c>
+      <c r="I11" s="19">
+        <f t="shared" si="0"/>
+        <v>800</v>
+      </c>
+      <c r="J11" s="18" t="s">
+        <v>3111</v>
+      </c>
+      <c r="K11" s="18" t="s">
+        <v>21</v>
+      </c>
+      <c r="L11" s="18" t="s">
+        <v>3107</v>
+      </c>
+      <c r="M11" s="18"/>
+      <c r="N11" s="18"/>
+      <c r="O11" s="18"/>
+      <c r="P11" s="18"/>
+      <c r="Q11" s="18">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="12" spans="1:18" x14ac:dyDescent="0.25">
+      <c r="A12" s="18"/>
+      <c r="B12" s="18" t="s">
+        <v>16</v>
+      </c>
+      <c r="C12" s="18" t="s">
+        <v>3142</v>
+      </c>
+      <c r="D12" s="18" t="s">
+        <v>3143</v>
+      </c>
+      <c r="E12" s="18" t="s">
+        <v>3144</v>
+      </c>
+      <c r="F12" s="18" t="s">
+        <v>26</v>
+      </c>
+      <c r="G12" s="19">
+        <v>890</v>
+      </c>
+      <c r="H12" s="19">
+        <v>30</v>
+      </c>
+      <c r="I12" s="19">
+        <f t="shared" si="0"/>
+        <v>860</v>
+      </c>
+      <c r="J12" s="18" t="s">
+        <v>3111</v>
+      </c>
+      <c r="K12" s="18" t="s">
+        <v>21</v>
+      </c>
+      <c r="L12" s="18" t="s">
+        <v>3107</v>
+      </c>
+      <c r="M12" s="18"/>
+      <c r="N12" s="18"/>
+      <c r="O12" s="18"/>
+      <c r="P12" s="18"/>
+      <c r="Q12" s="18">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="13" spans="1:18" x14ac:dyDescent="0.25">
+      <c r="A13" s="18"/>
+      <c r="B13" s="18" t="s">
+        <v>16</v>
+      </c>
+      <c r="C13" s="18" t="s">
+        <v>3148</v>
+      </c>
+      <c r="D13" s="18" t="s">
+        <v>3149</v>
+      </c>
+      <c r="E13" s="18" t="s">
+        <v>3150</v>
+      </c>
+      <c r="F13" s="19">
+        <v>8</v>
+      </c>
+      <c r="G13" s="19">
+        <v>910</v>
+      </c>
+      <c r="H13" s="19">
+        <v>30</v>
+      </c>
+      <c r="I13" s="19">
+        <f t="shared" si="0"/>
+        <v>880</v>
+      </c>
+      <c r="J13" s="18" t="s">
+        <v>3111</v>
+      </c>
+      <c r="K13" s="18" t="s">
+        <v>21</v>
+      </c>
+      <c r="L13" s="18" t="s">
+        <v>3107</v>
+      </c>
+      <c r="M13" s="18"/>
+      <c r="N13" s="18"/>
+      <c r="O13" s="18"/>
+      <c r="P13" s="18"/>
+      <c r="Q13" s="18">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="14" spans="1:18" x14ac:dyDescent="0.25">
+      <c r="A14" s="18"/>
+      <c r="B14" s="18" t="s">
+        <v>16</v>
+      </c>
+      <c r="C14" s="18" t="s">
+        <v>3157</v>
+      </c>
+      <c r="D14" s="18" t="s">
+        <v>3158</v>
+      </c>
+      <c r="E14" s="18" t="s">
+        <v>3159</v>
+      </c>
+      <c r="F14" s="19">
+        <v>12</v>
+      </c>
+      <c r="G14" s="19">
+        <v>20</v>
+      </c>
+      <c r="H14" s="19">
+        <v>20</v>
+      </c>
+      <c r="I14" s="19">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+      <c r="J14" s="18" t="s">
+        <v>3111</v>
+      </c>
+      <c r="K14" s="18" t="s">
+        <v>21</v>
+      </c>
+      <c r="L14" s="18" t="s">
+        <v>3107</v>
+      </c>
+      <c r="M14" s="18"/>
+      <c r="N14" s="18"/>
+      <c r="O14" s="18"/>
+      <c r="P14" s="18"/>
+      <c r="Q14" s="18">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="15" spans="1:18" x14ac:dyDescent="0.25">
+      <c r="A15" s="18"/>
+      <c r="B15" s="18" t="s">
+        <v>16</v>
+      </c>
+      <c r="C15" s="18" t="s">
+        <v>3160</v>
+      </c>
+      <c r="D15" s="18" t="s">
+        <v>3161</v>
+      </c>
+      <c r="E15" s="18" t="s">
+        <v>3162</v>
+      </c>
+      <c r="F15" s="18" t="s">
+        <v>26</v>
+      </c>
+      <c r="G15" s="19">
+        <v>1460</v>
+      </c>
+      <c r="H15" s="19">
+        <v>30</v>
+      </c>
+      <c r="I15" s="19">
+        <f t="shared" si="0"/>
+        <v>1430</v>
+      </c>
+      <c r="J15" s="18" t="s">
+        <v>3111</v>
+      </c>
+      <c r="K15" s="18" t="s">
+        <v>21</v>
+      </c>
+      <c r="L15" s="18" t="s">
+        <v>3107</v>
+      </c>
+      <c r="M15" s="18"/>
+      <c r="N15" s="18"/>
+      <c r="O15" s="18"/>
+      <c r="P15" s="18"/>
+      <c r="Q15" s="18">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="16" spans="1:18" x14ac:dyDescent="0.25">
+      <c r="A16" s="18"/>
+      <c r="B16" s="18" t="s">
+        <v>16</v>
+      </c>
+      <c r="C16" s="18" t="s">
+        <v>3163</v>
+      </c>
+      <c r="D16" s="18" t="s">
+        <v>3164</v>
+      </c>
+      <c r="E16" s="18" t="s">
+        <v>3165</v>
+      </c>
+      <c r="F16" s="19">
+        <v>7</v>
+      </c>
+      <c r="G16" s="19">
+        <v>800</v>
+      </c>
+      <c r="H16" s="19">
+        <v>30</v>
+      </c>
+      <c r="I16" s="19">
+        <f t="shared" si="0"/>
+        <v>770</v>
+      </c>
+      <c r="J16" s="18" t="s">
+        <v>3111</v>
+      </c>
+      <c r="K16" s="18" t="s">
+        <v>21</v>
+      </c>
+      <c r="L16" s="18" t="s">
+        <v>3107</v>
+      </c>
+      <c r="M16" s="18"/>
+      <c r="N16" s="18"/>
+      <c r="O16" s="18"/>
+      <c r="P16" s="18"/>
+      <c r="Q16" s="18">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="17" spans="1:18" x14ac:dyDescent="0.25">
+      <c r="A17" s="18"/>
+      <c r="B17" s="18" t="s">
+        <v>16</v>
+      </c>
+      <c r="C17" s="18" t="s">
+        <v>3169</v>
+      </c>
+      <c r="D17" s="18" t="s">
+        <v>3170</v>
+      </c>
+      <c r="E17" s="18" t="s">
+        <v>3171</v>
+      </c>
+      <c r="F17" s="18" t="s">
+        <v>26</v>
+      </c>
+      <c r="G17" s="19">
+        <v>950</v>
+      </c>
+      <c r="H17" s="19">
+        <v>30</v>
+      </c>
+      <c r="I17" s="19">
+        <f t="shared" si="0"/>
+        <v>920</v>
+      </c>
+      <c r="J17" s="18" t="s">
+        <v>3111</v>
+      </c>
+      <c r="K17" s="18" t="s">
+        <v>21</v>
+      </c>
+      <c r="L17" s="18" t="s">
+        <v>3107</v>
+      </c>
+      <c r="M17" s="18"/>
+      <c r="N17" s="18"/>
+      <c r="O17" s="18"/>
+      <c r="P17" s="18"/>
+      <c r="Q17" s="18">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="18" spans="1:18" x14ac:dyDescent="0.25">
+      <c r="A18" s="18"/>
+      <c r="B18" s="18" t="s">
+        <v>16</v>
+      </c>
+      <c r="C18" s="18" t="s">
+        <v>3172</v>
+      </c>
+      <c r="D18" s="18" t="s">
+        <v>3173</v>
+      </c>
+      <c r="E18" s="18" t="s">
+        <v>607</v>
+      </c>
+      <c r="F18" s="18" t="s">
+        <v>26</v>
+      </c>
+      <c r="G18" s="19">
+        <v>790</v>
+      </c>
+      <c r="H18" s="19">
+        <v>30</v>
+      </c>
+      <c r="I18" s="19">
+        <f t="shared" si="0"/>
+        <v>760</v>
+      </c>
+      <c r="J18" s="18" t="s">
+        <v>3111</v>
+      </c>
+      <c r="K18" s="18" t="s">
+        <v>21</v>
+      </c>
+      <c r="L18" s="18" t="s">
+        <v>3107</v>
+      </c>
+      <c r="M18" s="18"/>
+      <c r="N18" s="18"/>
+      <c r="O18" s="18"/>
+      <c r="P18" s="18"/>
+      <c r="Q18" s="18">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="19" spans="1:18" x14ac:dyDescent="0.25">
+      <c r="A19" s="18"/>
+      <c r="B19" s="18" t="s">
+        <v>16</v>
+      </c>
+      <c r="C19" s="18" t="s">
+        <v>205</v>
+      </c>
+      <c r="D19" s="18" t="s">
+        <v>3189</v>
+      </c>
+      <c r="E19" s="18" t="s">
+        <v>207</v>
+      </c>
+      <c r="F19" s="19">
+        <v>7</v>
+      </c>
+      <c r="G19" s="19">
+        <v>850</v>
+      </c>
+      <c r="H19" s="19">
+        <v>30</v>
+      </c>
+      <c r="I19" s="19">
+        <f t="shared" si="0"/>
+        <v>820</v>
+      </c>
+      <c r="J19" s="18" t="s">
+        <v>3111</v>
+      </c>
+      <c r="K19" s="18" t="s">
+        <v>21</v>
+      </c>
+      <c r="L19" s="18" t="s">
+        <v>3107</v>
+      </c>
+      <c r="M19" s="18"/>
+      <c r="N19" s="18"/>
+      <c r="O19" s="18"/>
+      <c r="P19" s="18"/>
+      <c r="Q19" s="18">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="20" spans="1:18" x14ac:dyDescent="0.25">
+      <c r="A20" s="18"/>
+      <c r="B20" s="18" t="s">
+        <v>16</v>
+      </c>
+      <c r="C20" s="18" t="s">
+        <v>3190</v>
+      </c>
+      <c r="D20" s="18" t="s">
+        <v>3191</v>
+      </c>
+      <c r="E20" s="18" t="s">
+        <v>3192</v>
+      </c>
+      <c r="F20" s="19">
+        <v>7</v>
+      </c>
+      <c r="G20" s="19">
+        <v>1510</v>
+      </c>
+      <c r="H20" s="19">
+        <v>30</v>
+      </c>
+      <c r="I20" s="19">
+        <f t="shared" si="0"/>
+        <v>1480</v>
+      </c>
+      <c r="J20" s="18" t="s">
+        <v>3111</v>
+      </c>
+      <c r="K20" s="18" t="s">
+        <v>21</v>
+      </c>
+      <c r="L20" s="18" t="s">
+        <v>3107</v>
+      </c>
+      <c r="M20" s="18"/>
+      <c r="N20" s="18"/>
+      <c r="O20" s="18"/>
+      <c r="P20" s="18"/>
+      <c r="Q20" s="18">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="21" spans="1:18" x14ac:dyDescent="0.25">
+      <c r="A21" s="18"/>
+      <c r="B21" s="18" t="s">
+        <v>16</v>
+      </c>
+      <c r="C21" s="18" t="s">
+        <v>3193</v>
+      </c>
+      <c r="D21" s="18" t="s">
+        <v>3194</v>
+      </c>
+      <c r="E21" s="18" t="s">
+        <v>3195</v>
+      </c>
+      <c r="F21" s="18" t="s">
+        <v>128</v>
+      </c>
+      <c r="G21" s="19">
+        <v>775</v>
+      </c>
+      <c r="H21" s="19">
+        <v>35</v>
+      </c>
+      <c r="I21" s="19">
+        <f t="shared" si="0"/>
+        <v>740</v>
+      </c>
+      <c r="J21" s="18" t="s">
+        <v>3111</v>
+      </c>
+      <c r="K21" s="18" t="s">
+        <v>21</v>
+      </c>
+      <c r="L21" s="18" t="s">
+        <v>3107</v>
+      </c>
+      <c r="M21" s="18"/>
+      <c r="N21" s="18"/>
+      <c r="O21" s="18"/>
+      <c r="P21" s="18"/>
+      <c r="Q21" s="18">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="22" spans="1:18" x14ac:dyDescent="0.25">
+      <c r="A22" s="18"/>
+      <c r="B22" s="18" t="s">
+        <v>16</v>
+      </c>
+      <c r="C22" s="18" t="s">
+        <v>701</v>
+      </c>
+      <c r="D22" s="18" t="s">
+        <v>3196</v>
+      </c>
+      <c r="E22" s="18" t="s">
+        <v>703</v>
+      </c>
+      <c r="F22" s="18" t="s">
+        <v>217</v>
+      </c>
+      <c r="G22" s="19">
+        <v>825</v>
+      </c>
+      <c r="H22" s="19">
+        <v>25</v>
+      </c>
+      <c r="I22" s="19">
+        <f t="shared" si="0"/>
+        <v>800</v>
+      </c>
+      <c r="J22" s="18" t="s">
+        <v>3111</v>
+      </c>
+      <c r="K22" s="18" t="s">
+        <v>21</v>
+      </c>
+      <c r="L22" s="18" t="s">
+        <v>3107</v>
+      </c>
+      <c r="M22" s="18"/>
+      <c r="N22" s="18"/>
+      <c r="O22" s="18"/>
+      <c r="P22" s="18"/>
+      <c r="Q22" s="18">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="23" spans="1:18" x14ac:dyDescent="0.25">
+      <c r="A23" s="18"/>
+      <c r="B23" s="18" t="s">
+        <v>16</v>
+      </c>
+      <c r="C23" s="18" t="s">
+        <v>3206</v>
+      </c>
+      <c r="D23" s="18" t="s">
+        <v>3207</v>
+      </c>
+      <c r="E23" s="18" t="s">
+        <v>3208</v>
+      </c>
+      <c r="F23" s="18" t="s">
+        <v>217</v>
+      </c>
+      <c r="G23" s="19">
+        <v>1555</v>
+      </c>
+      <c r="H23" s="19">
+        <v>25</v>
+      </c>
+      <c r="I23" s="19">
+        <f t="shared" si="0"/>
+        <v>1530</v>
+      </c>
+      <c r="J23" s="18" t="s">
+        <v>3111</v>
+      </c>
+      <c r="K23" s="18" t="s">
+        <v>21</v>
+      </c>
+      <c r="L23" s="18" t="s">
+        <v>3107</v>
+      </c>
+      <c r="M23" s="18"/>
+      <c r="N23" s="18"/>
+      <c r="O23" s="18"/>
+      <c r="P23" s="18"/>
+      <c r="Q23" s="18">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="24" spans="1:18" x14ac:dyDescent="0.25">
+      <c r="A24" s="18"/>
+      <c r="B24" s="18" t="s">
+        <v>16</v>
+      </c>
+      <c r="C24" s="18" t="s">
+        <v>1870</v>
+      </c>
+      <c r="D24" s="18" t="s">
+        <v>3216</v>
+      </c>
+      <c r="E24" s="18" t="s">
+        <v>1872</v>
+      </c>
+      <c r="F24" s="18" t="s">
+        <v>113</v>
+      </c>
+      <c r="G24" s="19">
+        <v>805</v>
+      </c>
+      <c r="H24" s="19">
+        <v>35</v>
+      </c>
+      <c r="I24" s="19">
+        <f t="shared" si="0"/>
+        <v>770</v>
+      </c>
+      <c r="J24" s="18" t="s">
+        <v>3111</v>
+      </c>
+      <c r="K24" s="18" t="s">
+        <v>21</v>
+      </c>
+      <c r="L24" s="18" t="s">
+        <v>3107</v>
+      </c>
+      <c r="M24" s="18"/>
+      <c r="N24" s="18"/>
+      <c r="O24" s="18"/>
+      <c r="P24" s="18"/>
+      <c r="Q24" s="18">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="25" spans="1:18" x14ac:dyDescent="0.25">
+      <c r="A25" s="18"/>
+      <c r="B25" s="18" t="s">
+        <v>16</v>
+      </c>
+      <c r="C25" s="18" t="s">
+        <v>3217</v>
+      </c>
+      <c r="D25" s="18" t="s">
+        <v>3218</v>
+      </c>
+      <c r="E25" s="18" t="s">
+        <v>3219</v>
+      </c>
+      <c r="F25" s="18" t="s">
+        <v>26</v>
+      </c>
+      <c r="G25" s="19">
+        <v>850</v>
+      </c>
+      <c r="H25" s="19">
+        <v>30</v>
+      </c>
+      <c r="I25" s="19">
+        <f t="shared" si="0"/>
+        <v>820</v>
+      </c>
+      <c r="J25" s="18" t="s">
+        <v>3111</v>
+      </c>
+      <c r="K25" s="18" t="s">
+        <v>21</v>
+      </c>
+      <c r="L25" s="18" t="s">
+        <v>3107</v>
+      </c>
+      <c r="M25" s="18"/>
+      <c r="N25" s="18"/>
+      <c r="O25" s="18"/>
+      <c r="P25" s="18"/>
+      <c r="Q25" s="18">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="26" spans="1:18" x14ac:dyDescent="0.25">
+      <c r="A26" s="18"/>
+      <c r="B26" s="18" t="s">
+        <v>16</v>
+      </c>
+      <c r="C26" s="18" t="s">
+        <v>3236</v>
+      </c>
+      <c r="D26" s="18" t="s">
+        <v>3237</v>
+      </c>
+      <c r="E26" s="18" t="s">
+        <v>3238</v>
+      </c>
+      <c r="F26" s="19">
+        <v>8</v>
+      </c>
+      <c r="G26" s="19">
+        <v>0</v>
+      </c>
+      <c r="H26" s="19">
+        <v>25</v>
+      </c>
+      <c r="I26" s="19">
+        <f>-H26</f>
+        <v>-25</v>
+      </c>
+      <c r="J26" s="18" t="s">
+        <v>3111</v>
+      </c>
+      <c r="K26" s="18" t="s">
+        <v>21</v>
+      </c>
+      <c r="L26" s="18" t="s">
+        <v>3107</v>
+      </c>
+      <c r="M26" s="18"/>
+      <c r="N26" s="18"/>
+      <c r="O26" s="18"/>
+      <c r="P26" s="18"/>
+      <c r="Q26" s="18">
+        <v>1</v>
+      </c>
+      <c r="R26" s="6">
+        <f>H26</f>
+        <v>25</v>
+      </c>
+    </row>
+    <row r="27" spans="1:18" x14ac:dyDescent="0.25">
+      <c r="A27" s="18"/>
+      <c r="B27" s="18" t="s">
+        <v>16</v>
+      </c>
+      <c r="C27" s="18" t="s">
+        <v>147</v>
+      </c>
+      <c r="D27" s="18" t="s">
+        <v>3122</v>
+      </c>
+      <c r="E27" s="18" t="s">
+        <v>3123</v>
+      </c>
+      <c r="F27" s="18" t="s">
+        <v>68</v>
+      </c>
+      <c r="G27" s="19">
+        <v>1170</v>
+      </c>
+      <c r="H27" s="19">
+        <v>20</v>
+      </c>
+      <c r="I27" s="19">
+        <f>G27-H27</f>
+        <v>1150</v>
+      </c>
+      <c r="J27" s="18" t="s">
+        <v>21</v>
+      </c>
+      <c r="K27" s="18" t="s">
+        <v>21</v>
+      </c>
+      <c r="L27" s="18" t="s">
+        <v>3107</v>
+      </c>
+      <c r="M27" s="18"/>
+      <c r="N27" s="18"/>
+      <c r="O27" s="18"/>
+      <c r="P27" s="18"/>
+      <c r="Q27" s="18">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="28" spans="1:18" x14ac:dyDescent="0.25">
+      <c r="A28" s="18"/>
+      <c r="B28" s="18" t="s">
+        <v>16</v>
+      </c>
+      <c r="C28" s="18" t="s">
+        <v>65</v>
+      </c>
+      <c r="D28" s="18" t="s">
+        <v>3132</v>
+      </c>
+      <c r="E28" s="18" t="s">
+        <v>67</v>
+      </c>
+      <c r="F28" s="18" t="s">
+        <v>68</v>
+      </c>
+      <c r="G28" s="19">
+        <v>0</v>
+      </c>
+      <c r="H28" s="19">
+        <v>20</v>
+      </c>
+      <c r="I28" s="19">
+        <f>-H28</f>
+        <v>-20</v>
+      </c>
+      <c r="J28" s="18" t="s">
+        <v>21</v>
+      </c>
+      <c r="K28" s="18" t="s">
+        <v>21</v>
+      </c>
+      <c r="L28" s="18" t="s">
+        <v>3107</v>
+      </c>
+      <c r="M28" s="18"/>
+      <c r="N28" s="18"/>
+      <c r="O28" s="18"/>
+      <c r="P28" s="18"/>
+      <c r="Q28" s="18">
+        <v>1</v>
+      </c>
+      <c r="R28" s="6">
+        <f>H28</f>
+        <v>20</v>
+      </c>
+    </row>
+    <row r="29" spans="1:18" x14ac:dyDescent="0.25">
+      <c r="A29" s="18"/>
+      <c r="B29" s="18" t="s">
+        <v>16</v>
+      </c>
+      <c r="C29" s="18" t="s">
+        <v>3174</v>
+      </c>
+      <c r="D29" s="18" t="s">
+        <v>3175</v>
+      </c>
+      <c r="E29" s="18" t="s">
+        <v>3176</v>
+      </c>
+      <c r="F29" s="18" t="s">
+        <v>68</v>
+      </c>
+      <c r="G29" s="19">
+        <v>1370</v>
+      </c>
+      <c r="H29" s="19">
+        <v>20</v>
+      </c>
+      <c r="I29" s="19">
+        <f t="shared" ref="I29:I34" si="1">G29-H29</f>
+        <v>1350</v>
+      </c>
+      <c r="J29" s="18" t="s">
+        <v>21</v>
+      </c>
+      <c r="K29" s="18" t="s">
+        <v>21</v>
+      </c>
+      <c r="L29" s="18" t="s">
+        <v>3107</v>
+      </c>
+      <c r="M29" s="18"/>
+      <c r="N29" s="18"/>
+      <c r="O29" s="18"/>
+      <c r="P29" s="18"/>
+      <c r="Q29" s="18">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="30" spans="1:18" x14ac:dyDescent="0.25">
+      <c r="A30" s="18"/>
+      <c r="B30" s="18" t="s">
+        <v>16</v>
+      </c>
+      <c r="C30" s="18" t="s">
+        <v>1509</v>
+      </c>
+      <c r="D30" s="18" t="s">
+        <v>3183</v>
+      </c>
+      <c r="E30" s="18" t="s">
+        <v>1511</v>
+      </c>
+      <c r="F30" s="18" t="s">
+        <v>72</v>
+      </c>
+      <c r="G30" s="19">
+        <v>2090</v>
+      </c>
+      <c r="H30" s="19">
+        <v>30</v>
+      </c>
+      <c r="I30" s="19">
+        <f t="shared" si="1"/>
+        <v>2060</v>
+      </c>
+      <c r="J30" s="18" t="s">
+        <v>21</v>
+      </c>
+      <c r="K30" s="18" t="s">
+        <v>21</v>
+      </c>
+      <c r="L30" s="18" t="s">
+        <v>3107</v>
+      </c>
+      <c r="M30" s="25" t="s">
+        <v>398</v>
+      </c>
+      <c r="N30" s="18"/>
+      <c r="O30" s="18"/>
+      <c r="P30" s="18"/>
+      <c r="Q30" s="18">
+        <v>1</v>
+      </c>
+      <c r="R30" s="6">
+        <f>H30</f>
+        <v>30</v>
+      </c>
+    </row>
+    <row r="31" spans="1:18" x14ac:dyDescent="0.25">
+      <c r="A31" s="18"/>
+      <c r="B31" s="18" t="s">
+        <v>16</v>
+      </c>
+      <c r="C31" s="18" t="s">
+        <v>3197</v>
+      </c>
+      <c r="D31" s="18" t="s">
+        <v>3198</v>
+      </c>
+      <c r="E31" s="18" t="s">
+        <v>3199</v>
+      </c>
+      <c r="F31" s="18" t="s">
+        <v>72</v>
+      </c>
+      <c r="G31" s="19">
+        <v>945</v>
+      </c>
+      <c r="H31" s="19">
+        <v>25</v>
+      </c>
+      <c r="I31" s="19">
+        <f t="shared" si="1"/>
+        <v>920</v>
+      </c>
+      <c r="J31" s="18" t="s">
+        <v>21</v>
+      </c>
+      <c r="K31" s="18" t="s">
+        <v>21</v>
+      </c>
+      <c r="L31" s="18" t="s">
+        <v>3107</v>
+      </c>
+      <c r="M31" s="18"/>
+      <c r="N31" s="18"/>
+      <c r="O31" s="18"/>
+      <c r="P31" s="18"/>
+      <c r="Q31" s="18">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="32" spans="1:18" x14ac:dyDescent="0.25">
+      <c r="A32" s="18"/>
+      <c r="B32" s="18" t="s">
+        <v>16</v>
+      </c>
+      <c r="C32" s="18" t="s">
+        <v>3203</v>
+      </c>
+      <c r="D32" s="18" t="s">
+        <v>3204</v>
+      </c>
+      <c r="E32" s="18" t="s">
+        <v>3205</v>
+      </c>
+      <c r="F32" s="18" t="s">
+        <v>88</v>
+      </c>
+      <c r="G32" s="19">
+        <v>605</v>
+      </c>
+      <c r="H32" s="19">
+        <v>25</v>
+      </c>
+      <c r="I32" s="19">
+        <f t="shared" si="1"/>
+        <v>580</v>
+      </c>
+      <c r="J32" s="18" t="s">
+        <v>21</v>
+      </c>
+      <c r="K32" s="18" t="s">
+        <v>21</v>
+      </c>
+      <c r="L32" s="18" t="s">
+        <v>3107</v>
+      </c>
+      <c r="M32" s="18"/>
+      <c r="N32" s="18"/>
+      <c r="O32" s="18"/>
+      <c r="P32" s="18"/>
+      <c r="Q32" s="18">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="33" spans="1:18" x14ac:dyDescent="0.25">
+      <c r="A33" s="18"/>
+      <c r="B33" s="18" t="s">
+        <v>16</v>
+      </c>
+      <c r="C33" s="18" t="s">
+        <v>2832</v>
+      </c>
+      <c r="D33" s="18" t="s">
+        <v>3209</v>
+      </c>
+      <c r="E33" s="18" t="s">
+        <v>2834</v>
+      </c>
+      <c r="F33" s="19">
+        <v>2</v>
+      </c>
+      <c r="G33" s="19">
+        <v>1070</v>
+      </c>
+      <c r="H33" s="19">
+        <v>30</v>
+      </c>
+      <c r="I33" s="19">
+        <f t="shared" si="1"/>
+        <v>1040</v>
+      </c>
+      <c r="J33" s="18" t="s">
+        <v>21</v>
+      </c>
+      <c r="K33" s="18" t="s">
+        <v>21</v>
+      </c>
+      <c r="L33" s="18" t="s">
+        <v>3107</v>
+      </c>
+      <c r="M33" s="18"/>
+      <c r="N33" s="18"/>
+      <c r="O33" s="18"/>
+      <c r="P33" s="18"/>
+      <c r="Q33" s="18">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="34" spans="1:18" x14ac:dyDescent="0.25">
+      <c r="A34" s="18"/>
+      <c r="B34" s="18" t="s">
+        <v>16</v>
+      </c>
+      <c r="C34" s="18" t="s">
+        <v>3226</v>
+      </c>
+      <c r="D34" s="18" t="s">
+        <v>3227</v>
+      </c>
+      <c r="E34" s="18" t="s">
+        <v>3228</v>
+      </c>
+      <c r="F34" s="18" t="s">
+        <v>72</v>
+      </c>
+      <c r="G34" s="19">
+        <v>1345</v>
+      </c>
+      <c r="H34" s="19">
+        <v>25</v>
+      </c>
+      <c r="I34" s="19">
+        <f t="shared" si="1"/>
+        <v>1320</v>
+      </c>
+      <c r="J34" s="18" t="s">
+        <v>21</v>
+      </c>
+      <c r="K34" s="18" t="s">
+        <v>21</v>
+      </c>
+      <c r="L34" s="18" t="s">
+        <v>3107</v>
+      </c>
+      <c r="M34" s="18"/>
+      <c r="N34" s="18"/>
+      <c r="O34" s="18"/>
+      <c r="P34" s="18"/>
+      <c r="Q34" s="18">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="35" spans="1:18" x14ac:dyDescent="0.25">
+      <c r="A35" s="18"/>
+      <c r="B35" s="18" t="s">
+        <v>16</v>
+      </c>
+      <c r="C35" s="18" t="s">
+        <v>3229</v>
+      </c>
+      <c r="D35" s="18" t="s">
+        <v>3230</v>
+      </c>
+      <c r="E35" s="18" t="s">
+        <v>3231</v>
+      </c>
+      <c r="F35" s="19">
+        <v>2</v>
+      </c>
+      <c r="G35" s="19">
+        <v>0</v>
+      </c>
+      <c r="H35" s="19">
+        <v>30</v>
+      </c>
+      <c r="I35" s="19">
+        <f>-H35</f>
+        <v>-30</v>
+      </c>
+      <c r="J35" s="18" t="s">
+        <v>21</v>
+      </c>
+      <c r="K35" s="18" t="s">
+        <v>21</v>
+      </c>
+      <c r="L35" s="18" t="s">
+        <v>3107</v>
+      </c>
+      <c r="M35" s="18"/>
+      <c r="N35" s="18"/>
+      <c r="O35" s="18"/>
+      <c r="P35" s="18"/>
+      <c r="Q35" s="18">
+        <v>1</v>
+      </c>
+      <c r="R35" s="6">
+        <f t="shared" ref="R35:R37" si="2">H35</f>
+        <v>30</v>
+      </c>
+    </row>
+    <row r="36" spans="1:18" x14ac:dyDescent="0.25">
+      <c r="A36" s="18"/>
+      <c r="B36" s="18" t="s">
+        <v>16</v>
+      </c>
+      <c r="C36" s="18" t="s">
+        <v>3056</v>
+      </c>
+      <c r="D36" s="18" t="s">
+        <v>3235</v>
+      </c>
+      <c r="E36" s="18" t="s">
+        <v>416</v>
+      </c>
+      <c r="F36" s="19">
+        <v>12</v>
+      </c>
+      <c r="G36" s="19">
+        <v>0</v>
+      </c>
+      <c r="H36" s="19">
+        <v>30</v>
+      </c>
+      <c r="I36" s="19">
+        <f>-H36</f>
+        <v>-30</v>
+      </c>
+      <c r="J36" s="18" t="s">
+        <v>21</v>
+      </c>
+      <c r="K36" s="18" t="s">
+        <v>21</v>
+      </c>
+      <c r="L36" s="18" t="s">
+        <v>3107</v>
+      </c>
+      <c r="M36" s="18"/>
+      <c r="N36" s="18"/>
+      <c r="O36" s="18"/>
+      <c r="P36" s="18"/>
+      <c r="Q36" s="18">
+        <v>1</v>
+      </c>
+      <c r="R36" s="6">
+        <f t="shared" si="2"/>
+        <v>30</v>
+      </c>
+    </row>
+    <row r="37" spans="1:18" x14ac:dyDescent="0.25">
+      <c r="A37" s="18"/>
+      <c r="B37" s="18" t="s">
+        <v>16</v>
+      </c>
+      <c r="C37" s="18" t="s">
+        <v>3242</v>
+      </c>
+      <c r="D37" s="18" t="s">
+        <v>3243</v>
+      </c>
+      <c r="E37" s="18" t="s">
+        <v>3244</v>
+      </c>
+      <c r="F37" s="19">
+        <v>12</v>
+      </c>
+      <c r="G37" s="19">
+        <v>0</v>
+      </c>
+      <c r="H37" s="19">
+        <v>40</v>
+      </c>
+      <c r="I37" s="19">
+        <f>-H37</f>
+        <v>-40</v>
+      </c>
+      <c r="J37" s="18" t="s">
+        <v>21</v>
+      </c>
+      <c r="K37" s="18" t="s">
+        <v>21</v>
+      </c>
+      <c r="L37" s="18" t="s">
+        <v>3107</v>
+      </c>
+      <c r="M37" s="18"/>
+      <c r="N37" s="18"/>
+      <c r="O37" s="18"/>
+      <c r="P37" s="18"/>
+      <c r="Q37" s="18">
+        <v>1</v>
+      </c>
+      <c r="R37" s="6">
+        <f t="shared" si="2"/>
+        <v>40</v>
+      </c>
+    </row>
+    <row r="38" spans="1:18" x14ac:dyDescent="0.25">
+      <c r="A38" s="18" t="s">
+        <v>62</v>
+      </c>
+      <c r="B38" s="18" t="s">
+        <v>16</v>
+      </c>
+      <c r="C38" s="18" t="s">
+        <v>3248</v>
+      </c>
+      <c r="D38" s="18"/>
+      <c r="E38" s="18" t="s">
+        <v>3249</v>
+      </c>
+      <c r="F38" s="18" t="s">
+        <v>68</v>
+      </c>
+      <c r="G38" s="19">
+        <v>25</v>
+      </c>
+      <c r="H38" s="19">
+        <v>25</v>
+      </c>
+      <c r="I38" s="19">
+        <f>G38-H38</f>
+        <v>0</v>
+      </c>
+      <c r="J38" s="18" t="s">
+        <v>21</v>
+      </c>
+      <c r="K38" s="18" t="s">
+        <v>21</v>
+      </c>
+      <c r="L38" s="18" t="s">
+        <v>3107</v>
+      </c>
+      <c r="M38" s="18"/>
+      <c r="N38" s="18"/>
+      <c r="O38" s="18"/>
+      <c r="P38" s="18"/>
+      <c r="Q38" s="18">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="39" spans="1:18" x14ac:dyDescent="0.25">
+      <c r="A39" s="18"/>
+      <c r="B39" s="18" t="s">
+        <v>16</v>
+      </c>
+      <c r="C39" s="18" t="s">
+        <v>1972</v>
+      </c>
+      <c r="D39" s="18" t="s">
+        <v>3106</v>
+      </c>
+      <c r="E39" s="18" t="s">
+        <v>1974</v>
+      </c>
+      <c r="F39" s="19">
+        <v>10</v>
+      </c>
+      <c r="G39" s="19">
+        <v>795</v>
+      </c>
+      <c r="H39" s="19">
+        <v>25</v>
+      </c>
+      <c r="I39" s="19">
+        <f>G39-H39</f>
+        <v>770</v>
+      </c>
+      <c r="J39" s="18" t="s">
+        <v>165</v>
+      </c>
+      <c r="K39" s="18" t="s">
+        <v>21</v>
+      </c>
+      <c r="L39" s="18" t="s">
+        <v>3107</v>
+      </c>
+      <c r="M39" s="18"/>
+      <c r="N39" s="18"/>
+      <c r="O39" s="18"/>
+      <c r="P39" s="18"/>
+      <c r="Q39" s="18">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="40" spans="1:18" x14ac:dyDescent="0.25">
+      <c r="A40" s="18"/>
+      <c r="B40" s="18" t="s">
+        <v>16</v>
+      </c>
+      <c r="C40" s="18" t="s">
+        <v>3126</v>
+      </c>
+      <c r="D40" s="18" t="s">
+        <v>3127</v>
+      </c>
+      <c r="E40" s="18" t="s">
+        <v>3128</v>
+      </c>
+      <c r="F40" s="19">
+        <v>1</v>
+      </c>
+      <c r="G40" s="19">
+        <v>0</v>
+      </c>
+      <c r="H40" s="19">
+        <v>25</v>
+      </c>
+      <c r="I40" s="19">
+        <f>-H40</f>
+        <v>-25</v>
+      </c>
+      <c r="J40" s="18" t="s">
+        <v>165</v>
+      </c>
+      <c r="K40" s="18" t="s">
+        <v>21</v>
+      </c>
+      <c r="L40" s="18" t="s">
+        <v>3107</v>
+      </c>
+      <c r="M40" s="18"/>
+      <c r="N40" s="18"/>
+      <c r="O40" s="18"/>
+      <c r="P40" s="18"/>
+      <c r="Q40" s="18">
+        <v>1</v>
+      </c>
+      <c r="R40" s="6">
+        <f>H40</f>
+        <v>25</v>
+      </c>
+    </row>
+    <row r="41" spans="1:18" x14ac:dyDescent="0.25">
+      <c r="A41" s="18"/>
+      <c r="B41" s="18" t="s">
+        <v>16</v>
+      </c>
+      <c r="C41" s="18" t="s">
+        <v>3129</v>
+      </c>
+      <c r="D41" s="18" t="s">
+        <v>3130</v>
+      </c>
+      <c r="E41" s="18" t="s">
+        <v>3131</v>
+      </c>
+      <c r="F41" s="19">
+        <v>3</v>
+      </c>
+      <c r="G41" s="19">
+        <v>1635</v>
+      </c>
+      <c r="H41" s="19">
+        <v>25</v>
+      </c>
+      <c r="I41" s="19">
+        <f t="shared" ref="I41:I46" si="3">G41-H41</f>
+        <v>1610</v>
+      </c>
+      <c r="J41" s="18" t="s">
+        <v>165</v>
+      </c>
+      <c r="K41" s="18" t="s">
+        <v>21</v>
+      </c>
+      <c r="L41" s="18" t="s">
+        <v>3107</v>
+      </c>
+      <c r="M41" s="18"/>
+      <c r="N41" s="18"/>
+      <c r="O41" s="18"/>
+      <c r="P41" s="18"/>
+      <c r="Q41" s="18">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="42" spans="1:18" x14ac:dyDescent="0.25">
+      <c r="A42" s="18"/>
+      <c r="B42" s="18" t="s">
+        <v>16</v>
+      </c>
+      <c r="C42" s="18" t="s">
+        <v>820</v>
+      </c>
+      <c r="D42" s="18" t="s">
+        <v>3133</v>
+      </c>
+      <c r="E42" s="18" t="s">
+        <v>3134</v>
+      </c>
+      <c r="F42" s="19">
+        <v>1</v>
+      </c>
+      <c r="G42" s="19">
+        <v>25</v>
+      </c>
+      <c r="H42" s="19">
+        <v>25</v>
+      </c>
+      <c r="I42" s="19">
+        <f t="shared" si="3"/>
+        <v>0</v>
+      </c>
+      <c r="J42" s="18" t="s">
+        <v>165</v>
+      </c>
+      <c r="K42" s="18" t="s">
+        <v>21</v>
+      </c>
+      <c r="L42" s="18" t="s">
+        <v>3107</v>
+      </c>
+      <c r="M42" s="18"/>
+      <c r="N42" s="18"/>
+      <c r="O42" s="18"/>
+      <c r="P42" s="18"/>
+      <c r="Q42" s="18">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="43" spans="1:18" x14ac:dyDescent="0.25">
+      <c r="A43" s="18"/>
+      <c r="B43" s="18" t="s">
+        <v>16</v>
+      </c>
+      <c r="C43" s="18" t="s">
+        <v>991</v>
+      </c>
+      <c r="D43" s="18" t="s">
+        <v>3138</v>
+      </c>
+      <c r="E43" s="18" t="s">
+        <v>993</v>
+      </c>
+      <c r="F43" s="18" t="s">
+        <v>88</v>
+      </c>
+      <c r="G43" s="19">
+        <v>795</v>
+      </c>
+      <c r="H43" s="19">
+        <v>25</v>
+      </c>
+      <c r="I43" s="19">
+        <f t="shared" si="3"/>
+        <v>770</v>
+      </c>
+      <c r="J43" s="18" t="s">
+        <v>165</v>
+      </c>
+      <c r="K43" s="18" t="s">
+        <v>21</v>
+      </c>
+      <c r="L43" s="18" t="s">
+        <v>3107</v>
+      </c>
+      <c r="M43" s="18"/>
+      <c r="N43" s="18"/>
+      <c r="O43" s="18"/>
+      <c r="P43" s="18"/>
+      <c r="Q43" s="18">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="44" spans="1:18" x14ac:dyDescent="0.25">
+      <c r="A44" s="18"/>
+      <c r="B44" s="18" t="s">
+        <v>16</v>
+      </c>
+      <c r="C44" s="18" t="s">
+        <v>3151</v>
+      </c>
+      <c r="D44" s="18" t="s">
+        <v>3152</v>
+      </c>
+      <c r="E44" s="18" t="s">
+        <v>3153</v>
+      </c>
+      <c r="F44" s="19">
+        <v>1</v>
+      </c>
+      <c r="G44" s="19">
+        <v>815</v>
+      </c>
+      <c r="H44" s="19">
+        <v>25</v>
+      </c>
+      <c r="I44" s="19">
+        <f t="shared" si="3"/>
+        <v>790</v>
+      </c>
+      <c r="J44" s="18" t="s">
+        <v>165</v>
+      </c>
+      <c r="K44" s="18" t="s">
+        <v>21</v>
+      </c>
+      <c r="L44" s="18" t="s">
+        <v>3107</v>
+      </c>
+      <c r="M44" s="18"/>
+      <c r="N44" s="18"/>
+      <c r="O44" s="18"/>
+      <c r="P44" s="18"/>
+      <c r="Q44" s="18">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="45" spans="1:18" x14ac:dyDescent="0.25">
+      <c r="A45" s="18"/>
+      <c r="B45" s="18" t="s">
+        <v>16</v>
+      </c>
+      <c r="C45" s="18" t="s">
+        <v>3154</v>
+      </c>
+      <c r="D45" s="18" t="s">
+        <v>3155</v>
+      </c>
+      <c r="E45" s="18" t="s">
+        <v>3156</v>
+      </c>
+      <c r="F45" s="19">
+        <v>4</v>
+      </c>
+      <c r="G45" s="19">
+        <v>1310</v>
+      </c>
+      <c r="H45" s="19">
+        <v>25</v>
+      </c>
+      <c r="I45" s="19">
+        <f t="shared" si="3"/>
+        <v>1285</v>
+      </c>
+      <c r="J45" s="18" t="s">
+        <v>165</v>
+      </c>
+      <c r="K45" s="18" t="s">
+        <v>21</v>
+      </c>
+      <c r="L45" s="18" t="s">
+        <v>3107</v>
+      </c>
+      <c r="M45" s="25" t="s">
+        <v>398</v>
+      </c>
+      <c r="N45" s="18"/>
+      <c r="O45" s="18"/>
+      <c r="P45" s="18"/>
+      <c r="Q45" s="18">
+        <v>1</v>
+      </c>
+      <c r="R45" s="6">
+        <f>H45</f>
+        <v>25</v>
+      </c>
+    </row>
+    <row r="46" spans="1:18" x14ac:dyDescent="0.25">
+      <c r="A46" s="18"/>
+      <c r="B46" s="18" t="s">
+        <v>16</v>
+      </c>
+      <c r="C46" s="18" t="s">
+        <v>3166</v>
+      </c>
+      <c r="D46" s="18" t="s">
+        <v>3167</v>
+      </c>
+      <c r="E46" s="18" t="s">
+        <v>3168</v>
+      </c>
+      <c r="F46" s="19">
+        <v>1</v>
+      </c>
+      <c r="G46" s="19">
+        <v>465</v>
+      </c>
+      <c r="H46" s="19">
+        <v>25</v>
+      </c>
+      <c r="I46" s="19">
+        <f t="shared" si="3"/>
+        <v>440</v>
+      </c>
+      <c r="J46" s="18" t="s">
+        <v>165</v>
+      </c>
+      <c r="K46" s="18" t="s">
+        <v>21</v>
+      </c>
+      <c r="L46" s="18" t="s">
+        <v>3107</v>
+      </c>
+      <c r="M46" s="18"/>
+      <c r="N46" s="18"/>
+      <c r="O46" s="18"/>
+      <c r="P46" s="18"/>
+      <c r="Q46" s="18">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="47" spans="1:18" x14ac:dyDescent="0.25">
+      <c r="A47" s="18"/>
+      <c r="B47" s="18" t="s">
+        <v>16</v>
+      </c>
+      <c r="C47" s="18" t="s">
+        <v>3177</v>
+      </c>
+      <c r="D47" s="18" t="s">
+        <v>3178</v>
+      </c>
+      <c r="E47" s="18" t="s">
+        <v>3179</v>
+      </c>
+      <c r="F47" s="19">
+        <v>1</v>
+      </c>
+      <c r="G47" s="19">
+        <v>0</v>
+      </c>
+      <c r="H47" s="19">
+        <v>25</v>
+      </c>
+      <c r="I47" s="19">
+        <f>-H47</f>
+        <v>-25</v>
+      </c>
+      <c r="J47" s="18" t="s">
+        <v>165</v>
+      </c>
+      <c r="K47" s="18" t="s">
+        <v>21</v>
+      </c>
+      <c r="L47" s="18" t="s">
+        <v>3107</v>
+      </c>
+      <c r="M47" s="18"/>
+      <c r="N47" s="18"/>
+      <c r="O47" s="18"/>
+      <c r="P47" s="18"/>
+      <c r="Q47" s="18">
+        <v>1</v>
+      </c>
+      <c r="R47" s="6">
+        <f>H47</f>
+        <v>25</v>
+      </c>
+    </row>
+    <row r="48" spans="1:18" x14ac:dyDescent="0.25">
+      <c r="A48" s="18"/>
+      <c r="B48" s="18" t="s">
+        <v>16</v>
+      </c>
+      <c r="C48" s="18" t="s">
+        <v>3180</v>
+      </c>
+      <c r="D48" s="18" t="s">
+        <v>3181</v>
+      </c>
+      <c r="E48" s="18" t="s">
+        <v>3182</v>
+      </c>
+      <c r="F48" s="19">
+        <v>1</v>
+      </c>
+      <c r="G48" s="19">
+        <v>825</v>
+      </c>
+      <c r="H48" s="19">
+        <v>25</v>
+      </c>
+      <c r="I48" s="19">
+        <f>G48-H48</f>
+        <v>800</v>
+      </c>
+      <c r="J48" s="18" t="s">
+        <v>165</v>
+      </c>
+      <c r="K48" s="18" t="s">
+        <v>21</v>
+      </c>
+      <c r="L48" s="18" t="s">
+        <v>3107</v>
+      </c>
+      <c r="M48" s="18"/>
+      <c r="N48" s="18"/>
+      <c r="O48" s="18"/>
+      <c r="P48" s="18"/>
+      <c r="Q48" s="18">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="49" spans="1:18" x14ac:dyDescent="0.25">
+      <c r="A49" s="18"/>
+      <c r="B49" s="18" t="s">
+        <v>16</v>
+      </c>
+      <c r="C49" s="18" t="s">
+        <v>3184</v>
+      </c>
+      <c r="D49" s="18" t="s">
+        <v>3185</v>
+      </c>
+      <c r="E49" s="18" t="s">
+        <v>3186</v>
+      </c>
+      <c r="F49" s="19">
+        <v>3</v>
+      </c>
+      <c r="G49" s="19">
+        <v>0</v>
+      </c>
+      <c r="H49" s="19">
+        <v>25</v>
+      </c>
+      <c r="I49" s="19">
+        <f>-H49</f>
+        <v>-25</v>
+      </c>
+      <c r="J49" s="18" t="s">
+        <v>165</v>
+      </c>
+      <c r="K49" s="18" t="s">
+        <v>21</v>
+      </c>
+      <c r="L49" s="18" t="s">
+        <v>3107</v>
+      </c>
+      <c r="M49" s="18"/>
+      <c r="N49" s="18"/>
+      <c r="O49" s="18"/>
+      <c r="P49" s="18"/>
+      <c r="Q49" s="18">
+        <v>1</v>
+      </c>
+      <c r="R49" s="6">
+        <f>H49</f>
+        <v>25</v>
+      </c>
+    </row>
+    <row r="50" spans="1:18" x14ac:dyDescent="0.25">
+      <c r="A50" s="18"/>
+      <c r="B50" s="18" t="s">
+        <v>16</v>
+      </c>
+      <c r="C50" s="18" t="s">
+        <v>2252</v>
+      </c>
+      <c r="D50" s="18" t="s">
+        <v>3187</v>
+      </c>
+      <c r="E50" s="18" t="s">
+        <v>3188</v>
+      </c>
+      <c r="F50" s="19">
+        <v>1</v>
+      </c>
+      <c r="G50" s="19">
+        <v>765</v>
+      </c>
+      <c r="H50" s="19">
+        <v>25</v>
+      </c>
+      <c r="I50" s="19">
+        <f t="shared" ref="I50:I55" si="4">G50-H50</f>
+        <v>740</v>
+      </c>
+      <c r="J50" s="18" t="s">
+        <v>165</v>
+      </c>
+      <c r="K50" s="18" t="s">
+        <v>21</v>
+      </c>
+      <c r="L50" s="18" t="s">
+        <v>3107</v>
+      </c>
+      <c r="M50" s="18"/>
+      <c r="N50" s="18"/>
+      <c r="O50" s="18"/>
+      <c r="P50" s="18"/>
+      <c r="Q50" s="18">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="51" spans="1:18" x14ac:dyDescent="0.25">
+      <c r="A51" s="18"/>
+      <c r="B51" s="18" t="s">
+        <v>16</v>
+      </c>
+      <c r="C51" s="18" t="s">
+        <v>3200</v>
+      </c>
+      <c r="D51" s="18" t="s">
+        <v>3201</v>
+      </c>
+      <c r="E51" s="18" t="s">
+        <v>3202</v>
+      </c>
+      <c r="F51" s="19">
+        <v>10</v>
+      </c>
+      <c r="G51" s="19">
+        <v>775</v>
+      </c>
+      <c r="H51" s="19">
+        <v>25</v>
+      </c>
+      <c r="I51" s="19">
+        <f t="shared" si="4"/>
+        <v>750</v>
+      </c>
+      <c r="J51" s="18" t="s">
+        <v>165</v>
+      </c>
+      <c r="K51" s="18" t="s">
+        <v>21</v>
+      </c>
+      <c r="L51" s="18" t="s">
+        <v>3107</v>
+      </c>
+      <c r="M51" s="18"/>
+      <c r="N51" s="18"/>
+      <c r="O51" s="18"/>
+      <c r="P51" s="18"/>
+      <c r="Q51" s="18">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="52" spans="1:18" x14ac:dyDescent="0.25">
+      <c r="A52" s="18"/>
+      <c r="B52" s="18" t="s">
+        <v>16</v>
+      </c>
+      <c r="C52" s="18" t="s">
+        <v>3210</v>
+      </c>
+      <c r="D52" s="18" t="s">
+        <v>3211</v>
+      </c>
+      <c r="E52" s="18" t="s">
+        <v>3212</v>
+      </c>
+      <c r="F52" s="18" t="s">
+        <v>85</v>
+      </c>
+      <c r="G52" s="19">
+        <v>2460</v>
+      </c>
+      <c r="H52" s="19">
+        <v>20</v>
+      </c>
+      <c r="I52" s="19">
+        <f t="shared" si="4"/>
+        <v>2440</v>
+      </c>
+      <c r="J52" s="18" t="s">
+        <v>165</v>
+      </c>
+      <c r="K52" s="18" t="s">
+        <v>21</v>
+      </c>
+      <c r="L52" s="18" t="s">
+        <v>3107</v>
+      </c>
+      <c r="M52" s="25" t="s">
+        <v>398</v>
+      </c>
+      <c r="N52" s="18"/>
+      <c r="O52" s="18"/>
+      <c r="P52" s="18"/>
+      <c r="Q52" s="18">
+        <v>1</v>
+      </c>
+      <c r="R52" s="6">
+        <f>H52</f>
+        <v>20</v>
+      </c>
+    </row>
+    <row r="53" spans="1:18" x14ac:dyDescent="0.25">
+      <c r="A53" s="18"/>
+      <c r="B53" s="18" t="s">
+        <v>16</v>
+      </c>
+      <c r="C53" s="18" t="s">
+        <v>3213</v>
+      </c>
+      <c r="D53" s="18" t="s">
+        <v>3214</v>
+      </c>
+      <c r="E53" s="18" t="s">
+        <v>3215</v>
+      </c>
+      <c r="F53" s="19">
+        <v>3</v>
+      </c>
+      <c r="G53" s="19">
+        <v>945</v>
+      </c>
+      <c r="H53" s="19">
+        <v>25</v>
+      </c>
+      <c r="I53" s="19">
+        <f t="shared" si="4"/>
+        <v>920</v>
+      </c>
+      <c r="J53" s="18" t="s">
+        <v>165</v>
+      </c>
+      <c r="K53" s="18" t="s">
+        <v>21</v>
+      </c>
+      <c r="L53" s="18" t="s">
+        <v>3107</v>
+      </c>
+      <c r="M53" s="18"/>
+      <c r="N53" s="18"/>
+      <c r="O53" s="18"/>
+      <c r="P53" s="18"/>
+      <c r="Q53" s="18">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="54" spans="1:18" x14ac:dyDescent="0.25">
+      <c r="A54" s="18"/>
+      <c r="B54" s="18" t="s">
+        <v>16</v>
+      </c>
+      <c r="C54" s="18" t="s">
+        <v>3220</v>
+      </c>
+      <c r="D54" s="18" t="s">
+        <v>3221</v>
+      </c>
+      <c r="E54" s="18" t="s">
+        <v>3222</v>
+      </c>
+      <c r="F54" s="19">
+        <v>4</v>
+      </c>
+      <c r="G54" s="19">
+        <v>465</v>
+      </c>
+      <c r="H54" s="19">
+        <v>25</v>
+      </c>
+      <c r="I54" s="19">
+        <f t="shared" si="4"/>
+        <v>440</v>
+      </c>
+      <c r="J54" s="18" t="s">
+        <v>165</v>
+      </c>
+      <c r="K54" s="18" t="s">
+        <v>21</v>
+      </c>
+      <c r="L54" s="18" t="s">
+        <v>3107</v>
+      </c>
+      <c r="M54" s="18"/>
+      <c r="N54" s="18"/>
+      <c r="O54" s="18"/>
+      <c r="P54" s="18"/>
+      <c r="Q54" s="18">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="55" spans="1:18" x14ac:dyDescent="0.25">
+      <c r="A55" s="18"/>
+      <c r="B55" s="18" t="s">
+        <v>16</v>
+      </c>
+      <c r="C55" s="18" t="s">
+        <v>3223</v>
+      </c>
+      <c r="D55" s="18" t="s">
+        <v>3224</v>
+      </c>
+      <c r="E55" s="18" t="s">
+        <v>3225</v>
+      </c>
+      <c r="F55" s="19">
+        <v>5</v>
+      </c>
+      <c r="G55" s="19">
+        <v>825</v>
+      </c>
+      <c r="H55" s="19">
+        <v>25</v>
+      </c>
+      <c r="I55" s="19">
+        <f t="shared" si="4"/>
+        <v>800</v>
+      </c>
+      <c r="J55" s="18" t="s">
+        <v>165</v>
+      </c>
+      <c r="K55" s="18" t="s">
+        <v>21</v>
+      </c>
+      <c r="L55" s="18" t="s">
+        <v>3107</v>
+      </c>
+      <c r="M55" s="18"/>
+      <c r="N55" s="18"/>
+      <c r="O55" s="18"/>
+      <c r="P55" s="18"/>
+      <c r="Q55" s="18">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="56" spans="1:18" x14ac:dyDescent="0.25">
+      <c r="A56" s="18"/>
+      <c r="B56" s="18" t="s">
+        <v>16</v>
+      </c>
+      <c r="C56" s="18" t="s">
+        <v>3232</v>
+      </c>
+      <c r="D56" s="18" t="s">
+        <v>3233</v>
+      </c>
+      <c r="E56" s="18" t="s">
+        <v>3234</v>
+      </c>
+      <c r="F56" s="19">
+        <v>4</v>
+      </c>
+      <c r="G56" s="19">
+        <v>0</v>
+      </c>
+      <c r="H56" s="19">
+        <v>25</v>
+      </c>
+      <c r="I56" s="19">
+        <f>-H56</f>
+        <v>-25</v>
+      </c>
+      <c r="J56" s="18" t="s">
+        <v>165</v>
+      </c>
+      <c r="K56" s="18" t="s">
+        <v>21</v>
+      </c>
+      <c r="L56" s="18" t="s">
+        <v>3107</v>
+      </c>
+      <c r="M56" s="18"/>
+      <c r="N56" s="18"/>
+      <c r="O56" s="18"/>
+      <c r="P56" s="18"/>
+      <c r="Q56" s="18">
+        <v>1</v>
+      </c>
+      <c r="R56" s="6">
+        <f t="shared" ref="R56:R58" si="5">H56</f>
+        <v>25</v>
+      </c>
+    </row>
+    <row r="57" spans="1:18" x14ac:dyDescent="0.25">
+      <c r="A57" s="18"/>
+      <c r="B57" s="18" t="s">
+        <v>16</v>
+      </c>
+      <c r="C57" s="18" t="s">
+        <v>3239</v>
+      </c>
+      <c r="D57" s="18" t="s">
+        <v>3240</v>
+      </c>
+      <c r="E57" s="18" t="s">
+        <v>3241</v>
+      </c>
+      <c r="F57" s="19">
+        <v>3</v>
+      </c>
+      <c r="G57" s="19">
+        <v>0</v>
+      </c>
+      <c r="H57" s="19">
+        <v>25</v>
+      </c>
+      <c r="I57" s="19">
+        <f>-H57</f>
+        <v>-25</v>
+      </c>
+      <c r="J57" s="18" t="s">
+        <v>165</v>
+      </c>
+      <c r="K57" s="18" t="s">
+        <v>21</v>
+      </c>
+      <c r="L57" s="18" t="s">
+        <v>3107</v>
+      </c>
+      <c r="M57" s="18"/>
+      <c r="N57" s="18"/>
+      <c r="O57" s="18"/>
+      <c r="P57" s="18"/>
+      <c r="Q57" s="18">
+        <v>1</v>
+      </c>
+      <c r="R57" s="6">
+        <f t="shared" si="5"/>
+        <v>25</v>
+      </c>
+    </row>
+    <row r="58" spans="1:18" x14ac:dyDescent="0.25">
+      <c r="A58" s="18" t="s">
+        <v>62</v>
+      </c>
+      <c r="B58" s="18" t="s">
+        <v>16</v>
+      </c>
+      <c r="C58" s="18" t="s">
+        <v>3245</v>
+      </c>
+      <c r="D58" s="18"/>
+      <c r="E58" s="18" t="s">
+        <v>2432</v>
+      </c>
+      <c r="F58" s="19">
+        <v>5</v>
+      </c>
+      <c r="G58" s="19">
+        <v>0</v>
+      </c>
+      <c r="H58" s="19">
+        <v>25</v>
+      </c>
+      <c r="I58" s="19">
+        <f>-H58</f>
+        <v>-25</v>
+      </c>
+      <c r="J58" s="18" t="s">
+        <v>165</v>
+      </c>
+      <c r="K58" s="18" t="s">
+        <v>21</v>
+      </c>
+      <c r="L58" s="18" t="s">
+        <v>3107</v>
+      </c>
+      <c r="M58" s="18"/>
+      <c r="N58" s="18"/>
+      <c r="O58" s="18"/>
+      <c r="P58" s="18"/>
+      <c r="Q58" s="18">
+        <v>1</v>
+      </c>
+      <c r="R58" s="6">
+        <f t="shared" si="5"/>
+        <v>25</v>
+      </c>
+    </row>
+    <row r="59" spans="1:18" x14ac:dyDescent="0.25">
+      <c r="A59" s="18" t="s">
+        <v>62</v>
+      </c>
+      <c r="B59" s="18" t="s">
+        <v>16</v>
+      </c>
+      <c r="C59" s="18" t="s">
+        <v>3246</v>
+      </c>
+      <c r="D59" s="18"/>
+      <c r="E59" s="18" t="s">
+        <v>3247</v>
+      </c>
+      <c r="F59" s="19">
+        <v>3</v>
+      </c>
+      <c r="G59" s="19">
+        <v>6170</v>
+      </c>
+      <c r="H59" s="19">
+        <v>50</v>
+      </c>
+      <c r="I59" s="19">
+        <f>G59-H59</f>
+        <v>6120</v>
+      </c>
+      <c r="J59" s="18" t="s">
+        <v>165</v>
+      </c>
+      <c r="K59" s="18" t="s">
+        <v>21</v>
+      </c>
+      <c r="L59" s="18" t="s">
+        <v>3107</v>
+      </c>
+      <c r="M59" s="18"/>
+      <c r="N59" s="18"/>
+      <c r="O59" s="18"/>
+      <c r="P59" s="18"/>
+      <c r="Q59" s="18">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="60" spans="1:18" x14ac:dyDescent="0.25">
+      <c r="A60" s="18" t="s">
+        <v>62</v>
+      </c>
+      <c r="B60" s="18" t="s">
+        <v>16</v>
+      </c>
+      <c r="C60" s="19">
+        <v>898460039</v>
+      </c>
+      <c r="D60" s="18"/>
+      <c r="E60" s="18" t="s">
+        <v>2432</v>
+      </c>
+      <c r="F60" s="19">
+        <v>5</v>
+      </c>
+      <c r="G60" s="19">
+        <v>0</v>
+      </c>
+      <c r="H60" s="19">
+        <v>25</v>
+      </c>
+      <c r="I60" s="19">
+        <f>-H60</f>
+        <v>-25</v>
+      </c>
+      <c r="J60" s="18" t="s">
+        <v>165</v>
+      </c>
+      <c r="K60" s="18" t="s">
+        <v>21</v>
+      </c>
+      <c r="L60" s="18" t="s">
+        <v>3107</v>
+      </c>
+      <c r="M60" s="18"/>
+      <c r="N60" s="18"/>
+      <c r="O60" s="18"/>
+      <c r="P60" s="18"/>
+      <c r="Q60" s="18">
+        <v>1</v>
+      </c>
+      <c r="R60" s="6">
+        <f>H60</f>
+        <v>25</v>
+      </c>
+    </row>
+    <row r="62" spans="1:18" x14ac:dyDescent="0.25">
+      <c r="D62" s="1">
+        <f>COUNTA(D3:D60)</f>
+        <v>54</v>
+      </c>
+      <c r="G62" s="1">
+        <f t="shared" ref="G62:Q62" si="6">SUBTOTAL(9,G3:G60)</f>
+        <v>47815</v>
+      </c>
+      <c r="H62" s="1">
+        <f t="shared" si="6"/>
+        <v>1585</v>
+      </c>
+      <c r="I62" s="1">
+        <f t="shared" si="6"/>
+        <v>46230</v>
+      </c>
+      <c r="J62" s="1">
+        <f t="shared" si="6"/>
+        <v>0</v>
+      </c>
+      <c r="K62" s="1">
+        <f t="shared" si="6"/>
+        <v>0</v>
+      </c>
+      <c r="L62" s="1">
+        <f t="shared" si="6"/>
+        <v>0</v>
+      </c>
+      <c r="M62" s="1">
+        <f t="shared" si="6"/>
+        <v>0</v>
+      </c>
+      <c r="N62" s="1">
+        <f t="shared" si="6"/>
+        <v>0</v>
+      </c>
+      <c r="O62" s="1">
+        <f t="shared" si="6"/>
+        <v>0</v>
+      </c>
+      <c r="P62" s="1">
+        <f t="shared" si="6"/>
+        <v>0</v>
+      </c>
+      <c r="Q62" s="1">
+        <f t="shared" si="6"/>
+        <v>58</v>
+      </c>
+    </row>
+    <row r="63" spans="1:18" x14ac:dyDescent="0.25">
+      <c r="H63">
+        <f>-14*17</f>
+        <v>-238</v>
+      </c>
+    </row>
+    <row r="64" spans="1:18" x14ac:dyDescent="0.25">
+      <c r="A64" s="1" t="s">
+        <v>16</v>
+      </c>
+      <c r="C64" s="47" t="s">
+        <v>89</v>
+      </c>
+      <c r="D64" s="47"/>
+      <c r="E64" s="4" t="s">
+        <v>90</v>
+      </c>
+      <c r="H64">
+        <f>-6*25</f>
+        <v>-150</v>
+      </c>
+      <c r="K64" s="7" t="s">
+        <v>165</v>
+      </c>
+      <c r="L64" s="7" t="s">
+        <v>91</v>
+      </c>
+      <c r="M64" s="7" t="s">
+        <v>90</v>
+      </c>
+      <c r="O64" s="4" t="s">
+        <v>92</v>
+      </c>
+    </row>
+    <row r="65" spans="1:16" x14ac:dyDescent="0.25">
+      <c r="A65" t="s">
+        <v>3107</v>
+      </c>
+      <c r="B65" s="3" t="s">
+        <v>93</v>
+      </c>
+      <c r="C65" s="48">
+        <f>SUMIFS(I$3:I$60,B$3:B$60,A$64,L$3:L$60,A$65)</f>
+        <v>46230</v>
+      </c>
+      <c r="D65" s="48"/>
+      <c r="E65" s="3">
+        <f>SUMIFS(Q$3:Q$60,B$3:B$60,A$64,L$3:L$60,A$65)</f>
+        <v>58</v>
+      </c>
+      <c r="F65" t="s">
+        <v>94</v>
+      </c>
+      <c r="H65">
+        <f>-3*30</f>
+        <v>-90</v>
+      </c>
+      <c r="K65" t="s">
+        <v>95</v>
+      </c>
+      <c r="L65">
+        <f>SUMIFS(G$3:G$60,J$3:J$60,K$64)</f>
+        <v>19070</v>
+      </c>
+      <c r="M65">
+        <f>SUMIFS(Q$3:Q$60,J$3:J$60,K$64)-INT(COUNTIFS(J$3:J$60,K$64,M$3:M$60,"*gộp*")/2)</f>
+        <v>22</v>
+      </c>
+      <c r="O65" t="s">
+        <v>165</v>
+      </c>
+      <c r="P65">
+        <f>L70</f>
+        <v>18610</v>
+      </c>
+    </row>
+    <row r="66" spans="1:16" x14ac:dyDescent="0.25">
+      <c r="B66" s="2" t="s">
+        <v>97</v>
+      </c>
+      <c r="C66" s="49">
+        <v>0</v>
+      </c>
+      <c r="D66" s="49"/>
+      <c r="K66" t="s">
+        <v>98</v>
+      </c>
+      <c r="L66">
+        <f>-SUMIFS(H$3:H$60,J$3:J$60,K$64)+M66*5</f>
+        <v>-460</v>
+      </c>
+      <c r="M66">
+        <f>SUMIFS(Q$3:Q$60,J$3:J$60,K$64)-INT(COUNTIFS(J$3:J$60,K$64,M$3:M$60,"*gộp*")/2)</f>
+        <v>22</v>
+      </c>
+      <c r="O66" t="s">
+        <v>3250</v>
+      </c>
+      <c r="P66">
+        <f>L78</f>
+        <v>18827</v>
+      </c>
+    </row>
+    <row r="67" spans="1:16" x14ac:dyDescent="0.25">
+      <c r="B67" s="2" t="s">
+        <v>99</v>
+      </c>
+      <c r="C67" s="49">
+        <f>-SUMIFS(I$3:I$60,B$3:B$60,A$64,P$3:P$60,"xx",N$3:N$60,"x")</f>
+        <v>0</v>
+      </c>
+      <c r="D67" s="49"/>
+      <c r="E67" s="2">
+        <f>SUMIFS(Q$3:Q$60,B$3:B$60,A$64,P$3:P$60,"xx",N$3:N$60,"x")</f>
+        <v>0</v>
+      </c>
+      <c r="K67" t="s">
+        <v>100</v>
+      </c>
+      <c r="O67" t="s">
+        <v>21</v>
+      </c>
+      <c r="P67">
+        <f>L86</f>
+        <v>8244</v>
+      </c>
+    </row>
+    <row r="68" spans="1:16" x14ac:dyDescent="0.25">
+      <c r="B68" s="4" t="s">
+        <v>101</v>
+      </c>
+      <c r="C68" s="47">
+        <f>SUBTOTAL(9,C65:C67)</f>
+        <v>46230</v>
+      </c>
+      <c r="D68" s="47"/>
+      <c r="E68">
+        <f>E65</f>
+        <v>58</v>
+      </c>
+      <c r="K68" s="2" t="s">
+        <v>102</v>
+      </c>
+      <c r="O68" t="s">
+        <v>20</v>
+      </c>
+      <c r="P68">
+        <f>L94</f>
+        <v>795</v>
+      </c>
+    </row>
+    <row r="69" spans="1:16" x14ac:dyDescent="0.25">
+      <c r="B69" s="2" t="s">
+        <v>104</v>
+      </c>
+      <c r="C69" s="45"/>
+      <c r="D69" s="45"/>
+      <c r="K69" s="2" t="s">
+        <v>105</v>
+      </c>
+      <c r="O69" t="s">
+        <v>103</v>
+      </c>
+      <c r="P69">
+        <f>-C72</f>
+        <v>-46230</v>
+      </c>
+    </row>
+    <row r="70" spans="1:16" x14ac:dyDescent="0.25">
+      <c r="B70" s="8" t="s">
+        <v>107</v>
+      </c>
+      <c r="C70" s="45"/>
+      <c r="D70" s="45"/>
+      <c r="L70" s="9">
+        <f>SUBTOTAL(9,L65:L69)</f>
+        <v>18610</v>
+      </c>
+      <c r="M70" s="9">
+        <f>M65</f>
+        <v>22</v>
+      </c>
+      <c r="O70" s="4" t="s">
+        <v>106</v>
+      </c>
+      <c r="P70" s="4">
+        <f>SUBTOTAL(9,P65:P69)</f>
+        <v>246</v>
+      </c>
+    </row>
+    <row r="72" spans="1:16" x14ac:dyDescent="0.25">
+      <c r="B72" s="1" t="s">
+        <v>108</v>
+      </c>
+      <c r="C72" s="46">
+        <f>C68+C69+C70</f>
+        <v>46230</v>
+      </c>
+      <c r="D72" s="46"/>
+      <c r="E72" s="1" t="s">
+        <v>109</v>
+      </c>
+      <c r="K72" s="7" t="s">
+        <v>3111</v>
+      </c>
+      <c r="L72" s="7" t="s">
+        <v>91</v>
+      </c>
+      <c r="M72" s="7" t="s">
+        <v>90</v>
+      </c>
+    </row>
+    <row r="73" spans="1:16" x14ac:dyDescent="0.25">
+      <c r="K73" t="s">
+        <v>95</v>
+      </c>
+      <c r="L73">
+        <f>SUMIFS(G$3:G$60,J$3:J$60,K$72)</f>
+        <v>19305</v>
+      </c>
+      <c r="M73">
+        <f>SUMIFS(Q$3:Q$60,J$3:J$60,K$72)-INT(COUNTIFS(J$3:J$60,K$72,M$3:M$60,"*gộp*")/2)</f>
+        <v>23</v>
+      </c>
+    </row>
+    <row r="74" spans="1:16" x14ac:dyDescent="0.25">
+      <c r="K74" t="s">
+        <v>98</v>
+      </c>
+      <c r="L74">
+        <f>SUM(H63:H65)</f>
+        <v>-478</v>
+      </c>
+      <c r="M74">
+        <f>SUMIFS(Q$3:Q$60,J$3:J$60,K$72)</f>
+        <v>23</v>
+      </c>
+    </row>
+    <row r="75" spans="1:16" x14ac:dyDescent="0.25">
+      <c r="K75" t="s">
+        <v>100</v>
+      </c>
+    </row>
+    <row r="76" spans="1:16" x14ac:dyDescent="0.25">
+      <c r="K76" s="2" t="s">
+        <v>102</v>
+      </c>
+    </row>
+    <row r="77" spans="1:16" x14ac:dyDescent="0.25">
+      <c r="K77" s="2" t="s">
+        <v>105</v>
+      </c>
+    </row>
+    <row r="78" spans="1:16" x14ac:dyDescent="0.25">
+      <c r="L78" s="9">
+        <f>SUBTOTAL(9,L73:L77)</f>
+        <v>18827</v>
+      </c>
+      <c r="M78" s="9">
+        <f>M73</f>
+        <v>23</v>
+      </c>
+    </row>
+    <row r="80" spans="1:16" x14ac:dyDescent="0.25">
+      <c r="K80" s="7" t="s">
+        <v>21</v>
+      </c>
+      <c r="L80" s="7" t="s">
+        <v>91</v>
+      </c>
+      <c r="M80" s="7" t="s">
+        <v>90</v>
+      </c>
+    </row>
+    <row r="81" spans="11:13" x14ac:dyDescent="0.25">
+      <c r="K81" t="s">
+        <v>95</v>
+      </c>
+      <c r="L81">
+        <f>SUMIFS(G$3:G$60,J$3:J$60,K$80)</f>
+        <v>8620</v>
+      </c>
+      <c r="M81">
+        <f>SUMIFS(Q$3:Q$60,J$3:J$60,K$80)-INT(COUNTIFS(J$3:J$60,K$80,M$3:M$60,"*gộp*")/2)</f>
+        <v>12</v>
+      </c>
+    </row>
+    <row r="82" spans="11:13" x14ac:dyDescent="0.25">
+      <c r="K82" t="s">
+        <v>98</v>
+      </c>
+      <c r="L82">
+        <f>-SUMIFS(H$3:H$60,J$3:J$60,K$80)+M82*5</f>
+        <v>-260</v>
+      </c>
+      <c r="M82">
+        <f>SUMIFS(Q$3:Q$60,J$3:J$60,K$80)-INT(COUNTIFS(J$3:J$60,K$80,M$3:M$60,"*gộp*")/2)</f>
+        <v>12</v>
+      </c>
+    </row>
+    <row r="83" spans="11:13" x14ac:dyDescent="0.25">
+      <c r="K83" t="s">
+        <v>100</v>
+      </c>
+      <c r="L83">
+        <f>-M83*2</f>
+        <v>-116</v>
+      </c>
+      <c r="M83">
+        <f>E68-(COUNTIFS(M$3:M$60,"*gộp*")/2)-COUNTIFS(M$3:M$60,"*đơn trả*")-COUNTIFS(M$3:M$60,"*hàng tỉnh*")</f>
+        <v>58</v>
+      </c>
+    </row>
+    <row r="84" spans="11:13" x14ac:dyDescent="0.25">
+      <c r="K84" s="2" t="s">
+        <v>102</v>
+      </c>
+    </row>
+    <row r="85" spans="11:13" x14ac:dyDescent="0.25">
+      <c r="K85" s="2" t="s">
+        <v>105</v>
+      </c>
+    </row>
+    <row r="86" spans="11:13" x14ac:dyDescent="0.25">
+      <c r="L86" s="9">
+        <f>SUBTOTAL(9,L81:L85)</f>
+        <v>8244</v>
+      </c>
+      <c r="M86" s="9">
+        <f>M81</f>
+        <v>12</v>
+      </c>
+    </row>
+    <row r="88" spans="11:13" x14ac:dyDescent="0.25">
+      <c r="K88" s="7" t="s">
+        <v>20</v>
+      </c>
+      <c r="L88" s="7" t="s">
+        <v>91</v>
+      </c>
+      <c r="M88" s="7" t="s">
+        <v>90</v>
+      </c>
+    </row>
+    <row r="89" spans="11:13" x14ac:dyDescent="0.25">
+      <c r="K89" t="s">
+        <v>95</v>
+      </c>
+      <c r="L89">
+        <f>SUMIFS(G$3:G$60,J$3:J$60,K$88)</f>
+        <v>820</v>
+      </c>
+      <c r="M89">
+        <f>SUMIFS(Q$3:Q$60,J$3:J$60,K$88)-INT(COUNTIFS(J$3:J$60,K$88,M$3:M$60,"*gộp*")/2)</f>
+        <v>1</v>
+      </c>
+    </row>
+    <row r="90" spans="11:13" x14ac:dyDescent="0.25">
+      <c r="K90" t="s">
+        <v>98</v>
+      </c>
+      <c r="L90">
+        <f>-SUMIFS(H$3:H$60,J$3:J$60,K$88)+M90*5</f>
+        <v>-25</v>
+      </c>
+      <c r="M90">
+        <f>SUMIFS(Q$3:Q$60,J$3:J$60,K$88)-INT(COUNTIFS(J$3:J$60,K$88,M$3:M$60,"*gộp*")/2)</f>
+        <v>1</v>
+      </c>
+    </row>
+    <row r="91" spans="11:13" x14ac:dyDescent="0.25">
+      <c r="K91" t="s">
+        <v>100</v>
+      </c>
+    </row>
+    <row r="92" spans="11:13" x14ac:dyDescent="0.25">
+      <c r="K92" s="2" t="s">
+        <v>102</v>
+      </c>
+    </row>
+    <row r="93" spans="11:13" x14ac:dyDescent="0.25">
+      <c r="K93" s="2" t="s">
+        <v>105</v>
+      </c>
+    </row>
+    <row r="94" spans="11:13" x14ac:dyDescent="0.25">
+      <c r="L94" s="9">
+        <f>SUBTOTAL(9,L89:L93)</f>
+        <v>795</v>
+      </c>
+      <c r="M94" s="9">
+        <f>M89</f>
+        <v>1</v>
+      </c>
+    </row>
+  </sheetData>
+  <autoFilter ref="A2:P60" xr:uid="{00000000-0009-0000-0000-000019000000}">
+    <sortState xmlns:xlrd2="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata2" ref="A3:P60">
+      <sortCondition ref="J2:J60"/>
+    </sortState>
+  </autoFilter>
+  <mergeCells count="8">
+    <mergeCell ref="C69:D69"/>
+    <mergeCell ref="C70:D70"/>
+    <mergeCell ref="C72:D72"/>
+    <mergeCell ref="C64:D64"/>
+    <mergeCell ref="C65:D65"/>
+    <mergeCell ref="C66:D66"/>
+    <mergeCell ref="C67:D67"/>
+    <mergeCell ref="C68:D68"/>
+  </mergeCells>
+  <pageMargins left="0.75" right="0.75" top="0.75" bottom="0.5" header="0.5" footer="0.75"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet26.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{A5D9B982-EAEB-4F31-86BF-4D059AFDEA27}">
   <sheetPr>
     <tabColor rgb="FF0070C0"/>
   </sheetPr>
-  <dimension ref="A1:E32"/>
+  <dimension ref="A1:E31"/>
   <sheetFormatPr defaultColWidth="9.140625" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="9.42578125" style="30" bestFit="1" customWidth="1"/>
@@ -58750,7 +62356,7 @@
   <sheetData>
     <row r="1" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A1" s="30" t="s">
-        <v>2994</v>
+        <v>3096</v>
       </c>
       <c r="B1" s="30">
         <v>2026</v>
@@ -58758,19 +62364,19 @@
     </row>
     <row r="2" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A2" s="31" t="s">
-        <v>2995</v>
+        <v>3097</v>
       </c>
       <c r="B2" s="31" t="s">
-        <v>2996</v>
+        <v>3098</v>
       </c>
       <c r="C2" s="31" t="s">
-        <v>2997</v>
+        <v>3099</v>
       </c>
       <c r="D2" s="31" t="s">
-        <v>2998</v>
+        <v>3100</v>
       </c>
       <c r="E2" s="31" t="s">
-        <v>2999</v>
+        <v>3101</v>
       </c>
     </row>
     <row r="3" spans="1:5" x14ac:dyDescent="0.25">
@@ -58786,11 +62392,11 @@
         <v>0</v>
       </c>
       <c r="D3" s="33" cm="1">
-        <f t="array" ref="D3" ca="1">IFERROR(SUM(COUNTIF(INDIRECT("'"&amp;TEXT(A3,"DD-MM")&amp;"'!M3:M200"),{"*đơn trả*","*hàng tỉnh*"})),0)</f>
+        <f t="array" aca="1" ref="D3" ca="1">IFERROR(SUM(COUNTIF(INDIRECT("'"&amp;TEXT(A3,"DD-MM")&amp;"'!M3:M200"),{"*đơn trả*","*hàng tỉnh*"})),0)</f>
         <v>0</v>
       </c>
       <c r="E3" s="33">
-        <f t="shared" ref="E3:E28" ca="1" si="0">B3-C3-D3</f>
+        <f t="shared" ref="E3:E27" ca="1" si="0">B3-C3-D3</f>
         <v>21</v>
       </c>
     </row>
@@ -58807,7 +62413,7 @@
         <v>0</v>
       </c>
       <c r="D4" s="33" cm="1">
-        <f t="array" ref="D4" ca="1">IFERROR(SUM(COUNTIF(INDIRECT("'"&amp;TEXT(A4,"DD-MM")&amp;"'!M3:M200"),{"*đơn trả*","*hàng tỉnh*"})),0)</f>
+        <f t="array" aca="1" ref="D4" ca="1">IFERROR(SUM(COUNTIF(INDIRECT("'"&amp;TEXT(A4,"DD-MM")&amp;"'!M3:M200"),{"*đơn trả*","*hàng tỉnh*"})),0)</f>
         <v>0</v>
       </c>
       <c r="E4" s="33">
@@ -58820,11 +62426,11 @@
         <v>46115</v>
       </c>
       <c r="B5" s="33">
-        <f t="shared" ref="B5:B28" ca="1" si="1">IFERROR(COUNTIF(INDIRECT("'"&amp;TEXT(A5,"dd-mm")&amp;"'!L3:L200"),TEXT(A5,"dd-mm")&amp;"-"&amp;B$1),0)</f>
+        <f t="shared" ref="B5:B27" ca="1" si="1">IFERROR(COUNTIF(INDIRECT("'"&amp;TEXT(A5,"dd-mm")&amp;"'!L3:L200"),TEXT(A5,"dd-mm")&amp;"-"&amp;B$1),0)</f>
         <v>51</v>
       </c>
       <c r="C5" s="33">
-        <f t="shared" ref="C5:C28" ca="1" si="2">IFERROR(COUNTIF(INDIRECT("'"&amp;TEXT(A5,"DD-MM")&amp;"'!M3:M200"),"*gộp*")/2,0)</f>
+        <f t="shared" ref="C5:C27" ca="1" si="2">IFERROR(COUNTIF(INDIRECT("'"&amp;TEXT(A5,"DD-MM")&amp;"'!M3:M200"),"*gộp*")/2,0)</f>
         <v>2</v>
       </c>
       <c r="D5" s="33" cm="1">
@@ -59283,7 +62889,7 @@
       </c>
       <c r="B27" s="33">
         <f t="shared" ca="1" si="1"/>
-        <v>0</v>
+        <v>58</v>
       </c>
       <c r="C27" s="33">
         <f t="shared" ca="1" si="2"/>
@@ -59295,78 +62901,57 @@
       </c>
       <c r="E27" s="33">
         <f t="shared" ca="1" si="0"/>
-        <v>0</v>
+        <v>58</v>
       </c>
     </row>
     <row r="28" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A28" s="32">
-        <v>46142</v>
-      </c>
-      <c r="B28" s="33">
-        <f t="shared" ca="1" si="1"/>
-        <v>0</v>
-      </c>
-      <c r="C28" s="33">
-        <f t="shared" ca="1" si="2"/>
-        <v>0</v>
-      </c>
-      <c r="D28" s="33" cm="1">
-        <f t="array" aca="1" ref="D28" ca="1">IFERROR(SUM(COUNTIF(INDIRECT("'"&amp;TEXT(A28,"DD-MM")&amp;"'!M3:M200"),{"*đơn trả*","*hàng tỉnh*"})),0)</f>
-        <v>0</v>
-      </c>
-      <c r="E28" s="33">
-        <f t="shared" ca="1" si="0"/>
-        <v>0</v>
+      <c r="D28" s="34" t="s">
+        <v>3102</v>
+      </c>
+      <c r="E28" s="34">
+        <f ca="1">SUBTOTAL(9,E3:E27)</f>
+        <v>1183</v>
       </c>
     </row>
     <row r="29" spans="1:5" x14ac:dyDescent="0.25">
       <c r="D29" s="34" t="s">
-        <v>3000</v>
-      </c>
-      <c r="E29" s="34">
-        <f ca="1">SUBTOTAL(9,E3:E28)</f>
-        <v>1125</v>
-      </c>
-    </row>
-    <row r="30" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="D30" s="34" t="s">
-        <v>3001</v>
-      </c>
-      <c r="E30" s="34" cm="1">
-        <f t="array" ref="E30" ca="1">SUMPRODUCT(
+        <v>3103</v>
+      </c>
+      <c r="E29" s="34" cm="1">
+        <f t="array" aca="1" ref="E29" ca="1">SUMPRODUCT(
     IFERROR(
         SUMIF(
-            INDIRECT("'"&amp;TEXT(A3:A28,"dd-mm")&amp;"'!O:O"),
+            INDIRECT("'"&amp;TEXT(A3:A27,"dd-mm")&amp;"'!O:O"),
             "tổng",
-            INDIRECT("'"&amp;TEXT(A3:A28,"dd-mm")&amp;"'!P:P")
+            INDIRECT("'"&amp;TEXT(A3:A27,"dd-mm")&amp;"'!P:P")
         ),
     0)
 )</f>
-        <v>6463</v>
+        <v>5909</v>
+      </c>
+    </row>
+    <row r="30" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="D30" s="34" t="s">
+        <v>3104</v>
+      </c>
+      <c r="E30" s="34">
+        <f ca="1">-E28*2</f>
+        <v>-2366</v>
       </c>
     </row>
     <row r="31" spans="1:5" x14ac:dyDescent="0.25">
       <c r="D31" s="34" t="s">
-        <v>3002</v>
+        <v>3105</v>
       </c>
       <c r="E31" s="34">
-        <f ca="1">-E29*2</f>
-        <v>-2250</v>
-      </c>
-    </row>
-    <row r="32" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="D32" s="34" t="s">
-        <v>3003</v>
-      </c>
-      <c r="E32" s="34">
-        <f ca="1">SUBTOTAL(9,E30:E31)</f>
-        <v>4213</v>
+        <f ca="1">SUBTOTAL(9,E29:E30)</f>
+        <v>3543</v>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A2:E28" xr:uid="{00000000-0009-0000-0000-000017000000}"/>
+  <autoFilter ref="A2:E27" xr:uid="{00000000-0009-0000-0000-000018000000}"/>
   <phoneticPr fontId="6" type="noConversion"/>
-  <conditionalFormatting sqref="C3:D28">
+  <conditionalFormatting sqref="C3:D27">
     <cfRule type="expression" dxfId="0" priority="1">
       <formula>C3&lt;&gt;0</formula>
     </cfRule>
@@ -61516,10 +65101,10 @@
       <c r="A57" s="1" t="s">
         <v>16</v>
       </c>
-      <c r="C57" s="45" t="s">
+      <c r="C57" s="47" t="s">
         <v>89</v>
       </c>
-      <c r="D57" s="45"/>
+      <c r="D57" s="47"/>
       <c r="E57" s="4" t="s">
         <v>90</v>
       </c>
@@ -61547,11 +65132,11 @@
       <c r="B58" s="3" t="s">
         <v>93</v>
       </c>
-      <c r="C58" s="46">
+      <c r="C58" s="48">
         <f>SUMIFS(I$3:I$53,B$3:B$53,A$57,L$3:L$53,A$58)</f>
         <v>29790</v>
       </c>
-      <c r="D58" s="46"/>
+      <c r="D58" s="48"/>
       <c r="E58" s="3">
         <f>SUMIFS(Q$3:Q$53,B$3:B$53,A$57,L$3:L$53,A$58)</f>
         <v>51</v>
@@ -61586,10 +65171,10 @@
       <c r="B59" s="2" t="s">
         <v>97</v>
       </c>
-      <c r="C59" s="47">
+      <c r="C59" s="49">
         <v>0</v>
       </c>
-      <c r="D59" s="47"/>
+      <c r="D59" s="49"/>
       <c r="K59" t="s">
         <v>98</v>
       </c>
@@ -61613,11 +65198,11 @@
       <c r="B60" s="2" t="s">
         <v>99</v>
       </c>
-      <c r="C60" s="47">
+      <c r="C60" s="49">
         <f>-SUMIFS(I$3:I$53,B$3:B$53,A$57,P$3:P$53,"xx",N$3:N$53,"x")</f>
         <v>0</v>
       </c>
-      <c r="D60" s="47"/>
+      <c r="D60" s="49"/>
       <c r="E60" s="2">
         <f>SUMIFS(Q$3:Q$53,B$3:B$53,A$57,P$3:P$53,"xx",N$3:N$53,"x")</f>
         <v>0</v>
@@ -61645,11 +65230,11 @@
       <c r="B61" s="4" t="s">
         <v>101</v>
       </c>
-      <c r="C61" s="45">
+      <c r="C61" s="47">
         <f>SUBTOTAL(9,C58:C60)</f>
         <v>29790</v>
       </c>
-      <c r="D61" s="45"/>
+      <c r="D61" s="47"/>
       <c r="E61">
         <f>E58</f>
         <v>51</v>
@@ -61669,8 +65254,8 @@
       <c r="B62" s="2" t="s">
         <v>104</v>
       </c>
-      <c r="C62" s="43"/>
-      <c r="D62" s="43"/>
+      <c r="C62" s="45"/>
+      <c r="D62" s="45"/>
       <c r="K62" s="2" t="s">
         <v>105</v>
       </c>
@@ -61686,8 +65271,8 @@
       <c r="B63" s="8" t="s">
         <v>107</v>
       </c>
-      <c r="C63" s="43"/>
-      <c r="D63" s="43"/>
+      <c r="C63" s="45"/>
+      <c r="D63" s="45"/>
       <c r="K63" s="10" t="s">
         <v>323</v>
       </c>
@@ -61709,11 +65294,11 @@
       <c r="B65" s="1" t="s">
         <v>108</v>
       </c>
-      <c r="C65" s="44">
+      <c r="C65" s="46">
         <f>C61+C62+C63</f>
         <v>29790</v>
       </c>
-      <c r="D65" s="44"/>
+      <c r="D65" s="46"/>
       <c r="E65" s="1" t="s">
         <v>109</v>
       </c>
@@ -63667,10 +67252,10 @@
       <c r="A48" s="1" t="s">
         <v>16</v>
       </c>
-      <c r="C48" s="45" t="s">
+      <c r="C48" s="47" t="s">
         <v>89</v>
       </c>
-      <c r="D48" s="45"/>
+      <c r="D48" s="47"/>
       <c r="E48" s="4" t="s">
         <v>90</v>
       </c>
@@ -63698,11 +67283,11 @@
       <c r="B49" s="3" t="s">
         <v>93</v>
       </c>
-      <c r="C49" s="46">
+      <c r="C49" s="48">
         <f>SUMIFS(I$3:I$44,B$3:B$44,A$48,L$3:L$44,A$49)</f>
         <v>20745</v>
       </c>
-      <c r="D49" s="46"/>
+      <c r="D49" s="48"/>
       <c r="E49" s="3">
         <f>SUMIFS(Q$3:Q$44,B$3:B$44,A$48,L$3:L$44,A$49)</f>
         <v>40</v>
@@ -63737,10 +67322,10 @@
       <c r="B50" s="2" t="s">
         <v>97</v>
       </c>
-      <c r="C50" s="47">
+      <c r="C50" s="49">
         <v>0</v>
       </c>
-      <c r="D50" s="47"/>
+      <c r="D50" s="49"/>
       <c r="K50" t="s">
         <v>98</v>
       </c>
@@ -63764,11 +67349,11 @@
       <c r="B51" s="2" t="s">
         <v>99</v>
       </c>
-      <c r="C51" s="47">
+      <c r="C51" s="49">
         <f>-SUMIFS(I$3:I$44,B$3:B$44,A$48,P$3:P$44,"xx",N$3:N$44,"x")</f>
         <v>-970</v>
       </c>
-      <c r="D51" s="47"/>
+      <c r="D51" s="49"/>
       <c r="E51" s="2">
         <f>SUMIFS(Q$3:Q$44,B$3:B$44,A$48,P$3:P$44,"xx",N$3:N$44,"x")</f>
         <v>2</v>
@@ -63788,11 +67373,11 @@
       <c r="B52" s="4" t="s">
         <v>101</v>
       </c>
-      <c r="C52" s="45">
+      <c r="C52" s="47">
         <f>SUBTOTAL(9,C49:C51)</f>
         <v>19775</v>
       </c>
-      <c r="D52" s="45"/>
+      <c r="D52" s="47"/>
       <c r="E52">
         <f>E49</f>
         <v>40</v>
@@ -63818,8 +67403,8 @@
       <c r="B53" s="2" t="s">
         <v>104</v>
       </c>
-      <c r="C53" s="43"/>
-      <c r="D53" s="43"/>
+      <c r="C53" s="45"/>
+      <c r="D53" s="45"/>
       <c r="K53" s="2" t="s">
         <v>105</v>
       </c>
@@ -63835,8 +67420,8 @@
       <c r="B54" s="8" t="s">
         <v>107</v>
       </c>
-      <c r="C54" s="43"/>
-      <c r="D54" s="43"/>
+      <c r="C54" s="45"/>
+      <c r="D54" s="45"/>
       <c r="L54" s="9">
         <f>SUBTOTAL(9,L49:L53)</f>
         <v>8722</v>
@@ -63857,11 +67442,11 @@
       <c r="B56" s="1" t="s">
         <v>108</v>
       </c>
-      <c r="C56" s="44">
+      <c r="C56" s="46">
         <f>C52+C53+C54</f>
         <v>19775</v>
       </c>
-      <c r="D56" s="44"/>
+      <c r="D56" s="46"/>
       <c r="E56" s="1" t="s">
         <v>109</v>
       </c>
@@ -66310,10 +69895,10 @@
       <c r="A59" s="1" t="s">
         <v>16</v>
       </c>
-      <c r="C59" s="45" t="s">
+      <c r="C59" s="47" t="s">
         <v>89</v>
       </c>
-      <c r="D59" s="45"/>
+      <c r="D59" s="47"/>
       <c r="E59" s="4" t="s">
         <v>90</v>
       </c>
@@ -66341,11 +69926,11 @@
       <c r="B60" s="3" t="s">
         <v>93</v>
       </c>
-      <c r="C60" s="46">
+      <c r="C60" s="48">
         <f>SUMIFS(I$3:I$55,B$3:B$55,A$59,L$3:L$55,A$60)</f>
         <v>33510</v>
       </c>
-      <c r="D60" s="46"/>
+      <c r="D60" s="48"/>
       <c r="E60" s="3">
         <f>SUMIFS(Q$3:Q$55,B$3:B$55,A$59,L$3:L$55,A$60)</f>
         <v>52</v>
@@ -66380,10 +69965,10 @@
       <c r="B61" s="2" t="s">
         <v>97</v>
       </c>
-      <c r="C61" s="47">
+      <c r="C61" s="49">
         <v>0</v>
       </c>
-      <c r="D61" s="47"/>
+      <c r="D61" s="49"/>
       <c r="K61" t="s">
         <v>98</v>
       </c>
@@ -66407,11 +69992,11 @@
       <c r="B62" s="2" t="s">
         <v>99</v>
       </c>
-      <c r="C62" s="47">
+      <c r="C62" s="49">
         <f>-SUMIFS(I$3:I$55,B$3:B$55,A$59,P$3:P$55,"xx",N$3:N$55,"x")</f>
         <v>-860</v>
       </c>
-      <c r="D62" s="47"/>
+      <c r="D62" s="49"/>
       <c r="E62" s="2">
         <f>SUMIFS(Q$3:Q$55,B$3:B$55,A$59,P$3:P$55,"xx",N$3:N$55,"x")</f>
         <v>1</v>
@@ -66439,11 +70024,11 @@
       <c r="B63" s="4" t="s">
         <v>101</v>
       </c>
-      <c r="C63" s="45">
+      <c r="C63" s="47">
         <f>SUBTOTAL(9,C60:C62)</f>
         <v>32650</v>
       </c>
-      <c r="D63" s="45"/>
+      <c r="D63" s="47"/>
       <c r="E63">
         <f>E60</f>
         <v>52</v>
@@ -66463,8 +70048,8 @@
       <c r="B64" s="2" t="s">
         <v>104</v>
       </c>
-      <c r="C64" s="43"/>
-      <c r="D64" s="43"/>
+      <c r="C64" s="45"/>
+      <c r="D64" s="45"/>
       <c r="K64" s="2" t="s">
         <v>105</v>
       </c>
@@ -66480,8 +70065,8 @@
       <c r="B65" s="8" t="s">
         <v>107</v>
       </c>
-      <c r="C65" s="43"/>
-      <c r="D65" s="43"/>
+      <c r="C65" s="45"/>
+      <c r="D65" s="45"/>
       <c r="L65" s="9">
         <f>SUBTOTAL(9,L60:L64)</f>
         <v>8748</v>
@@ -66495,11 +70080,11 @@
       <c r="B67" s="1" t="s">
         <v>108</v>
       </c>
-      <c r="C67" s="44">
+      <c r="C67" s="46">
         <f>C63+C64+C65</f>
         <v>32650</v>
       </c>
-      <c r="D67" s="44"/>
+      <c r="D67" s="46"/>
       <c r="E67" s="1" t="s">
         <v>109</v>
       </c>
@@ -67861,10 +71446,10 @@
       <c r="A33" s="1" t="s">
         <v>16</v>
       </c>
-      <c r="C33" s="45" t="s">
+      <c r="C33" s="47" t="s">
         <v>89</v>
       </c>
-      <c r="D33" s="45"/>
+      <c r="D33" s="47"/>
       <c r="E33" s="4" t="s">
         <v>90</v>
       </c>
@@ -67892,11 +71477,11 @@
       <c r="B34" s="3" t="s">
         <v>93</v>
       </c>
-      <c r="C34" s="48">
+      <c r="C34" s="50">
         <f>SUMIFS(I$3:I$29,B$3:B$29,A$33,L$3:L$29,A$34)+I32</f>
         <v>24145</v>
       </c>
-      <c r="D34" s="46"/>
+      <c r="D34" s="48"/>
       <c r="E34" s="3">
         <f>SUMIFS(Q$3:Q$29,B$3:B$29,A$33,L$3:L$29,A$34)</f>
         <v>25</v>
@@ -67931,10 +71516,10 @@
       <c r="B35" s="2" t="s">
         <v>97</v>
       </c>
-      <c r="C35" s="47">
+      <c r="C35" s="49">
         <v>0</v>
       </c>
-      <c r="D35" s="47"/>
+      <c r="D35" s="49"/>
       <c r="K35" t="s">
         <v>98</v>
       </c>
@@ -67958,11 +71543,11 @@
       <c r="B36" s="2" t="s">
         <v>99</v>
       </c>
-      <c r="C36" s="47">
+      <c r="C36" s="49">
         <f>-SUMIFS(I$3:I$29,B$3:B$29,A$33,P$3:P$29,"xx",N$3:N$29,"x")</f>
         <v>-1715</v>
       </c>
-      <c r="D36" s="47"/>
+      <c r="D36" s="49"/>
       <c r="E36" s="2">
         <f>SUMIFS(Q$3:Q$29,B$3:B$29,A$33,P$3:P$29,"xx",N$3:N$29,"x")</f>
         <v>2</v>
@@ -67990,11 +71575,11 @@
       <c r="B37" s="4" t="s">
         <v>101</v>
       </c>
-      <c r="C37" s="45">
+      <c r="C37" s="47">
         <f>SUBTOTAL(9,C34:C36)</f>
         <v>22430</v>
       </c>
-      <c r="D37" s="45"/>
+      <c r="D37" s="47"/>
       <c r="E37">
         <f>E34</f>
         <v>25</v>
@@ -68013,10 +71598,10 @@
       <c r="B38" s="2" t="s">
         <v>104</v>
       </c>
-      <c r="C38" s="43">
+      <c r="C38" s="45">
         <v>-70</v>
       </c>
-      <c r="D38" s="43"/>
+      <c r="D38" s="45"/>
       <c r="K38" s="2" t="s">
         <v>105</v>
       </c>
@@ -68035,8 +71620,8 @@
       <c r="B39" s="8" t="s">
         <v>107</v>
       </c>
-      <c r="C39" s="43"/>
-      <c r="D39" s="43"/>
+      <c r="C39" s="45"/>
+      <c r="D39" s="45"/>
       <c r="K39" s="10" t="s">
         <v>664</v>
       </c>
@@ -68073,11 +71658,11 @@
       <c r="B42" s="1" t="s">
         <v>108</v>
       </c>
-      <c r="C42" s="44">
+      <c r="C42" s="46">
         <f>C37+C38+C39</f>
         <v>22360</v>
       </c>
-      <c r="D42" s="44"/>
+      <c r="D42" s="46"/>
       <c r="E42" s="1" t="s">
         <v>109</v>
       </c>
@@ -70376,10 +73961,10 @@
       <c r="A51" s="1" t="s">
         <v>16</v>
       </c>
-      <c r="C51" s="45" t="s">
+      <c r="C51" s="47" t="s">
         <v>89</v>
       </c>
-      <c r="D51" s="45"/>
+      <c r="D51" s="47"/>
       <c r="E51" s="4" t="s">
         <v>90</v>
       </c>
@@ -70407,11 +73992,11 @@
       <c r="B52" s="3" t="s">
         <v>93</v>
       </c>
-      <c r="C52" s="46">
+      <c r="C52" s="48">
         <f>SUMIFS(I$3:I$47,B$3:B$47,A$51,L$3:L$47,A$52)</f>
         <v>25380</v>
       </c>
-      <c r="D52" s="46"/>
+      <c r="D52" s="48"/>
       <c r="E52" s="3">
         <f>SUMIFS(Q$3:Q$47,B$3:B$47,A$51,L$3:L$47,A$52)</f>
         <v>43</v>
@@ -70446,10 +74031,10 @@
       <c r="B53" s="2" t="s">
         <v>97</v>
       </c>
-      <c r="C53" s="47">
+      <c r="C53" s="49">
         <v>0</v>
       </c>
-      <c r="D53" s="47"/>
+      <c r="D53" s="49"/>
       <c r="K53" t="s">
         <v>98</v>
       </c>
@@ -70473,11 +74058,11 @@
       <c r="B54" s="2" t="s">
         <v>99</v>
       </c>
-      <c r="C54" s="47">
+      <c r="C54" s="49">
         <f>-SUMIFS(I$3:I$47,B$3:B$47,A$51,P$3:P$47,"xx",N$3:N$47,"x")</f>
         <v>-710</v>
       </c>
-      <c r="D54" s="47"/>
+      <c r="D54" s="49"/>
       <c r="E54" s="2">
         <f>SUMIFS(Q$3:Q$47,B$3:B$47,A$51,P$3:P$47,"xx",N$3:N$47,"x")</f>
         <v>3</v>
@@ -70505,11 +74090,11 @@
       <c r="B55" s="4" t="s">
         <v>101</v>
       </c>
-      <c r="C55" s="45">
+      <c r="C55" s="47">
         <f>SUBTOTAL(9,C52:C54)</f>
         <v>24670</v>
       </c>
-      <c r="D55" s="45"/>
+      <c r="D55" s="47"/>
       <c r="E55">
         <f>E52</f>
         <v>43</v>
@@ -70529,8 +74114,8 @@
       <c r="B56" s="2" t="s">
         <v>104</v>
       </c>
-      <c r="C56" s="43"/>
-      <c r="D56" s="43"/>
+      <c r="C56" s="45"/>
+      <c r="D56" s="45"/>
       <c r="K56" s="2" t="s">
         <v>105</v>
       </c>
@@ -70546,8 +74131,8 @@
       <c r="B57" s="8" t="s">
         <v>107</v>
       </c>
-      <c r="C57" s="43"/>
-      <c r="D57" s="43"/>
+      <c r="C57" s="45"/>
+      <c r="D57" s="45"/>
       <c r="L57" s="9">
         <f>SUBTOTAL(9,L52:L56)</f>
         <v>4847</v>
@@ -70568,11 +74153,11 @@
       <c r="B59" s="1" t="s">
         <v>108</v>
       </c>
-      <c r="C59" s="44">
+      <c r="C59" s="46">
         <f>C55+C56+C57</f>
         <v>24670</v>
       </c>
-      <c r="D59" s="44"/>
+      <c r="D59" s="46"/>
       <c r="E59" s="1" t="s">
         <v>109</v>
       </c>
@@ -72556,10 +76141,10 @@
       <c r="A43" s="1" t="s">
         <v>16</v>
       </c>
-      <c r="C43" s="45" t="s">
+      <c r="C43" s="47" t="s">
         <v>89</v>
       </c>
-      <c r="D43" s="45"/>
+      <c r="D43" s="47"/>
       <c r="E43" s="4" t="s">
         <v>90</v>
       </c>
@@ -72587,11 +76172,11 @@
       <c r="B44" s="3" t="s">
         <v>93</v>
       </c>
-      <c r="C44" s="46">
+      <c r="C44" s="48">
         <f>SUMIFS(I$3:I$39,B$3:B$39,A$43,L$3:L$39,A$44)</f>
         <v>23985</v>
       </c>
-      <c r="D44" s="46"/>
+      <c r="D44" s="48"/>
       <c r="E44" s="3">
         <f>SUMIFS(Q$3:Q$39,B$3:B$39,A$43,L$3:L$39,A$44)</f>
         <v>37</v>
@@ -72622,10 +76207,10 @@
       <c r="B45" s="2" t="s">
         <v>97</v>
       </c>
-      <c r="C45" s="47">
+      <c r="C45" s="49">
         <v>0</v>
       </c>
-      <c r="D45" s="47"/>
+      <c r="D45" s="49"/>
       <c r="K45" t="s">
         <v>98</v>
       </c>
@@ -72649,11 +76234,11 @@
       <c r="B46" s="2" t="s">
         <v>99</v>
       </c>
-      <c r="C46" s="47">
+      <c r="C46" s="49">
         <f>-SUMIFS(I$3:I$39,B$3:B$39,A$43,P$3:P$39,"xx",N$3:N$39,"x")</f>
         <v>0</v>
       </c>
-      <c r="D46" s="47"/>
+      <c r="D46" s="49"/>
       <c r="E46" s="2">
         <f>SUMIFS(Q$3:Q$39,B$3:B$39,A$43,P$3:P$39,"xx",N$3:N$39,"x")</f>
         <v>0</v>
@@ -72681,11 +76266,11 @@
       <c r="B47" s="4" t="s">
         <v>101</v>
       </c>
-      <c r="C47" s="45">
+      <c r="C47" s="47">
         <f>SUBTOTAL(9,C44:C46)</f>
         <v>23985</v>
       </c>
-      <c r="D47" s="45"/>
+      <c r="D47" s="47"/>
       <c r="E47">
         <f>E44</f>
         <v>37</v>
@@ -72705,8 +76290,8 @@
       <c r="B48" s="2" t="s">
         <v>104</v>
       </c>
-      <c r="C48" s="43"/>
-      <c r="D48" s="43"/>
+      <c r="C48" s="45"/>
+      <c r="D48" s="45"/>
       <c r="K48" s="2" t="s">
         <v>105</v>
       </c>
@@ -72722,8 +76307,8 @@
       <c r="B49" s="8" t="s">
         <v>107</v>
       </c>
-      <c r="C49" s="43"/>
-      <c r="D49" s="43"/>
+      <c r="C49" s="45"/>
+      <c r="D49" s="45"/>
       <c r="L49" s="9">
         <f>SUBTOTAL(9,L44:L48)</f>
         <v>7556</v>
@@ -72737,11 +76322,11 @@
       <c r="B51" s="1" t="s">
         <v>108</v>
       </c>
-      <c r="C51" s="44">
+      <c r="C51" s="46">
         <f>C47+C48+C49</f>
         <v>23985</v>
       </c>
-      <c r="D51" s="44"/>
+      <c r="D51" s="46"/>
       <c r="E51" s="1" t="s">
         <v>109</v>
       </c>
@@ -75386,10 +78971,10 @@
       <c r="A58" s="1" t="s">
         <v>16</v>
       </c>
-      <c r="C58" s="45" t="s">
+      <c r="C58" s="47" t="s">
         <v>89</v>
       </c>
-      <c r="D58" s="45"/>
+      <c r="D58" s="47"/>
       <c r="E58" s="4" t="s">
         <v>90</v>
       </c>
@@ -75417,11 +79002,11 @@
       <c r="B59" s="3" t="s">
         <v>93</v>
       </c>
-      <c r="C59" s="46">
+      <c r="C59" s="48">
         <f>SUMIFS(I$3:I$55,B$3:B$55,A$58,L$3:L$55,A$59)</f>
         <v>43676</v>
       </c>
-      <c r="D59" s="46"/>
+      <c r="D59" s="48"/>
       <c r="E59" s="3">
         <f>SUMIFS(Q$3:Q$55,B$3:B$55,A$58,L$3:L$55,A$59)</f>
         <v>51</v>
@@ -75452,10 +79037,10 @@
       <c r="B60" s="2" t="s">
         <v>97</v>
       </c>
-      <c r="C60" s="47">
+      <c r="C60" s="49">
         <v>0</v>
       </c>
-      <c r="D60" s="47"/>
+      <c r="D60" s="49"/>
       <c r="K60" t="s">
         <v>98</v>
       </c>
@@ -75479,11 +79064,11 @@
       <c r="B61" s="2" t="s">
         <v>99</v>
       </c>
-      <c r="C61" s="47">
+      <c r="C61" s="49">
         <f>-SUMIFS(I$3:I$55,B$3:B$55,A$58,P$3:P$55,"xx",N$3:N$55,"x")</f>
         <v>-975</v>
       </c>
-      <c r="D61" s="47"/>
+      <c r="D61" s="49"/>
       <c r="E61" s="2">
         <f>SUMIFS(Q$3:Q$55,B$3:B$55,A$58,P$3:P$55,"xx",N$3:N$55,"x")</f>
         <v>2</v>
@@ -75503,11 +79088,11 @@
       <c r="B62" s="4" t="s">
         <v>101</v>
       </c>
-      <c r="C62" s="45">
+      <c r="C62" s="47">
         <f>SUBTOTAL(9,C59:C61)</f>
         <v>42701</v>
       </c>
-      <c r="D62" s="45"/>
+      <c r="D62" s="47"/>
       <c r="E62">
         <f>E59</f>
         <v>51</v>
@@ -75533,8 +79118,8 @@
       <c r="B63" s="2" t="s">
         <v>104</v>
       </c>
-      <c r="C63" s="43"/>
-      <c r="D63" s="43"/>
+      <c r="C63" s="45"/>
+      <c r="D63" s="45"/>
       <c r="K63" s="2" t="s">
         <v>105</v>
       </c>
@@ -75550,8 +79135,8 @@
       <c r="B64" s="8" t="s">
         <v>107</v>
       </c>
-      <c r="C64" s="43"/>
-      <c r="D64" s="43"/>
+      <c r="C64" s="45"/>
+      <c r="D64" s="45"/>
       <c r="L64" s="9">
         <f>SUBTOTAL(9,L59:L63)</f>
         <v>9811</v>
@@ -75565,11 +79150,11 @@
       <c r="B66" s="1" t="s">
         <v>108</v>
       </c>
-      <c r="C66" s="44">
+      <c r="C66" s="46">
         <f>C62+C63+C64</f>
         <v>42701</v>
       </c>
-      <c r="D66" s="44"/>
+      <c r="D66" s="46"/>
       <c r="E66" s="1" t="s">
         <v>109</v>
       </c>

--- a/data/Apr/InternalDailyReport.xlsx
+++ b/data/Apr/InternalDailyReport.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\Work\Freelance\TextInputter\data\Apr\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{E8714206-4EC6-4B27-809B-E512127A59AD}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{FAEC1CF1-2D37-4293-B3C7-3F95D92CFCE7}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" firstSheet="11" activeTab="25" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" firstSheet="11" activeTab="23" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="01-04" sheetId="2" r:id="rId1"/>
@@ -108,7 +108,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="11399" uniqueCount="3251">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="11400" uniqueCount="3252">
   <si>
     <t>Tình trạng TT</t>
   </si>
@@ -9861,6 +9861,9 @@
   </si>
   <si>
     <t>at 29-04</t>
+  </si>
+  <si>
+    <t>ư</t>
   </si>
 </sst>
 </file>
@@ -58734,8 +58737,8 @@
       <c r="B55" s="2" t="s">
         <v>97</v>
       </c>
-      <c r="C55" s="49">
-        <v>0</v>
+      <c r="C55" s="49" t="s">
+        <v>3251</v>
       </c>
       <c r="D55" s="49"/>
       <c r="K55" t="s">
@@ -59149,22 +59152,22 @@
     </sortState>
   </autoFilter>
   <mergeCells count="16">
+    <mergeCell ref="C53:D53"/>
+    <mergeCell ref="C54:D54"/>
+    <mergeCell ref="C55:D55"/>
+    <mergeCell ref="C56:D56"/>
+    <mergeCell ref="C57:D57"/>
+    <mergeCell ref="C58:D58"/>
+    <mergeCell ref="C59:D59"/>
+    <mergeCell ref="C61:D61"/>
+    <mergeCell ref="C63:D63"/>
+    <mergeCell ref="C64:D64"/>
     <mergeCell ref="C71:D71"/>
     <mergeCell ref="C65:D65"/>
     <mergeCell ref="C66:D66"/>
     <mergeCell ref="C67:D67"/>
     <mergeCell ref="C68:D68"/>
     <mergeCell ref="C69:D69"/>
-    <mergeCell ref="C58:D58"/>
-    <mergeCell ref="C59:D59"/>
-    <mergeCell ref="C61:D61"/>
-    <mergeCell ref="C63:D63"/>
-    <mergeCell ref="C64:D64"/>
-    <mergeCell ref="C53:D53"/>
-    <mergeCell ref="C54:D54"/>
-    <mergeCell ref="C55:D55"/>
-    <mergeCell ref="C56:D56"/>
-    <mergeCell ref="C57:D57"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="0.75" bottom="0.5" header="0.5" footer="0.75"/>
 </worksheet>

--- a/data/Apr/InternalDailyReport.xlsx
+++ b/data/Apr/InternalDailyReport.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\Work\Freelance\TextInputter\data\Apr\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{FAEC1CF1-2D37-4293-B3C7-3F95D92CFCE7}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{87B02493-7529-413D-91E3-1D0958980E39}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" firstSheet="11" activeTab="23" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -10069,11 +10069,11 @@
     <xf numFmtId="0" fontId="0" fillId="10" borderId="0" xfId="0" applyFill="1"/>
     <xf numFmtId="0" fontId="5" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1"/>
     <xf numFmtId="3" fontId="5" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
-    <xf numFmtId="0" fontId="3" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="0" fillId="3" borderId="0" xfId="0" applyFill="1"/>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
+    <xf numFmtId="0" fontId="3" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
     <xf numFmtId="3" fontId="0" fillId="3" borderId="0" xfId="0" applyNumberFormat="1" applyFill="1"/>
   </cellXfs>
   <cellStyles count="2">
@@ -11343,10 +11343,10 @@
       <c r="A27" s="1" t="s">
         <v>16</v>
       </c>
-      <c r="C27" s="47" t="s">
+      <c r="C27" s="45" t="s">
         <v>89</v>
       </c>
-      <c r="D27" s="47"/>
+      <c r="D27" s="45"/>
       <c r="E27" s="4" t="s">
         <v>90</v>
       </c>
@@ -11374,11 +11374,11 @@
       <c r="B28" s="3" t="s">
         <v>93</v>
       </c>
-      <c r="C28" s="48">
+      <c r="C28" s="46">
         <f>SUMIFS(I$3:I$23,B$3:B$23,A$27,L$3:L$23,A$28)</f>
         <v>11295</v>
       </c>
-      <c r="D28" s="48"/>
+      <c r="D28" s="46"/>
       <c r="E28" s="3">
         <f>SUMIFS(Q$3:Q$23,B$3:B$23,A$27,L$3:L$23,A$28)</f>
         <v>21</v>
@@ -11409,10 +11409,10 @@
       <c r="B29" s="2" t="s">
         <v>97</v>
       </c>
-      <c r="C29" s="49">
+      <c r="C29" s="47">
         <v>0</v>
       </c>
-      <c r="D29" s="49"/>
+      <c r="D29" s="47"/>
       <c r="K29" t="s">
         <v>98</v>
       </c>
@@ -11436,11 +11436,11 @@
       <c r="B30" s="2" t="s">
         <v>99</v>
       </c>
-      <c r="C30" s="49">
+      <c r="C30" s="47">
         <f>-SUMIFS(I$3:I$23,B$3:B$23,A$27,P$3:P$23,"xx",N$3:N$23,"x")</f>
         <v>0</v>
       </c>
-      <c r="D30" s="49"/>
+      <c r="D30" s="47"/>
       <c r="E30" s="2">
         <f>SUMIFS(Q$3:Q$23,B$3:B$23,A$27,P$3:P$23,"xx",N$3:N$23,"x")</f>
         <v>0</v>
@@ -11460,11 +11460,11 @@
       <c r="B31" s="4" t="s">
         <v>101</v>
       </c>
-      <c r="C31" s="47">
+      <c r="C31" s="45">
         <f>SUBTOTAL(9,C28:C30)</f>
         <v>11295</v>
       </c>
-      <c r="D31" s="47"/>
+      <c r="D31" s="45"/>
       <c r="E31">
         <f>E28</f>
         <v>21</v>
@@ -11484,8 +11484,8 @@
       <c r="B32" s="2" t="s">
         <v>104</v>
       </c>
-      <c r="C32" s="45"/>
-      <c r="D32" s="45"/>
+      <c r="C32" s="48"/>
+      <c r="D32" s="48"/>
       <c r="K32" s="2" t="s">
         <v>105</v>
       </c>
@@ -11501,8 +11501,8 @@
       <c r="B33" s="8" t="s">
         <v>107</v>
       </c>
-      <c r="C33" s="45"/>
-      <c r="D33" s="45"/>
+      <c r="C33" s="48"/>
+      <c r="D33" s="48"/>
       <c r="L33" s="9">
         <f>SUBTOTAL(9,L28:L32)</f>
         <v>7314</v>
@@ -11516,11 +11516,11 @@
       <c r="B35" s="1" t="s">
         <v>108</v>
       </c>
-      <c r="C35" s="46">
+      <c r="C35" s="49">
         <f>C31+C32+C33</f>
         <v>11295</v>
       </c>
-      <c r="D35" s="46"/>
+      <c r="D35" s="49"/>
       <c r="E35" s="1" t="s">
         <v>109</v>
       </c>
@@ -13621,10 +13621,10 @@
       <c r="A47" s="1" t="s">
         <v>16</v>
       </c>
-      <c r="C47" s="47" t="s">
+      <c r="C47" s="45" t="s">
         <v>89</v>
       </c>
-      <c r="D47" s="47"/>
+      <c r="D47" s="45"/>
       <c r="E47" s="4" t="s">
         <v>90</v>
       </c>
@@ -13652,11 +13652,11 @@
       <c r="B48" s="3" t="s">
         <v>93</v>
       </c>
-      <c r="C48" s="48">
+      <c r="C48" s="46">
         <f>SUMIFS(I$3:I$43,B$3:B$43,A$47,L$3:L$43,A$48)</f>
         <v>28800</v>
       </c>
-      <c r="D48" s="48"/>
+      <c r="D48" s="46"/>
       <c r="E48" s="3">
         <f>SUMIFS(Q$3:Q$43,B$3:B$43,A$47,L$3:L$43,A$48)</f>
         <v>41</v>
@@ -13691,10 +13691,10 @@
       <c r="B49" s="2" t="s">
         <v>97</v>
       </c>
-      <c r="C49" s="49">
+      <c r="C49" s="47">
         <v>0</v>
       </c>
-      <c r="D49" s="49"/>
+      <c r="D49" s="47"/>
       <c r="K49" t="s">
         <v>98</v>
       </c>
@@ -13718,11 +13718,11 @@
       <c r="B50" s="2" t="s">
         <v>99</v>
       </c>
-      <c r="C50" s="49">
+      <c r="C50" s="47">
         <f>-SUMIFS(I$3:I$43,B$3:B$43,A$47,P$3:P$43,"xx",N$3:N$43,"x")</f>
         <v>0</v>
       </c>
-      <c r="D50" s="49"/>
+      <c r="D50" s="47"/>
       <c r="E50" s="2">
         <f>SUMIFS(Q$3:Q$43,B$3:B$43,A$47,P$3:P$43,"xx",N$3:N$43,"x")</f>
         <v>0</v>
@@ -13750,11 +13750,11 @@
       <c r="B51" s="4" t="s">
         <v>101</v>
       </c>
-      <c r="C51" s="47">
+      <c r="C51" s="45">
         <f>SUBTOTAL(9,C48:C50)</f>
         <v>28800</v>
       </c>
-      <c r="D51" s="47"/>
+      <c r="D51" s="45"/>
       <c r="E51">
         <f>E48</f>
         <v>41</v>
@@ -13774,8 +13774,8 @@
       <c r="B52" s="2" t="s">
         <v>104</v>
       </c>
-      <c r="C52" s="45"/>
-      <c r="D52" s="45"/>
+      <c r="C52" s="48"/>
+      <c r="D52" s="48"/>
       <c r="K52" s="2" t="s">
         <v>105</v>
       </c>
@@ -13791,8 +13791,8 @@
       <c r="B53" s="8" t="s">
         <v>107</v>
       </c>
-      <c r="C53" s="45"/>
-      <c r="D53" s="45"/>
+      <c r="C53" s="48"/>
+      <c r="D53" s="48"/>
       <c r="L53" s="9">
         <f>SUBTOTAL(9,L48:L52)</f>
         <v>3498</v>
@@ -13813,11 +13813,11 @@
       <c r="B55" s="1" t="s">
         <v>108</v>
       </c>
-      <c r="C55" s="46">
+      <c r="C55" s="49">
         <f>C51+C52+C53</f>
         <v>28800</v>
       </c>
-      <c r="D55" s="46"/>
+      <c r="D55" s="49"/>
       <c r="E55" s="1" t="s">
         <v>109</v>
       </c>
@@ -17002,10 +17002,10 @@
       <c r="A70" s="1" t="s">
         <v>16</v>
       </c>
-      <c r="C70" s="47" t="s">
+      <c r="C70" s="45" t="s">
         <v>89</v>
       </c>
-      <c r="D70" s="47"/>
+      <c r="D70" s="45"/>
       <c r="E70" s="4" t="s">
         <v>90</v>
       </c>
@@ -17033,11 +17033,11 @@
       <c r="B71" s="3" t="s">
         <v>93</v>
       </c>
-      <c r="C71" s="48">
+      <c r="C71" s="46">
         <f>SUMIFS(I$3:I$66,B$3:B$66,A$70,L$3:L$66,A$71)</f>
         <v>40275</v>
       </c>
-      <c r="D71" s="48"/>
+      <c r="D71" s="46"/>
       <c r="E71" s="3">
         <f>SUMIFS(Q$3:Q$66,B$3:B$66,A$70,L$3:L$66,A$71)</f>
         <v>63</v>
@@ -17072,10 +17072,10 @@
       <c r="B72" s="2" t="s">
         <v>97</v>
       </c>
-      <c r="C72" s="49">
+      <c r="C72" s="47">
         <v>0</v>
       </c>
-      <c r="D72" s="49"/>
+      <c r="D72" s="47"/>
       <c r="K72" t="s">
         <v>98</v>
       </c>
@@ -17099,11 +17099,11 @@
       <c r="B73" s="2" t="s">
         <v>99</v>
       </c>
-      <c r="C73" s="49">
+      <c r="C73" s="47">
         <f>-SUMIFS(I$3:I$66,B$3:B$66,A$70,P$3:P$66,"xx",N$3:N$66,"x")</f>
         <v>-790</v>
       </c>
-      <c r="D73" s="49"/>
+      <c r="D73" s="47"/>
       <c r="E73" s="2">
         <f>SUMIFS(Q$3:Q$66,B$3:B$66,A$70,P$3:P$66,"xx",N$3:N$66,"x")</f>
         <v>1</v>
@@ -17123,11 +17123,11 @@
       <c r="B74" s="4" t="s">
         <v>101</v>
       </c>
-      <c r="C74" s="47">
+      <c r="C74" s="45">
         <f>SUBTOTAL(9,C71:C73)</f>
         <v>39485</v>
       </c>
-      <c r="D74" s="47"/>
+      <c r="D74" s="45"/>
       <c r="E74">
         <f>E71</f>
         <v>63</v>
@@ -17147,8 +17147,8 @@
       <c r="B75" s="2" t="s">
         <v>104</v>
       </c>
-      <c r="C75" s="45"/>
-      <c r="D75" s="45"/>
+      <c r="C75" s="48"/>
+      <c r="D75" s="48"/>
       <c r="K75" s="2" t="s">
         <v>105</v>
       </c>
@@ -17164,8 +17164,8 @@
       <c r="B76" s="8" t="s">
         <v>107</v>
       </c>
-      <c r="C76" s="45"/>
-      <c r="D76" s="45"/>
+      <c r="C76" s="48"/>
+      <c r="D76" s="48"/>
       <c r="L76" s="9">
         <f>SUBTOTAL(9,L71:L75)</f>
         <v>15833</v>
@@ -17194,11 +17194,11 @@
       <c r="B78" s="1" t="s">
         <v>108</v>
       </c>
-      <c r="C78" s="46">
+      <c r="C78" s="49">
         <f>C74+C75+C76</f>
         <v>39485</v>
       </c>
-      <c r="D78" s="46"/>
+      <c r="D78" s="49"/>
       <c r="E78" s="1" t="s">
         <v>109</v>
       </c>
@@ -18650,10 +18650,10 @@
       <c r="A30" s="1" t="s">
         <v>16</v>
       </c>
-      <c r="C30" s="47" t="s">
+      <c r="C30" s="45" t="s">
         <v>89</v>
       </c>
-      <c r="D30" s="47"/>
+      <c r="D30" s="45"/>
       <c r="E30" s="4" t="s">
         <v>90</v>
       </c>
@@ -18681,11 +18681,11 @@
       <c r="B31" s="3" t="s">
         <v>93</v>
       </c>
-      <c r="C31" s="48">
+      <c r="C31" s="46">
         <f>SUMIFS(I$3:I$26,B$3:B$26,A$30,L$3:L$26,A$31)</f>
         <v>10860</v>
       </c>
-      <c r="D31" s="48"/>
+      <c r="D31" s="46"/>
       <c r="E31" s="3">
         <f>SUMIFS(Q$3:Q$26,B$3:B$26,A$30,L$3:L$26,A$31)</f>
         <v>20</v>
@@ -18720,10 +18720,10 @@
       <c r="B32" s="2" t="s">
         <v>97</v>
       </c>
-      <c r="C32" s="49">
+      <c r="C32" s="47">
         <v>0</v>
       </c>
-      <c r="D32" s="49"/>
+      <c r="D32" s="47"/>
       <c r="K32" t="s">
         <v>98</v>
       </c>
@@ -18747,11 +18747,11 @@
       <c r="B33" s="2" t="s">
         <v>99</v>
       </c>
-      <c r="C33" s="49">
+      <c r="C33" s="47">
         <f>-SUMIFS(I$3:I$26,B$3:B$26,A$30,P$3:P$26,"xx",N$3:N$26,"x")</f>
         <v>-2910</v>
       </c>
-      <c r="D33" s="49"/>
+      <c r="D33" s="47"/>
       <c r="E33" s="2">
         <f>SUMIFS(Q$3:Q$26,B$3:B$26,A$30,P$3:P$26,"xx",N$3:N$26,"x")</f>
         <v>4</v>
@@ -18771,11 +18771,11 @@
       <c r="B34" s="4" t="s">
         <v>101</v>
       </c>
-      <c r="C34" s="47">
+      <c r="C34" s="45">
         <f>SUBTOTAL(9,C31:C33)</f>
         <v>7950</v>
       </c>
-      <c r="D34" s="47"/>
+      <c r="D34" s="45"/>
       <c r="E34">
         <f>E31</f>
         <v>20</v>
@@ -18801,8 +18801,8 @@
       <c r="B35" s="2" t="s">
         <v>104</v>
       </c>
-      <c r="C35" s="45"/>
-      <c r="D35" s="45"/>
+      <c r="C35" s="48"/>
+      <c r="D35" s="48"/>
       <c r="K35" s="2" t="s">
         <v>105</v>
       </c>
@@ -18818,8 +18818,8 @@
       <c r="B36" s="8" t="s">
         <v>107</v>
       </c>
-      <c r="C36" s="45"/>
-      <c r="D36" s="45"/>
+      <c r="C36" s="48"/>
+      <c r="D36" s="48"/>
       <c r="L36" s="9">
         <f>SUBTOTAL(9,L31:L35)</f>
         <v>-328</v>
@@ -18840,11 +18840,11 @@
       <c r="B38" s="1" t="s">
         <v>108</v>
       </c>
-      <c r="C38" s="46">
+      <c r="C38" s="49">
         <f>C34+C35+C36</f>
         <v>7950</v>
       </c>
-      <c r="D38" s="46"/>
+      <c r="D38" s="49"/>
       <c r="E38" s="1" t="s">
         <v>109</v>
       </c>
@@ -20655,10 +20655,10 @@
       <c r="A39" s="1" t="s">
         <v>16</v>
       </c>
-      <c r="C39" s="47" t="s">
+      <c r="C39" s="45" t="s">
         <v>89</v>
       </c>
-      <c r="D39" s="47"/>
+      <c r="D39" s="45"/>
       <c r="E39" s="4" t="s">
         <v>90</v>
       </c>
@@ -20686,11 +20686,11 @@
       <c r="B40" s="3" t="s">
         <v>93</v>
       </c>
-      <c r="C40" s="48">
+      <c r="C40" s="46">
         <f>SUMIFS(I$3:I$35,B$3:B$35,A$39,L$3:L$35,A$40)</f>
         <v>22860</v>
       </c>
-      <c r="D40" s="48"/>
+      <c r="D40" s="46"/>
       <c r="E40" s="3">
         <f>SUMIFS(Q$3:Q$35,B$3:B$35,A$39,L$3:L$35,A$40)</f>
         <v>32</v>
@@ -20725,10 +20725,10 @@
       <c r="B41" s="2" t="s">
         <v>97</v>
       </c>
-      <c r="C41" s="49">
+      <c r="C41" s="47">
         <v>0</v>
       </c>
-      <c r="D41" s="49"/>
+      <c r="D41" s="47"/>
       <c r="K41" t="s">
         <v>98</v>
       </c>
@@ -20752,11 +20752,11 @@
       <c r="B42" s="2" t="s">
         <v>99</v>
       </c>
-      <c r="C42" s="49">
+      <c r="C42" s="47">
         <f>-SUMIFS(I$3:I$35,B$3:B$35,A$39,P$3:P$35,"xx",N$3:N$35,"x")</f>
         <v>-870</v>
       </c>
-      <c r="D42" s="49"/>
+      <c r="D42" s="47"/>
       <c r="E42" s="2">
         <f>SUMIFS(Q$3:Q$35,B$3:B$35,A$39,P$3:P$35,"xx",N$3:N$35,"x")</f>
         <v>1</v>
@@ -20776,11 +20776,11 @@
       <c r="B43" s="4" t="s">
         <v>101</v>
       </c>
-      <c r="C43" s="47">
+      <c r="C43" s="45">
         <f>SUBTOTAL(9,C40:C42)</f>
         <v>21990</v>
       </c>
-      <c r="D43" s="47"/>
+      <c r="D43" s="45"/>
       <c r="E43">
         <f>E40</f>
         <v>32</v>
@@ -20800,8 +20800,8 @@
       <c r="B44" s="2" t="s">
         <v>104</v>
       </c>
-      <c r="C44" s="45"/>
-      <c r="D44" s="45"/>
+      <c r="C44" s="48"/>
+      <c r="D44" s="48"/>
       <c r="K44" s="2" t="s">
         <v>105</v>
       </c>
@@ -20817,8 +20817,8 @@
       <c r="B45" s="8" t="s">
         <v>107</v>
       </c>
-      <c r="C45" s="45"/>
-      <c r="D45" s="45"/>
+      <c r="C45" s="48"/>
+      <c r="D45" s="48"/>
       <c r="L45" s="9">
         <f>SUBTOTAL(9,L40:L44)</f>
         <v>5050</v>
@@ -20839,11 +20839,11 @@
       <c r="B47" s="1" t="s">
         <v>108</v>
       </c>
-      <c r="C47" s="46">
+      <c r="C47" s="49">
         <f>C43+C44+C45</f>
         <v>21990</v>
       </c>
-      <c r="D47" s="46"/>
+      <c r="D47" s="49"/>
       <c r="E47" s="1" t="s">
         <v>109</v>
       </c>
@@ -23419,10 +23419,10 @@
       <c r="A56" s="1" t="s">
         <v>16</v>
       </c>
-      <c r="C56" s="47" t="s">
+      <c r="C56" s="45" t="s">
         <v>89</v>
       </c>
-      <c r="D56" s="47"/>
+      <c r="D56" s="45"/>
       <c r="E56" s="4" t="s">
         <v>90</v>
       </c>
@@ -23450,11 +23450,11 @@
       <c r="B57" s="3" t="s">
         <v>93</v>
       </c>
-      <c r="C57" s="48">
+      <c r="C57" s="46">
         <f>SUMIFS(I$3:I$52,B$3:B$52,A$56,L$3:L$52,A$57)</f>
         <v>28155</v>
       </c>
-      <c r="D57" s="48"/>
+      <c r="D57" s="46"/>
       <c r="E57" s="3">
         <f>SUMIFS(Q$3:Q$52,B$3:B$52,A$56,L$3:L$52,A$57)</f>
         <v>49</v>
@@ -23485,10 +23485,10 @@
       <c r="B58" s="2" t="s">
         <v>97</v>
       </c>
-      <c r="C58" s="49">
+      <c r="C58" s="47">
         <v>0</v>
       </c>
-      <c r="D58" s="49"/>
+      <c r="D58" s="47"/>
       <c r="K58" t="s">
         <v>98</v>
       </c>
@@ -23512,11 +23512,11 @@
       <c r="B59" s="2" t="s">
         <v>99</v>
       </c>
-      <c r="C59" s="49">
+      <c r="C59" s="47">
         <f>-SUMIFS(I$3:I$52,B$3:B$52,A$56,P$3:P$52,"xx",N$3:N$52,"x")</f>
         <v>-3155</v>
       </c>
-      <c r="D59" s="49"/>
+      <c r="D59" s="47"/>
       <c r="E59" s="2">
         <f>SUMIFS(Q$3:Q$52,B$3:B$52,A$56,P$3:P$52,"xx",N$3:N$52,"x")</f>
         <v>2</v>
@@ -23536,11 +23536,11 @@
       <c r="B60" s="4" t="s">
         <v>101</v>
       </c>
-      <c r="C60" s="47">
+      <c r="C60" s="45">
         <f>SUBTOTAL(9,C57:C59)</f>
         <v>25000</v>
       </c>
-      <c r="D60" s="47"/>
+      <c r="D60" s="45"/>
       <c r="E60">
         <f>E57</f>
         <v>49</v>
@@ -23560,8 +23560,8 @@
       <c r="B61" s="2" t="s">
         <v>104</v>
       </c>
-      <c r="C61" s="45"/>
-      <c r="D61" s="45"/>
+      <c r="C61" s="48"/>
+      <c r="D61" s="48"/>
       <c r="K61" s="2" t="s">
         <v>105</v>
       </c>
@@ -23577,8 +23577,8 @@
       <c r="B62" s="8" t="s">
         <v>107</v>
       </c>
-      <c r="C62" s="45"/>
-      <c r="D62" s="45"/>
+      <c r="C62" s="48"/>
+      <c r="D62" s="48"/>
       <c r="L62" s="9">
         <f>SUBTOTAL(9,L57:L61)</f>
         <v>7146</v>
@@ -23599,11 +23599,11 @@
       <c r="B64" s="1" t="s">
         <v>108</v>
       </c>
-      <c r="C64" s="46">
+      <c r="C64" s="49">
         <f>C60+C61+C62</f>
         <v>25000</v>
       </c>
-      <c r="D64" s="46"/>
+      <c r="D64" s="49"/>
       <c r="E64" s="1" t="s">
         <v>109</v>
       </c>
@@ -26212,10 +26212,10 @@
       <c r="A57" s="1" t="s">
         <v>16</v>
       </c>
-      <c r="C57" s="47" t="s">
+      <c r="C57" s="45" t="s">
         <v>89</v>
       </c>
-      <c r="D57" s="47"/>
+      <c r="D57" s="45"/>
       <c r="E57" s="4" t="s">
         <v>90</v>
       </c>
@@ -26243,11 +26243,11 @@
       <c r="B58" s="3" t="s">
         <v>93</v>
       </c>
-      <c r="C58" s="48">
+      <c r="C58" s="46">
         <f>SUMIFS(I$3:I$53,B$3:B$53,A$57,L$3:L$53,A$58)</f>
         <v>30480</v>
       </c>
-      <c r="D58" s="48"/>
+      <c r="D58" s="46"/>
       <c r="E58" s="3">
         <f>SUMIFS(Q$3:Q$53,B$3:B$53,A$57,L$3:L$53,A$58)</f>
         <v>51</v>
@@ -26282,10 +26282,10 @@
       <c r="B59" s="2" t="s">
         <v>97</v>
       </c>
-      <c r="C59" s="49">
+      <c r="C59" s="47">
         <v>0</v>
       </c>
-      <c r="D59" s="49"/>
+      <c r="D59" s="47"/>
       <c r="K59" t="s">
         <v>98</v>
       </c>
@@ -26309,11 +26309,11 @@
       <c r="B60" s="2" t="s">
         <v>99</v>
       </c>
-      <c r="C60" s="49">
+      <c r="C60" s="47">
         <f>-SUMIFS(I$3:I$53,B$3:B$53,A$57,P$3:P$53,"xx",N$3:N$53,"x")</f>
         <v>0</v>
       </c>
-      <c r="D60" s="49"/>
+      <c r="D60" s="47"/>
       <c r="E60" s="2">
         <f>SUMIFS(Q$3:Q$53,B$3:B$53,A$57,P$3:P$53,"xx",N$3:N$53,"x")</f>
         <v>0</v>
@@ -26333,11 +26333,11 @@
       <c r="B61" s="4" t="s">
         <v>101</v>
       </c>
-      <c r="C61" s="47">
+      <c r="C61" s="45">
         <f>SUBTOTAL(9,C58:C60)</f>
         <v>30480</v>
       </c>
-      <c r="D61" s="47"/>
+      <c r="D61" s="45"/>
       <c r="E61">
         <f>E58</f>
         <v>51</v>
@@ -26357,8 +26357,8 @@
       <c r="B62" s="2" t="s">
         <v>104</v>
       </c>
-      <c r="C62" s="45"/>
-      <c r="D62" s="45"/>
+      <c r="C62" s="48"/>
+      <c r="D62" s="48"/>
       <c r="K62" s="2" t="s">
         <v>105</v>
       </c>
@@ -26374,8 +26374,8 @@
       <c r="B63" s="8" t="s">
         <v>107</v>
       </c>
-      <c r="C63" s="45"/>
-      <c r="D63" s="45"/>
+      <c r="C63" s="48"/>
+      <c r="D63" s="48"/>
       <c r="L63" s="9">
         <f>SUBTOTAL(9,L58:L62)</f>
         <v>13705</v>
@@ -26396,11 +26396,11 @@
       <c r="B65" s="1" t="s">
         <v>108</v>
       </c>
-      <c r="C65" s="46">
+      <c r="C65" s="49">
         <f>C61+C62+C63</f>
         <v>30480</v>
       </c>
-      <c r="D65" s="46"/>
+      <c r="D65" s="49"/>
       <c r="E65" s="1" t="s">
         <v>109</v>
       </c>
@@ -28368,10 +28368,10 @@
       <c r="A42" s="1" t="s">
         <v>16</v>
       </c>
-      <c r="C42" s="47" t="s">
+      <c r="C42" s="45" t="s">
         <v>89</v>
       </c>
-      <c r="D42" s="47"/>
+      <c r="D42" s="45"/>
       <c r="E42" s="4" t="s">
         <v>90</v>
       </c>
@@ -28399,11 +28399,11 @@
       <c r="B43" s="3" t="s">
         <v>93</v>
       </c>
-      <c r="C43" s="48">
+      <c r="C43" s="46">
         <f>SUMIFS(I$3:I$38,B$3:B$38,A$42,L$3:L$38,A$43)</f>
         <v>16055</v>
       </c>
-      <c r="D43" s="48"/>
+      <c r="D43" s="46"/>
       <c r="E43" s="3">
         <f>SUMIFS(Q$3:Q$38,B$3:B$38,A$42,L$3:L$38,A$43)</f>
         <v>33</v>
@@ -28434,10 +28434,10 @@
       <c r="B44" s="2" t="s">
         <v>97</v>
       </c>
-      <c r="C44" s="49">
+      <c r="C44" s="47">
         <v>0</v>
       </c>
-      <c r="D44" s="49"/>
+      <c r="D44" s="47"/>
       <c r="K44" t="s">
         <v>98</v>
       </c>
@@ -28461,11 +28461,11 @@
       <c r="B45" s="2" t="s">
         <v>99</v>
       </c>
-      <c r="C45" s="49">
+      <c r="C45" s="47">
         <f>-SUMIFS(I$3:I$38,B$3:B$38,A$42,P$3:P$38,"xx",N$3:N$38,"x")</f>
         <v>-3310</v>
       </c>
-      <c r="D45" s="49"/>
+      <c r="D45" s="47"/>
       <c r="E45" s="2">
         <f>SUMIFS(Q$3:Q$38,B$3:B$38,A$42,P$3:P$38,"xx",N$3:N$38,"x")</f>
         <v>4</v>
@@ -28485,11 +28485,11 @@
       <c r="B46" s="4" t="s">
         <v>101</v>
       </c>
-      <c r="C46" s="47">
+      <c r="C46" s="45">
         <f>SUBTOTAL(9,C43:C45)</f>
         <v>12745</v>
       </c>
-      <c r="D46" s="47"/>
+      <c r="D46" s="45"/>
       <c r="E46">
         <f>E43</f>
         <v>33</v>
@@ -28509,8 +28509,8 @@
       <c r="B47" s="2" t="s">
         <v>104</v>
       </c>
-      <c r="C47" s="45"/>
-      <c r="D47" s="45"/>
+      <c r="C47" s="48"/>
+      <c r="D47" s="48"/>
       <c r="K47" s="2" t="s">
         <v>105</v>
       </c>
@@ -28532,8 +28532,8 @@
       <c r="B48" s="8" t="s">
         <v>107</v>
       </c>
-      <c r="C48" s="45"/>
-      <c r="D48" s="45"/>
+      <c r="C48" s="48"/>
+      <c r="D48" s="48"/>
       <c r="L48" s="9">
         <f>SUBTOTAL(9,L43:L47)</f>
         <v>840</v>
@@ -28554,11 +28554,11 @@
       <c r="B50" s="1" t="s">
         <v>108</v>
       </c>
-      <c r="C50" s="46">
+      <c r="C50" s="49">
         <f>C46+C47+C48</f>
         <v>12745</v>
       </c>
-      <c r="D50" s="46"/>
+      <c r="D50" s="49"/>
       <c r="E50" s="1" t="s">
         <v>109</v>
       </c>
@@ -33133,10 +33133,10 @@
       <c r="A101" s="1" t="s">
         <v>16</v>
       </c>
-      <c r="C101" s="47" t="s">
+      <c r="C101" s="45" t="s">
         <v>89</v>
       </c>
-      <c r="D101" s="47"/>
+      <c r="D101" s="45"/>
       <c r="E101" s="4" t="s">
         <v>90</v>
       </c>
@@ -33164,11 +33164,11 @@
       <c r="B102" s="3" t="s">
         <v>93</v>
       </c>
-      <c r="C102" s="48">
+      <c r="C102" s="46">
         <f>SUMIFS(I$3:I$97,B$3:B$97,A$101,L$3:L$97,A$102)</f>
         <v>56435</v>
       </c>
-      <c r="D102" s="48"/>
+      <c r="D102" s="46"/>
       <c r="E102" s="3">
         <f>SUMIFS(Q$3:Q$97,B$3:B$97,A$101,L$3:L$97,A$102)</f>
         <v>95</v>
@@ -33203,10 +33203,10 @@
       <c r="B103" s="2" t="s">
         <v>97</v>
       </c>
-      <c r="C103" s="49">
+      <c r="C103" s="47">
         <v>0</v>
       </c>
-      <c r="D103" s="49"/>
+      <c r="D103" s="47"/>
       <c r="K103" t="s">
         <v>98</v>
       </c>
@@ -33230,11 +33230,11 @@
       <c r="B104" s="2" t="s">
         <v>99</v>
       </c>
-      <c r="C104" s="49">
+      <c r="C104" s="47">
         <f>-SUMIFS(I$3:I$97,B$3:B$97,A$101,P$3:P$97,"xx",N$3:N$97,"x")</f>
         <v>-2780</v>
       </c>
-      <c r="D104" s="49"/>
+      <c r="D104" s="47"/>
       <c r="E104" s="2">
         <f>SUMIFS(Q$3:Q$97,B$3:B$97,A$101,P$3:P$97,"xx",N$3:N$97,"x")</f>
         <v>3</v>
@@ -33254,11 +33254,11 @@
       <c r="B105" s="4" t="s">
         <v>101</v>
       </c>
-      <c r="C105" s="47">
+      <c r="C105" s="45">
         <f>SUBTOTAL(9,C102:C104)</f>
         <v>53655</v>
       </c>
-      <c r="D105" s="47"/>
+      <c r="D105" s="45"/>
       <c r="E105">
         <f>E102</f>
         <v>95</v>
@@ -33278,8 +33278,8 @@
       <c r="B106" s="2" t="s">
         <v>104</v>
       </c>
-      <c r="C106" s="45"/>
-      <c r="D106" s="45"/>
+      <c r="C106" s="48"/>
+      <c r="D106" s="48"/>
       <c r="K106" s="2" t="s">
         <v>105</v>
       </c>
@@ -33295,8 +33295,8 @@
       <c r="B107" s="8" t="s">
         <v>107</v>
       </c>
-      <c r="C107" s="45"/>
-      <c r="D107" s="45"/>
+      <c r="C107" s="48"/>
+      <c r="D107" s="48"/>
       <c r="L107" s="9">
         <f>SUBTOTAL(9,L102:L106)</f>
         <v>8245</v>
@@ -33317,11 +33317,11 @@
       <c r="B109" s="1" t="s">
         <v>108</v>
       </c>
-      <c r="C109" s="46">
+      <c r="C109" s="49">
         <f>C105+C106+C107</f>
         <v>53655</v>
       </c>
-      <c r="D109" s="46"/>
+      <c r="D109" s="49"/>
       <c r="E109" s="1" t="s">
         <v>109</v>
       </c>
@@ -36450,10 +36450,10 @@
       <c r="A68" s="1" t="s">
         <v>16</v>
       </c>
-      <c r="C68" s="47" t="s">
+      <c r="C68" s="45" t="s">
         <v>89</v>
       </c>
-      <c r="D68" s="47"/>
+      <c r="D68" s="45"/>
       <c r="E68" s="4" t="s">
         <v>90</v>
       </c>
@@ -36481,11 +36481,11 @@
       <c r="B69" s="3" t="s">
         <v>93</v>
       </c>
-      <c r="C69" s="48">
+      <c r="C69" s="46">
         <f>SUMIFS(I$3:I$64,B$3:B$64,A$68,L$3:L$64,A$69)</f>
         <v>47670</v>
       </c>
-      <c r="D69" s="48"/>
+      <c r="D69" s="46"/>
       <c r="E69" s="3">
         <f>SUMIFS(Q$3:Q$64,B$3:B$64,A$68,L$3:L$64,A$69)</f>
         <v>58</v>
@@ -36520,10 +36520,10 @@
       <c r="B70" s="2" t="s">
         <v>97</v>
       </c>
-      <c r="C70" s="49">
+      <c r="C70" s="47">
         <v>0</v>
       </c>
-      <c r="D70" s="49"/>
+      <c r="D70" s="47"/>
       <c r="K70" t="s">
         <v>98</v>
       </c>
@@ -36547,11 +36547,11 @@
       <c r="B71" s="2" t="s">
         <v>99</v>
       </c>
-      <c r="C71" s="49">
+      <c r="C71" s="47">
         <f>-SUMIFS(I$3:I$64,B$3:B$64,A$68,P$3:P$64,"xx",N$3:N$64,"x")</f>
         <v>-5360</v>
       </c>
-      <c r="D71" s="49"/>
+      <c r="D71" s="47"/>
       <c r="E71" s="2">
         <f>SUMIFS(Q$3:Q$64,B$3:B$64,A$68,P$3:P$64,"xx",N$3:N$64,"x")</f>
         <v>5</v>
@@ -36571,11 +36571,11 @@
       <c r="B72" s="4" t="s">
         <v>101</v>
       </c>
-      <c r="C72" s="47">
+      <c r="C72" s="45">
         <f>SUBTOTAL(9,C69:C71)</f>
         <v>42310</v>
       </c>
-      <c r="D72" s="47"/>
+      <c r="D72" s="45"/>
       <c r="E72">
         <f>E69</f>
         <v>58</v>
@@ -36595,8 +36595,8 @@
       <c r="B73" s="2" t="s">
         <v>104</v>
       </c>
-      <c r="C73" s="45"/>
-      <c r="D73" s="45"/>
+      <c r="C73" s="48"/>
+      <c r="D73" s="48"/>
       <c r="K73" s="2" t="s">
         <v>105</v>
       </c>
@@ -36612,8 +36612,8 @@
       <c r="B74" s="8" t="s">
         <v>107</v>
       </c>
-      <c r="C74" s="45"/>
-      <c r="D74" s="45"/>
+      <c r="C74" s="48"/>
+      <c r="D74" s="48"/>
       <c r="L74" s="9">
         <f>SUBTOTAL(9,L69:L73)</f>
         <v>6850</v>
@@ -36634,11 +36634,11 @@
       <c r="B76" s="1" t="s">
         <v>108</v>
       </c>
-      <c r="C76" s="46">
+      <c r="C76" s="49">
         <f>C72+C73+C74</f>
         <v>42310</v>
       </c>
-      <c r="D76" s="46"/>
+      <c r="D76" s="49"/>
       <c r="E76" s="1" t="s">
         <v>109</v>
       </c>
@@ -39391,10 +39391,10 @@
       <c r="A60" s="1" t="s">
         <v>16</v>
       </c>
-      <c r="C60" s="47" t="s">
+      <c r="C60" s="45" t="s">
         <v>89</v>
       </c>
-      <c r="D60" s="47"/>
+      <c r="D60" s="45"/>
       <c r="E60" s="4" t="s">
         <v>90</v>
       </c>
@@ -39422,11 +39422,11 @@
       <c r="B61" s="3" t="s">
         <v>93</v>
       </c>
-      <c r="C61" s="48">
+      <c r="C61" s="46">
         <f>SUMIFS(I$3:I$56,B$3:B$56,A$60,L$3:L$56,A$61)</f>
         <v>50515</v>
       </c>
-      <c r="D61" s="48"/>
+      <c r="D61" s="46"/>
       <c r="E61" s="3">
         <f>SUMIFS(Q$3:Q$56,B$3:B$56,A$60,L$3:L$56,A$61)</f>
         <v>54</v>
@@ -39461,10 +39461,10 @@
       <c r="B62" s="2" t="s">
         <v>97</v>
       </c>
-      <c r="C62" s="49">
+      <c r="C62" s="47">
         <v>0</v>
       </c>
-      <c r="D62" s="49"/>
+      <c r="D62" s="47"/>
       <c r="K62" t="s">
         <v>98</v>
       </c>
@@ -39488,11 +39488,11 @@
       <c r="B63" s="2" t="s">
         <v>99</v>
       </c>
-      <c r="C63" s="49">
+      <c r="C63" s="47">
         <f>-SUMIFS(I$3:I$56,B$3:B$56,A$60,P$3:P$56,"xx",N$3:N$56,"x")</f>
         <v>0</v>
       </c>
-      <c r="D63" s="49"/>
+      <c r="D63" s="47"/>
       <c r="E63" s="2">
         <f>SUMIFS(Q$3:Q$56,B$3:B$56,A$60,P$3:P$56,"xx",N$3:N$56,"x")</f>
         <v>0</v>
@@ -39520,11 +39520,11 @@
       <c r="B64" s="4" t="s">
         <v>101</v>
       </c>
-      <c r="C64" s="47">
+      <c r="C64" s="45">
         <f>SUBTOTAL(9,C61:C63)</f>
         <v>50515</v>
       </c>
-      <c r="D64" s="47"/>
+      <c r="D64" s="45"/>
       <c r="E64">
         <f>E61</f>
         <v>54</v>
@@ -39544,8 +39544,8 @@
       <c r="B65" s="2" t="s">
         <v>104</v>
       </c>
-      <c r="C65" s="45"/>
-      <c r="D65" s="45"/>
+      <c r="C65" s="48"/>
+      <c r="D65" s="48"/>
       <c r="I65">
         <v>33514</v>
       </c>
@@ -39564,8 +39564,8 @@
       <c r="B66" s="8" t="s">
         <v>107</v>
       </c>
-      <c r="C66" s="45"/>
-      <c r="D66" s="45"/>
+      <c r="C66" s="48"/>
+      <c r="D66" s="48"/>
       <c r="I66">
         <v>33379</v>
       </c>
@@ -39598,11 +39598,11 @@
       <c r="B68" s="1" t="s">
         <v>108</v>
       </c>
-      <c r="C68" s="46">
+      <c r="C68" s="49">
         <f>C64+C65+C66</f>
         <v>50515</v>
       </c>
-      <c r="D68" s="46"/>
+      <c r="D68" s="49"/>
       <c r="E68" s="1" t="s">
         <v>109</v>
       </c>
@@ -40811,10 +40811,10 @@
       <c r="A28" s="1" t="s">
         <v>16</v>
       </c>
-      <c r="C28" s="47" t="s">
+      <c r="C28" s="45" t="s">
         <v>89</v>
       </c>
-      <c r="D28" s="47"/>
+      <c r="D28" s="45"/>
       <c r="E28" s="4" t="s">
         <v>90</v>
       </c>
@@ -40842,11 +40842,11 @@
       <c r="B29" s="3" t="s">
         <v>93</v>
       </c>
-      <c r="C29" s="48">
+      <c r="C29" s="46">
         <f>SUMIFS(I$3:I$24,B$3:B$24,A$28,L$3:L$24,A$29)</f>
         <v>7205</v>
       </c>
-      <c r="D29" s="48"/>
+      <c r="D29" s="46"/>
       <c r="E29" s="3">
         <f>SUMIFS(Q$3:Q$24,B$3:B$24,A$28,L$3:L$24,A$29)</f>
         <v>22</v>
@@ -40881,10 +40881,10 @@
       <c r="B30" s="2" t="s">
         <v>97</v>
       </c>
-      <c r="C30" s="49">
+      <c r="C30" s="47">
         <v>0</v>
       </c>
-      <c r="D30" s="49"/>
+      <c r="D30" s="47"/>
       <c r="K30" t="s">
         <v>98</v>
       </c>
@@ -40908,11 +40908,11 @@
       <c r="B31" s="2" t="s">
         <v>99</v>
       </c>
-      <c r="C31" s="49">
+      <c r="C31" s="47">
         <f>-SUMIFS(I$3:I$24,B$3:B$24,A$28,P$3:P$24,"xx",N$3:N$24,"x")</f>
         <v>0</v>
       </c>
-      <c r="D31" s="49"/>
+      <c r="D31" s="47"/>
       <c r="E31" s="2">
         <f>SUMIFS(Q$3:Q$24,B$3:B$24,A$28,P$3:P$24,"xx",N$3:N$24,"x")</f>
         <v>0</v>
@@ -40940,11 +40940,11 @@
       <c r="B32" s="4" t="s">
         <v>101</v>
       </c>
-      <c r="C32" s="47">
+      <c r="C32" s="45">
         <f>SUBTOTAL(9,C29:C31)</f>
         <v>7205</v>
       </c>
-      <c r="D32" s="47"/>
+      <c r="D32" s="45"/>
       <c r="E32">
         <f>E29</f>
         <v>22</v>
@@ -40964,8 +40964,8 @@
       <c r="B33" s="2" t="s">
         <v>104</v>
       </c>
-      <c r="C33" s="45"/>
-      <c r="D33" s="45"/>
+      <c r="C33" s="48"/>
+      <c r="D33" s="48"/>
       <c r="K33" s="2" t="s">
         <v>105</v>
       </c>
@@ -40981,8 +40981,8 @@
       <c r="B34" s="8" t="s">
         <v>107</v>
       </c>
-      <c r="C34" s="45"/>
-      <c r="D34" s="45"/>
+      <c r="C34" s="48"/>
+      <c r="D34" s="48"/>
       <c r="L34" s="9">
         <f>SUBTOTAL(9,L29:L33)</f>
         <v>2296</v>
@@ -40996,11 +40996,11 @@
       <c r="B36" s="1" t="s">
         <v>108</v>
       </c>
-      <c r="C36" s="46">
+      <c r="C36" s="49">
         <f>C32+C33+C34</f>
         <v>7205</v>
       </c>
-      <c r="D36" s="46"/>
+      <c r="D36" s="49"/>
       <c r="E36" s="1" t="s">
         <v>109</v>
       </c>
@@ -43889,10 +43889,10 @@
       <c r="A65" s="1" t="s">
         <v>16</v>
       </c>
-      <c r="C65" s="47" t="s">
+      <c r="C65" s="45" t="s">
         <v>89</v>
       </c>
-      <c r="D65" s="47"/>
+      <c r="D65" s="45"/>
       <c r="E65" s="4" t="s">
         <v>90</v>
       </c>
@@ -43920,11 +43920,11 @@
       <c r="B66" s="3" t="s">
         <v>93</v>
       </c>
-      <c r="C66" s="48">
+      <c r="C66" s="46">
         <f>SUMIFS(I$3:I$61,B$3:B$61,A$65,L$3:L$61,A$66)</f>
         <v>34740</v>
       </c>
-      <c r="D66" s="48"/>
+      <c r="D66" s="46"/>
       <c r="E66" s="3">
         <f>SUMIFS(Q$3:Q$61,B$3:B$61,A$65,L$3:L$61,A$66)</f>
         <v>59</v>
@@ -43959,10 +43959,10 @@
       <c r="B67" s="2" t="s">
         <v>97</v>
       </c>
-      <c r="C67" s="49">
+      <c r="C67" s="47">
         <v>0</v>
       </c>
-      <c r="D67" s="49"/>
+      <c r="D67" s="47"/>
       <c r="K67" t="s">
         <v>98</v>
       </c>
@@ -43986,11 +43986,11 @@
       <c r="B68" s="2" t="s">
         <v>99</v>
       </c>
-      <c r="C68" s="49">
+      <c r="C68" s="47">
         <f>-SUMIFS(I$3:I$61,B$3:B$61,A$65,P$3:P$61,"xx",N$3:N$61,"x")</f>
         <v>0</v>
       </c>
-      <c r="D68" s="49"/>
+      <c r="D68" s="47"/>
       <c r="E68" s="2">
         <f>SUMIFS(Q$3:Q$61,B$3:B$61,A$65,P$3:P$61,"xx",N$3:N$61,"x")</f>
         <v>0</v>
@@ -44010,11 +44010,11 @@
       <c r="B69" s="4" t="s">
         <v>101</v>
       </c>
-      <c r="C69" s="47">
+      <c r="C69" s="45">
         <f>SUBTOTAL(9,C66:C68)</f>
         <v>34740</v>
       </c>
-      <c r="D69" s="47"/>
+      <c r="D69" s="45"/>
       <c r="E69">
         <f>E66</f>
         <v>59</v>
@@ -44034,8 +44034,8 @@
       <c r="B70" s="2" t="s">
         <v>104</v>
       </c>
-      <c r="C70" s="45"/>
-      <c r="D70" s="45"/>
+      <c r="C70" s="48"/>
+      <c r="D70" s="48"/>
       <c r="K70" s="2" t="s">
         <v>105</v>
       </c>
@@ -44051,8 +44051,8 @@
       <c r="B71" s="8" t="s">
         <v>107</v>
       </c>
-      <c r="C71" s="45"/>
-      <c r="D71" s="45"/>
+      <c r="C71" s="48"/>
+      <c r="D71" s="48"/>
       <c r="L71" s="9">
         <f>SUBTOTAL(9,L66:L70)</f>
         <v>26296</v>
@@ -44073,11 +44073,11 @@
       <c r="B73" s="1" t="s">
         <v>108</v>
       </c>
-      <c r="C73" s="46">
+      <c r="C73" s="49">
         <f>C69+C70+C71</f>
         <v>34740</v>
       </c>
-      <c r="D73" s="46"/>
+      <c r="D73" s="49"/>
       <c r="E73" s="1" t="s">
         <v>109</v>
       </c>
@@ -47264,10 +47264,10 @@
       <c r="A70" s="1" t="s">
         <v>16</v>
       </c>
-      <c r="C70" s="47" t="s">
+      <c r="C70" s="45" t="s">
         <v>89</v>
       </c>
-      <c r="D70" s="47"/>
+      <c r="D70" s="45"/>
       <c r="E70" s="4" t="s">
         <v>90</v>
       </c>
@@ -47295,11 +47295,11 @@
       <c r="B71" s="3" t="s">
         <v>93</v>
       </c>
-      <c r="C71" s="48">
+      <c r="C71" s="46">
         <f>SUMIFS(I$3:I$66,B$3:B$66,A$70,L$3:L$66,A$71)</f>
         <v>50540</v>
       </c>
-      <c r="D71" s="48"/>
+      <c r="D71" s="46"/>
       <c r="E71" s="3">
         <f>SUMIFS(Q$3:Q$66,B$3:B$66,A$70,L$3:L$66,A$71)</f>
         <v>64</v>
@@ -47333,10 +47333,10 @@
       <c r="B72" s="2" t="s">
         <v>97</v>
       </c>
-      <c r="C72" s="49">
+      <c r="C72" s="47">
         <v>0</v>
       </c>
-      <c r="D72" s="49"/>
+      <c r="D72" s="47"/>
       <c r="K72" t="s">
         <v>98</v>
       </c>
@@ -47359,11 +47359,11 @@
       <c r="B73" s="2" t="s">
         <v>99</v>
       </c>
-      <c r="C73" s="49">
+      <c r="C73" s="47">
         <f>-SUMIFS(I$3:I$66,B$3:B$66,A$70,P$3:P$66,"xx",N$3:N$66,"x")</f>
         <v>0</v>
       </c>
-      <c r="D73" s="49"/>
+      <c r="D73" s="47"/>
       <c r="E73" s="2">
         <f>SUMIFS(Q$3:Q$66,B$3:B$66,A$70,P$3:P$66,"xx",N$3:N$66,"x")</f>
         <v>0</v>
@@ -47386,11 +47386,11 @@
       <c r="B74" s="4" t="s">
         <v>101</v>
       </c>
-      <c r="C74" s="47">
+      <c r="C74" s="45">
         <f>SUBTOTAL(9,C71:C73)</f>
         <v>50540</v>
       </c>
-      <c r="D74" s="47"/>
+      <c r="D74" s="45"/>
       <c r="E74">
         <f>E71</f>
         <v>64</v>
@@ -47413,8 +47413,8 @@
       <c r="B75" s="2" t="s">
         <v>104</v>
       </c>
-      <c r="C75" s="45"/>
-      <c r="D75" s="45"/>
+      <c r="C75" s="48"/>
+      <c r="D75" s="48"/>
       <c r="G75" s="10" t="s">
         <v>2580</v>
       </c>
@@ -47437,8 +47437,8 @@
       <c r="B76" s="8" t="s">
         <v>107</v>
       </c>
-      <c r="C76" s="45"/>
-      <c r="D76" s="45"/>
+      <c r="C76" s="48"/>
+      <c r="D76" s="48"/>
       <c r="L76" s="9">
         <f>SUBTOTAL(9,L71:L75)</f>
         <v>24613</v>
@@ -47452,11 +47452,11 @@
       <c r="B78" s="1" t="s">
         <v>108</v>
       </c>
-      <c r="C78" s="46">
+      <c r="C78" s="49">
         <f>C74+C75+C76</f>
         <v>50540</v>
       </c>
-      <c r="D78" s="46"/>
+      <c r="D78" s="49"/>
       <c r="E78" s="1" t="s">
         <v>109</v>
       </c>
@@ -50022,10 +50022,10 @@
       <c r="A57" s="1" t="s">
         <v>16</v>
       </c>
-      <c r="C57" s="47" t="s">
+      <c r="C57" s="45" t="s">
         <v>89</v>
       </c>
-      <c r="D57" s="47"/>
+      <c r="D57" s="45"/>
       <c r="E57" s="4" t="s">
         <v>90</v>
       </c>
@@ -50053,11 +50053,11 @@
       <c r="B58" s="3" t="s">
         <v>93</v>
       </c>
-      <c r="C58" s="48">
+      <c r="C58" s="46">
         <f>SUMIFS(I$3:I$53,B$3:B$53,A$57,L$3:L$53,A$58)</f>
         <v>33955</v>
       </c>
-      <c r="D58" s="48"/>
+      <c r="D58" s="46"/>
       <c r="E58" s="3">
         <f>SUMIFS(Q$3:Q$53,B$3:B$53,A$57,L$3:L$53,A$58)</f>
         <v>50</v>
@@ -50092,10 +50092,10 @@
       <c r="B59" s="2" t="s">
         <v>97</v>
       </c>
-      <c r="C59" s="49">
+      <c r="C59" s="47">
         <v>0</v>
       </c>
-      <c r="D59" s="49"/>
+      <c r="D59" s="47"/>
       <c r="K59" t="s">
         <v>98</v>
       </c>
@@ -50119,11 +50119,11 @@
       <c r="B60" s="2" t="s">
         <v>99</v>
       </c>
-      <c r="C60" s="49">
+      <c r="C60" s="47">
         <f>-SUMIFS(I$3:I$53,B$3:B$53,A$57,P$3:P$53,"xx",N$3:N$53,"x")</f>
         <v>-765</v>
       </c>
-      <c r="D60" s="49"/>
+      <c r="D60" s="47"/>
       <c r="E60" s="2">
         <f>SUMIFS(Q$3:Q$53,B$3:B$53,A$57,P$3:P$53,"xx",N$3:N$53,"x")</f>
         <v>1</v>
@@ -50143,11 +50143,11 @@
       <c r="B61" s="4" t="s">
         <v>101</v>
       </c>
-      <c r="C61" s="47">
+      <c r="C61" s="45">
         <f>SUBTOTAL(9,C58:C60)</f>
         <v>33190</v>
       </c>
-      <c r="D61" s="47"/>
+      <c r="D61" s="45"/>
       <c r="E61">
         <f>E58</f>
         <v>50</v>
@@ -50169,8 +50169,8 @@
       <c r="B62" s="2" t="s">
         <v>104</v>
       </c>
-      <c r="C62" s="45"/>
-      <c r="D62" s="45"/>
+      <c r="C62" s="48"/>
+      <c r="D62" s="48"/>
       <c r="K62" s="2" t="s">
         <v>105</v>
       </c>
@@ -50186,8 +50186,8 @@
       <c r="B63" s="8" t="s">
         <v>107</v>
       </c>
-      <c r="C63" s="45"/>
-      <c r="D63" s="45"/>
+      <c r="C63" s="48"/>
+      <c r="D63" s="48"/>
       <c r="L63" s="9">
         <f>SUBTOTAL(9,L58:L62)</f>
         <v>19225</v>
@@ -50201,11 +50201,11 @@
       <c r="B65" s="1" t="s">
         <v>108</v>
       </c>
-      <c r="C65" s="46">
+      <c r="C65" s="49">
         <f>C61+C62+C63</f>
         <v>33190</v>
       </c>
-      <c r="D65" s="46"/>
+      <c r="D65" s="49"/>
       <c r="E65" s="1" t="s">
         <v>109</v>
       </c>
@@ -56027,10 +56027,10 @@
       <c r="A129" s="1" t="s">
         <v>16</v>
       </c>
-      <c r="C129" s="47" t="s">
+      <c r="C129" s="45" t="s">
         <v>89</v>
       </c>
-      <c r="D129" s="47"/>
+      <c r="D129" s="45"/>
       <c r="E129" s="4" t="s">
         <v>90</v>
       </c>
@@ -56061,11 +56061,11 @@
       <c r="B130" s="3" t="s">
         <v>93</v>
       </c>
-      <c r="C130" s="48">
+      <c r="C130" s="46">
         <f>SUMIFS(I$3:I$125,B$3:B$125,A$129,L$3:L$125,A$130)</f>
         <v>88515</v>
       </c>
-      <c r="D130" s="48"/>
+      <c r="D130" s="46"/>
       <c r="E130" s="3">
         <f>SUMIFS(Q$3:Q$125,B$3:B$125,A$129,L$3:L$125,A$130)</f>
         <v>120</v>
@@ -56100,10 +56100,10 @@
       <c r="B131" s="2" t="s">
         <v>97</v>
       </c>
-      <c r="C131" s="49">
+      <c r="C131" s="47">
         <v>0</v>
       </c>
-      <c r="D131" s="49"/>
+      <c r="D131" s="47"/>
       <c r="K131" t="s">
         <v>98</v>
       </c>
@@ -56127,11 +56127,11 @@
       <c r="B132" s="2" t="s">
         <v>99</v>
       </c>
-      <c r="C132" s="49">
+      <c r="C132" s="47">
         <f>-SUMIFS(I$3:I$125,B$3:B$125,A$129,P$3:P$125,"xx",N$3:N$125,"x")</f>
         <v>-5870</v>
       </c>
-      <c r="D132" s="49"/>
+      <c r="D132" s="47"/>
       <c r="E132" s="2">
         <f>SUMIFS(Q$3:Q$125,B$3:B$125,A$129,P$3:P$125,"xx",N$3:N$125,"x")</f>
         <v>7</v>
@@ -56151,11 +56151,11 @@
       <c r="B133" s="4" t="s">
         <v>101</v>
       </c>
-      <c r="C133" s="47">
+      <c r="C133" s="45">
         <f>SUBTOTAL(9,C130:C132)</f>
         <v>82645</v>
       </c>
-      <c r="D133" s="47"/>
+      <c r="D133" s="45"/>
       <c r="E133">
         <f>E130</f>
         <v>120</v>
@@ -56175,8 +56175,8 @@
       <c r="B134" s="2" t="s">
         <v>104</v>
       </c>
-      <c r="C134" s="45"/>
-      <c r="D134" s="45"/>
+      <c r="C134" s="48"/>
+      <c r="D134" s="48"/>
       <c r="K134" s="2" t="s">
         <v>105</v>
       </c>
@@ -56192,10 +56192,10 @@
       <c r="B135" s="8" t="s">
         <v>107</v>
       </c>
-      <c r="C135" s="45">
+      <c r="C135" s="48">
         <v>790</v>
       </c>
-      <c r="D135" s="45"/>
+      <c r="D135" s="48"/>
       <c r="L135" s="9">
         <f>SUBTOTAL(9,L130:L134)</f>
         <v>24905</v>
@@ -56222,11 +56222,11 @@
       <c r="B137" s="1" t="s">
         <v>108</v>
       </c>
-      <c r="C137" s="46">
+      <c r="C137" s="49">
         <f>C133+C134+C135</f>
         <v>83435</v>
       </c>
-      <c r="D137" s="46"/>
+      <c r="D137" s="49"/>
       <c r="E137" s="1" t="s">
         <v>109</v>
       </c>
@@ -58667,10 +58667,10 @@
       <c r="A53" s="1" t="s">
         <v>16</v>
       </c>
-      <c r="C53" s="47" t="s">
+      <c r="C53" s="45" t="s">
         <v>89</v>
       </c>
-      <c r="D53" s="47"/>
+      <c r="D53" s="45"/>
       <c r="E53" s="4" t="s">
         <v>90</v>
       </c>
@@ -58698,11 +58698,11 @@
       <c r="B54" s="3" t="s">
         <v>93</v>
       </c>
-      <c r="C54" s="48">
+      <c r="C54" s="46">
         <f>SUMIFS(I$3:I$49,B$3:B$49,A$53,L$3:L$49,A$54)</f>
         <v>38441</v>
       </c>
-      <c r="D54" s="48"/>
+      <c r="D54" s="46"/>
       <c r="E54" s="3">
         <f>SUMIFS(Q$3:Q$49,B$3:B$49,A$53,L$3:L$49,A$54)</f>
         <v>45</v>
@@ -58737,10 +58737,10 @@
       <c r="B55" s="2" t="s">
         <v>97</v>
       </c>
-      <c r="C55" s="49" t="s">
+      <c r="C55" s="47" t="s">
         <v>3251</v>
       </c>
-      <c r="D55" s="49"/>
+      <c r="D55" s="47"/>
       <c r="K55" t="s">
         <v>98</v>
       </c>
@@ -58764,11 +58764,11 @@
       <c r="B56" s="2" t="s">
         <v>99</v>
       </c>
-      <c r="C56" s="49">
+      <c r="C56" s="47">
         <f>-SUMIFS(I$3:I$49,B$3:B$49,A$53,P$3:P$49,"xx",N$3:N$49,"x")</f>
         <v>-750</v>
       </c>
-      <c r="D56" s="49"/>
+      <c r="D56" s="47"/>
       <c r="E56" s="2">
         <f>SUMIFS(Q$3:Q$49,B$3:B$49,A$53,P$3:P$49,"xx",N$3:N$49,"x")</f>
         <v>1</v>
@@ -58796,11 +58796,11 @@
       <c r="B57" s="4" t="s">
         <v>101</v>
       </c>
-      <c r="C57" s="47">
+      <c r="C57" s="45">
         <f>SUBTOTAL(9,C54:C56)</f>
         <v>37691</v>
       </c>
-      <c r="D57" s="47"/>
+      <c r="D57" s="45"/>
       <c r="E57">
         <f>E54</f>
         <v>45</v>
@@ -58820,8 +58820,8 @@
       <c r="B58" s="2" t="s">
         <v>104</v>
       </c>
-      <c r="C58" s="45"/>
-      <c r="D58" s="45"/>
+      <c r="C58" s="48"/>
+      <c r="D58" s="48"/>
       <c r="K58" s="2" t="s">
         <v>105</v>
       </c>
@@ -58843,8 +58843,8 @@
       <c r="B59" s="8" t="s">
         <v>107</v>
       </c>
-      <c r="C59" s="45"/>
-      <c r="D59" s="45"/>
+      <c r="C59" s="48"/>
+      <c r="D59" s="48"/>
       <c r="L59" s="9">
         <f>SUBTOTAL(9,L54:L58)</f>
         <v>18525</v>
@@ -58865,11 +58865,11 @@
       <c r="B61" s="1" t="s">
         <v>108</v>
       </c>
-      <c r="C61" s="46">
+      <c r="C61" s="49">
         <f>C57+C58+C59</f>
         <v>37691</v>
       </c>
-      <c r="D61" s="46"/>
+      <c r="D61" s="49"/>
       <c r="E61" s="1" t="s">
         <v>109</v>
       </c>
@@ -58900,10 +58900,10 @@
       <c r="A63" s="1" t="s">
         <v>16</v>
       </c>
-      <c r="C63" s="47" t="s">
+      <c r="C63" s="45" t="s">
         <v>89</v>
       </c>
-      <c r="D63" s="47"/>
+      <c r="D63" s="45"/>
       <c r="E63" s="4" t="s">
         <v>90</v>
       </c>
@@ -58926,11 +58926,11 @@
       <c r="B64" s="3" t="s">
         <v>93</v>
       </c>
-      <c r="C64" s="48">
+      <c r="C64" s="46">
         <f>SUMIFS(I$3:I$49,B$3:B$49,A$63,L$3:L$49,A$64)</f>
         <v>450</v>
       </c>
-      <c r="D64" s="48"/>
+      <c r="D64" s="46"/>
       <c r="E64" s="3">
         <f>SUMIFS(Q$3:Q$49,B$3:B$49,A$63,L$3:L$49,A$64)</f>
         <v>1</v>
@@ -58946,10 +58946,10 @@
       <c r="B65" s="2" t="s">
         <v>97</v>
       </c>
-      <c r="C65" s="49">
+      <c r="C65" s="47">
         <v>0</v>
       </c>
-      <c r="D65" s="49"/>
+      <c r="D65" s="47"/>
       <c r="K65" s="2" t="s">
         <v>102</v>
       </c>
@@ -58958,8 +58958,8 @@
       <c r="B66" s="2" t="s">
         <v>99</v>
       </c>
-      <c r="C66" s="49"/>
-      <c r="D66" s="49"/>
+      <c r="C66" s="47"/>
+      <c r="D66" s="47"/>
       <c r="E66" s="2"/>
       <c r="K66" s="2" t="s">
         <v>105</v>
@@ -58969,11 +58969,11 @@
       <c r="B67" s="4" t="s">
         <v>101</v>
       </c>
-      <c r="C67" s="47">
+      <c r="C67" s="45">
         <f>SUBTOTAL(9,C64:C66)</f>
         <v>450</v>
       </c>
-      <c r="D67" s="47"/>
+      <c r="D67" s="45"/>
       <c r="E67">
         <f>E64</f>
         <v>1</v>
@@ -58982,7 +58982,7 @@
         <v>3026</v>
       </c>
       <c r="L67" s="29">
-        <v>-475</v>
+        <v>-480</v>
       </c>
       <c r="M67" s="29" t="s">
         <v>451</v>
@@ -58992,8 +58992,8 @@
       <c r="B68" s="2" t="s">
         <v>104</v>
       </c>
-      <c r="C68" s="45"/>
-      <c r="D68" s="45"/>
+      <c r="C68" s="48"/>
+      <c r="D68" s="48"/>
       <c r="L68" s="9">
         <f>SUBTOTAL(9,L62:L66)</f>
         <v>10016</v>
@@ -59007,8 +59007,8 @@
       <c r="B69" s="8" t="s">
         <v>107</v>
       </c>
-      <c r="C69" s="45"/>
-      <c r="D69" s="45"/>
+      <c r="C69" s="48"/>
+      <c r="D69" s="48"/>
     </row>
     <row r="70" spans="2:13" x14ac:dyDescent="0.25">
       <c r="K70" s="7" t="s">
@@ -59025,11 +59025,11 @@
       <c r="B71" s="1" t="s">
         <v>108</v>
       </c>
-      <c r="C71" s="46">
+      <c r="C71" s="49">
         <f>C67+C68+C69</f>
         <v>450</v>
       </c>
-      <c r="D71" s="46"/>
+      <c r="D71" s="49"/>
       <c r="E71" s="1" t="s">
         <v>109</v>
       </c>
@@ -59152,22 +59152,22 @@
     </sortState>
   </autoFilter>
   <mergeCells count="16">
-    <mergeCell ref="C53:D53"/>
-    <mergeCell ref="C54:D54"/>
-    <mergeCell ref="C55:D55"/>
-    <mergeCell ref="C56:D56"/>
-    <mergeCell ref="C57:D57"/>
-    <mergeCell ref="C58:D58"/>
-    <mergeCell ref="C59:D59"/>
-    <mergeCell ref="C61:D61"/>
-    <mergeCell ref="C63:D63"/>
-    <mergeCell ref="C64:D64"/>
     <mergeCell ref="C71:D71"/>
     <mergeCell ref="C65:D65"/>
     <mergeCell ref="C66:D66"/>
     <mergeCell ref="C67:D67"/>
     <mergeCell ref="C68:D68"/>
     <mergeCell ref="C69:D69"/>
+    <mergeCell ref="C58:D58"/>
+    <mergeCell ref="C59:D59"/>
+    <mergeCell ref="C61:D61"/>
+    <mergeCell ref="C63:D63"/>
+    <mergeCell ref="C64:D64"/>
+    <mergeCell ref="C53:D53"/>
+    <mergeCell ref="C54:D54"/>
+    <mergeCell ref="C55:D55"/>
+    <mergeCell ref="C56:D56"/>
+    <mergeCell ref="C57:D57"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="0.75" bottom="0.5" header="0.5" footer="0.75"/>
 </worksheet>
@@ -61935,10 +61935,10 @@
       <c r="A64" s="1" t="s">
         <v>16</v>
       </c>
-      <c r="C64" s="47" t="s">
+      <c r="C64" s="45" t="s">
         <v>89</v>
       </c>
-      <c r="D64" s="47"/>
+      <c r="D64" s="45"/>
       <c r="E64" s="4" t="s">
         <v>90</v>
       </c>
@@ -61966,11 +61966,11 @@
       <c r="B65" s="3" t="s">
         <v>93</v>
       </c>
-      <c r="C65" s="48">
+      <c r="C65" s="46">
         <f>SUMIFS(I$3:I$60,B$3:B$60,A$64,L$3:L$60,A$65)</f>
         <v>46230</v>
       </c>
-      <c r="D65" s="48"/>
+      <c r="D65" s="46"/>
       <c r="E65" s="3">
         <f>SUMIFS(Q$3:Q$60,B$3:B$60,A$64,L$3:L$60,A$65)</f>
         <v>58</v>
@@ -62005,10 +62005,10 @@
       <c r="B66" s="2" t="s">
         <v>97</v>
       </c>
-      <c r="C66" s="49">
+      <c r="C66" s="47">
         <v>0</v>
       </c>
-      <c r="D66" s="49"/>
+      <c r="D66" s="47"/>
       <c r="K66" t="s">
         <v>98</v>
       </c>
@@ -62032,11 +62032,11 @@
       <c r="B67" s="2" t="s">
         <v>99</v>
       </c>
-      <c r="C67" s="49">
+      <c r="C67" s="47">
         <f>-SUMIFS(I$3:I$60,B$3:B$60,A$64,P$3:P$60,"xx",N$3:N$60,"x")</f>
         <v>0</v>
       </c>
-      <c r="D67" s="49"/>
+      <c r="D67" s="47"/>
       <c r="E67" s="2">
         <f>SUMIFS(Q$3:Q$60,B$3:B$60,A$64,P$3:P$60,"xx",N$3:N$60,"x")</f>
         <v>0</v>
@@ -62056,11 +62056,11 @@
       <c r="B68" s="4" t="s">
         <v>101</v>
       </c>
-      <c r="C68" s="47">
+      <c r="C68" s="45">
         <f>SUBTOTAL(9,C65:C67)</f>
         <v>46230</v>
       </c>
-      <c r="D68" s="47"/>
+      <c r="D68" s="45"/>
       <c r="E68">
         <f>E65</f>
         <v>58</v>
@@ -62080,8 +62080,8 @@
       <c r="B69" s="2" t="s">
         <v>104</v>
       </c>
-      <c r="C69" s="45"/>
-      <c r="D69" s="45"/>
+      <c r="C69" s="48"/>
+      <c r="D69" s="48"/>
       <c r="K69" s="2" t="s">
         <v>105</v>
       </c>
@@ -62097,8 +62097,8 @@
       <c r="B70" s="8" t="s">
         <v>107</v>
       </c>
-      <c r="C70" s="45"/>
-      <c r="D70" s="45"/>
+      <c r="C70" s="48"/>
+      <c r="D70" s="48"/>
       <c r="L70" s="9">
         <f>SUBTOTAL(9,L65:L69)</f>
         <v>18610</v>
@@ -62119,11 +62119,11 @@
       <c r="B72" s="1" t="s">
         <v>108</v>
       </c>
-      <c r="C72" s="46">
+      <c r="C72" s="49">
         <f>C68+C69+C70</f>
         <v>46230</v>
       </c>
-      <c r="D72" s="46"/>
+      <c r="D72" s="49"/>
       <c r="E72" s="1" t="s">
         <v>109</v>
       </c>
@@ -65104,10 +65104,10 @@
       <c r="A57" s="1" t="s">
         <v>16</v>
       </c>
-      <c r="C57" s="47" t="s">
+      <c r="C57" s="45" t="s">
         <v>89</v>
       </c>
-      <c r="D57" s="47"/>
+      <c r="D57" s="45"/>
       <c r="E57" s="4" t="s">
         <v>90</v>
       </c>
@@ -65135,11 +65135,11 @@
       <c r="B58" s="3" t="s">
         <v>93</v>
       </c>
-      <c r="C58" s="48">
+      <c r="C58" s="46">
         <f>SUMIFS(I$3:I$53,B$3:B$53,A$57,L$3:L$53,A$58)</f>
         <v>29790</v>
       </c>
-      <c r="D58" s="48"/>
+      <c r="D58" s="46"/>
       <c r="E58" s="3">
         <f>SUMIFS(Q$3:Q$53,B$3:B$53,A$57,L$3:L$53,A$58)</f>
         <v>51</v>
@@ -65174,10 +65174,10 @@
       <c r="B59" s="2" t="s">
         <v>97</v>
       </c>
-      <c r="C59" s="49">
+      <c r="C59" s="47">
         <v>0</v>
       </c>
-      <c r="D59" s="49"/>
+      <c r="D59" s="47"/>
       <c r="K59" t="s">
         <v>98</v>
       </c>
@@ -65201,11 +65201,11 @@
       <c r="B60" s="2" t="s">
         <v>99</v>
       </c>
-      <c r="C60" s="49">
+      <c r="C60" s="47">
         <f>-SUMIFS(I$3:I$53,B$3:B$53,A$57,P$3:P$53,"xx",N$3:N$53,"x")</f>
         <v>0</v>
       </c>
-      <c r="D60" s="49"/>
+      <c r="D60" s="47"/>
       <c r="E60" s="2">
         <f>SUMIFS(Q$3:Q$53,B$3:B$53,A$57,P$3:P$53,"xx",N$3:N$53,"x")</f>
         <v>0</v>
@@ -65233,11 +65233,11 @@
       <c r="B61" s="4" t="s">
         <v>101</v>
       </c>
-      <c r="C61" s="47">
+      <c r="C61" s="45">
         <f>SUBTOTAL(9,C58:C60)</f>
         <v>29790</v>
       </c>
-      <c r="D61" s="47"/>
+      <c r="D61" s="45"/>
       <c r="E61">
         <f>E58</f>
         <v>51</v>
@@ -65257,8 +65257,8 @@
       <c r="B62" s="2" t="s">
         <v>104</v>
       </c>
-      <c r="C62" s="45"/>
-      <c r="D62" s="45"/>
+      <c r="C62" s="48"/>
+      <c r="D62" s="48"/>
       <c r="K62" s="2" t="s">
         <v>105</v>
       </c>
@@ -65274,8 +65274,8 @@
       <c r="B63" s="8" t="s">
         <v>107</v>
       </c>
-      <c r="C63" s="45"/>
-      <c r="D63" s="45"/>
+      <c r="C63" s="48"/>
+      <c r="D63" s="48"/>
       <c r="K63" s="10" t="s">
         <v>323</v>
       </c>
@@ -65297,11 +65297,11 @@
       <c r="B65" s="1" t="s">
         <v>108</v>
       </c>
-      <c r="C65" s="46">
+      <c r="C65" s="49">
         <f>C61+C62+C63</f>
         <v>29790</v>
       </c>
-      <c r="D65" s="46"/>
+      <c r="D65" s="49"/>
       <c r="E65" s="1" t="s">
         <v>109</v>
       </c>
@@ -67255,10 +67255,10 @@
       <c r="A48" s="1" t="s">
         <v>16</v>
       </c>
-      <c r="C48" s="47" t="s">
+      <c r="C48" s="45" t="s">
         <v>89</v>
       </c>
-      <c r="D48" s="47"/>
+      <c r="D48" s="45"/>
       <c r="E48" s="4" t="s">
         <v>90</v>
       </c>
@@ -67286,11 +67286,11 @@
       <c r="B49" s="3" t="s">
         <v>93</v>
       </c>
-      <c r="C49" s="48">
+      <c r="C49" s="46">
         <f>SUMIFS(I$3:I$44,B$3:B$44,A$48,L$3:L$44,A$49)</f>
         <v>20745</v>
       </c>
-      <c r="D49" s="48"/>
+      <c r="D49" s="46"/>
       <c r="E49" s="3">
         <f>SUMIFS(Q$3:Q$44,B$3:B$44,A$48,L$3:L$44,A$49)</f>
         <v>40</v>
@@ -67325,10 +67325,10 @@
       <c r="B50" s="2" t="s">
         <v>97</v>
       </c>
-      <c r="C50" s="49">
+      <c r="C50" s="47">
         <v>0</v>
       </c>
-      <c r="D50" s="49"/>
+      <c r="D50" s="47"/>
       <c r="K50" t="s">
         <v>98</v>
       </c>
@@ -67352,11 +67352,11 @@
       <c r="B51" s="2" t="s">
         <v>99</v>
       </c>
-      <c r="C51" s="49">
+      <c r="C51" s="47">
         <f>-SUMIFS(I$3:I$44,B$3:B$44,A$48,P$3:P$44,"xx",N$3:N$44,"x")</f>
         <v>-970</v>
       </c>
-      <c r="D51" s="49"/>
+      <c r="D51" s="47"/>
       <c r="E51" s="2">
         <f>SUMIFS(Q$3:Q$44,B$3:B$44,A$48,P$3:P$44,"xx",N$3:N$44,"x")</f>
         <v>2</v>
@@ -67376,11 +67376,11 @@
       <c r="B52" s="4" t="s">
         <v>101</v>
       </c>
-      <c r="C52" s="47">
+      <c r="C52" s="45">
         <f>SUBTOTAL(9,C49:C51)</f>
         <v>19775</v>
       </c>
-      <c r="D52" s="47"/>
+      <c r="D52" s="45"/>
       <c r="E52">
         <f>E49</f>
         <v>40</v>
@@ -67406,8 +67406,8 @@
       <c r="B53" s="2" t="s">
         <v>104</v>
       </c>
-      <c r="C53" s="45"/>
-      <c r="D53" s="45"/>
+      <c r="C53" s="48"/>
+      <c r="D53" s="48"/>
       <c r="K53" s="2" t="s">
         <v>105</v>
       </c>
@@ -67423,8 +67423,8 @@
       <c r="B54" s="8" t="s">
         <v>107</v>
       </c>
-      <c r="C54" s="45"/>
-      <c r="D54" s="45"/>
+      <c r="C54" s="48"/>
+      <c r="D54" s="48"/>
       <c r="L54" s="9">
         <f>SUBTOTAL(9,L49:L53)</f>
         <v>8722</v>
@@ -67445,11 +67445,11 @@
       <c r="B56" s="1" t="s">
         <v>108</v>
       </c>
-      <c r="C56" s="46">
+      <c r="C56" s="49">
         <f>C52+C53+C54</f>
         <v>19775</v>
       </c>
-      <c r="D56" s="46"/>
+      <c r="D56" s="49"/>
       <c r="E56" s="1" t="s">
         <v>109</v>
       </c>
@@ -69898,10 +69898,10 @@
       <c r="A59" s="1" t="s">
         <v>16</v>
       </c>
-      <c r="C59" s="47" t="s">
+      <c r="C59" s="45" t="s">
         <v>89</v>
       </c>
-      <c r="D59" s="47"/>
+      <c r="D59" s="45"/>
       <c r="E59" s="4" t="s">
         <v>90</v>
       </c>
@@ -69929,11 +69929,11 @@
       <c r="B60" s="3" t="s">
         <v>93</v>
       </c>
-      <c r="C60" s="48">
+      <c r="C60" s="46">
         <f>SUMIFS(I$3:I$55,B$3:B$55,A$59,L$3:L$55,A$60)</f>
         <v>33510</v>
       </c>
-      <c r="D60" s="48"/>
+      <c r="D60" s="46"/>
       <c r="E60" s="3">
         <f>SUMIFS(Q$3:Q$55,B$3:B$55,A$59,L$3:L$55,A$60)</f>
         <v>52</v>
@@ -69968,10 +69968,10 @@
       <c r="B61" s="2" t="s">
         <v>97</v>
       </c>
-      <c r="C61" s="49">
+      <c r="C61" s="47">
         <v>0</v>
       </c>
-      <c r="D61" s="49"/>
+      <c r="D61" s="47"/>
       <c r="K61" t="s">
         <v>98</v>
       </c>
@@ -69995,11 +69995,11 @@
       <c r="B62" s="2" t="s">
         <v>99</v>
       </c>
-      <c r="C62" s="49">
+      <c r="C62" s="47">
         <f>-SUMIFS(I$3:I$55,B$3:B$55,A$59,P$3:P$55,"xx",N$3:N$55,"x")</f>
         <v>-860</v>
       </c>
-      <c r="D62" s="49"/>
+      <c r="D62" s="47"/>
       <c r="E62" s="2">
         <f>SUMIFS(Q$3:Q$55,B$3:B$55,A$59,P$3:P$55,"xx",N$3:N$55,"x")</f>
         <v>1</v>
@@ -70027,11 +70027,11 @@
       <c r="B63" s="4" t="s">
         <v>101</v>
       </c>
-      <c r="C63" s="47">
+      <c r="C63" s="45">
         <f>SUBTOTAL(9,C60:C62)</f>
         <v>32650</v>
       </c>
-      <c r="D63" s="47"/>
+      <c r="D63" s="45"/>
       <c r="E63">
         <f>E60</f>
         <v>52</v>
@@ -70051,8 +70051,8 @@
       <c r="B64" s="2" t="s">
         <v>104</v>
       </c>
-      <c r="C64" s="45"/>
-      <c r="D64" s="45"/>
+      <c r="C64" s="48"/>
+      <c r="D64" s="48"/>
       <c r="K64" s="2" t="s">
         <v>105</v>
       </c>
@@ -70068,8 +70068,8 @@
       <c r="B65" s="8" t="s">
         <v>107</v>
       </c>
-      <c r="C65" s="45"/>
-      <c r="D65" s="45"/>
+      <c r="C65" s="48"/>
+      <c r="D65" s="48"/>
       <c r="L65" s="9">
         <f>SUBTOTAL(9,L60:L64)</f>
         <v>8748</v>
@@ -70083,11 +70083,11 @@
       <c r="B67" s="1" t="s">
         <v>108</v>
       </c>
-      <c r="C67" s="46">
+      <c r="C67" s="49">
         <f>C63+C64+C65</f>
         <v>32650</v>
       </c>
-      <c r="D67" s="46"/>
+      <c r="D67" s="49"/>
       <c r="E67" s="1" t="s">
         <v>109</v>
       </c>
@@ -71449,10 +71449,10 @@
       <c r="A33" s="1" t="s">
         <v>16</v>
       </c>
-      <c r="C33" s="47" t="s">
+      <c r="C33" s="45" t="s">
         <v>89</v>
       </c>
-      <c r="D33" s="47"/>
+      <c r="D33" s="45"/>
       <c r="E33" s="4" t="s">
         <v>90</v>
       </c>
@@ -71484,7 +71484,7 @@
         <f>SUMIFS(I$3:I$29,B$3:B$29,A$33,L$3:L$29,A$34)+I32</f>
         <v>24145</v>
       </c>
-      <c r="D34" s="48"/>
+      <c r="D34" s="46"/>
       <c r="E34" s="3">
         <f>SUMIFS(Q$3:Q$29,B$3:B$29,A$33,L$3:L$29,A$34)</f>
         <v>25</v>
@@ -71519,10 +71519,10 @@
       <c r="B35" s="2" t="s">
         <v>97</v>
       </c>
-      <c r="C35" s="49">
+      <c r="C35" s="47">
         <v>0</v>
       </c>
-      <c r="D35" s="49"/>
+      <c r="D35" s="47"/>
       <c r="K35" t="s">
         <v>98</v>
       </c>
@@ -71546,11 +71546,11 @@
       <c r="B36" s="2" t="s">
         <v>99</v>
       </c>
-      <c r="C36" s="49">
+      <c r="C36" s="47">
         <f>-SUMIFS(I$3:I$29,B$3:B$29,A$33,P$3:P$29,"xx",N$3:N$29,"x")</f>
         <v>-1715</v>
       </c>
-      <c r="D36" s="49"/>
+      <c r="D36" s="47"/>
       <c r="E36" s="2">
         <f>SUMIFS(Q$3:Q$29,B$3:B$29,A$33,P$3:P$29,"xx",N$3:N$29,"x")</f>
         <v>2</v>
@@ -71578,11 +71578,11 @@
       <c r="B37" s="4" t="s">
         <v>101</v>
       </c>
-      <c r="C37" s="47">
+      <c r="C37" s="45">
         <f>SUBTOTAL(9,C34:C36)</f>
         <v>22430</v>
       </c>
-      <c r="D37" s="47"/>
+      <c r="D37" s="45"/>
       <c r="E37">
         <f>E34</f>
         <v>25</v>
@@ -71601,10 +71601,10 @@
       <c r="B38" s="2" t="s">
         <v>104</v>
       </c>
-      <c r="C38" s="45">
+      <c r="C38" s="48">
         <v>-70</v>
       </c>
-      <c r="D38" s="45"/>
+      <c r="D38" s="48"/>
       <c r="K38" s="2" t="s">
         <v>105</v>
       </c>
@@ -71623,8 +71623,8 @@
       <c r="B39" s="8" t="s">
         <v>107</v>
       </c>
-      <c r="C39" s="45"/>
-      <c r="D39" s="45"/>
+      <c r="C39" s="48"/>
+      <c r="D39" s="48"/>
       <c r="K39" s="10" t="s">
         <v>664</v>
       </c>
@@ -71661,11 +71661,11 @@
       <c r="B42" s="1" t="s">
         <v>108</v>
       </c>
-      <c r="C42" s="46">
+      <c r="C42" s="49">
         <f>C37+C38+C39</f>
         <v>22360</v>
       </c>
-      <c r="D42" s="46"/>
+      <c r="D42" s="49"/>
       <c r="E42" s="1" t="s">
         <v>109</v>
       </c>
@@ -73964,10 +73964,10 @@
       <c r="A51" s="1" t="s">
         <v>16</v>
       </c>
-      <c r="C51" s="47" t="s">
+      <c r="C51" s="45" t="s">
         <v>89</v>
       </c>
-      <c r="D51" s="47"/>
+      <c r="D51" s="45"/>
       <c r="E51" s="4" t="s">
         <v>90</v>
       </c>
@@ -73995,11 +73995,11 @@
       <c r="B52" s="3" t="s">
         <v>93</v>
       </c>
-      <c r="C52" s="48">
+      <c r="C52" s="46">
         <f>SUMIFS(I$3:I$47,B$3:B$47,A$51,L$3:L$47,A$52)</f>
         <v>25380</v>
       </c>
-      <c r="D52" s="48"/>
+      <c r="D52" s="46"/>
       <c r="E52" s="3">
         <f>SUMIFS(Q$3:Q$47,B$3:B$47,A$51,L$3:L$47,A$52)</f>
         <v>43</v>
@@ -74034,10 +74034,10 @@
       <c r="B53" s="2" t="s">
         <v>97</v>
       </c>
-      <c r="C53" s="49">
+      <c r="C53" s="47">
         <v>0</v>
       </c>
-      <c r="D53" s="49"/>
+      <c r="D53" s="47"/>
       <c r="K53" t="s">
         <v>98</v>
       </c>
@@ -74061,11 +74061,11 @@
       <c r="B54" s="2" t="s">
         <v>99</v>
       </c>
-      <c r="C54" s="49">
+      <c r="C54" s="47">
         <f>-SUMIFS(I$3:I$47,B$3:B$47,A$51,P$3:P$47,"xx",N$3:N$47,"x")</f>
         <v>-710</v>
       </c>
-      <c r="D54" s="49"/>
+      <c r="D54" s="47"/>
       <c r="E54" s="2">
         <f>SUMIFS(Q$3:Q$47,B$3:B$47,A$51,P$3:P$47,"xx",N$3:N$47,"x")</f>
         <v>3</v>
@@ -74093,11 +74093,11 @@
       <c r="B55" s="4" t="s">
         <v>101</v>
       </c>
-      <c r="C55" s="47">
+      <c r="C55" s="45">
         <f>SUBTOTAL(9,C52:C54)</f>
         <v>24670</v>
       </c>
-      <c r="D55" s="47"/>
+      <c r="D55" s="45"/>
       <c r="E55">
         <f>E52</f>
         <v>43</v>
@@ -74117,8 +74117,8 @@
       <c r="B56" s="2" t="s">
         <v>104</v>
       </c>
-      <c r="C56" s="45"/>
-      <c r="D56" s="45"/>
+      <c r="C56" s="48"/>
+      <c r="D56" s="48"/>
       <c r="K56" s="2" t="s">
         <v>105</v>
       </c>
@@ -74134,8 +74134,8 @@
       <c r="B57" s="8" t="s">
         <v>107</v>
       </c>
-      <c r="C57" s="45"/>
-      <c r="D57" s="45"/>
+      <c r="C57" s="48"/>
+      <c r="D57" s="48"/>
       <c r="L57" s="9">
         <f>SUBTOTAL(9,L52:L56)</f>
         <v>4847</v>
@@ -74156,11 +74156,11 @@
       <c r="B59" s="1" t="s">
         <v>108</v>
       </c>
-      <c r="C59" s="46">
+      <c r="C59" s="49">
         <f>C55+C56+C57</f>
         <v>24670</v>
       </c>
-      <c r="D59" s="46"/>
+      <c r="D59" s="49"/>
       <c r="E59" s="1" t="s">
         <v>109</v>
       </c>
@@ -76144,10 +76144,10 @@
       <c r="A43" s="1" t="s">
         <v>16</v>
       </c>
-      <c r="C43" s="47" t="s">
+      <c r="C43" s="45" t="s">
         <v>89</v>
       </c>
-      <c r="D43" s="47"/>
+      <c r="D43" s="45"/>
       <c r="E43" s="4" t="s">
         <v>90</v>
       </c>
@@ -76175,11 +76175,11 @@
       <c r="B44" s="3" t="s">
         <v>93</v>
       </c>
-      <c r="C44" s="48">
+      <c r="C44" s="46">
         <f>SUMIFS(I$3:I$39,B$3:B$39,A$43,L$3:L$39,A$44)</f>
         <v>23985</v>
       </c>
-      <c r="D44" s="48"/>
+      <c r="D44" s="46"/>
       <c r="E44" s="3">
         <f>SUMIFS(Q$3:Q$39,B$3:B$39,A$43,L$3:L$39,A$44)</f>
         <v>37</v>
@@ -76210,10 +76210,10 @@
       <c r="B45" s="2" t="s">
         <v>97</v>
       </c>
-      <c r="C45" s="49">
+      <c r="C45" s="47">
         <v>0</v>
       </c>
-      <c r="D45" s="49"/>
+      <c r="D45" s="47"/>
       <c r="K45" t="s">
         <v>98</v>
       </c>
@@ -76237,11 +76237,11 @@
       <c r="B46" s="2" t="s">
         <v>99</v>
       </c>
-      <c r="C46" s="49">
+      <c r="C46" s="47">
         <f>-SUMIFS(I$3:I$39,B$3:B$39,A$43,P$3:P$39,"xx",N$3:N$39,"x")</f>
         <v>0</v>
       </c>
-      <c r="D46" s="49"/>
+      <c r="D46" s="47"/>
       <c r="E46" s="2">
         <f>SUMIFS(Q$3:Q$39,B$3:B$39,A$43,P$3:P$39,"xx",N$3:N$39,"x")</f>
         <v>0</v>
@@ -76269,11 +76269,11 @@
       <c r="B47" s="4" t="s">
         <v>101</v>
       </c>
-      <c r="C47" s="47">
+      <c r="C47" s="45">
         <f>SUBTOTAL(9,C44:C46)</f>
         <v>23985</v>
       </c>
-      <c r="D47" s="47"/>
+      <c r="D47" s="45"/>
       <c r="E47">
         <f>E44</f>
         <v>37</v>
@@ -76293,8 +76293,8 @@
       <c r="B48" s="2" t="s">
         <v>104</v>
       </c>
-      <c r="C48" s="45"/>
-      <c r="D48" s="45"/>
+      <c r="C48" s="48"/>
+      <c r="D48" s="48"/>
       <c r="K48" s="2" t="s">
         <v>105</v>
       </c>
@@ -76310,8 +76310,8 @@
       <c r="B49" s="8" t="s">
         <v>107</v>
       </c>
-      <c r="C49" s="45"/>
-      <c r="D49" s="45"/>
+      <c r="C49" s="48"/>
+      <c r="D49" s="48"/>
       <c r="L49" s="9">
         <f>SUBTOTAL(9,L44:L48)</f>
         <v>7556</v>
@@ -76325,11 +76325,11 @@
       <c r="B51" s="1" t="s">
         <v>108</v>
       </c>
-      <c r="C51" s="46">
+      <c r="C51" s="49">
         <f>C47+C48+C49</f>
         <v>23985</v>
       </c>
-      <c r="D51" s="46"/>
+      <c r="D51" s="49"/>
       <c r="E51" s="1" t="s">
         <v>109</v>
       </c>
@@ -78974,10 +78974,10 @@
       <c r="A58" s="1" t="s">
         <v>16</v>
       </c>
-      <c r="C58" s="47" t="s">
+      <c r="C58" s="45" t="s">
         <v>89</v>
       </c>
-      <c r="D58" s="47"/>
+      <c r="D58" s="45"/>
       <c r="E58" s="4" t="s">
         <v>90</v>
       </c>
@@ -79005,11 +79005,11 @@
       <c r="B59" s="3" t="s">
         <v>93</v>
       </c>
-      <c r="C59" s="48">
+      <c r="C59" s="46">
         <f>SUMIFS(I$3:I$55,B$3:B$55,A$58,L$3:L$55,A$59)</f>
         <v>43676</v>
       </c>
-      <c r="D59" s="48"/>
+      <c r="D59" s="46"/>
       <c r="E59" s="3">
         <f>SUMIFS(Q$3:Q$55,B$3:B$55,A$58,L$3:L$55,A$59)</f>
         <v>51</v>
@@ -79040,10 +79040,10 @@
       <c r="B60" s="2" t="s">
         <v>97</v>
       </c>
-      <c r="C60" s="49">
+      <c r="C60" s="47">
         <v>0</v>
       </c>
-      <c r="D60" s="49"/>
+      <c r="D60" s="47"/>
       <c r="K60" t="s">
         <v>98</v>
       </c>
@@ -79067,11 +79067,11 @@
       <c r="B61" s="2" t="s">
         <v>99</v>
       </c>
-      <c r="C61" s="49">
+      <c r="C61" s="47">
         <f>-SUMIFS(I$3:I$55,B$3:B$55,A$58,P$3:P$55,"xx",N$3:N$55,"x")</f>
         <v>-975</v>
       </c>
-      <c r="D61" s="49"/>
+      <c r="D61" s="47"/>
       <c r="E61" s="2">
         <f>SUMIFS(Q$3:Q$55,B$3:B$55,A$58,P$3:P$55,"xx",N$3:N$55,"x")</f>
         <v>2</v>
@@ -79091,11 +79091,11 @@
       <c r="B62" s="4" t="s">
         <v>101</v>
       </c>
-      <c r="C62" s="47">
+      <c r="C62" s="45">
         <f>SUBTOTAL(9,C59:C61)</f>
         <v>42701</v>
       </c>
-      <c r="D62" s="47"/>
+      <c r="D62" s="45"/>
       <c r="E62">
         <f>E59</f>
         <v>51</v>
@@ -79121,8 +79121,8 @@
       <c r="B63" s="2" t="s">
         <v>104</v>
       </c>
-      <c r="C63" s="45"/>
-      <c r="D63" s="45"/>
+      <c r="C63" s="48"/>
+      <c r="D63" s="48"/>
       <c r="K63" s="2" t="s">
         <v>105</v>
       </c>
@@ -79138,8 +79138,8 @@
       <c r="B64" s="8" t="s">
         <v>107</v>
       </c>
-      <c r="C64" s="45"/>
-      <c r="D64" s="45"/>
+      <c r="C64" s="48"/>
+      <c r="D64" s="48"/>
       <c r="L64" s="9">
         <f>SUBTOTAL(9,L59:L63)</f>
         <v>9811</v>
@@ -79153,11 +79153,11 @@
       <c r="B66" s="1" t="s">
         <v>108</v>
       </c>
-      <c r="C66" s="46">
+      <c r="C66" s="49">
         <f>C62+C63+C64</f>
         <v>42701</v>
       </c>
-      <c r="D66" s="46"/>
+      <c r="D66" s="49"/>
       <c r="E66" s="1" t="s">
         <v>109</v>
       </c>
